--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -877,7 +877,7 @@
     <row r="1">
       <c r="A1" s="81" t="inlineStr">
         <is>
-          <t>Last Updated: April 24, 2026 06:59 AM</t>
+          <t>Last Updated: April 24, 2026 08:08 AM</t>
         </is>
       </c>
     </row>
@@ -2872,23 +2872,27 @@
       </c>
       <c r="B10" s="73" t="inlineStr">
         <is>
-          <t>157345533677</t>
-        </is>
-      </c>
-      <c r="C10" s="73" t="inlineStr"/>
+          <t>159420375799</t>
+        </is>
+      </c>
+      <c r="C10" s="73" t="inlineStr">
+        <is>
+          <t>2025-11864</t>
+        </is>
+      </c>
       <c r="D10" s="73" t="inlineStr">
         <is>
-          <t>Customer Relationship Manager Platform- Wyoming</t>
+          <t>Temporary Service Provider Services as Required</t>
         </is>
       </c>
       <c r="E10" s="73" t="inlineStr">
         <is>
-          <t>Wyoming Retirement System</t>
+          <t>Port of Portland</t>
         </is>
       </c>
       <c r="F10" s="73" t="inlineStr">
         <is>
-          <t>Wyoming</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="G10" s="73" t="inlineStr">
@@ -2905,23 +2909,19 @@
       </c>
       <c r="K10" s="73" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="L10" s="73" t="n"/>
       <c r="M10" s="73" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
-        </is>
-      </c>
-      <c r="N10" s="73" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="N10" s="73" t="inlineStr"/>
       <c r="O10" s="73" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="P10" s="73" t="inlineStr"/>
@@ -2935,12 +2935,12 @@
       <c r="X10" s="73" t="inlineStr"/>
       <c r="Y10" s="73" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="Z10" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/157345533677</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/159420375799</t>
         </is>
       </c>
       <c r="AA10" s="73" t="inlineStr"/>
@@ -2951,27 +2951,23 @@
       </c>
       <c r="B11" s="73" t="inlineStr">
         <is>
-          <t>159420375799</t>
-        </is>
-      </c>
-      <c r="C11" s="73" t="inlineStr">
-        <is>
-          <t>2025-11864</t>
-        </is>
-      </c>
+          <t>158191708863</t>
+        </is>
+      </c>
+      <c r="C11" s="73" t="inlineStr"/>
       <c r="D11" s="73" t="inlineStr">
         <is>
-          <t>Temporary Service Provider Services as Required</t>
+          <t>Information Technology Services</t>
         </is>
       </c>
       <c r="E11" s="73" t="inlineStr">
         <is>
-          <t>Port of Portland</t>
+          <t>Pine City</t>
         </is>
       </c>
       <c r="F11" s="73" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="G11" s="73" t="inlineStr">
@@ -2988,16 +2984,22 @@
       </c>
       <c r="K11" s="73" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="L11" s="73" t="n"/>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="L11" s="75" t="n">
+        <v>43330</v>
+      </c>
       <c r="M11" s="73" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
-        </is>
-      </c>
-      <c r="N11" s="73" t="inlineStr"/>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N11" s="73" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="O11" s="73" t="inlineStr">
         <is>
           <t>Abhishek Zalani</t>
@@ -3014,12 +3016,12 @@
       <c r="X11" s="73" t="inlineStr"/>
       <c r="Y11" s="73" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="Z11" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/159420375799</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/158191708863</t>
         </is>
       </c>
       <c r="AA11" s="73" t="inlineStr"/>
@@ -3030,23 +3032,23 @@
       </c>
       <c r="B12" s="73" t="inlineStr">
         <is>
-          <t>158191708863</t>
+          <t>157345533677</t>
         </is>
       </c>
       <c r="C12" s="73" t="inlineStr"/>
       <c r="D12" s="73" t="inlineStr">
         <is>
-          <t>Information Technology Services</t>
+          <t>Customer Relationship Manager Platform- Wyoming</t>
         </is>
       </c>
       <c r="E12" s="73" t="inlineStr">
         <is>
-          <t>Pine City</t>
+          <t>Wyoming Retirement System</t>
         </is>
       </c>
       <c r="F12" s="73" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Wyoming</t>
         </is>
       </c>
       <c r="G12" s="73" t="inlineStr">
@@ -3066,22 +3068,20 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="L12" s="75" t="n">
-        <v>43330</v>
-      </c>
+      <c r="L12" s="73" t="n"/>
       <c r="M12" s="73" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="N12" s="73" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O12" s="73" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Arshdeep Kaur</t>
         </is>
       </c>
       <c r="P12" s="73" t="inlineStr"/>
@@ -3095,12 +3095,12 @@
       <c r="X12" s="73" t="inlineStr"/>
       <c r="Y12" s="73" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="Z12" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/158191708863</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/157345533677</t>
         </is>
       </c>
       <c r="AA12" s="73" t="inlineStr"/>
@@ -3692,18 +3692,18 @@
       </c>
       <c r="B20" s="73" t="inlineStr">
         <is>
-          <t>164634450618</t>
+          <t>166098266830</t>
         </is>
       </c>
       <c r="C20" s="73" t="inlineStr"/>
       <c r="D20" s="73" t="inlineStr">
         <is>
-          <t>Development and Implementation of Comprehensive Data Governance Policy</t>
+          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
         </is>
       </c>
       <c r="E20" s="73" t="inlineStr">
         <is>
-          <t>Wake County Public School System</t>
+          <t>Mecklenburg County</t>
         </is>
       </c>
       <c r="F20" s="73" t="inlineStr">
@@ -3723,22 +3723,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="K20" s="73" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
+      <c r="K20" s="73" t="inlineStr"/>
       <c r="L20" s="73" t="n"/>
       <c r="M20" s="73" t="inlineStr">
         <is>
-          <t>Training;Consulting</t>
-        </is>
-      </c>
-      <c r="N20" s="73" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
+          <t>Audits and Assessment</t>
+        </is>
+      </c>
+      <c r="N20" s="73" t="inlineStr"/>
       <c r="O20" s="73" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
@@ -3760,7 +3752,7 @@
       </c>
       <c r="Z20" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/164634450618</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
         </is>
       </c>
       <c r="AA20" s="73" t="inlineStr"/>
@@ -3771,18 +3763,18 @@
       </c>
       <c r="B21" s="73" t="inlineStr">
         <is>
-          <t>166098266830</t>
+          <t>164634450618</t>
         </is>
       </c>
       <c r="C21" s="73" t="inlineStr"/>
       <c r="D21" s="73" t="inlineStr">
         <is>
-          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
+          <t>Development and Implementation of Comprehensive Data Governance Policy</t>
         </is>
       </c>
       <c r="E21" s="73" t="inlineStr">
         <is>
-          <t>Mecklenburg County</t>
+          <t>Wake County Public School System</t>
         </is>
       </c>
       <c r="F21" s="73" t="inlineStr">
@@ -3802,14 +3794,22 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="K21" s="73" t="inlineStr"/>
+      <c r="K21" s="73" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
       <c r="L21" s="73" t="n"/>
       <c r="M21" s="73" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
-        </is>
-      </c>
-      <c r="N21" s="73" t="inlineStr"/>
+          <t>Training;Consulting</t>
+        </is>
+      </c>
+      <c r="N21" s="73" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
       <c r="O21" s="73" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="Z21" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/164634450618</t>
         </is>
       </c>
       <c r="AA21" s="73" t="inlineStr"/>
@@ -4138,23 +4138,27 @@
       </c>
       <c r="B26" s="73" t="inlineStr">
         <is>
-          <t>163703775952</t>
-        </is>
-      </c>
-      <c r="C26" s="73" t="inlineStr"/>
+          <t>167226058440</t>
+        </is>
+      </c>
+      <c r="C26" s="73" t="inlineStr">
+        <is>
+          <t>186063</t>
+        </is>
+      </c>
       <c r="D26" s="73" t="inlineStr">
         <is>
-          <t>IT Consultant</t>
+          <t>REQUEST FOR PROPOSAL 186063: Internal Audit Services</t>
         </is>
       </c>
       <c r="E26" s="73" t="inlineStr">
         <is>
-          <t>Dupage County</t>
+          <t>City of Detroit</t>
         </is>
       </c>
       <c r="F26" s="73" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G26" s="73" t="inlineStr">
@@ -4174,16 +4178,22 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="L26" s="73" t="n"/>
+      <c r="L26" s="75" t="n">
+        <v>46000</v>
+      </c>
       <c r="M26" s="73" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
-        </is>
-      </c>
-      <c r="N26" s="73" t="inlineStr"/>
+          <t>Audits and Assessment</t>
+        </is>
+      </c>
+      <c r="N26" s="73" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O26" s="73" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="P26" s="73" t="inlineStr"/>
@@ -4197,12 +4207,12 @@
       <c r="X26" s="73" t="inlineStr"/>
       <c r="Y26" s="73" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z26" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/163703775952</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/167226058440</t>
         </is>
       </c>
       <c r="AA26" s="73" t="inlineStr"/>
@@ -4213,27 +4223,23 @@
       </c>
       <c r="B27" s="73" t="inlineStr">
         <is>
-          <t>167226058440</t>
-        </is>
-      </c>
-      <c r="C27" s="73" t="inlineStr">
-        <is>
-          <t>186063</t>
-        </is>
-      </c>
+          <t>163703775952</t>
+        </is>
+      </c>
+      <c r="C27" s="73" t="inlineStr"/>
       <c r="D27" s="73" t="inlineStr">
         <is>
-          <t>REQUEST FOR PROPOSAL 186063: Internal Audit Services</t>
+          <t>IT Consultant</t>
         </is>
       </c>
       <c r="E27" s="73" t="inlineStr">
         <is>
-          <t>City of Detroit</t>
+          <t>Dupage County</t>
         </is>
       </c>
       <c r="F27" s="73" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="G27" s="73" t="inlineStr">
@@ -4253,22 +4259,16 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="L27" s="75" t="n">
-        <v>46000</v>
-      </c>
+      <c r="L27" s="73" t="n"/>
       <c r="M27" s="73" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
-        </is>
-      </c>
-      <c r="N27" s="73" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="N27" s="73" t="inlineStr"/>
       <c r="O27" s="73" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Arshdeep Kaur</t>
         </is>
       </c>
       <c r="P27" s="73" t="inlineStr"/>
@@ -4282,12 +4282,12 @@
       <c r="X27" s="73" t="inlineStr"/>
       <c r="Y27" s="73" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="Z27" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/167226058440</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/163703775952</t>
         </is>
       </c>
       <c r="AA27" s="73" t="inlineStr"/>
@@ -5503,13 +5503,17 @@
       </c>
       <c r="B43" s="73" t="inlineStr">
         <is>
-          <t>182109882089</t>
-        </is>
-      </c>
-      <c r="C43" s="73" t="inlineStr"/>
+          <t>240974373562</t>
+        </is>
+      </c>
+      <c r="C43" s="73" t="inlineStr">
+        <is>
+          <t>Consolidated IT Services Bench</t>
+        </is>
+      </c>
       <c r="D43" s="73" t="inlineStr">
         <is>
-          <t>Enterprise Software Application Services Bench</t>
+          <t xml:space="preserve">Consolidated IT Services Bench </t>
         </is>
       </c>
       <c r="E43" s="73" t="inlineStr">
@@ -5560,7 +5564,7 @@
       <c r="R43" s="73" t="inlineStr"/>
       <c r="S43" s="73" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="T43" s="73" t="inlineStr"/>
@@ -5575,14 +5579,10 @@
       </c>
       <c r="Z43" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/182109882089</t>
-        </is>
-      </c>
-      <c r="AA43" s="73" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/240974373562</t>
+        </is>
+      </c>
+      <c r="AA43" s="73" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="73" t="n">
@@ -5590,17 +5590,13 @@
       </c>
       <c r="B44" s="73" t="inlineStr">
         <is>
-          <t>240974373562</t>
-        </is>
-      </c>
-      <c r="C44" s="73" t="inlineStr">
-        <is>
-          <t>Consolidated IT Services Bench</t>
-        </is>
-      </c>
+          <t>182109882089</t>
+        </is>
+      </c>
+      <c r="C44" s="73" t="inlineStr"/>
       <c r="D44" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consolidated IT Services Bench </t>
+          <t>Enterprise Software Application Services Bench</t>
         </is>
       </c>
       <c r="E44" s="73" t="inlineStr">
@@ -5651,7 +5647,7 @@
       <c r="R44" s="73" t="inlineStr"/>
       <c r="S44" s="73" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="T44" s="73" t="inlineStr"/>
@@ -5666,10 +5662,14 @@
       </c>
       <c r="Z44" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/240974373562</t>
-        </is>
-      </c>
-      <c r="AA44" s="73" t="inlineStr"/>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/182109882089</t>
+        </is>
+      </c>
+      <c r="AA44" s="73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="73" t="n">
@@ -6001,13 +6001,13 @@
       </c>
       <c r="B49" s="73" t="inlineStr">
         <is>
-          <t>181172764371</t>
+          <t>181172763351</t>
         </is>
       </c>
       <c r="C49" s="73" t="inlineStr"/>
       <c r="D49" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">INFORMATION TECHNOLOGY CONSULTANT SERVICES	</t>
+          <t>Network and IT Security Consultant Services</t>
         </is>
       </c>
       <c r="E49" s="73" t="inlineStr">
@@ -6034,25 +6034,19 @@
       </c>
       <c r="K49" s="73" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="L49" s="75" t="n">
-        <v>179860</v>
-      </c>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="L49" s="73" t="n"/>
       <c r="M49" s="73" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N49" s="73" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N49" s="73" t="inlineStr"/>
       <c r="O49" s="73" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="P49" s="73" t="inlineStr"/>
@@ -6071,7 +6065,7 @@
       </c>
       <c r="Z49" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/181172764371</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/181172763351</t>
         </is>
       </c>
       <c r="AA49" s="73" t="inlineStr"/>
@@ -6082,13 +6076,13 @@
       </c>
       <c r="B50" s="73" t="inlineStr">
         <is>
-          <t>181172763351</t>
+          <t>181172764371</t>
         </is>
       </c>
       <c r="C50" s="73" t="inlineStr"/>
       <c r="D50" s="73" t="inlineStr">
         <is>
-          <t>Network and IT Security Consultant Services</t>
+          <t xml:space="preserve">INFORMATION TECHNOLOGY CONSULTANT SERVICES	</t>
         </is>
       </c>
       <c r="E50" s="73" t="inlineStr">
@@ -6115,19 +6109,25 @@
       </c>
       <c r="K50" s="73" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="L50" s="73" t="n"/>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="L50" s="75" t="n">
+        <v>179860</v>
+      </c>
       <c r="M50" s="73" t="inlineStr">
         <is>
-          <t>Consulting</t>
-        </is>
-      </c>
-      <c r="N50" s="73" t="inlineStr"/>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N50" s="73" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
       <c r="O50" s="73" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="P50" s="73" t="inlineStr"/>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="Z50" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/181172763351</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/181172764371</t>
         </is>
       </c>
       <c r="AA50" s="73" t="inlineStr"/>
@@ -7475,36 +7475,40 @@
       </c>
       <c r="B67" s="73" t="inlineStr">
         <is>
-          <t>180942915280</t>
-        </is>
-      </c>
-      <c r="C67" s="73" t="inlineStr">
-        <is>
-          <t>2023-RFP-012</t>
-        </is>
-      </c>
+          <t>178922700534</t>
+        </is>
+      </c>
+      <c r="C67" s="73" t="inlineStr"/>
       <c r="D67" s="73" t="inlineStr">
         <is>
-          <t>Enterprise Database Management Software Solution (Re-Bid)</t>
+          <t>Data Platform</t>
         </is>
       </c>
       <c r="E67" s="73" t="inlineStr">
         <is>
-          <t>Neoride</t>
+          <t xml:space="preserve">University of Michigan </t>
         </is>
       </c>
       <c r="F67" s="73" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G67" s="73" t="inlineStr">
         <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="H67" s="73" t="inlineStr"/>
-      <c r="I67" s="73" t="inlineStr"/>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="H67" s="73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I67" s="73" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
       <c r="J67" s="73" t="inlineStr">
         <is>
           <t>2025-10-24</t>
@@ -7515,9 +7519,7 @@
           <t>2025-10-24</t>
         </is>
       </c>
-      <c r="L67" s="75" t="n">
-        <v>1100000</v>
-      </c>
+      <c r="L67" s="73" t="n"/>
       <c r="M67" s="73" t="inlineStr">
         <is>
           <t>Platform Implementation (ERP, CRMs)</t>
@@ -7530,11 +7532,15 @@
       </c>
       <c r="O67" s="73" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="P67" s="73" t="inlineStr"/>
-      <c r="Q67" s="73" t="inlineStr"/>
+      <c r="Q67" s="73" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
       <c r="R67" s="73" t="inlineStr"/>
       <c r="S67" s="73" t="inlineStr"/>
       <c r="T67" s="73" t="inlineStr"/>
@@ -7544,12 +7550,12 @@
       <c r="X67" s="73" t="inlineStr"/>
       <c r="Y67" s="73" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="Z67" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/180942915280</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/178922700534</t>
         </is>
       </c>
       <c r="AA67" s="73" t="inlineStr"/>
@@ -7560,32 +7566,40 @@
       </c>
       <c r="B68" s="73" t="inlineStr">
         <is>
-          <t>178774810310</t>
+          <t>176000104170</t>
         </is>
       </c>
       <c r="C68" s="73" t="inlineStr"/>
       <c r="D68" s="73" t="inlineStr">
         <is>
-          <t>Workday AMS Support Services</t>
+          <t>IT Disaster Recovery Plan</t>
         </is>
       </c>
       <c r="E68" s="73" t="inlineStr">
         <is>
-          <t>City of Olathe</t>
+          <t>Washington County</t>
         </is>
       </c>
       <c r="F68" s="73" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="G68" s="73" t="inlineStr">
         <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="H68" s="73" t="inlineStr"/>
-      <c r="I68" s="73" t="inlineStr"/>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="H68" s="73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I68" s="73" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
       <c r="J68" s="73" t="inlineStr">
         <is>
           <t>2025-10-24</t>
@@ -7599,21 +7613,25 @@
       <c r="L68" s="73" t="n"/>
       <c r="M68" s="73" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N68" s="73" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O68" s="73" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="P68" s="73" t="inlineStr"/>
-      <c r="Q68" s="73" t="inlineStr"/>
+      <c r="Q68" s="73" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
       <c r="R68" s="73" t="inlineStr"/>
       <c r="S68" s="73" t="inlineStr"/>
       <c r="T68" s="73" t="inlineStr"/>
@@ -7628,7 +7646,7 @@
       </c>
       <c r="Z68" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/178774810310</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/176000104170</t>
         </is>
       </c>
       <c r="AA68" s="73" t="inlineStr"/>
@@ -7639,23 +7657,27 @@
       </c>
       <c r="B69" s="73" t="inlineStr">
         <is>
-          <t>183648627418</t>
-        </is>
-      </c>
-      <c r="C69" s="73" t="inlineStr"/>
+          <t>180942915280</t>
+        </is>
+      </c>
+      <c r="C69" s="73" t="inlineStr">
+        <is>
+          <t>2023-RFP-012</t>
+        </is>
+      </c>
       <c r="D69" s="73" t="inlineStr">
         <is>
-          <t>Data Migration Services (Rebid)</t>
+          <t>Enterprise Database Management Software Solution (Re-Bid)</t>
         </is>
       </c>
       <c r="E69" s="73" t="inlineStr">
         <is>
-          <t>Huntington Park</t>
+          <t>Neoride</t>
         </is>
       </c>
       <c r="F69" s="73" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G69" s="73" t="inlineStr">
@@ -7676,11 +7698,11 @@
         </is>
       </c>
       <c r="L69" s="75" t="n">
-        <v>40350</v>
+        <v>1100000</v>
       </c>
       <c r="M69" s="73" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="N69" s="73" t="inlineStr">
@@ -7690,7 +7712,7 @@
       </c>
       <c r="O69" s="73" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="P69" s="73" t="inlineStr"/>
@@ -7704,12 +7726,12 @@
       <c r="X69" s="73" t="inlineStr"/>
       <c r="Y69" s="73" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="Z69" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/183648627418</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/180942915280</t>
         </is>
       </c>
       <c r="AA69" s="73" t="inlineStr"/>
@@ -7720,40 +7742,32 @@
       </c>
       <c r="B70" s="73" t="inlineStr">
         <is>
-          <t>178922700534</t>
+          <t>178774810310</t>
         </is>
       </c>
       <c r="C70" s="73" t="inlineStr"/>
       <c r="D70" s="73" t="inlineStr">
         <is>
-          <t>Data Platform</t>
+          <t>Workday AMS Support Services</t>
         </is>
       </c>
       <c r="E70" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">University of Michigan </t>
+          <t>City of Olathe</t>
         </is>
       </c>
       <c r="F70" s="73" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="G70" s="73" t="inlineStr">
         <is>
-          <t>Interview</t>
-        </is>
-      </c>
-      <c r="H70" s="73" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I70" s="73" t="inlineStr">
-        <is>
-          <t>Interview</t>
-        </is>
-      </c>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H70" s="73" t="inlineStr"/>
+      <c r="I70" s="73" t="inlineStr"/>
       <c r="J70" s="73" t="inlineStr">
         <is>
           <t>2025-10-24</t>
@@ -7767,7 +7781,7 @@
       <c r="L70" s="73" t="n"/>
       <c r="M70" s="73" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N70" s="73" t="inlineStr">
@@ -7777,15 +7791,11 @@
       </c>
       <c r="O70" s="73" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="P70" s="73" t="inlineStr"/>
-      <c r="Q70" s="73" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
+      <c r="Q70" s="73" t="inlineStr"/>
       <c r="R70" s="73" t="inlineStr"/>
       <c r="S70" s="73" t="inlineStr"/>
       <c r="T70" s="73" t="inlineStr"/>
@@ -7800,7 +7810,7 @@
       </c>
       <c r="Z70" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/178922700534</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/178774810310</t>
         </is>
       </c>
       <c r="AA70" s="73" t="inlineStr"/>
@@ -7811,40 +7821,32 @@
       </c>
       <c r="B71" s="73" t="inlineStr">
         <is>
-          <t>176000104170</t>
+          <t>183648627418</t>
         </is>
       </c>
       <c r="C71" s="73" t="inlineStr"/>
       <c r="D71" s="73" t="inlineStr">
         <is>
-          <t>IT Disaster Recovery Plan</t>
+          <t>Data Migration Services (Rebid)</t>
         </is>
       </c>
       <c r="E71" s="73" t="inlineStr">
         <is>
-          <t>Washington County</t>
+          <t>Huntington Park</t>
         </is>
       </c>
       <c r="F71" s="73" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G71" s="73" t="inlineStr">
         <is>
-          <t>Interview</t>
-        </is>
-      </c>
-      <c r="H71" s="73" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I71" s="73" t="inlineStr">
-        <is>
-          <t>Interview</t>
-        </is>
-      </c>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H71" s="73" t="inlineStr"/>
+      <c r="I71" s="73" t="inlineStr"/>
       <c r="J71" s="73" t="inlineStr">
         <is>
           <t>2025-10-24</t>
@@ -7855,15 +7857,17 @@
           <t>2025-10-24</t>
         </is>
       </c>
-      <c r="L71" s="73" t="n"/>
+      <c r="L71" s="75" t="n">
+        <v>40350</v>
+      </c>
       <c r="M71" s="73" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="N71" s="73" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O71" s="73" t="inlineStr">
@@ -7872,11 +7876,7 @@
         </is>
       </c>
       <c r="P71" s="73" t="inlineStr"/>
-      <c r="Q71" s="73" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
+      <c r="Q71" s="73" t="inlineStr"/>
       <c r="R71" s="73" t="inlineStr"/>
       <c r="S71" s="73" t="inlineStr"/>
       <c r="T71" s="73" t="inlineStr"/>
@@ -7886,12 +7886,12 @@
       <c r="X71" s="73" t="inlineStr"/>
       <c r="Y71" s="73" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="Z71" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/176000104170</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/183648627418</t>
         </is>
       </c>
       <c r="AA71" s="73" t="inlineStr"/>
@@ -9354,44 +9354,32 @@
       </c>
       <c r="B90" s="73" t="inlineStr">
         <is>
-          <t>183188250349</t>
-        </is>
-      </c>
-      <c r="C90" s="73" t="inlineStr">
-        <is>
-          <t>NDERFP250709</t>
-        </is>
-      </c>
+          <t>169109642958</t>
+        </is>
+      </c>
+      <c r="C90" s="73" t="inlineStr"/>
       <c r="D90" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nebraska Literacy Data Dashboard (NLDD) </t>
+          <t>CYBER SECURITY MANAGED SERVICES</t>
         </is>
       </c>
       <c r="E90" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Nebraska Department of Education</t>
+          <t>City of Santa Monica</t>
         </is>
       </c>
       <c r="F90" s="73" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G90" s="73" t="inlineStr">
         <is>
-          <t>Interview</t>
-        </is>
-      </c>
-      <c r="H90" s="73" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I90" s="73" t="inlineStr">
-        <is>
-          <t>Interview</t>
-        </is>
-      </c>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H90" s="73" t="inlineStr"/>
+      <c r="I90" s="73" t="inlineStr"/>
       <c r="J90" s="73" t="inlineStr">
         <is>
           <t>2025-10-31</t>
@@ -9399,27 +9387,27 @@
       </c>
       <c r="K90" s="73" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="L90" s="73" t="n"/>
       <c r="M90" s="73" t="inlineStr">
         <is>
-          <t>Consulting</t>
-        </is>
-      </c>
-      <c r="N90" s="73" t="inlineStr"/>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N90" s="73" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O90" s="73" t="inlineStr">
         <is>
           <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="P90" s="73" t="inlineStr"/>
-      <c r="Q90" s="73" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
+      <c r="Q90" s="73" t="inlineStr"/>
       <c r="R90" s="73" t="inlineStr"/>
       <c r="S90" s="73" t="inlineStr"/>
       <c r="T90" s="73" t="inlineStr"/>
@@ -9429,12 +9417,12 @@
       <c r="X90" s="73" t="inlineStr"/>
       <c r="Y90" s="73" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Z90" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/183188250349</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/169109642958</t>
         </is>
       </c>
       <c r="AA90" s="73" t="inlineStr"/>
@@ -9445,23 +9433,23 @@
       </c>
       <c r="B91" s="73" t="inlineStr">
         <is>
-          <t>195685931707</t>
+          <t>173703397101</t>
         </is>
       </c>
       <c r="C91" s="73" t="inlineStr"/>
       <c r="D91" s="73" t="inlineStr">
         <is>
-          <t>Relational Database Administration &amp; Support Services</t>
+          <t>CYBER RISK CONSULTANT</t>
         </is>
       </c>
       <c r="E91" s="73" t="inlineStr">
         <is>
-          <t>Navajo Nation</t>
+          <t>The Public Entity Joint Insurance fund</t>
         </is>
       </c>
       <c r="F91" s="73" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="G91" s="73" t="inlineStr">
@@ -9478,21 +9466,19 @@
       </c>
       <c r="K91" s="73" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="L91" s="75" t="n">
-        <v>225000</v>
-      </c>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="L91" s="73" t="n"/>
       <c r="M91" s="73" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N91" s="73" t="inlineStr"/>
       <c r="O91" s="73" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="P91" s="73" t="inlineStr"/>
@@ -9506,12 +9492,12 @@
       <c r="X91" s="73" t="inlineStr"/>
       <c r="Y91" s="73" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="Z91" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/195685931707</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/173703397101</t>
         </is>
       </c>
       <c r="AA91" s="73" t="inlineStr"/>
@@ -9522,32 +9508,44 @@
       </c>
       <c r="B92" s="73" t="inlineStr">
         <is>
-          <t>183644305108</t>
-        </is>
-      </c>
-      <c r="C92" s="73" t="inlineStr"/>
+          <t>183188250349</t>
+        </is>
+      </c>
+      <c r="C92" s="73" t="inlineStr">
+        <is>
+          <t>NDERFP250709</t>
+        </is>
+      </c>
       <c r="D92" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cybersecurity Risk Assessment </t>
+          <t xml:space="preserve">Nebraska Literacy Data Dashboard (NLDD) </t>
         </is>
       </c>
       <c r="E92" s="73" t="inlineStr">
         <is>
-          <t>Michigan Advocacy Program</t>
+          <t xml:space="preserve"> Nebraska Department of Education</t>
         </is>
       </c>
       <c r="F92" s="73" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="G92" s="73" t="inlineStr">
         <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="H92" s="73" t="inlineStr"/>
-      <c r="I92" s="73" t="inlineStr"/>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="H92" s="73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I92" s="73" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
       <c r="J92" s="73" t="inlineStr">
         <is>
           <t>2025-10-31</t>
@@ -9555,25 +9553,27 @@
       </c>
       <c r="K92" s="73" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="L92" s="75" t="n">
-        <v>66000</v>
-      </c>
-      <c r="M92" s="73" t="inlineStr"/>
-      <c r="N92" s="73" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="L92" s="73" t="n"/>
+      <c r="M92" s="73" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N92" s="73" t="inlineStr"/>
       <c r="O92" s="73" t="inlineStr">
         <is>
           <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="P92" s="73" t="inlineStr"/>
-      <c r="Q92" s="73" t="inlineStr"/>
+      <c r="Q92" s="73" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
       <c r="R92" s="73" t="inlineStr"/>
       <c r="S92" s="73" t="inlineStr"/>
       <c r="T92" s="73" t="inlineStr"/>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="Z92" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/183644305108</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/183188250349</t>
         </is>
       </c>
       <c r="AA92" s="73" t="inlineStr"/>
@@ -9599,27 +9599,23 @@
       </c>
       <c r="B93" s="73" t="inlineStr">
         <is>
-          <t>195157537481</t>
-        </is>
-      </c>
-      <c r="C93" s="73" t="inlineStr">
-        <is>
-          <t>NET-14311_2025_10_18_11_27_13_61</t>
-        </is>
-      </c>
+          <t>183644305108</t>
+        </is>
+      </c>
+      <c r="C93" s="73" t="inlineStr"/>
       <c r="D93" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internet Technology Services </t>
+          <t xml:space="preserve">Cybersecurity Risk Assessment </t>
         </is>
       </c>
       <c r="E93" s="73" t="inlineStr">
         <is>
-          <t>Township of Deerfield</t>
+          <t>Michigan Advocacy Program</t>
         </is>
       </c>
       <c r="F93" s="73" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G93" s="73" t="inlineStr">
@@ -9636,20 +9632,16 @@
       </c>
       <c r="K93" s="73" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="L93" s="75" t="n">
-        <v>16920</v>
-      </c>
-      <c r="M93" s="73" t="inlineStr">
-        <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
+        <v>66000</v>
+      </c>
+      <c r="M93" s="73" t="inlineStr"/>
       <c r="N93" s="73" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O93" s="73" t="inlineStr">
@@ -9668,12 +9660,12 @@
       <c r="X93" s="73" t="inlineStr"/>
       <c r="Y93" s="73" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="Z93" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/195157537481</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/183644305108</t>
         </is>
       </c>
       <c r="AA93" s="73" t="inlineStr"/>
@@ -9684,23 +9676,23 @@
       </c>
       <c r="B94" s="73" t="inlineStr">
         <is>
-          <t>169109642958</t>
+          <t>195685931707</t>
         </is>
       </c>
       <c r="C94" s="73" t="inlineStr"/>
       <c r="D94" s="73" t="inlineStr">
         <is>
-          <t>CYBER SECURITY MANAGED SERVICES</t>
+          <t>Relational Database Administration &amp; Support Services</t>
         </is>
       </c>
       <c r="E94" s="73" t="inlineStr">
         <is>
-          <t>City of Santa Monica</t>
+          <t>Navajo Nation</t>
         </is>
       </c>
       <c r="F94" s="73" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="G94" s="73" t="inlineStr">
@@ -9717,23 +9709,21 @@
       </c>
       <c r="K94" s="73" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="L94" s="73" t="n"/>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="L94" s="75" t="n">
+        <v>225000</v>
+      </c>
       <c r="M94" s="73" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N94" s="73" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
+          <t>Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N94" s="73" t="inlineStr"/>
       <c r="O94" s="73" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="P94" s="73" t="inlineStr"/>
@@ -9747,12 +9737,12 @@
       <c r="X94" s="73" t="inlineStr"/>
       <c r="Y94" s="73" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z94" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/169109642958</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/195685931707</t>
         </is>
       </c>
       <c r="AA94" s="73" t="inlineStr"/>
@@ -9763,18 +9753,22 @@
       </c>
       <c r="B95" s="73" t="inlineStr">
         <is>
-          <t>173703397101</t>
-        </is>
-      </c>
-      <c r="C95" s="73" t="inlineStr"/>
+          <t>195157537481</t>
+        </is>
+      </c>
+      <c r="C95" s="73" t="inlineStr">
+        <is>
+          <t>NET-14311_2025_10_18_11_27_13_61</t>
+        </is>
+      </c>
       <c r="D95" s="73" t="inlineStr">
         <is>
-          <t>CYBER RISK CONSULTANT</t>
+          <t xml:space="preserve">Internet Technology Services </t>
         </is>
       </c>
       <c r="E95" s="73" t="inlineStr">
         <is>
-          <t>The Public Entity Joint Insurance fund</t>
+          <t>Township of Deerfield</t>
         </is>
       </c>
       <c r="F95" s="73" t="inlineStr">
@@ -9796,16 +9790,22 @@
       </c>
       <c r="K95" s="73" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="L95" s="73" t="n"/>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="L95" s="75" t="n">
+        <v>16920</v>
+      </c>
       <c r="M95" s="73" t="inlineStr">
         <is>
-          <t>Consulting</t>
-        </is>
-      </c>
-      <c r="N95" s="73" t="inlineStr"/>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N95" s="73" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
       <c r="O95" s="73" t="inlineStr">
         <is>
           <t>Abhishek Zalani</t>
@@ -9822,12 +9822,12 @@
       <c r="X95" s="73" t="inlineStr"/>
       <c r="Y95" s="73" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z95" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/173703397101</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/195157537481</t>
         </is>
       </c>
       <c r="AA95" s="73" t="inlineStr"/>
@@ -10249,23 +10249,23 @@
       </c>
       <c r="B101" s="73" t="inlineStr">
         <is>
-          <t>181350073058</t>
+          <t>189574763220</t>
         </is>
       </c>
       <c r="C101" s="73" t="inlineStr"/>
       <c r="D101" s="73" t="inlineStr">
         <is>
-          <t>ACCOUNT CLAIM AND IDENTITY VERIFICATION SOFTWARE</t>
+          <t>DPS/ECN RFP PSAPs Cybersecurity Training</t>
         </is>
       </c>
       <c r="E101" s="73" t="inlineStr">
         <is>
-          <t>Michigan State University</t>
+          <t>Minnesota Department of Public Safety</t>
         </is>
       </c>
       <c r="F101" s="73" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="G101" s="73" t="inlineStr">
@@ -10285,16 +10285,18 @@
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="L101" s="73" t="n"/>
+      <c r="L101" s="75" t="n">
+        <v>28800</v>
+      </c>
       <c r="M101" s="73" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="N101" s="73" t="inlineStr"/>
       <c r="O101" s="73" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="P101" s="73" t="inlineStr"/>
@@ -10308,12 +10310,12 @@
       <c r="X101" s="73" t="inlineStr"/>
       <c r="Y101" s="73" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z101" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/181350073058</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/189574763220</t>
         </is>
       </c>
       <c r="AA101" s="73" t="inlineStr"/>
@@ -10324,23 +10326,23 @@
       </c>
       <c r="B102" s="73" t="inlineStr">
         <is>
-          <t>189574763220</t>
+          <t>181350073058</t>
         </is>
       </c>
       <c r="C102" s="73" t="inlineStr"/>
       <c r="D102" s="73" t="inlineStr">
         <is>
-          <t>DPS/ECN RFP PSAPs Cybersecurity Training</t>
+          <t>ACCOUNT CLAIM AND IDENTITY VERIFICATION SOFTWARE</t>
         </is>
       </c>
       <c r="E102" s="73" t="inlineStr">
         <is>
-          <t>Minnesota Department of Public Safety</t>
+          <t>Michigan State University</t>
         </is>
       </c>
       <c r="F102" s="73" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G102" s="73" t="inlineStr">
@@ -10360,18 +10362,16 @@
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="L102" s="75" t="n">
-        <v>28800</v>
-      </c>
+      <c r="L102" s="73" t="n"/>
       <c r="M102" s="73" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="N102" s="73" t="inlineStr"/>
       <c r="O102" s="73" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="P102" s="73" t="inlineStr"/>
@@ -10385,12 +10385,12 @@
       <c r="X102" s="73" t="inlineStr"/>
       <c r="Y102" s="73" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="Z102" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/189574763220</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/181350073058</t>
         </is>
       </c>
       <c r="AA102" s="73" t="inlineStr"/>
@@ -11537,23 +11537,23 @@
       </c>
       <c r="B117" s="73" t="inlineStr">
         <is>
-          <t>211100515005</t>
+          <t>179112632005</t>
         </is>
       </c>
       <c r="C117" s="73" t="inlineStr"/>
       <c r="D117" s="73" t="inlineStr">
         <is>
-          <t>Managed Services for Oracle PeopleSoft in AWS Cloud</t>
+          <t>Snake River Water Headwaters Data Dashboard</t>
         </is>
       </c>
       <c r="E117" s="73" t="inlineStr">
         <is>
-          <t>Central Washington University</t>
+          <t>Teton Conservation District</t>
         </is>
       </c>
       <c r="F117" s="73" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Wyoming</t>
         </is>
       </c>
       <c r="G117" s="73" t="inlineStr">
@@ -11576,7 +11576,7 @@
       <c r="L117" s="73" t="n"/>
       <c r="M117" s="73" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting;Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="N117" s="73" t="inlineStr"/>
@@ -11596,12 +11596,12 @@
       <c r="X117" s="73" t="inlineStr"/>
       <c r="Y117" s="73" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="Z117" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/211100515005</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/179112632005</t>
         </is>
       </c>
       <c r="AA117" s="73" t="inlineStr"/>
@@ -11863,23 +11863,23 @@
       </c>
       <c r="B121" s="73" t="inlineStr">
         <is>
-          <t>179112632005</t>
+          <t>211100515005</t>
         </is>
       </c>
       <c r="C121" s="73" t="inlineStr"/>
       <c r="D121" s="73" t="inlineStr">
         <is>
-          <t>Snake River Water Headwaters Data Dashboard</t>
+          <t>Managed Services for Oracle PeopleSoft in AWS Cloud</t>
         </is>
       </c>
       <c r="E121" s="73" t="inlineStr">
         <is>
-          <t>Teton Conservation District</t>
+          <t>Central Washington University</t>
         </is>
       </c>
       <c r="F121" s="73" t="inlineStr">
         <is>
-          <t>Wyoming</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G121" s="73" t="inlineStr">
@@ -11902,7 +11902,7 @@
       <c r="L121" s="73" t="n"/>
       <c r="M121" s="73" t="inlineStr">
         <is>
-          <t>Consulting;Platform Implementation (ERP, CRMs)</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N121" s="73" t="inlineStr"/>
@@ -11922,12 +11922,12 @@
       <c r="X121" s="73" t="inlineStr"/>
       <c r="Y121" s="73" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z121" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/179112632005</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/211100515005</t>
         </is>
       </c>
       <c r="AA121" s="73" t="inlineStr"/>
@@ -13903,23 +13903,23 @@
       </c>
       <c r="B147" s="73" t="inlineStr">
         <is>
-          <t>200821843696</t>
+          <t>205597215459</t>
         </is>
       </c>
       <c r="C147" s="73" t="inlineStr"/>
       <c r="D147" s="73" t="inlineStr">
         <is>
-          <t>OFFLINE - Information Technology Services</t>
+          <t>SharePoint Migration &amp; LegalServer Integration Project</t>
         </is>
       </c>
       <c r="E147" s="73" t="inlineStr">
         <is>
-          <t>Vineland Housing Authority</t>
+          <t>Legal Aid Society of Mid-New York, Inc. (LASMNY)</t>
         </is>
       </c>
       <c r="F147" s="73" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G147" s="73" t="inlineStr">
@@ -13936,20 +13936,18 @@
       </c>
       <c r="K147" s="73" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L147" s="75" t="n">
-        <v>59920</v>
-      </c>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="L147" s="73" t="n"/>
       <c r="M147" s="73" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="N147" s="73" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O147" s="73" t="inlineStr">
@@ -13968,12 +13966,12 @@
       <c r="X147" s="73" t="inlineStr"/>
       <c r="Y147" s="73" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="Z147" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/200821843696</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/205597215459</t>
         </is>
       </c>
       <c r="AA147" s="73" t="inlineStr"/>
@@ -13984,23 +13982,23 @@
       </c>
       <c r="B148" s="73" t="inlineStr">
         <is>
-          <t>205597215459</t>
+          <t>200821843696</t>
         </is>
       </c>
       <c r="C148" s="73" t="inlineStr"/>
       <c r="D148" s="73" t="inlineStr">
         <is>
-          <t>SharePoint Migration &amp; LegalServer Integration Project</t>
+          <t>OFFLINE - Information Technology Services</t>
         </is>
       </c>
       <c r="E148" s="73" t="inlineStr">
         <is>
-          <t>Legal Aid Society of Mid-New York, Inc. (LASMNY)</t>
+          <t>Vineland Housing Authority</t>
         </is>
       </c>
       <c r="F148" s="73" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="G148" s="73" t="inlineStr">
@@ -14017,18 +14015,20 @@
       </c>
       <c r="K148" s="73" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="L148" s="73" t="n"/>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="L148" s="75" t="n">
+        <v>59920</v>
+      </c>
       <c r="M148" s="73" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N148" s="73" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O148" s="73" t="inlineStr">
@@ -14047,12 +14047,12 @@
       <c r="X148" s="73" t="inlineStr"/>
       <c r="Y148" s="73" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="Z148" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/205597215459</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/200821843696</t>
         </is>
       </c>
       <c r="AA148" s="73" t="inlineStr"/>
@@ -14790,23 +14790,23 @@
       </c>
       <c r="B158" s="73" t="inlineStr">
         <is>
-          <t>205597216474</t>
+          <t>215453148909</t>
         </is>
       </c>
       <c r="C158" s="73" t="inlineStr"/>
       <c r="D158" s="73" t="inlineStr">
         <is>
-          <t>Offline Digital Accessibility Services</t>
+          <t>Information Technology (IT) Consultant Services</t>
         </is>
       </c>
       <c r="E158" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harper College </t>
+          <t xml:space="preserve">Township of Bloomfield </t>
         </is>
       </c>
       <c r="F158" s="73" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="G158" s="73" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="K158" s="73" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="L158" s="73" t="n"/>
@@ -14832,10 +14832,14 @@
           <t>Consulting</t>
         </is>
       </c>
-      <c r="N158" s="73" t="inlineStr"/>
+      <c r="N158" s="73" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
       <c r="O158" s="73" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="P158" s="73" t="inlineStr"/>
@@ -14849,12 +14853,12 @@
       <c r="X158" s="73" t="inlineStr"/>
       <c r="Y158" s="73" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z158" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/205597216474</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/215453148909</t>
         </is>
       </c>
       <c r="AA158" s="73" t="inlineStr"/>
@@ -14940,23 +14944,23 @@
       </c>
       <c r="B160" s="73" t="inlineStr">
         <is>
-          <t>215453148909</t>
+          <t>205597216474</t>
         </is>
       </c>
       <c r="C160" s="73" t="inlineStr"/>
       <c r="D160" s="73" t="inlineStr">
         <is>
-          <t>Information Technology (IT) Consultant Services</t>
+          <t>Offline Digital Accessibility Services</t>
         </is>
       </c>
       <c r="E160" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Township of Bloomfield </t>
+          <t xml:space="preserve">Harper College </t>
         </is>
       </c>
       <c r="F160" s="73" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="G160" s="73" t="inlineStr">
@@ -14973,7 +14977,7 @@
       </c>
       <c r="K160" s="73" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="L160" s="73" t="n"/>
@@ -14982,14 +14986,10 @@
           <t>Consulting</t>
         </is>
       </c>
-      <c r="N160" s="73" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
+      <c r="N160" s="73" t="inlineStr"/>
       <c r="O160" s="73" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="P160" s="73" t="inlineStr"/>
@@ -15003,12 +15003,12 @@
       <c r="X160" s="73" t="inlineStr"/>
       <c r="Y160" s="73" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="Z160" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/215453148909</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/205597216474</t>
         </is>
       </c>
       <c r="AA160" s="73" t="inlineStr"/>
@@ -15825,23 +15825,23 @@
       </c>
       <c r="B171" s="73" t="inlineStr">
         <is>
-          <t>200822611705</t>
+          <t>203838417649</t>
         </is>
       </c>
       <c r="C171" s="73" t="inlineStr"/>
       <c r="D171" s="73" t="inlineStr">
         <is>
-          <t>Public Records Request Management System</t>
+          <t>RFP - 2026 Professional &amp; IT Services - Fair &amp; Open Process - Computer Services</t>
         </is>
       </c>
       <c r="E171" s="73" t="inlineStr">
         <is>
-          <t>Ohio Department of Natural Resources</t>
+          <t>Watchung Borough</t>
         </is>
       </c>
       <c r="F171" s="73" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="G171" s="73" t="inlineStr">
@@ -15864,13 +15864,17 @@
       <c r="L171" s="73" t="n"/>
       <c r="M171" s="73" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
-        </is>
-      </c>
-      <c r="N171" s="73" t="inlineStr"/>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N171" s="73" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
       <c r="O171" s="73" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="P171" s="73" t="inlineStr"/>
@@ -15884,12 +15888,12 @@
       <c r="X171" s="73" t="inlineStr"/>
       <c r="Y171" s="73" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="Z171" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/200822611705</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/203838417649</t>
         </is>
       </c>
       <c r="AA171" s="73" t="inlineStr"/>
@@ -15900,23 +15904,23 @@
       </c>
       <c r="B172" s="73" t="inlineStr">
         <is>
-          <t>199601365715</t>
+          <t>200822611705</t>
         </is>
       </c>
       <c r="C172" s="73" t="inlineStr"/>
       <c r="D172" s="73" t="inlineStr">
         <is>
-          <t>Contracted IT Support Services</t>
+          <t>Public Records Request Management System</t>
         </is>
       </c>
       <c r="E172" s="73" t="inlineStr">
         <is>
-          <t>ECS4Kids</t>
+          <t>Ohio Department of Natural Resources</t>
         </is>
       </c>
       <c r="F172" s="73" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G172" s="73" t="inlineStr">
@@ -15931,23 +15935,21 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="K172" s="73" t="inlineStr"/>
-      <c r="L172" s="75" t="n">
-        <v>291141</v>
-      </c>
+      <c r="K172" s="73" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="L172" s="73" t="n"/>
       <c r="M172" s="73" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N172" s="73" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
+          <t>Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="N172" s="73" t="inlineStr"/>
       <c r="O172" s="73" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="P172" s="73" t="inlineStr"/>
@@ -15966,7 +15968,7 @@
       </c>
       <c r="Z172" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/200822611705</t>
         </is>
       </c>
       <c r="AA172" s="73" t="inlineStr"/>
@@ -16062,23 +16064,23 @@
       </c>
       <c r="B174" s="73" t="inlineStr">
         <is>
-          <t>203838417649</t>
+          <t>199601365715</t>
         </is>
       </c>
       <c r="C174" s="73" t="inlineStr"/>
       <c r="D174" s="73" t="inlineStr">
         <is>
-          <t>RFP - 2026 Professional &amp; IT Services - Fair &amp; Open Process - Computer Services</t>
+          <t>Contracted IT Support Services</t>
         </is>
       </c>
       <c r="E174" s="73" t="inlineStr">
         <is>
-          <t>Watchung Borough</t>
+          <t>ECS4Kids</t>
         </is>
       </c>
       <c r="F174" s="73" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G174" s="73" t="inlineStr">
@@ -16093,20 +16095,18 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="K174" s="73" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="L174" s="73" t="n"/>
+      <c r="K174" s="73" t="inlineStr"/>
+      <c r="L174" s="75" t="n">
+        <v>291141</v>
+      </c>
       <c r="M174" s="73" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N174" s="73" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O174" s="73" t="inlineStr">
@@ -16125,12 +16125,12 @@
       <c r="X174" s="73" t="inlineStr"/>
       <c r="Y174" s="73" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z174" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/203838417649</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
         </is>
       </c>
       <c r="AA174" s="73" t="inlineStr"/>
@@ -16315,27 +16315,23 @@
       </c>
       <c r="B177" s="73" t="inlineStr">
         <is>
-          <t>211098716921</t>
-        </is>
-      </c>
-      <c r="C177" s="73" t="inlineStr">
-        <is>
-          <t>STATE 0000000159SL</t>
-        </is>
-      </c>
+          <t>203233555138</t>
+        </is>
+      </c>
+      <c r="C177" s="73" t="inlineStr"/>
       <c r="D177" s="73" t="inlineStr">
         <is>
-          <t>Endpoint Data Loss Prevention Security Services (REBID)</t>
+          <t>PROFESSIONAL INFORMATION TECHNOLOGY (IT) SERVICES</t>
         </is>
       </c>
       <c r="E177" s="73" t="inlineStr">
         <is>
-          <t>Missouri Information Technology Services Division</t>
+          <t>Avon Lake Regional Water</t>
         </is>
       </c>
       <c r="F177" s="73" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G177" s="73" t="inlineStr">
@@ -16350,7 +16346,7 @@
       </c>
       <c r="I177" s="73" t="inlineStr">
         <is>
-          <t>BAFO</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J177" s="73" t="inlineStr">
@@ -16360,16 +16356,20 @@
       </c>
       <c r="K177" s="73" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="L177" s="73" t="n"/>
       <c r="M177" s="73" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N177" s="73" t="inlineStr"/>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N177" s="73" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
       <c r="O177" s="73" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
@@ -16377,15 +16377,15 @@
       </c>
       <c r="P177" s="73" t="inlineStr">
         <is>
-          <t>BAFO</t>
-        </is>
-      </c>
-      <c r="Q177" s="73" t="inlineStr"/>
-      <c r="R177" s="73" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q177" s="73" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="R177" s="73" t="inlineStr"/>
       <c r="S177" s="73" t="inlineStr"/>
       <c r="T177" s="73" t="inlineStr"/>
       <c r="U177" s="73" t="inlineStr"/>
@@ -16394,12 +16394,12 @@
       <c r="X177" s="73" t="inlineStr"/>
       <c r="Y177" s="73" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="Z177" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/211098716921</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/203233555138</t>
         </is>
       </c>
       <c r="AA177" s="73" t="inlineStr"/>
@@ -16410,23 +16410,27 @@
       </c>
       <c r="B178" s="73" t="inlineStr">
         <is>
-          <t>203233555138</t>
-        </is>
-      </c>
-      <c r="C178" s="73" t="inlineStr"/>
+          <t>211098716921</t>
+        </is>
+      </c>
+      <c r="C178" s="73" t="inlineStr">
+        <is>
+          <t>STATE 0000000159SL</t>
+        </is>
+      </c>
       <c r="D178" s="73" t="inlineStr">
         <is>
-          <t>PROFESSIONAL INFORMATION TECHNOLOGY (IT) SERVICES</t>
+          <t>Endpoint Data Loss Prevention Security Services (REBID)</t>
         </is>
       </c>
       <c r="E178" s="73" t="inlineStr">
         <is>
-          <t>Avon Lake Regional Water</t>
+          <t>Missouri Information Technology Services Division</t>
         </is>
       </c>
       <c r="F178" s="73" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="G178" s="73" t="inlineStr">
@@ -16441,7 +16445,7 @@
       </c>
       <c r="I178" s="73" t="inlineStr">
         <is>
-          <t>Interview</t>
+          <t>BAFO</t>
         </is>
       </c>
       <c r="J178" s="73" t="inlineStr">
@@ -16451,20 +16455,16 @@
       </c>
       <c r="K178" s="73" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="L178" s="73" t="n"/>
       <c r="M178" s="73" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N178" s="73" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
+          <t>Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N178" s="73" t="inlineStr"/>
       <c r="O178" s="73" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
@@ -16472,15 +16472,15 @@
       </c>
       <c r="P178" s="73" t="inlineStr">
         <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q178" s="73" t="inlineStr">
-        <is>
-          <t>2026-01-09</t>
-        </is>
-      </c>
-      <c r="R178" s="73" t="inlineStr"/>
+          <t>BAFO</t>
+        </is>
+      </c>
+      <c r="Q178" s="73" t="inlineStr"/>
+      <c r="R178" s="73" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
       <c r="S178" s="73" t="inlineStr"/>
       <c r="T178" s="73" t="inlineStr"/>
       <c r="U178" s="73" t="inlineStr"/>
@@ -16489,12 +16489,12 @@
       <c r="X178" s="73" t="inlineStr"/>
       <c r="Y178" s="73" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z178" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/203233555138</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/211098716921</t>
         </is>
       </c>
       <c r="AA178" s="73" t="inlineStr"/>
@@ -17805,40 +17805,32 @@
       </c>
       <c r="B195" s="73" t="inlineStr">
         <is>
-          <t>215719776967</t>
+          <t>200525516480</t>
         </is>
       </c>
       <c r="C195" s="73" t="inlineStr"/>
       <c r="D195" s="73" t="inlineStr">
         <is>
-          <t>Medical Licensure / Records Database Maintenance System</t>
+          <t>INFORMATION AND CYBERSECURITY SERVICES</t>
         </is>
       </c>
       <c r="E195" s="73" t="inlineStr">
         <is>
-          <t>West Virginia Board of Medicine</t>
+          <t xml:space="preserve">Washington State Department of Enterprise Services </t>
         </is>
       </c>
       <c r="F195" s="73" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G195" s="73" t="inlineStr">
         <is>
-          <t>Interview</t>
-        </is>
-      </c>
-      <c r="H195" s="73" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I195" s="73" t="inlineStr">
-        <is>
-          <t>Interview</t>
-        </is>
-      </c>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H195" s="73" t="inlineStr"/>
+      <c r="I195" s="73" t="inlineStr"/>
       <c r="J195" s="73" t="inlineStr">
         <is>
           <t>2025-12-03</t>
@@ -17846,33 +17838,23 @@
       </c>
       <c r="K195" s="73" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="L195" s="75" t="n">
-        <v>666000</v>
-      </c>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="L195" s="73" t="n"/>
       <c r="M195" s="73" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
-        </is>
-      </c>
-      <c r="N195" s="73" t="inlineStr">
-        <is>
-          <t>Offline;Portal</t>
-        </is>
-      </c>
+          <t>Managed Services (MSP);Staff Augmentation;Support &amp; Maintenance;Consulting</t>
+        </is>
+      </c>
+      <c r="N195" s="73" t="inlineStr"/>
       <c r="O195" s="73" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="P195" s="73" t="inlineStr"/>
-      <c r="Q195" s="73" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
+      <c r="Q195" s="73" t="inlineStr"/>
       <c r="R195" s="73" t="inlineStr"/>
       <c r="S195" s="73" t="inlineStr"/>
       <c r="T195" s="73" t="inlineStr"/>
@@ -17882,12 +17864,12 @@
       <c r="X195" s="73" t="inlineStr"/>
       <c r="Y195" s="73" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z195" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/215719776967</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/200525516480</t>
         </is>
       </c>
       <c r="AA195" s="73" t="inlineStr"/>
@@ -17898,32 +17880,40 @@
       </c>
       <c r="B196" s="73" t="inlineStr">
         <is>
-          <t>253070244584</t>
+          <t>215719776967</t>
         </is>
       </c>
       <c r="C196" s="73" t="inlineStr"/>
       <c r="D196" s="73" t="inlineStr">
         <is>
-          <t>Website Theme Upgrade and Compatibility Improvements</t>
+          <t>Medical Licensure / Records Database Maintenance System</t>
         </is>
       </c>
       <c r="E196" s="73" t="inlineStr">
         <is>
-          <t>Collier County</t>
+          <t>West Virginia Board of Medicine</t>
         </is>
       </c>
       <c r="F196" s="73" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G196" s="73" t="inlineStr">
         <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="H196" s="73" t="inlineStr"/>
-      <c r="I196" s="73" t="inlineStr"/>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="H196" s="73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I196" s="73" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
       <c r="J196" s="73" t="inlineStr">
         <is>
           <t>2025-12-03</t>
@@ -17931,23 +17921,33 @@
       </c>
       <c r="K196" s="73" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="L196" s="73" t="n"/>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="L196" s="75" t="n">
+        <v>666000</v>
+      </c>
       <c r="M196" s="73" t="inlineStr">
         <is>
-          <t>Consulting</t>
-        </is>
-      </c>
-      <c r="N196" s="73" t="inlineStr"/>
+          <t>Modernization / Migration</t>
+        </is>
+      </c>
+      <c r="N196" s="73" t="inlineStr">
+        <is>
+          <t>Offline;Portal</t>
+        </is>
+      </c>
       <c r="O196" s="73" t="inlineStr">
         <is>
-          <t>Vinay Srinivasan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="P196" s="73" t="inlineStr"/>
-      <c r="Q196" s="73" t="inlineStr"/>
+      <c r="Q196" s="73" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
       <c r="R196" s="73" t="inlineStr"/>
       <c r="S196" s="73" t="inlineStr"/>
       <c r="T196" s="73" t="inlineStr"/>
@@ -17957,12 +17957,12 @@
       <c r="X196" s="73" t="inlineStr"/>
       <c r="Y196" s="73" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z196" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/253070244584</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/215719776967</t>
         </is>
       </c>
       <c r="AA196" s="73" t="inlineStr"/>
@@ -17973,23 +17973,23 @@
       </c>
       <c r="B197" s="73" t="inlineStr">
         <is>
-          <t>200525516480</t>
+          <t>253070244584</t>
         </is>
       </c>
       <c r="C197" s="73" t="inlineStr"/>
       <c r="D197" s="73" t="inlineStr">
         <is>
-          <t>INFORMATION AND CYBERSECURITY SERVICES</t>
+          <t>Website Theme Upgrade and Compatibility Improvements</t>
         </is>
       </c>
       <c r="E197" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington State Department of Enterprise Services </t>
+          <t>Collier County</t>
         </is>
       </c>
       <c r="F197" s="73" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G197" s="73" t="inlineStr">
@@ -18012,13 +18012,13 @@
       <c r="L197" s="73" t="n"/>
       <c r="M197" s="73" t="inlineStr">
         <is>
-          <t>Managed Services (MSP);Staff Augmentation;Support &amp; Maintenance;Consulting</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N197" s="73" t="inlineStr"/>
       <c r="O197" s="73" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Vinay Srinivasan</t>
         </is>
       </c>
       <c r="P197" s="73" t="inlineStr"/>
@@ -18032,12 +18032,12 @@
       <c r="X197" s="73" t="inlineStr"/>
       <c r="Y197" s="73" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="Z197" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/200525516480</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/253070244584</t>
         </is>
       </c>
       <c r="AA197" s="73" t="inlineStr"/>
@@ -18358,23 +18358,23 @@
       </c>
       <c r="B202" s="73" t="inlineStr">
         <is>
-          <t>213938568948</t>
+          <t>225968263907</t>
         </is>
       </c>
       <c r="C202" s="73" t="inlineStr"/>
       <c r="D202" s="73" t="inlineStr">
         <is>
-          <t>Managed Detection and Response (MDR) Services</t>
+          <t xml:space="preserve"> Information Technology Microsoft 365 Licensing for 2026</t>
         </is>
       </c>
       <c r="E202" s="73" t="inlineStr">
         <is>
-          <t>City of Pasadena</t>
+          <t xml:space="preserve">Barton County </t>
         </is>
       </c>
       <c r="F202" s="73" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="G202" s="73" t="inlineStr">
@@ -18397,7 +18397,7 @@
       <c r="L202" s="73" t="n"/>
       <c r="M202" s="73" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Reseller</t>
         </is>
       </c>
       <c r="N202" s="73" t="inlineStr">
@@ -18421,12 +18421,12 @@
       <c r="X202" s="73" t="inlineStr"/>
       <c r="Y202" s="73" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z202" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/213938568948</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/225968263907</t>
         </is>
       </c>
       <c r="AA202" s="73" t="inlineStr"/>
@@ -18437,23 +18437,23 @@
       </c>
       <c r="B203" s="73" t="inlineStr">
         <is>
-          <t>225968263907</t>
+          <t>213938568948</t>
         </is>
       </c>
       <c r="C203" s="73" t="inlineStr"/>
       <c r="D203" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Information Technology Microsoft 365 Licensing for 2026</t>
+          <t>Managed Detection and Response (MDR) Services</t>
         </is>
       </c>
       <c r="E203" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barton County </t>
+          <t>City of Pasadena</t>
         </is>
       </c>
       <c r="F203" s="73" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G203" s="73" t="inlineStr">
@@ -18476,7 +18476,7 @@
       <c r="L203" s="73" t="n"/>
       <c r="M203" s="73" t="inlineStr">
         <is>
-          <t>Reseller</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N203" s="73" t="inlineStr">
@@ -18500,12 +18500,12 @@
       <c r="X203" s="73" t="inlineStr"/>
       <c r="Y203" s="73" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z203" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/225968263907</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/213938568948</t>
         </is>
       </c>
       <c r="AA203" s="73" t="inlineStr"/>
@@ -18516,23 +18516,23 @@
       </c>
       <c r="B204" s="73" t="inlineStr">
         <is>
-          <t>231112581865</t>
+          <t>227566173914</t>
         </is>
       </c>
       <c r="C204" s="73" t="inlineStr"/>
       <c r="D204" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrated Data Management System </t>
+          <t>Digital Platform Maintenance and Enhancement for H2Ohio Administration</t>
         </is>
       </c>
       <c r="E204" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">County of York </t>
+          <t xml:space="preserve">Ohio Department of Agriculture </t>
         </is>
       </c>
       <c r="F204" s="73" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G204" s="73" t="inlineStr">
@@ -18555,17 +18555,13 @@
       <c r="L204" s="73" t="n"/>
       <c r="M204" s="73" t="inlineStr">
         <is>
-          <t>Consulting</t>
-        </is>
-      </c>
-      <c r="N204" s="73" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
+          <t>Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N204" s="73" t="inlineStr"/>
       <c r="O204" s="73" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="P204" s="73" t="inlineStr"/>
@@ -18579,12 +18575,12 @@
       <c r="X204" s="73" t="inlineStr"/>
       <c r="Y204" s="73" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z204" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/231112581865</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/227566173914</t>
         </is>
       </c>
       <c r="AA204" s="73" t="inlineStr"/>
@@ -18595,23 +18591,23 @@
       </c>
       <c r="B205" s="73" t="inlineStr">
         <is>
-          <t>211158518511</t>
+          <t>231112581865</t>
         </is>
       </c>
       <c r="C205" s="73" t="inlineStr"/>
       <c r="D205" s="73" t="inlineStr">
         <is>
-          <t>OFF-Computer Systems, Software Applications &amp; General Maintenance/IT Services</t>
+          <t xml:space="preserve">Integrated Data Management System </t>
         </is>
       </c>
       <c r="E205" s="73" t="inlineStr">
         <is>
-          <t>Township of West Caldwell</t>
+          <t xml:space="preserve">County of York </t>
         </is>
       </c>
       <c r="F205" s="73" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G205" s="73" t="inlineStr">
@@ -18628,20 +18624,18 @@
       </c>
       <c r="K205" s="73" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="L205" s="75" t="n">
-        <v>29940</v>
-      </c>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="L205" s="73" t="n"/>
       <c r="M205" s="73" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N205" s="73" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O205" s="73" t="inlineStr">
@@ -18660,12 +18654,12 @@
       <c r="X205" s="73" t="inlineStr"/>
       <c r="Y205" s="73" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z205" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/211158518511</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/231112581865</t>
         </is>
       </c>
       <c r="AA205" s="73" t="inlineStr"/>
@@ -18676,23 +18670,23 @@
       </c>
       <c r="B206" s="73" t="inlineStr">
         <is>
-          <t>220701567684</t>
+          <t>211158518511</t>
         </is>
       </c>
       <c r="C206" s="73" t="inlineStr"/>
       <c r="D206" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft Licensing 2025 </t>
+          <t>OFF-Computer Systems, Software Applications &amp; General Maintenance/IT Services</t>
         </is>
       </c>
       <c r="E206" s="73" t="inlineStr">
         <is>
-          <t>Wentzville School District</t>
+          <t>Township of West Caldwell</t>
         </is>
       </c>
       <c r="F206" s="73" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="G206" s="73" t="inlineStr">
@@ -18709,21 +18703,25 @@
       </c>
       <c r="K206" s="73" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="L206" s="75" t="n">
-        <v>224355</v>
+        <v>29940</v>
       </c>
       <c r="M206" s="73" t="inlineStr">
         <is>
-          <t>Reseller</t>
-        </is>
-      </c>
-      <c r="N206" s="73" t="inlineStr"/>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N206" s="73" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
       <c r="O206" s="73" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="P206" s="73" t="inlineStr"/>
@@ -18737,12 +18735,12 @@
       <c r="X206" s="73" t="inlineStr"/>
       <c r="Y206" s="73" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z206" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/220701567684</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/211158518511</t>
         </is>
       </c>
       <c r="AA206" s="73" t="inlineStr"/>
@@ -18753,23 +18751,23 @@
       </c>
       <c r="B207" s="73" t="inlineStr">
         <is>
-          <t>202092460757</t>
+          <t>220701567684</t>
         </is>
       </c>
       <c r="C207" s="73" t="inlineStr"/>
       <c r="D207" s="73" t="inlineStr">
         <is>
-          <t>Technical Staff Augmentation Consulting Services</t>
+          <t xml:space="preserve">Microsoft Licensing 2025 </t>
         </is>
       </c>
       <c r="E207" s="73" t="inlineStr">
         <is>
-          <t>New Mexico State University [NM]</t>
+          <t>Wentzville School District</t>
         </is>
       </c>
       <c r="F207" s="73" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="G207" s="73" t="inlineStr">
@@ -18786,23 +18784,21 @@
       </c>
       <c r="K207" s="73" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L207" s="73" t="n"/>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="L207" s="75" t="n">
+        <v>224355</v>
+      </c>
       <c r="M207" s="73" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
-        </is>
-      </c>
-      <c r="N207" s="73" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
+          <t>Reseller</t>
+        </is>
+      </c>
+      <c r="N207" s="73" t="inlineStr"/>
       <c r="O207" s="73" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="P207" s="73" t="inlineStr"/>
@@ -18816,12 +18812,12 @@
       <c r="X207" s="73" t="inlineStr"/>
       <c r="Y207" s="73" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z207" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/202092460757</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/220701567684</t>
         </is>
       </c>
       <c r="AA207" s="73" t="inlineStr"/>
@@ -18832,23 +18828,23 @@
       </c>
       <c r="B208" s="73" t="inlineStr">
         <is>
-          <t>227566173914</t>
+          <t>202092460757</t>
         </is>
       </c>
       <c r="C208" s="73" t="inlineStr"/>
       <c r="D208" s="73" t="inlineStr">
         <is>
-          <t>Digital Platform Maintenance and Enhancement for H2Ohio Administration</t>
+          <t>Technical Staff Augmentation Consulting Services</t>
         </is>
       </c>
       <c r="E208" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ohio Department of Agriculture </t>
+          <t>New Mexico State University [NM]</t>
         </is>
       </c>
       <c r="F208" s="73" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="G208" s="73" t="inlineStr">
@@ -18865,16 +18861,20 @@
       </c>
       <c r="K208" s="73" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="L208" s="73" t="n"/>
       <c r="M208" s="73" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N208" s="73" t="inlineStr"/>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="N208" s="73" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O208" s="73" t="inlineStr">
         <is>
           <t>Abhishek Zalani</t>
@@ -18891,12 +18891,12 @@
       <c r="X208" s="73" t="inlineStr"/>
       <c r="Y208" s="73" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z208" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/227566173914</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/202092460757</t>
         </is>
       </c>
       <c r="AA208" s="73" t="inlineStr"/>
@@ -20950,23 +20950,23 @@
       </c>
       <c r="B234" s="73" t="inlineStr">
         <is>
-          <t>222282811080</t>
+          <t>222376728277</t>
         </is>
       </c>
       <c r="C234" s="73" t="inlineStr"/>
       <c r="D234" s="73" t="inlineStr">
         <is>
-          <t>Training &amp; Consultation for Ellucian Colleague</t>
+          <t>Vulnerability Assessment, Cybersecurity Audit, &amp; Penetration Testing Services</t>
         </is>
       </c>
       <c r="E234" s="73" t="inlineStr">
         <is>
-          <t>Spartanburg Community College</t>
+          <t>Marina Coast Water District</t>
         </is>
       </c>
       <c r="F234" s="73" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G234" s="73" t="inlineStr">
@@ -20989,13 +20989,13 @@
       <c r="L234" s="73" t="n"/>
       <c r="M234" s="73" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N234" s="73" t="inlineStr"/>
       <c r="O234" s="73" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="P234" s="73" t="inlineStr"/>
@@ -21014,7 +21014,7 @@
       </c>
       <c r="Z234" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/222282811080</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/222376728277</t>
         </is>
       </c>
       <c r="AA234" s="73" t="inlineStr"/>
@@ -21025,23 +21025,23 @@
       </c>
       <c r="B235" s="73" t="inlineStr">
         <is>
-          <t>222376728277</t>
+          <t>222282811080</t>
         </is>
       </c>
       <c r="C235" s="73" t="inlineStr"/>
       <c r="D235" s="73" t="inlineStr">
         <is>
-          <t>Vulnerability Assessment, Cybersecurity Audit, &amp; Penetration Testing Services</t>
+          <t>Training &amp; Consultation for Ellucian Colleague</t>
         </is>
       </c>
       <c r="E235" s="73" t="inlineStr">
         <is>
-          <t>Marina Coast Water District</t>
+          <t>Spartanburg Community College</t>
         </is>
       </c>
       <c r="F235" s="73" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G235" s="73" t="inlineStr">
@@ -21064,13 +21064,13 @@
       <c r="L235" s="73" t="n"/>
       <c r="M235" s="73" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="N235" s="73" t="inlineStr"/>
       <c r="O235" s="73" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="P235" s="73" t="inlineStr"/>
@@ -21089,7 +21089,7 @@
       </c>
       <c r="Z235" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/222376728277</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/222282811080</t>
         </is>
       </c>
       <c r="AA235" s="73" t="inlineStr"/>
@@ -21268,28 +21268,28 @@
       </c>
       <c r="B238" s="73" t="inlineStr">
         <is>
-          <t>216534904514</t>
+          <t>232534112960</t>
         </is>
       </c>
       <c r="C238" s="73" t="inlineStr"/>
       <c r="D238" s="73" t="inlineStr">
         <is>
-          <t>OFF-Regional Data Portal Consultant Services</t>
+          <t xml:space="preserve">Information Technology Services </t>
         </is>
       </c>
       <c r="E238" s="73" t="inlineStr">
         <is>
-          <t>Pioneer Valley Planning Commission</t>
+          <t>Oklahoma City Urban RenewalAuthority (OCURA)</t>
         </is>
       </c>
       <c r="F238" s="73" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="G238" s="73" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H238" s="73" t="inlineStr"/>
@@ -21304,22 +21304,16 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="L238" s="75" t="n">
-        <v>94350</v>
-      </c>
+      <c r="L238" s="73" t="n"/>
       <c r="M238" s="73" t="inlineStr">
         <is>
-          <t>Consulting</t>
-        </is>
-      </c>
-      <c r="N238" s="73" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N238" s="73" t="inlineStr"/>
       <c r="O238" s="73" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="P238" s="73" t="inlineStr"/>
@@ -21333,12 +21327,12 @@
       <c r="X238" s="73" t="inlineStr"/>
       <c r="Y238" s="73" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z238" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/216534904514</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/232534112960</t>
         </is>
       </c>
       <c r="AA238" s="73" t="inlineStr"/>
@@ -21349,23 +21343,23 @@
       </c>
       <c r="B239" s="73" t="inlineStr">
         <is>
-          <t>232534112960</t>
+          <t>216534904517</t>
         </is>
       </c>
       <c r="C239" s="73" t="inlineStr"/>
       <c r="D239" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Information Technology Services </t>
+          <t>INFORMATION TECHNOLOGY CONSULTANT AND SERVICES</t>
         </is>
       </c>
       <c r="E239" s="73" t="inlineStr">
         <is>
-          <t>Oklahoma City Urban RenewalAuthority (OCURA)</t>
+          <t>Stillwater Township</t>
         </is>
       </c>
       <c r="F239" s="73" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="G239" s="73" t="inlineStr">
@@ -21382,7 +21376,7 @@
       </c>
       <c r="K239" s="73" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="L239" s="73" t="n"/>
@@ -21391,7 +21385,11 @@
           <t>Managed Services (MSP)</t>
         </is>
       </c>
-      <c r="N239" s="73" t="inlineStr"/>
+      <c r="N239" s="73" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
       <c r="O239" s="73" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
@@ -21408,12 +21406,12 @@
       <c r="X239" s="73" t="inlineStr"/>
       <c r="Y239" s="73" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z239" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/232534112960</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/216534904517</t>
         </is>
       </c>
       <c r="AA239" s="73" t="inlineStr"/>
@@ -21424,28 +21422,28 @@
       </c>
       <c r="B240" s="73" t="inlineStr">
         <is>
-          <t>216534904517</t>
+          <t>216534904514</t>
         </is>
       </c>
       <c r="C240" s="73" t="inlineStr"/>
       <c r="D240" s="73" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY CONSULTANT AND SERVICES</t>
+          <t>OFF-Regional Data Portal Consultant Services</t>
         </is>
       </c>
       <c r="E240" s="73" t="inlineStr">
         <is>
-          <t>Stillwater Township</t>
+          <t>Pioneer Valley Planning Commission</t>
         </is>
       </c>
       <c r="F240" s="73" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="G240" s="73" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H240" s="73" t="inlineStr"/>
@@ -21457,13 +21455,15 @@
       </c>
       <c r="K240" s="73" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="L240" s="73" t="n"/>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="L240" s="75" t="n">
+        <v>94350</v>
+      </c>
       <c r="M240" s="73" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N240" s="73" t="inlineStr">
@@ -21473,7 +21473,7 @@
       </c>
       <c r="O240" s="73" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="P240" s="73" t="inlineStr"/>
@@ -21492,7 +21492,7 @@
       </c>
       <c r="Z240" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/216534904517</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/216534904514</t>
         </is>
       </c>
       <c r="AA240" s="73" t="inlineStr"/>
@@ -21756,13 +21756,17 @@
       </c>
       <c r="B244" s="73" t="inlineStr">
         <is>
-          <t>252347523776</t>
-        </is>
-      </c>
-      <c r="C244" s="73" t="inlineStr"/>
+          <t>254846547669</t>
+        </is>
+      </c>
+      <c r="C244" s="73" t="inlineStr">
+        <is>
+          <t>00002665</t>
+        </is>
+      </c>
       <c r="D244" s="73" t="inlineStr">
         <is>
-          <t>BTS On-Call Services - UI/UX &amp; SERVICE DESIGN</t>
+          <t>BTS On-Call Services - GENERAL APPLICATION DEVELOPMENT</t>
         </is>
       </c>
       <c r="E244" s="73" t="inlineStr">
@@ -21820,7 +21824,7 @@
       </c>
       <c r="Z244" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/252347523776</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/254846547669</t>
         </is>
       </c>
       <c r="AA244" s="73" t="inlineStr"/>
@@ -21831,13 +21835,13 @@
       </c>
       <c r="B245" s="73" t="inlineStr">
         <is>
-          <t>253056990937</t>
+          <t>254848701168</t>
         </is>
       </c>
       <c r="C245" s="73" t="inlineStr"/>
       <c r="D245" s="73" t="inlineStr">
         <is>
-          <t>BTS On-Call Services - SAP BASIS AND SYSTEM SUPPORT AND ENGINEERING</t>
+          <t>BTS On-Call Services - INFORMATION TECHNOLOGIES PLANNING, BUSINESS ANALYSIS, PROFESSIONAL DEVELOPMENT, AND PROCESS FACILITATION</t>
         </is>
       </c>
       <c r="E245" s="73" t="inlineStr">
@@ -21895,7 +21899,7 @@
       </c>
       <c r="Z245" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/253056990937</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/254848701168</t>
         </is>
       </c>
       <c r="AA245" s="73" t="inlineStr"/>
@@ -21906,13 +21910,13 @@
       </c>
       <c r="B246" s="73" t="inlineStr">
         <is>
-          <t>251773184703</t>
+          <t>253056991937</t>
         </is>
       </c>
       <c r="C246" s="73" t="inlineStr"/>
       <c r="D246" s="73" t="inlineStr">
         <is>
-          <t>BTS On-Call Services - WEB APPLICATION DEVELOPMENT</t>
+          <t>BTS On-Call Services - DATA PRODUCT &amp; PLATFORM DEVELOPMENT</t>
         </is>
       </c>
       <c r="E246" s="73" t="inlineStr">
@@ -21970,7 +21974,7 @@
       </c>
       <c r="Z246" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/251773184703</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/253056991937</t>
         </is>
       </c>
       <c r="AA246" s="73" t="inlineStr"/>
@@ -21981,13 +21985,13 @@
       </c>
       <c r="B247" s="73" t="inlineStr">
         <is>
-          <t>254848701154</t>
+          <t>252347523776</t>
         </is>
       </c>
       <c r="C247" s="73" t="inlineStr"/>
       <c r="D247" s="73" t="inlineStr">
         <is>
-          <t>BTS On-Call Services - SERVICENOW PLATFORM DEVELOPMENT</t>
+          <t>BTS On-Call Services - UI/UX &amp; SERVICE DESIGN</t>
         </is>
       </c>
       <c r="E247" s="73" t="inlineStr">
@@ -22045,7 +22049,7 @@
       </c>
       <c r="Z247" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/254848701154</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/252347523776</t>
         </is>
       </c>
       <c r="AA247" s="73" t="inlineStr"/>
@@ -22056,13 +22060,13 @@
       </c>
       <c r="B248" s="73" t="inlineStr">
         <is>
-          <t>254848701166</t>
+          <t>254848701154</t>
         </is>
       </c>
       <c r="C248" s="73" t="inlineStr"/>
       <c r="D248" s="73" t="inlineStr">
         <is>
-          <t>BTS On-Call Services - QUALITY ASSURANCE</t>
+          <t>BTS On-Call Services - SERVICENOW PLATFORM DEVELOPMENT</t>
         </is>
       </c>
       <c r="E248" s="73" t="inlineStr">
@@ -22120,7 +22124,7 @@
       </c>
       <c r="Z248" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/254848701166</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/254848701154</t>
         </is>
       </c>
       <c r="AA248" s="73" t="inlineStr"/>
@@ -22131,13 +22135,13 @@
       </c>
       <c r="B249" s="73" t="inlineStr">
         <is>
-          <t>252347523820</t>
+          <t>254848701166</t>
         </is>
       </c>
       <c r="C249" s="73" t="inlineStr"/>
       <c r="D249" s="73" t="inlineStr">
         <is>
-          <t>BTS On-Call Services - PROJECT MANAGEMENT</t>
+          <t>BTS On-Call Services - QUALITY ASSURANCE</t>
         </is>
       </c>
       <c r="E249" s="73" t="inlineStr">
@@ -22195,7 +22199,7 @@
       </c>
       <c r="Z249" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/252347523820</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/254848701166</t>
         </is>
       </c>
       <c r="AA249" s="73" t="inlineStr"/>
@@ -22206,13 +22210,13 @@
       </c>
       <c r="B250" s="73" t="inlineStr">
         <is>
-          <t>254846547686</t>
+          <t>251773184703</t>
         </is>
       </c>
       <c r="C250" s="73" t="inlineStr"/>
       <c r="D250" s="73" t="inlineStr">
         <is>
-          <t>BTS On-Call Services -SAP DEVELOPMENT</t>
+          <t>BTS On-Call Services - WEB APPLICATION DEVELOPMENT</t>
         </is>
       </c>
       <c r="E250" s="73" t="inlineStr">
@@ -22270,7 +22274,7 @@
       </c>
       <c r="Z250" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/254846547686</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/251773184703</t>
         </is>
       </c>
       <c r="AA250" s="73" t="inlineStr"/>
@@ -22281,13 +22285,13 @@
       </c>
       <c r="B251" s="73" t="inlineStr">
         <is>
-          <t>254846547704</t>
+          <t>253056990937</t>
         </is>
       </c>
       <c r="C251" s="73" t="inlineStr"/>
       <c r="D251" s="73" t="inlineStr">
         <is>
-          <t>BTS On-Call Services - PRODUCT MANAGEMENT SERVICES</t>
+          <t>BTS On-Call Services - SAP BASIS AND SYSTEM SUPPORT AND ENGINEERING</t>
         </is>
       </c>
       <c r="E251" s="73" t="inlineStr">
@@ -22345,7 +22349,7 @@
       </c>
       <c r="Z251" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/254846547704</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/253056990937</t>
         </is>
       </c>
       <c r="AA251" s="73" t="inlineStr"/>
@@ -22356,17 +22360,13 @@
       </c>
       <c r="B252" s="73" t="inlineStr">
         <is>
-          <t>254846547669</t>
-        </is>
-      </c>
-      <c r="C252" s="73" t="inlineStr">
-        <is>
-          <t>00002665</t>
-        </is>
-      </c>
+          <t>252347523820</t>
+        </is>
+      </c>
+      <c r="C252" s="73" t="inlineStr"/>
       <c r="D252" s="73" t="inlineStr">
         <is>
-          <t>BTS On-Call Services - GENERAL APPLICATION DEVELOPMENT</t>
+          <t>BTS On-Call Services - PROJECT MANAGEMENT</t>
         </is>
       </c>
       <c r="E252" s="73" t="inlineStr">
@@ -22424,7 +22424,7 @@
       </c>
       <c r="Z252" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/254846547669</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/252347523820</t>
         </is>
       </c>
       <c r="AA252" s="73" t="inlineStr"/>
@@ -22435,13 +22435,13 @@
       </c>
       <c r="B253" s="73" t="inlineStr">
         <is>
-          <t>254848701168</t>
+          <t>254846547686</t>
         </is>
       </c>
       <c r="C253" s="73" t="inlineStr"/>
       <c r="D253" s="73" t="inlineStr">
         <is>
-          <t>BTS On-Call Services - INFORMATION TECHNOLOGIES PLANNING, BUSINESS ANALYSIS, PROFESSIONAL DEVELOPMENT, AND PROCESS FACILITATION</t>
+          <t>BTS On-Call Services -SAP DEVELOPMENT</t>
         </is>
       </c>
       <c r="E253" s="73" t="inlineStr">
@@ -22499,7 +22499,7 @@
       </c>
       <c r="Z253" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/254848701168</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/254846547686</t>
         </is>
       </c>
       <c r="AA253" s="73" t="inlineStr"/>
@@ -22510,13 +22510,13 @@
       </c>
       <c r="B254" s="73" t="inlineStr">
         <is>
-          <t>253056991937</t>
+          <t>254846547704</t>
         </is>
       </c>
       <c r="C254" s="73" t="inlineStr"/>
       <c r="D254" s="73" t="inlineStr">
         <is>
-          <t>BTS On-Call Services - DATA PRODUCT &amp; PLATFORM DEVELOPMENT</t>
+          <t>BTS On-Call Services - PRODUCT MANAGEMENT SERVICES</t>
         </is>
       </c>
       <c r="E254" s="73" t="inlineStr">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="Z254" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/253056991937</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/254846547704</t>
         </is>
       </c>
       <c r="AA254" s="73" t="inlineStr"/>
@@ -23597,32 +23597,40 @@
       </c>
       <c r="B267" s="73" t="inlineStr">
         <is>
-          <t>231822297828</t>
+          <t>232534113012</t>
         </is>
       </c>
       <c r="C267" s="73" t="inlineStr"/>
       <c r="D267" s="73" t="inlineStr">
         <is>
-          <t>Technology Managed Service Provider</t>
+          <t>Constituent Relationship Management (CRM) System for the North Dakota Office of the Governor</t>
         </is>
       </c>
       <c r="E267" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">City of Two Rivers </t>
+          <t>Office of Management and Budget Facilities Division</t>
         </is>
       </c>
       <c r="F267" s="73" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>North Dakota</t>
         </is>
       </c>
       <c r="G267" s="73" t="inlineStr">
         <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="H267" s="73" t="inlineStr"/>
-      <c r="I267" s="73" t="inlineStr"/>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="H267" s="73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I267" s="73" t="inlineStr">
+        <is>
+          <t>BAFO</t>
+        </is>
+      </c>
       <c r="J267" s="73" t="inlineStr">
         <is>
           <t>2025-12-23</t>
@@ -23636,22 +23644,30 @@
       <c r="L267" s="73" t="n"/>
       <c r="M267" s="73" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="N267" s="73" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O267" s="73" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
-        </is>
-      </c>
-      <c r="P267" s="73" t="inlineStr"/>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="P267" s="73" t="inlineStr">
+        <is>
+          <t>BAFO</t>
+        </is>
+      </c>
       <c r="Q267" s="73" t="inlineStr"/>
-      <c r="R267" s="73" t="inlineStr"/>
+      <c r="R267" s="73" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
       <c r="S267" s="73" t="inlineStr"/>
       <c r="T267" s="73" t="inlineStr"/>
       <c r="U267" s="73" t="inlineStr"/>
@@ -23660,12 +23676,12 @@
       <c r="X267" s="73" t="inlineStr"/>
       <c r="Y267" s="73" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z267" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/231822297828</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/232534113012</t>
         </is>
       </c>
       <c r="AA267" s="73" t="inlineStr"/>
@@ -23676,40 +23692,32 @@
       </c>
       <c r="B268" s="73" t="inlineStr">
         <is>
-          <t>232534113012</t>
+          <t>231822297828</t>
         </is>
       </c>
       <c r="C268" s="73" t="inlineStr"/>
       <c r="D268" s="73" t="inlineStr">
         <is>
-          <t>Constituent Relationship Management (CRM) System for the North Dakota Office of the Governor</t>
+          <t>Technology Managed Service Provider</t>
         </is>
       </c>
       <c r="E268" s="73" t="inlineStr">
         <is>
-          <t>Office of Management and Budget Facilities Division</t>
+          <t xml:space="preserve">City of Two Rivers </t>
         </is>
       </c>
       <c r="F268" s="73" t="inlineStr">
         <is>
-          <t>North Dakota</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G268" s="73" t="inlineStr">
         <is>
-          <t>Interview</t>
-        </is>
-      </c>
-      <c r="H268" s="73" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I268" s="73" t="inlineStr">
-        <is>
-          <t>BAFO</t>
-        </is>
-      </c>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H268" s="73" t="inlineStr"/>
+      <c r="I268" s="73" t="inlineStr"/>
       <c r="J268" s="73" t="inlineStr">
         <is>
           <t>2025-12-23</t>
@@ -23723,30 +23731,22 @@
       <c r="L268" s="73" t="n"/>
       <c r="M268" s="73" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N268" s="73" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O268" s="73" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
-        </is>
-      </c>
-      <c r="P268" s="73" t="inlineStr">
-        <is>
-          <t>BAFO</t>
-        </is>
-      </c>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="P268" s="73" t="inlineStr"/>
       <c r="Q268" s="73" t="inlineStr"/>
-      <c r="R268" s="73" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
+      <c r="R268" s="73" t="inlineStr"/>
       <c r="S268" s="73" t="inlineStr"/>
       <c r="T268" s="73" t="inlineStr"/>
       <c r="U268" s="73" t="inlineStr"/>
@@ -23755,12 +23755,12 @@
       <c r="X268" s="73" t="inlineStr"/>
       <c r="Y268" s="73" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z268" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/232534113012</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/231822297828</t>
         </is>
       </c>
       <c r="AA268" s="73" t="inlineStr"/>
@@ -24314,27 +24314,23 @@
       </c>
       <c r="B276" s="73" t="inlineStr">
         <is>
-          <t>235608145596</t>
-        </is>
-      </c>
-      <c r="C276" s="73" t="inlineStr">
-        <is>
-          <t>K26-0033-25</t>
-        </is>
-      </c>
+          <t>235322596041</t>
+        </is>
+      </c>
+      <c r="C276" s="73" t="inlineStr"/>
       <c r="D276" s="73" t="inlineStr">
         <is>
-          <t>People’s Law Library Website Hosting, Maintenance &amp; Support Services</t>
+          <t>Information Technology Managed Services</t>
         </is>
       </c>
       <c r="E276" s="73" t="inlineStr">
         <is>
-          <t>The Administrative Office of the Courts (AOC)</t>
+          <t>Otero County [NM]</t>
         </is>
       </c>
       <c r="F276" s="73" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="G276" s="73" t="inlineStr">
@@ -24357,13 +24353,13 @@
       <c r="L276" s="73" t="n"/>
       <c r="M276" s="73" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N276" s="73" t="inlineStr"/>
       <c r="O276" s="73" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="P276" s="73" t="inlineStr"/>
@@ -24382,7 +24378,7 @@
       </c>
       <c r="Z276" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/235608145596</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/235322596041</t>
         </is>
       </c>
       <c r="AA276" s="73" t="inlineStr"/>
@@ -24393,23 +24389,27 @@
       </c>
       <c r="B277" s="73" t="inlineStr">
         <is>
-          <t>235322596041</t>
-        </is>
-      </c>
-      <c r="C277" s="73" t="inlineStr"/>
+          <t>235608145596</t>
+        </is>
+      </c>
+      <c r="C277" s="73" t="inlineStr">
+        <is>
+          <t>K26-0033-25</t>
+        </is>
+      </c>
       <c r="D277" s="73" t="inlineStr">
         <is>
-          <t>Information Technology Managed Services</t>
+          <t>People’s Law Library Website Hosting, Maintenance &amp; Support Services</t>
         </is>
       </c>
       <c r="E277" s="73" t="inlineStr">
         <is>
-          <t>Otero County [NM]</t>
+          <t>The Administrative Office of the Courts (AOC)</t>
         </is>
       </c>
       <c r="F277" s="73" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="G277" s="73" t="inlineStr">
@@ -24432,13 +24432,13 @@
       <c r="L277" s="73" t="n"/>
       <c r="M277" s="73" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N277" s="73" t="inlineStr"/>
       <c r="O277" s="73" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="P277" s="73" t="inlineStr"/>
@@ -24457,7 +24457,7 @@
       </c>
       <c r="Z277" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/235322596041</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/235608145596</t>
         </is>
       </c>
       <c r="AA277" s="73" t="inlineStr"/>
@@ -25869,23 +25869,23 @@
       </c>
       <c r="B295" s="73" t="inlineStr">
         <is>
-          <t>238644854496</t>
+          <t>250428612338</t>
         </is>
       </c>
       <c r="C295" s="73" t="inlineStr"/>
       <c r="D295" s="73" t="inlineStr">
         <is>
-          <t>Document Management System</t>
+          <t>offline - INFORMATION TECHNOLOGY SERVICES</t>
         </is>
       </c>
       <c r="E295" s="73" t="inlineStr">
         <is>
-          <t>Mid-Continent Public Library</t>
+          <t xml:space="preserve">CITY OF SUMMIT POLICE DEPARTMENT </t>
         </is>
       </c>
       <c r="F295" s="73" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="G295" s="73" t="inlineStr">
@@ -25902,23 +25902,23 @@
       </c>
       <c r="K295" s="73" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="L295" s="73" t="n"/>
       <c r="M295" s="73" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N295" s="73" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O295" s="73" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="P295" s="73" t="inlineStr"/>
@@ -25932,12 +25932,12 @@
       <c r="X295" s="73" t="inlineStr"/>
       <c r="Y295" s="73" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="Z295" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/238644854496</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/250428612338</t>
         </is>
       </c>
       <c r="AA295" s="73" t="inlineStr"/>
@@ -26027,23 +26027,23 @@
       </c>
       <c r="B297" s="73" t="inlineStr">
         <is>
-          <t>250428612338</t>
+          <t>238644854496</t>
         </is>
       </c>
       <c r="C297" s="73" t="inlineStr"/>
       <c r="D297" s="73" t="inlineStr">
         <is>
-          <t>offline - INFORMATION TECHNOLOGY SERVICES</t>
+          <t>Document Management System</t>
         </is>
       </c>
       <c r="E297" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">CITY OF SUMMIT POLICE DEPARTMENT </t>
+          <t>Mid-Continent Public Library</t>
         </is>
       </c>
       <c r="F297" s="73" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="G297" s="73" t="inlineStr">
@@ -26060,23 +26060,23 @@
       </c>
       <c r="K297" s="73" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="L297" s="73" t="n"/>
       <c r="M297" s="73" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="N297" s="73" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O297" s="73" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="P297" s="73" t="inlineStr"/>
@@ -26090,12 +26090,12 @@
       <c r="X297" s="73" t="inlineStr"/>
       <c r="Y297" s="73" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="Z297" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/250428612338</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/238644854496</t>
         </is>
       </c>
       <c r="AA297" s="73" t="inlineStr"/>
@@ -27005,23 +27005,23 @@
       </c>
       <c r="B309" s="73" t="inlineStr">
         <is>
-          <t>242650797784</t>
+          <t>259790264057</t>
         </is>
       </c>
       <c r="C309" s="73" t="inlineStr"/>
       <c r="D309" s="73" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY STAFF AUGMENTATION SERVICES</t>
+          <t>2601 Veeam Backup Basic MaintenanceInbo</t>
         </is>
       </c>
       <c r="E309" s="73" t="inlineStr">
         <is>
-          <t>New York State Energy Research and Development Authority (NYSERDA)</t>
+          <t>Franklin County Municipal Court</t>
         </is>
       </c>
       <c r="F309" s="73" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G309" s="73" t="inlineStr">
@@ -27041,20 +27041,18 @@
           <t>2026-01-13</t>
         </is>
       </c>
-      <c r="L309" s="73" t="n"/>
+      <c r="L309" s="75" t="n">
+        <v>12100</v>
+      </c>
       <c r="M309" s="73" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
-        </is>
-      </c>
-      <c r="N309" s="73" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
+          <t>Reseller</t>
+        </is>
+      </c>
+      <c r="N309" s="73" t="inlineStr"/>
       <c r="O309" s="73" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="P309" s="73" t="inlineStr"/>
@@ -27068,12 +27066,12 @@
       <c r="X309" s="73" t="inlineStr"/>
       <c r="Y309" s="73" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="Z309" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/242650797784</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/259790264057</t>
         </is>
       </c>
       <c r="AA309" s="73" t="inlineStr"/>
@@ -27084,23 +27082,23 @@
       </c>
       <c r="B310" s="73" t="inlineStr">
         <is>
-          <t>259790264057</t>
+          <t>242650797784</t>
         </is>
       </c>
       <c r="C310" s="73" t="inlineStr"/>
       <c r="D310" s="73" t="inlineStr">
         <is>
-          <t>2601 Veeam Backup Basic MaintenanceInbo</t>
+          <t>INFORMATION TECHNOLOGY STAFF AUGMENTATION SERVICES</t>
         </is>
       </c>
       <c r="E310" s="73" t="inlineStr">
         <is>
-          <t>Franklin County Municipal Court</t>
+          <t>New York State Energy Research and Development Authority (NYSERDA)</t>
         </is>
       </c>
       <c r="F310" s="73" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G310" s="73" t="inlineStr">
@@ -27120,18 +27118,20 @@
           <t>2026-01-13</t>
         </is>
       </c>
-      <c r="L310" s="75" t="n">
-        <v>12100</v>
-      </c>
+      <c r="L310" s="73" t="n"/>
       <c r="M310" s="73" t="inlineStr">
         <is>
-          <t>Reseller</t>
-        </is>
-      </c>
-      <c r="N310" s="73" t="inlineStr"/>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="N310" s="73" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O310" s="73" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="P310" s="73" t="inlineStr"/>
@@ -27145,12 +27145,12 @@
       <c r="X310" s="73" t="inlineStr"/>
       <c r="Y310" s="73" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="Z310" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/259790264057</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/242650797784</t>
         </is>
       </c>
       <c r="AA310" s="73" t="inlineStr"/>
@@ -27714,23 +27714,23 @@
       </c>
       <c r="B318" s="73" t="inlineStr">
         <is>
-          <t>238161229542</t>
+          <t>231116902097</t>
         </is>
       </c>
       <c r="C318" s="73" t="inlineStr"/>
       <c r="D318" s="73" t="inlineStr">
         <is>
-          <t>NETWORK SECURITY PENETRATION TESTING SERVICES</t>
+          <t>Timekeeping System</t>
         </is>
       </c>
       <c r="E318" s="73" t="inlineStr">
         <is>
-          <t>Greenville Utilities Commission</t>
+          <t>Temp Union High School District</t>
         </is>
       </c>
       <c r="F318" s="73" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="G318" s="73" t="inlineStr">
@@ -27753,17 +27753,17 @@
       <c r="L318" s="73" t="n"/>
       <c r="M318" s="73" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="N318" s="73" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O318" s="73" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="P318" s="73" t="inlineStr"/>
@@ -27777,12 +27777,12 @@
       <c r="X318" s="73" t="inlineStr"/>
       <c r="Y318" s="73" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z318" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/238161229542</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/231116902097</t>
         </is>
       </c>
       <c r="AA318" s="73" t="inlineStr"/>
@@ -27793,23 +27793,23 @@
       </c>
       <c r="B319" s="73" t="inlineStr">
         <is>
-          <t>231116902097</t>
+          <t>238161229542</t>
         </is>
       </c>
       <c r="C319" s="73" t="inlineStr"/>
       <c r="D319" s="73" t="inlineStr">
         <is>
-          <t>Timekeeping System</t>
+          <t>NETWORK SECURITY PENETRATION TESTING SERVICES</t>
         </is>
       </c>
       <c r="E319" s="73" t="inlineStr">
         <is>
-          <t>Temp Union High School District</t>
+          <t>Greenville Utilities Commission</t>
         </is>
       </c>
       <c r="F319" s="73" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G319" s="73" t="inlineStr">
@@ -27832,17 +27832,17 @@
       <c r="L319" s="73" t="n"/>
       <c r="M319" s="73" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="N319" s="73" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O319" s="73" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="P319" s="73" t="inlineStr"/>
@@ -27856,12 +27856,12 @@
       <c r="X319" s="73" t="inlineStr"/>
       <c r="Y319" s="73" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z319" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/231116902097</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/238161229542</t>
         </is>
       </c>
       <c r="AA319" s="73" t="inlineStr"/>
@@ -28204,23 +28204,27 @@
       </c>
       <c r="B324" s="73" t="inlineStr">
         <is>
-          <t>207661977336</t>
-        </is>
-      </c>
-      <c r="C324" s="73" t="inlineStr"/>
+          <t>255422637807</t>
+        </is>
+      </c>
+      <c r="C324" s="73" t="inlineStr">
+        <is>
+          <t>2026-RFP-00227</t>
+        </is>
+      </c>
       <c r="D324" s="73" t="inlineStr">
         <is>
-          <t>Cybersecurity &amp; It Support Services</t>
+          <t>Childcare Navigation Technology Platform</t>
         </is>
       </c>
       <c r="E324" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Greater New Bedford Regional Refuse Management District </t>
+          <t>County of San Mateo</t>
         </is>
       </c>
       <c r="F324" s="73" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G324" s="73" t="inlineStr">
@@ -28243,10 +28247,14 @@
       <c r="L324" s="73" t="n"/>
       <c r="M324" s="73" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N324" s="73" t="inlineStr"/>
+          <t>Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="N324" s="73" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O324" s="73" t="inlineStr">
         <is>
           <t>Ashutosh Chauhan</t>
@@ -28263,12 +28271,12 @@
       <c r="X324" s="73" t="inlineStr"/>
       <c r="Y324" s="73" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="Z324" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/207661977336</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/255422637807</t>
         </is>
       </c>
       <c r="AA324" s="73" t="inlineStr"/>
@@ -28433,32 +28441,28 @@
       </c>
       <c r="B327" s="73" t="inlineStr">
         <is>
-          <t>255422637807</t>
-        </is>
-      </c>
-      <c r="C327" s="73" t="inlineStr">
-        <is>
-          <t>2026-RFP-00227</t>
-        </is>
-      </c>
+          <t>235964612297</t>
+        </is>
+      </c>
+      <c r="C327" s="73" t="inlineStr"/>
       <c r="D327" s="73" t="inlineStr">
         <is>
-          <t>Childcare Navigation Technology Platform</t>
+          <t>AI Governance, Compliance, and Enablement Platform</t>
         </is>
       </c>
       <c r="E327" s="73" t="inlineStr">
         <is>
-          <t>County of San Mateo</t>
+          <t>North Central Texas Council of Governments</t>
         </is>
       </c>
       <c r="F327" s="73" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G327" s="73" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H327" s="73" t="inlineStr"/>
@@ -28476,14 +28480,10 @@
       <c r="L327" s="73" t="n"/>
       <c r="M327" s="73" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
-        </is>
-      </c>
-      <c r="N327" s="73" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N327" s="73" t="inlineStr"/>
       <c r="O327" s="73" t="inlineStr">
         <is>
           <t>Ashutosh Chauhan</t>
@@ -28492,7 +28492,11 @@
       <c r="P327" s="73" t="inlineStr"/>
       <c r="Q327" s="73" t="inlineStr"/>
       <c r="R327" s="73" t="inlineStr"/>
-      <c r="S327" s="73" t="inlineStr"/>
+      <c r="S327" s="73" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
       <c r="T327" s="73" t="inlineStr"/>
       <c r="U327" s="73" t="inlineStr"/>
       <c r="V327" s="73" t="inlineStr"/>
@@ -28500,12 +28504,12 @@
       <c r="X327" s="73" t="inlineStr"/>
       <c r="Y327" s="73" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z327" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/255422637807</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/235964612297</t>
         </is>
       </c>
       <c r="AA327" s="73" t="inlineStr"/>
@@ -28516,28 +28520,28 @@
       </c>
       <c r="B328" s="73" t="inlineStr">
         <is>
-          <t>235964612297</t>
+          <t>207661977336</t>
         </is>
       </c>
       <c r="C328" s="73" t="inlineStr"/>
       <c r="D328" s="73" t="inlineStr">
         <is>
-          <t>AI Governance, Compliance, and Enablement Platform</t>
+          <t>Cybersecurity &amp; It Support Services</t>
         </is>
       </c>
       <c r="E328" s="73" t="inlineStr">
         <is>
-          <t>North Central Texas Council of Governments</t>
+          <t xml:space="preserve">Greater New Bedford Regional Refuse Management District </t>
         </is>
       </c>
       <c r="F328" s="73" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="G328" s="73" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H328" s="73" t="inlineStr"/>
@@ -28555,7 +28559,7 @@
       <c r="L328" s="73" t="n"/>
       <c r="M328" s="73" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N328" s="73" t="inlineStr"/>
@@ -28567,11 +28571,7 @@
       <c r="P328" s="73" t="inlineStr"/>
       <c r="Q328" s="73" t="inlineStr"/>
       <c r="R328" s="73" t="inlineStr"/>
-      <c r="S328" s="73" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
+      <c r="S328" s="73" t="inlineStr"/>
       <c r="T328" s="73" t="inlineStr"/>
       <c r="U328" s="73" t="inlineStr"/>
       <c r="V328" s="73" t="inlineStr"/>
@@ -28579,12 +28579,12 @@
       <c r="X328" s="73" t="inlineStr"/>
       <c r="Y328" s="73" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z328" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/235964612297</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/207661977336</t>
         </is>
       </c>
       <c r="AA328" s="73" t="inlineStr"/>
@@ -28676,32 +28676,28 @@
       </c>
       <c r="B330" s="73" t="inlineStr">
         <is>
-          <t>255640222437</t>
-        </is>
-      </c>
-      <c r="C330" s="73" t="inlineStr">
-        <is>
-          <t>12198-2</t>
-        </is>
-      </c>
+          <t>267213774549</t>
+        </is>
+      </c>
+      <c r="C330" s="73" t="inlineStr"/>
       <c r="D330" s="73" t="inlineStr">
         <is>
-          <t>Salesforce Custom Development for Code &amp; Zoning Enforcement</t>
+          <t>FY25 Application, Infrastructure, Hosting and Cloud Computing Services</t>
         </is>
       </c>
       <c r="E330" s="73" t="inlineStr">
         <is>
-          <t>City of Greensboro</t>
+          <t>State of Alabama – Plumbers and Gas Fitters Examining Board</t>
         </is>
       </c>
       <c r="F330" s="73" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="G330" s="73" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H330" s="73" t="inlineStr"/>
@@ -28716,22 +28712,16 @@
           <t>2026-01-20</t>
         </is>
       </c>
-      <c r="L330" s="75" t="n">
-        <v>70430</v>
-      </c>
+      <c r="L330" s="73" t="n"/>
       <c r="M330" s="73" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
-        </is>
-      </c>
-      <c r="N330" s="73" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N330" s="73" t="inlineStr"/>
       <c r="O330" s="73" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="P330" s="73" t="inlineStr"/>
@@ -28745,12 +28735,12 @@
       <c r="X330" s="73" t="inlineStr"/>
       <c r="Y330" s="73" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z330" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/255640222437</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/267213774549</t>
         </is>
       </c>
       <c r="AA330" s="73" t="inlineStr"/>
@@ -28761,27 +28751,23 @@
       </c>
       <c r="B331" s="73" t="inlineStr">
         <is>
-          <t>255414899417</t>
-        </is>
-      </c>
-      <c r="C331" s="73" t="inlineStr">
-        <is>
-          <t>RFP26-41</t>
-        </is>
-      </c>
+          <t>208322135778</t>
+        </is>
+      </c>
+      <c r="C331" s="73" t="inlineStr"/>
       <c r="D331" s="73" t="inlineStr">
         <is>
-          <t>Web and Mobile App ADA Compliance</t>
+          <t>Cloud-Based Computerized Maintenance Management System and Enterprise Asset Management System</t>
         </is>
       </c>
       <c r="E331" s="73" t="inlineStr">
         <is>
-          <t>Los Alamos County</t>
+          <t>City of Scottsdale</t>
         </is>
       </c>
       <c r="F331" s="73" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="G331" s="73" t="inlineStr">
@@ -28804,13 +28790,13 @@
       <c r="L331" s="73" t="n"/>
       <c r="M331" s="73" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="N331" s="73" t="inlineStr"/>
       <c r="O331" s="73" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="P331" s="73" t="inlineStr"/>
@@ -28824,12 +28810,12 @@
       <c r="X331" s="73" t="inlineStr"/>
       <c r="Y331" s="73" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z331" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/255414899417</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/208322135778</t>
         </is>
       </c>
       <c r="AA331" s="73" t="inlineStr"/>
@@ -28840,23 +28826,23 @@
       </c>
       <c r="B332" s="73" t="inlineStr">
         <is>
-          <t>267213774549</t>
+          <t>161660191429</t>
         </is>
       </c>
       <c r="C332" s="73" t="inlineStr"/>
       <c r="D332" s="73" t="inlineStr">
         <is>
-          <t>FY25 Application, Infrastructure, Hosting and Cloud Computing Services</t>
+          <t>Cloud Services Migration</t>
         </is>
       </c>
       <c r="E332" s="73" t="inlineStr">
         <is>
-          <t>State of Alabama – Plumbers and Gas Fitters Examining Board</t>
+          <t>Orange County</t>
         </is>
       </c>
       <c r="F332" s="73" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G332" s="73" t="inlineStr">
@@ -28885,7 +28871,7 @@
       <c r="N332" s="73" t="inlineStr"/>
       <c r="O332" s="73" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="P332" s="73" t="inlineStr"/>
@@ -28899,12 +28885,12 @@
       <c r="X332" s="73" t="inlineStr"/>
       <c r="Y332" s="73" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="Z332" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/267213774549</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/161660191429</t>
         </is>
       </c>
       <c r="AA332" s="73" t="inlineStr"/>
@@ -28915,28 +28901,32 @@
       </c>
       <c r="B333" s="73" t="inlineStr">
         <is>
-          <t>161660191429</t>
-        </is>
-      </c>
-      <c r="C333" s="73" t="inlineStr"/>
+          <t>255640222437</t>
+        </is>
+      </c>
+      <c r="C333" s="73" t="inlineStr">
+        <is>
+          <t>12198-2</t>
+        </is>
+      </c>
       <c r="D333" s="73" t="inlineStr">
         <is>
-          <t>Cloud Services Migration</t>
+          <t>Salesforce Custom Development for Code &amp; Zoning Enforcement</t>
         </is>
       </c>
       <c r="E333" s="73" t="inlineStr">
         <is>
-          <t>Orange County</t>
+          <t>City of Greensboro</t>
         </is>
       </c>
       <c r="F333" s="73" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G333" s="73" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H333" s="73" t="inlineStr"/>
@@ -28951,13 +28941,19 @@
           <t>2026-01-20</t>
         </is>
       </c>
-      <c r="L333" s="73" t="n"/>
+      <c r="L333" s="75" t="n">
+        <v>70430</v>
+      </c>
       <c r="M333" s="73" t="inlineStr">
         <is>
-          <t>Consulting</t>
-        </is>
-      </c>
-      <c r="N333" s="73" t="inlineStr"/>
+          <t>Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="N333" s="73" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O333" s="73" t="inlineStr">
         <is>
           <t>Ashutosh Chauhan</t>
@@ -28974,12 +28970,12 @@
       <c r="X333" s="73" t="inlineStr"/>
       <c r="Y333" s="73" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="Z333" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/161660191429</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/255640222437</t>
         </is>
       </c>
       <c r="AA333" s="73" t="inlineStr"/>
@@ -28990,23 +28986,27 @@
       </c>
       <c r="B334" s="73" t="inlineStr">
         <is>
-          <t>208322135778</t>
-        </is>
-      </c>
-      <c r="C334" s="73" t="inlineStr"/>
+          <t>255414899417</t>
+        </is>
+      </c>
+      <c r="C334" s="73" t="inlineStr">
+        <is>
+          <t>RFP26-41</t>
+        </is>
+      </c>
       <c r="D334" s="73" t="inlineStr">
         <is>
-          <t>Cloud-Based Computerized Maintenance Management System and Enterprise Asset Management System</t>
+          <t>Web and Mobile App ADA Compliance</t>
         </is>
       </c>
       <c r="E334" s="73" t="inlineStr">
         <is>
-          <t>City of Scottsdale</t>
+          <t>Los Alamos County</t>
         </is>
       </c>
       <c r="F334" s="73" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="G334" s="73" t="inlineStr">
@@ -29029,13 +29029,13 @@
       <c r="L334" s="73" t="n"/>
       <c r="M334" s="73" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="N334" s="73" t="inlineStr"/>
       <c r="O334" s="73" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="P334" s="73" t="inlineStr"/>
@@ -29049,12 +29049,12 @@
       <c r="X334" s="73" t="inlineStr"/>
       <c r="Y334" s="73" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="Z334" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/208322135778</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/255414899417</t>
         </is>
       </c>
       <c r="AA334" s="73" t="inlineStr"/>
@@ -29227,27 +29227,23 @@
       </c>
       <c r="B337" s="73" t="inlineStr">
         <is>
-          <t>255422636750</t>
-        </is>
-      </c>
-      <c r="C337" s="73" t="inlineStr">
-        <is>
-          <t>RFP NO. 25-06 – IT</t>
-        </is>
-      </c>
+          <t>257228182254</t>
+        </is>
+      </c>
+      <c r="C337" s="73" t="inlineStr"/>
       <c r="D337" s="73" t="inlineStr">
         <is>
-          <t>Technology and Modernization Services</t>
+          <t>Microsoft Power Platform, Azure Data Services, and Azure Artificial Intelligence Services</t>
         </is>
       </c>
       <c r="E337" s="73" t="inlineStr">
         <is>
-          <t>Butler Metro Housing Authority</t>
+          <t xml:space="preserve">Bay Area Air Quality Management District </t>
         </is>
       </c>
       <c r="F337" s="73" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G337" s="73" t="inlineStr">
@@ -29270,7 +29266,7 @@
       <c r="L337" s="73" t="n"/>
       <c r="M337" s="73" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N337" s="73" t="inlineStr"/>
@@ -29290,12 +29286,12 @@
       <c r="X337" s="73" t="inlineStr"/>
       <c r="Y337" s="73" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="Z337" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/255422636750</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/257228182254</t>
         </is>
       </c>
       <c r="AA337" s="73" t="inlineStr"/>
@@ -29306,23 +29302,27 @@
       </c>
       <c r="B338" s="73" t="inlineStr">
         <is>
-          <t>257228182254</t>
-        </is>
-      </c>
-      <c r="C338" s="73" t="inlineStr"/>
+          <t>255422636750</t>
+        </is>
+      </c>
+      <c r="C338" s="73" t="inlineStr">
+        <is>
+          <t>RFP NO. 25-06 – IT</t>
+        </is>
+      </c>
       <c r="D338" s="73" t="inlineStr">
         <is>
-          <t>Microsoft Power Platform, Azure Data Services, and Azure Artificial Intelligence Services</t>
+          <t>Technology and Modernization Services</t>
         </is>
       </c>
       <c r="E338" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bay Area Air Quality Management District </t>
+          <t>Butler Metro Housing Authority</t>
         </is>
       </c>
       <c r="F338" s="73" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G338" s="73" t="inlineStr">
@@ -29345,7 +29345,7 @@
       <c r="L338" s="73" t="n"/>
       <c r="M338" s="73" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="N338" s="73" t="inlineStr"/>
@@ -29365,12 +29365,12 @@
       <c r="X338" s="73" t="inlineStr"/>
       <c r="Y338" s="73" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="Z338" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/257228182254</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/255422636750</t>
         </is>
       </c>
       <c r="AA338" s="73" t="inlineStr"/>
@@ -29557,27 +29557,23 @@
       </c>
       <c r="B341" s="73" t="inlineStr">
         <is>
-          <t>256863960825</t>
-        </is>
-      </c>
-      <c r="C341" s="73" t="inlineStr">
-        <is>
-          <t>RFP 25-71</t>
-        </is>
-      </c>
+          <t>223308058320</t>
+        </is>
+      </c>
+      <c r="C341" s="73" t="inlineStr"/>
       <c r="D341" s="73" t="inlineStr">
         <is>
-          <t>SEPA for Regional Cyber Incident Preparedness Project</t>
+          <t>ENTERPRISE RESOURCE PLANNING (ERP) SOFTWAREAND IMPLEMENTATION SERVICES</t>
         </is>
       </c>
       <c r="E341" s="73" t="inlineStr">
         <is>
-          <t>Montgomery County</t>
+          <t>Vero beach</t>
         </is>
       </c>
       <c r="F341" s="73" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G341" s="73" t="inlineStr">
@@ -29594,25 +29590,23 @@
       </c>
       <c r="K341" s="73" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="L341" s="75" t="n">
-        <v>37300</v>
-      </c>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="L341" s="73" t="n"/>
       <c r="M341" s="73" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="N341" s="73" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O341" s="73" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="P341" s="73" t="inlineStr"/>
@@ -29626,12 +29620,12 @@
       <c r="X341" s="73" t="inlineStr"/>
       <c r="Y341" s="73" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z341" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/256863960825</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/223308058320</t>
         </is>
       </c>
       <c r="AA341" s="73" t="inlineStr"/>
@@ -29642,27 +29636,27 @@
       </c>
       <c r="B342" s="73" t="inlineStr">
         <is>
-          <t>257293099725</t>
+          <t>256863960825</t>
         </is>
       </c>
       <c r="C342" s="73" t="inlineStr">
         <is>
-          <t>RFP 1100 PAB3025</t>
+          <t>RFP 25-71</t>
         </is>
       </c>
       <c r="D342" s="73" t="inlineStr">
         <is>
-          <t>ADMS Consultant Implementation/Upgrade Services</t>
+          <t>SEPA for Regional Cyber Incident Preparedness Project</t>
         </is>
       </c>
       <c r="E342" s="73" t="inlineStr">
         <is>
-          <t>City of Austin</t>
+          <t>Montgomery County</t>
         </is>
       </c>
       <c r="F342" s="73" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G342" s="73" t="inlineStr">
@@ -29679,11 +29673,11 @@
       </c>
       <c r="K342" s="73" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="L342" s="75" t="n">
-        <v>1800000</v>
+        <v>37300</v>
       </c>
       <c r="M342" s="73" t="inlineStr">
         <is>
@@ -29716,7 +29710,7 @@
       </c>
       <c r="Z342" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/257293099725</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/256863960825</t>
         </is>
       </c>
       <c r="AA342" s="73" t="inlineStr"/>
@@ -29727,23 +29721,27 @@
       </c>
       <c r="B343" s="73" t="inlineStr">
         <is>
-          <t>223308058320</t>
-        </is>
-      </c>
-      <c r="C343" s="73" t="inlineStr"/>
+          <t>257293099725</t>
+        </is>
+      </c>
+      <c r="C343" s="73" t="inlineStr">
+        <is>
+          <t>RFP 1100 PAB3025</t>
+        </is>
+      </c>
       <c r="D343" s="73" t="inlineStr">
         <is>
-          <t>ENTERPRISE RESOURCE PLANNING (ERP) SOFTWAREAND IMPLEMENTATION SERVICES</t>
+          <t>ADMS Consultant Implementation/Upgrade Services</t>
         </is>
       </c>
       <c r="E343" s="73" t="inlineStr">
         <is>
-          <t>Vero beach</t>
+          <t>City of Austin</t>
         </is>
       </c>
       <c r="F343" s="73" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G343" s="73" t="inlineStr">
@@ -29763,20 +29761,22 @@
           <t>2026-01-22</t>
         </is>
       </c>
-      <c r="L343" s="73" t="n"/>
+      <c r="L343" s="75" t="n">
+        <v>1800000</v>
+      </c>
       <c r="M343" s="73" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N343" s="73" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O343" s="73" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="P343" s="73" t="inlineStr"/>
@@ -29790,12 +29790,12 @@
       <c r="X343" s="73" t="inlineStr"/>
       <c r="Y343" s="73" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="Z343" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/223308058320</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/257293099725</t>
         </is>
       </c>
       <c r="AA343" s="73" t="inlineStr"/>
@@ -29891,23 +29891,23 @@
       </c>
       <c r="B345" s="73" t="inlineStr">
         <is>
-          <t>245627910888</t>
+          <t>255828500216</t>
         </is>
       </c>
       <c r="C345" s="73" t="inlineStr"/>
       <c r="D345" s="73" t="inlineStr">
         <is>
-          <t>Managed Services Support for Workforce Software</t>
+          <t>Oracle Database Maintenance and Support Services</t>
         </is>
       </c>
       <c r="E345" s="73" t="inlineStr">
         <is>
-          <t>Denver Public Schools</t>
+          <t xml:space="preserve">Corrections and Rehabilitation </t>
         </is>
       </c>
       <c r="F345" s="73" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Hawaii</t>
         </is>
       </c>
       <c r="G345" s="73" t="inlineStr">
@@ -29924,18 +29924,18 @@
       </c>
       <c r="K345" s="73" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="L345" s="73" t="n"/>
       <c r="M345" s="73" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N345" s="73" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O345" s="73" t="inlineStr">
@@ -29954,12 +29954,12 @@
       <c r="X345" s="73" t="inlineStr"/>
       <c r="Y345" s="73" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="Z345" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/245627910888</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/255828500216</t>
         </is>
       </c>
       <c r="AA345" s="73" t="inlineStr"/>
@@ -29970,32 +29970,28 @@
       </c>
       <c r="B346" s="73" t="inlineStr">
         <is>
-          <t>237725763303</t>
-        </is>
-      </c>
-      <c r="C346" s="73" t="inlineStr">
-        <is>
-          <t>25114</t>
-        </is>
-      </c>
+          <t>253070304989</t>
+        </is>
+      </c>
+      <c r="C346" s="73" t="inlineStr"/>
       <c r="D346" s="73" t="inlineStr">
         <is>
-          <t>SAP SuccessFactors Onboarding, Offboarding, Crossboarding Implementation Services</t>
+          <t xml:space="preserve">Computer &amp; Information Technology (IT) Services </t>
         </is>
       </c>
       <c r="E346" s="73" t="inlineStr">
         <is>
-          <t>Nebraska Public Power District</t>
+          <t>Town of Thompson</t>
         </is>
       </c>
       <c r="F346" s="73" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G346" s="73" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H346" s="73" t="inlineStr"/>
@@ -30010,19 +30006,13 @@
           <t>2026-01-23</t>
         </is>
       </c>
-      <c r="L346" s="75" t="n">
-        <v>52320</v>
-      </c>
+      <c r="L346" s="73" t="n"/>
       <c r="M346" s="73" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
-        </is>
-      </c>
-      <c r="N346" s="73" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N346" s="73" t="inlineStr"/>
       <c r="O346" s="73" t="inlineStr">
         <is>
           <t>Ashutosh Chauhan</t>
@@ -30039,12 +30029,12 @@
       <c r="X346" s="73" t="inlineStr"/>
       <c r="Y346" s="73" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="Z346" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/237725763303</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/253070304989</t>
         </is>
       </c>
       <c r="AA346" s="73" t="inlineStr"/>
@@ -30055,23 +30045,23 @@
       </c>
       <c r="B347" s="73" t="inlineStr">
         <is>
-          <t>253057083080</t>
+          <t>245627910888</t>
         </is>
       </c>
       <c r="C347" s="73" t="inlineStr"/>
       <c r="D347" s="73" t="inlineStr">
         <is>
-          <t>TL Consultant and Project Management for IT Projects</t>
+          <t>Managed Services Support for Workforce Software</t>
         </is>
       </c>
       <c r="E347" s="73" t="inlineStr">
         <is>
-          <t>Kane County</t>
+          <t>Denver Public Schools</t>
         </is>
       </c>
       <c r="F347" s="73" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G347" s="73" t="inlineStr">
@@ -30094,17 +30084,17 @@
       <c r="L347" s="73" t="n"/>
       <c r="M347" s="73" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N347" s="73" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O347" s="73" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="P347" s="73" t="inlineStr"/>
@@ -30118,12 +30108,12 @@
       <c r="X347" s="73" t="inlineStr"/>
       <c r="Y347" s="73" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="Z347" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/253057083080</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/245627910888</t>
         </is>
       </c>
       <c r="AA347" s="73" t="inlineStr"/>
@@ -30134,28 +30124,32 @@
       </c>
       <c r="B348" s="73" t="inlineStr">
         <is>
-          <t>253070304989</t>
-        </is>
-      </c>
-      <c r="C348" s="73" t="inlineStr"/>
+          <t>237725763303</t>
+        </is>
+      </c>
+      <c r="C348" s="73" t="inlineStr">
+        <is>
+          <t>25114</t>
+        </is>
+      </c>
       <c r="D348" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computer &amp; Information Technology (IT) Services </t>
+          <t>SAP SuccessFactors Onboarding, Offboarding, Crossboarding Implementation Services</t>
         </is>
       </c>
       <c r="E348" s="73" t="inlineStr">
         <is>
-          <t>Town of Thompson</t>
+          <t>Nebraska Public Power District</t>
         </is>
       </c>
       <c r="F348" s="73" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="G348" s="73" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H348" s="73" t="inlineStr"/>
@@ -30170,13 +30164,19 @@
           <t>2026-01-23</t>
         </is>
       </c>
-      <c r="L348" s="73" t="n"/>
+      <c r="L348" s="75" t="n">
+        <v>52320</v>
+      </c>
       <c r="M348" s="73" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N348" s="73" t="inlineStr"/>
+          <t>Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="N348" s="73" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="O348" s="73" t="inlineStr">
         <is>
           <t>Ashutosh Chauhan</t>
@@ -30193,12 +30193,12 @@
       <c r="X348" s="73" t="inlineStr"/>
       <c r="Y348" s="73" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z348" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/253070304989</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/237725763303</t>
         </is>
       </c>
       <c r="AA348" s="73" t="inlineStr"/>
@@ -30209,23 +30209,23 @@
       </c>
       <c r="B349" s="73" t="inlineStr">
         <is>
-          <t>255828500216</t>
+          <t>253057083080</t>
         </is>
       </c>
       <c r="C349" s="73" t="inlineStr"/>
       <c r="D349" s="73" t="inlineStr">
         <is>
-          <t>Oracle Database Maintenance and Support Services</t>
+          <t>TL Consultant and Project Management for IT Projects</t>
         </is>
       </c>
       <c r="E349" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrections and Rehabilitation </t>
+          <t>Kane County</t>
         </is>
       </c>
       <c r="F349" s="73" t="inlineStr">
         <is>
-          <t>Hawaii</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="G349" s="73" t="inlineStr">
@@ -30242,13 +30242,13 @@
       </c>
       <c r="K349" s="73" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="L349" s="73" t="n"/>
       <c r="M349" s="73" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N349" s="73" t="inlineStr">
@@ -30258,7 +30258,7 @@
       </c>
       <c r="O349" s="73" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="P349" s="73" t="inlineStr"/>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="Z349" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/255828500216</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/253057083080</t>
         </is>
       </c>
       <c r="AA349" s="73" t="inlineStr"/>
@@ -30369,23 +30369,27 @@
       </c>
       <c r="B351" s="73" t="inlineStr">
         <is>
-          <t>253057032914</t>
-        </is>
-      </c>
-      <c r="C351" s="73" t="inlineStr"/>
+          <t>255640222432</t>
+        </is>
+      </c>
+      <c r="C351" s="73" t="inlineStr">
+        <is>
+          <t>2026-086</t>
+        </is>
+      </c>
       <c r="D351" s="73" t="inlineStr">
         <is>
-          <t>Board of Elections Foundations Google</t>
+          <t>Microsoft Authorized License Reseller</t>
         </is>
       </c>
       <c r="E351" s="73" t="inlineStr">
         <is>
-          <t>New York State Board of Elections (NYSBOE)</t>
+          <t>Roanoke County</t>
         </is>
       </c>
       <c r="F351" s="73" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G351" s="73" t="inlineStr">
@@ -30408,10 +30412,14 @@
       <c r="L351" s="73" t="n"/>
       <c r="M351" s="73" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
-        </is>
-      </c>
-      <c r="N351" s="73" t="inlineStr"/>
+          <t>Reseller</t>
+        </is>
+      </c>
+      <c r="N351" s="73" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O351" s="73" t="inlineStr">
         <is>
           <t>Ashutosh Chauhan</t>
@@ -30433,7 +30441,7 @@
       </c>
       <c r="Z351" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/253057032914</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/255640222432</t>
         </is>
       </c>
       <c r="AA351" s="73" t="inlineStr"/>
@@ -30523,27 +30531,23 @@
       </c>
       <c r="B353" s="73" t="inlineStr">
         <is>
-          <t>255640222432</t>
-        </is>
-      </c>
-      <c r="C353" s="73" t="inlineStr">
-        <is>
-          <t>2026-086</t>
-        </is>
-      </c>
+          <t>253057032914</t>
+        </is>
+      </c>
+      <c r="C353" s="73" t="inlineStr"/>
       <c r="D353" s="73" t="inlineStr">
         <is>
-          <t>Microsoft Authorized License Reseller</t>
+          <t>Board of Elections Foundations Google</t>
         </is>
       </c>
       <c r="E353" s="73" t="inlineStr">
         <is>
-          <t>Roanoke County</t>
+          <t>New York State Board of Elections (NYSBOE)</t>
         </is>
       </c>
       <c r="F353" s="73" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G353" s="73" t="inlineStr">
@@ -30566,14 +30570,10 @@
       <c r="L353" s="73" t="n"/>
       <c r="M353" s="73" t="inlineStr">
         <is>
-          <t>Reseller</t>
-        </is>
-      </c>
-      <c r="N353" s="73" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
+          <t>Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="N353" s="73" t="inlineStr"/>
       <c r="O353" s="73" t="inlineStr">
         <is>
           <t>Ashutosh Chauhan</t>
@@ -30595,7 +30595,7 @@
       </c>
       <c r="Z353" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/255640222432</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/253057032914</t>
         </is>
       </c>
       <c r="AA353" s="73" t="inlineStr"/>
@@ -31130,23 +31130,23 @@
       </c>
       <c r="B360" s="73" t="inlineStr">
         <is>
-          <t>254846650094</t>
+          <t>267448777444</t>
         </is>
       </c>
       <c r="C360" s="73" t="inlineStr"/>
       <c r="D360" s="73" t="inlineStr">
         <is>
-          <t>IT Managed Services</t>
+          <t>OFF - Design, Hosting, and Implementation of the Town Website and Online Forms Platform</t>
         </is>
       </c>
       <c r="E360" s="73" t="inlineStr">
         <is>
-          <t>Kentuckiana Regional Planning &amp; Development Agency</t>
+          <t>THE TOWN OF IRONDEQUOIT</t>
         </is>
       </c>
       <c r="F360" s="73" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G360" s="73" t="inlineStr">
@@ -31163,23 +31163,23 @@
       </c>
       <c r="K360" s="73" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="L360" s="73" t="n"/>
       <c r="M360" s="73" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N360" s="73" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Offline;Email</t>
         </is>
       </c>
       <c r="O360" s="73" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="P360" s="73" t="inlineStr"/>
@@ -31193,12 +31193,12 @@
       <c r="X360" s="73" t="inlineStr"/>
       <c r="Y360" s="73" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z360" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/254846650094</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/267448777444</t>
         </is>
       </c>
       <c r="AA360" s="73" t="inlineStr"/>
@@ -31209,23 +31209,23 @@
       </c>
       <c r="B361" s="73" t="inlineStr">
         <is>
-          <t>267448777444</t>
+          <t>254846650094</t>
         </is>
       </c>
       <c r="C361" s="73" t="inlineStr"/>
       <c r="D361" s="73" t="inlineStr">
         <is>
-          <t>OFF - Design, Hosting, and Implementation of the Town Website and Online Forms Platform</t>
+          <t>IT Managed Services</t>
         </is>
       </c>
       <c r="E361" s="73" t="inlineStr">
         <is>
-          <t>THE TOWN OF IRONDEQUOIT</t>
+          <t>Kentuckiana Regional Planning &amp; Development Agency</t>
         </is>
       </c>
       <c r="F361" s="73" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="G361" s="73" t="inlineStr">
@@ -31242,23 +31242,23 @@
       </c>
       <c r="K361" s="73" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="L361" s="73" t="n"/>
       <c r="M361" s="73" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N361" s="73" t="inlineStr">
         <is>
-          <t>Offline;Email</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O361" s="73" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="P361" s="73" t="inlineStr"/>
@@ -31272,12 +31272,12 @@
       <c r="X361" s="73" t="inlineStr"/>
       <c r="Y361" s="73" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="Z361" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/267448777444</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/254846650094</t>
         </is>
       </c>
       <c r="AA361" s="73" t="inlineStr"/>
@@ -31679,23 +31679,23 @@
       </c>
       <c r="B367" s="73" t="inlineStr">
         <is>
-          <t>256863962865</t>
+          <t>256648178398</t>
         </is>
       </c>
       <c r="C367" s="73" t="inlineStr"/>
       <c r="D367" s="73" t="inlineStr">
         <is>
-          <t>PMIS Implementation Project</t>
+          <t>Data Management Plan Development</t>
         </is>
       </c>
       <c r="E367" s="73" t="inlineStr">
         <is>
-          <t>University of Maryland, Baltimore (University of UMB)</t>
+          <t>Texas A&amp;M Transportation Institute</t>
         </is>
       </c>
       <c r="F367" s="73" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G367" s="73" t="inlineStr">
@@ -31718,10 +31718,14 @@
       <c r="L367" s="73" t="n"/>
       <c r="M367" s="73" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
-        </is>
-      </c>
-      <c r="N367" s="73" t="inlineStr"/>
+          <t>Audits and Assessment</t>
+        </is>
+      </c>
+      <c r="N367" s="73" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O367" s="73" t="inlineStr">
         <is>
           <t>Savya Atrey</t>
@@ -31743,7 +31747,7 @@
       </c>
       <c r="Z367" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/256863962865</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/256648178398</t>
         </is>
       </c>
       <c r="AA367" s="73" t="inlineStr"/>
@@ -31754,23 +31758,23 @@
       </c>
       <c r="B368" s="73" t="inlineStr">
         <is>
-          <t>261923701472</t>
+          <t>256863962865</t>
         </is>
       </c>
       <c r="C368" s="73" t="inlineStr"/>
       <c r="D368" s="73" t="inlineStr">
         <is>
-          <t>EXTERNAL AND INTERNAL NETWORK PENETRATION TESTING SERVICES</t>
+          <t>PMIS Implementation Project</t>
         </is>
       </c>
       <c r="E368" s="73" t="inlineStr">
         <is>
-          <t>Miami University</t>
+          <t>University of Maryland, Baltimore (University of UMB)</t>
         </is>
       </c>
       <c r="F368" s="73" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="G368" s="73" t="inlineStr">
@@ -31793,13 +31797,13 @@
       <c r="L368" s="73" t="n"/>
       <c r="M368" s="73" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="N368" s="73" t="inlineStr"/>
       <c r="O368" s="73" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="P368" s="73" t="inlineStr"/>
@@ -31813,12 +31817,12 @@
       <c r="X368" s="73" t="inlineStr"/>
       <c r="Y368" s="73" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="Z368" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/261923701472</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/256863962865</t>
         </is>
       </c>
       <c r="AA368" s="73" t="inlineStr"/>
@@ -31829,23 +31833,23 @@
       </c>
       <c r="B369" s="73" t="inlineStr">
         <is>
-          <t>256648178398</t>
+          <t>261923701472</t>
         </is>
       </c>
       <c r="C369" s="73" t="inlineStr"/>
       <c r="D369" s="73" t="inlineStr">
         <is>
-          <t>Data Management Plan Development</t>
+          <t>EXTERNAL AND INTERNAL NETWORK PENETRATION TESTING SERVICES</t>
         </is>
       </c>
       <c r="E369" s="73" t="inlineStr">
         <is>
-          <t>Texas A&amp;M Transportation Institute</t>
+          <t>Miami University</t>
         </is>
       </c>
       <c r="F369" s="73" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G369" s="73" t="inlineStr">
@@ -31868,17 +31872,13 @@
       <c r="L369" s="73" t="n"/>
       <c r="M369" s="73" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
-        </is>
-      </c>
-      <c r="N369" s="73" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N369" s="73" t="inlineStr"/>
       <c r="O369" s="73" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="P369" s="73" t="inlineStr"/>
@@ -31892,12 +31892,12 @@
       <c r="X369" s="73" t="inlineStr"/>
       <c r="Y369" s="73" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z369" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/256648178398</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/261923701472</t>
         </is>
       </c>
       <c r="AA369" s="73" t="inlineStr"/>
@@ -32224,23 +32224,23 @@
       </c>
       <c r="B374" s="73" t="inlineStr">
         <is>
-          <t>278975444717</t>
+          <t>254846611170</t>
         </is>
       </c>
       <c r="C374" s="73" t="inlineStr"/>
       <c r="D374" s="73" t="inlineStr">
         <is>
-          <t>Cemetery Database Management and Support</t>
+          <t>Information Technology Service Management (ITSM) Software Purchase and Implementation</t>
         </is>
       </c>
       <c r="E374" s="73" t="inlineStr">
         <is>
-          <t>City of Fitchburg</t>
+          <t>Port of Long Beach</t>
         </is>
       </c>
       <c r="F374" s="73" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G374" s="73" t="inlineStr">
@@ -32257,19 +32257,19 @@
       </c>
       <c r="K374" s="73" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="L374" s="73" t="n"/>
       <c r="M374" s="73" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="N374" s="73" t="inlineStr"/>
       <c r="O374" s="73" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="P374" s="73" t="inlineStr"/>
@@ -32283,12 +32283,12 @@
       <c r="X374" s="73" t="inlineStr"/>
       <c r="Y374" s="73" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="Z374" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/278975444717</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/254846611170</t>
         </is>
       </c>
       <c r="AA374" s="73" t="inlineStr"/>
@@ -32299,23 +32299,23 @@
       </c>
       <c r="B375" s="73" t="inlineStr">
         <is>
-          <t>254846611170</t>
+          <t>264548349664</t>
         </is>
       </c>
       <c r="C375" s="73" t="inlineStr"/>
       <c r="D375" s="73" t="inlineStr">
         <is>
-          <t>Information Technology Service Management (ITSM) Software Purchase and Implementation</t>
+          <t xml:space="preserve">Software Development </t>
         </is>
       </c>
       <c r="E375" s="73" t="inlineStr">
         <is>
-          <t>Port of Long Beach</t>
+          <t>Lorain County Veterans Service Commission</t>
         </is>
       </c>
       <c r="F375" s="73" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G375" s="73" t="inlineStr">
@@ -32332,13 +32332,13 @@
       </c>
       <c r="K375" s="73" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="L375" s="73" t="n"/>
       <c r="M375" s="73" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N375" s="73" t="inlineStr"/>
@@ -32358,12 +32358,12 @@
       <c r="X375" s="73" t="inlineStr"/>
       <c r="Y375" s="73" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z375" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/254846611170</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/264548349664</t>
         </is>
       </c>
       <c r="AA375" s="73" t="inlineStr"/>
@@ -32374,23 +32374,23 @@
       </c>
       <c r="B376" s="73" t="inlineStr">
         <is>
-          <t>264548349664</t>
+          <t>278975444717</t>
         </is>
       </c>
       <c r="C376" s="73" t="inlineStr"/>
       <c r="D376" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software Development </t>
+          <t>Cemetery Database Management and Support</t>
         </is>
       </c>
       <c r="E376" s="73" t="inlineStr">
         <is>
-          <t>Lorain County Veterans Service Commission</t>
+          <t>City of Fitchburg</t>
         </is>
       </c>
       <c r="F376" s="73" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="G376" s="73" t="inlineStr">
@@ -32407,19 +32407,19 @@
       </c>
       <c r="K376" s="73" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="L376" s="73" t="n"/>
       <c r="M376" s="73" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N376" s="73" t="inlineStr"/>
       <c r="O376" s="73" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="P376" s="73" t="inlineStr"/>
@@ -32433,12 +32433,12 @@
       <c r="X376" s="73" t="inlineStr"/>
       <c r="Y376" s="73" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Z376" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/264548349664</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/278975444717</t>
         </is>
       </c>
       <c r="AA376" s="73" t="inlineStr"/>
@@ -32534,23 +32534,27 @@
       </c>
       <c r="B378" s="73" t="inlineStr">
         <is>
-          <t>199601365719</t>
-        </is>
-      </c>
-      <c r="C378" s="73" t="inlineStr"/>
+          <t>264042757860</t>
+        </is>
+      </c>
+      <c r="C378" s="73" t="inlineStr">
+        <is>
+          <t>AMHIT-2026-0994</t>
+        </is>
+      </c>
       <c r="D378" s="73" t="inlineStr">
         <is>
-          <t>Cloud Managed Service Provider</t>
+          <t>UMass Amherst IT Services Assessment</t>
         </is>
       </c>
       <c r="E378" s="73" t="inlineStr">
         <is>
-          <t>Illinois Department of Innovation and Technology [IL]</t>
+          <t>University of Massachusetts</t>
         </is>
       </c>
       <c r="F378" s="73" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="G378" s="73" t="inlineStr">
@@ -32570,10 +32574,12 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="L378" s="73" t="n"/>
+      <c r="L378" s="75" t="n">
+        <v>93150</v>
+      </c>
       <c r="M378" s="73" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="N378" s="73" t="inlineStr">
@@ -32583,7 +32589,7 @@
       </c>
       <c r="O378" s="73" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="P378" s="73" t="inlineStr"/>
@@ -32597,12 +32603,12 @@
       <c r="X378" s="73" t="inlineStr"/>
       <c r="Y378" s="73" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z378" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/199601365719</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/264042757860</t>
         </is>
       </c>
       <c r="AA378" s="73" t="inlineStr"/>
@@ -32613,23 +32619,23 @@
       </c>
       <c r="B379" s="73" t="inlineStr">
         <is>
-          <t>255414924015</t>
+          <t>199601365719</t>
         </is>
       </c>
       <c r="C379" s="73" t="inlineStr"/>
       <c r="D379" s="73" t="inlineStr">
         <is>
-          <t>Tyler Enterprise ERP (Munis) Optimization</t>
+          <t>Cloud Managed Service Provider</t>
         </is>
       </c>
       <c r="E379" s="73" t="inlineStr">
         <is>
-          <t>COUNTY OF ALBANY</t>
+          <t>Illinois Department of Innovation and Technology [IL]</t>
         </is>
       </c>
       <c r="F379" s="73" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="G379" s="73" t="inlineStr">
@@ -32646,13 +32652,13 @@
       </c>
       <c r="K379" s="73" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="L379" s="73" t="n"/>
       <c r="M379" s="73" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N379" s="73" t="inlineStr">
@@ -32676,12 +32682,12 @@
       <c r="X379" s="73" t="inlineStr"/>
       <c r="Y379" s="73" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z379" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/255414924015</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/199601365719</t>
         </is>
       </c>
       <c r="AA379" s="73" t="inlineStr"/>
@@ -32692,27 +32698,23 @@
       </c>
       <c r="B380" s="73" t="inlineStr">
         <is>
-          <t>264042757860</t>
-        </is>
-      </c>
-      <c r="C380" s="73" t="inlineStr">
-        <is>
-          <t>AMHIT-2026-0994</t>
-        </is>
-      </c>
+          <t>255414924015</t>
+        </is>
+      </c>
+      <c r="C380" s="73" t="inlineStr"/>
       <c r="D380" s="73" t="inlineStr">
         <is>
-          <t>UMass Amherst IT Services Assessment</t>
+          <t>Tyler Enterprise ERP (Munis) Optimization</t>
         </is>
       </c>
       <c r="E380" s="73" t="inlineStr">
         <is>
-          <t>University of Massachusetts</t>
+          <t>COUNTY OF ALBANY</t>
         </is>
       </c>
       <c r="F380" s="73" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G380" s="73" t="inlineStr">
@@ -32729,15 +32731,13 @@
       </c>
       <c r="K380" s="73" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="L380" s="75" t="n">
-        <v>93150</v>
-      </c>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="L380" s="73" t="n"/>
       <c r="M380" s="73" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="N380" s="73" t="inlineStr">
@@ -32747,7 +32747,7 @@
       </c>
       <c r="O380" s="73" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="P380" s="73" t="inlineStr"/>
@@ -32761,12 +32761,12 @@
       <c r="X380" s="73" t="inlineStr"/>
       <c r="Y380" s="73" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="Z380" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/264042757860</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/255414924015</t>
         </is>
       </c>
       <c r="AA380" s="73" t="inlineStr"/>
@@ -33107,36 +33107,40 @@
       </c>
       <c r="B385" s="73" t="inlineStr">
         <is>
-          <t>269387571901</t>
-        </is>
-      </c>
-      <c r="C385" s="73" t="inlineStr">
-        <is>
-          <t>RTC 26-05</t>
-        </is>
-      </c>
+          <t>238161230535</t>
+        </is>
+      </c>
+      <c r="C385" s="73" t="inlineStr"/>
       <c r="D385" s="73" t="inlineStr">
         <is>
-          <t>RTC ERP Evaluator Services</t>
+          <t>Oracle Implementation Evaluation (Offline)</t>
         </is>
       </c>
       <c r="E385" s="73" t="inlineStr">
         <is>
-          <t>Regional Transportation Commission</t>
+          <t>Rochester City School District</t>
         </is>
       </c>
       <c r="F385" s="73" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G385" s="73" t="inlineStr">
         <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="H385" s="73" t="inlineStr"/>
-      <c r="I385" s="73" t="inlineStr"/>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="H385" s="73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I385" s="73" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
       <c r="J385" s="73" t="inlineStr">
         <is>
           <t>2026-02-05</t>
@@ -33147,26 +33151,32 @@
           <t>2026-02-05</t>
         </is>
       </c>
-      <c r="L385" s="75" t="n">
-        <v>78300</v>
-      </c>
+      <c r="L385" s="73" t="n"/>
       <c r="M385" s="73" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Consulting;Audits and Assessment</t>
         </is>
       </c>
       <c r="N385" s="73" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O385" s="73" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
-        </is>
-      </c>
-      <c r="P385" s="73" t="inlineStr"/>
-      <c r="Q385" s="73" t="inlineStr"/>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="P385" s="73" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q385" s="73" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
       <c r="R385" s="73" t="inlineStr"/>
       <c r="S385" s="73" t="inlineStr"/>
       <c r="T385" s="73" t="inlineStr"/>
@@ -33176,12 +33186,12 @@
       <c r="X385" s="73" t="inlineStr"/>
       <c r="Y385" s="73" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z385" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/269387571901</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/238161230535</t>
         </is>
       </c>
       <c r="AA385" s="73" t="inlineStr"/>
@@ -33192,40 +33202,36 @@
       </c>
       <c r="B386" s="73" t="inlineStr">
         <is>
-          <t>238161230535</t>
-        </is>
-      </c>
-      <c r="C386" s="73" t="inlineStr"/>
+          <t>269387571901</t>
+        </is>
+      </c>
+      <c r="C386" s="73" t="inlineStr">
+        <is>
+          <t>RTC 26-05</t>
+        </is>
+      </c>
       <c r="D386" s="73" t="inlineStr">
         <is>
-          <t>Oracle Implementation Evaluation (Offline)</t>
+          <t>RTC ERP Evaluator Services</t>
         </is>
       </c>
       <c r="E386" s="73" t="inlineStr">
         <is>
-          <t>Rochester City School District</t>
+          <t>Regional Transportation Commission</t>
         </is>
       </c>
       <c r="F386" s="73" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="G386" s="73" t="inlineStr">
         <is>
-          <t>Interview</t>
-        </is>
-      </c>
-      <c r="H386" s="73" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I386" s="73" t="inlineStr">
-        <is>
-          <t>Interview</t>
-        </is>
-      </c>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H386" s="73" t="inlineStr"/>
+      <c r="I386" s="73" t="inlineStr"/>
       <c r="J386" s="73" t="inlineStr">
         <is>
           <t>2026-02-05</t>
@@ -33236,32 +33242,26 @@
           <t>2026-02-05</t>
         </is>
       </c>
-      <c r="L386" s="73" t="n"/>
+      <c r="L386" s="75" t="n">
+        <v>78300</v>
+      </c>
       <c r="M386" s="73" t="inlineStr">
         <is>
-          <t>Consulting;Audits and Assessment</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N386" s="73" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O386" s="73" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
-        </is>
-      </c>
-      <c r="P386" s="73" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q386" s="73" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
+          <t>Savya Atrey</t>
+        </is>
+      </c>
+      <c r="P386" s="73" t="inlineStr"/>
+      <c r="Q386" s="73" t="inlineStr"/>
       <c r="R386" s="73" t="inlineStr"/>
       <c r="S386" s="73" t="inlineStr"/>
       <c r="T386" s="73" t="inlineStr"/>
@@ -33271,12 +33271,12 @@
       <c r="X386" s="73" t="inlineStr"/>
       <c r="Y386" s="73" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z386" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/238161230535</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/269387571901</t>
         </is>
       </c>
       <c r="AA386" s="73" t="inlineStr"/>
@@ -33898,18 +33898,18 @@
       </c>
       <c r="B394" s="73" t="inlineStr">
         <is>
-          <t>264972738293</t>
+          <t>276106770108</t>
         </is>
       </c>
       <c r="C394" s="73" t="inlineStr"/>
       <c r="D394" s="73" t="inlineStr">
         <is>
-          <t>Custom Events Calendar Web Application</t>
+          <t xml:space="preserve">Enterprise Data &amp; AI Strategy and Governance </t>
         </is>
       </c>
       <c r="E394" s="73" t="inlineStr">
         <is>
-          <t>City of Mansfield</t>
+          <t>Electric Reliability Council of Texas</t>
         </is>
       </c>
       <c r="F394" s="73" t="inlineStr">
@@ -33919,7 +33919,7 @@
       </c>
       <c r="G394" s="73" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H394" s="73" t="inlineStr"/>
@@ -33931,23 +33931,19 @@
       </c>
       <c r="K394" s="73" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="L394" s="73" t="n"/>
       <c r="M394" s="73" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
-        </is>
-      </c>
-      <c r="N394" s="73" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N394" s="73" t="inlineStr"/>
       <c r="O394" s="73" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="P394" s="73" t="inlineStr"/>
@@ -33961,12 +33957,12 @@
       <c r="X394" s="73" t="inlineStr"/>
       <c r="Y394" s="73" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="Z394" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/264972738293</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/276106770108</t>
         </is>
       </c>
       <c r="AA394" s="73" t="inlineStr"/>
@@ -33977,23 +33973,27 @@
       </c>
       <c r="B395" s="73" t="inlineStr">
         <is>
-          <t>276106770108</t>
-        </is>
-      </c>
-      <c r="C395" s="73" t="inlineStr"/>
+          <t>259789462223</t>
+        </is>
+      </c>
+      <c r="C395" s="73" t="inlineStr">
+        <is>
+          <t>RFQ1791333</t>
+        </is>
+      </c>
       <c r="D395" s="73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Data &amp; AI Strategy and Governance </t>
+          <t>Technology for Applications, Logistics, Operations, and Network</t>
         </is>
       </c>
       <c r="E395" s="73" t="inlineStr">
         <is>
-          <t>Electric Reliability Council of Texas</t>
+          <t>Department of Homeland Security, Transportation Security Administration</t>
         </is>
       </c>
       <c r="F395" s="73" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="G395" s="73" t="inlineStr">
@@ -34016,13 +34016,17 @@
       <c r="L395" s="73" t="n"/>
       <c r="M395" s="73" t="inlineStr">
         <is>
-          <t>Consulting</t>
-        </is>
-      </c>
-      <c r="N395" s="73" t="inlineStr"/>
+          <t>Consulting;Modernization / Migration;Platform Implementation (ERP, CRMs);Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N395" s="73" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O395" s="73" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="P395" s="73" t="inlineStr"/>
@@ -34036,12 +34040,12 @@
       <c r="X395" s="73" t="inlineStr"/>
       <c r="Y395" s="73" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="Z395" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/276106770108</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/259789462223</t>
         </is>
       </c>
       <c r="AA395" s="73" t="inlineStr"/>
@@ -34052,32 +34056,28 @@
       </c>
       <c r="B396" s="73" t="inlineStr">
         <is>
-          <t>259789462223</t>
-        </is>
-      </c>
-      <c r="C396" s="73" t="inlineStr">
-        <is>
-          <t>RFQ1791333</t>
-        </is>
-      </c>
+          <t>264972738293</t>
+        </is>
+      </c>
+      <c r="C396" s="73" t="inlineStr"/>
       <c r="D396" s="73" t="inlineStr">
         <is>
-          <t>Technology for Applications, Logistics, Operations, and Network</t>
+          <t>Custom Events Calendar Web Application</t>
         </is>
       </c>
       <c r="E396" s="73" t="inlineStr">
         <is>
-          <t>Department of Homeland Security, Transportation Security Administration</t>
+          <t>City of Mansfield</t>
         </is>
       </c>
       <c r="F396" s="73" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G396" s="73" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H396" s="73" t="inlineStr"/>
@@ -34089,23 +34089,23 @@
       </c>
       <c r="K396" s="73" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="L396" s="73" t="n"/>
       <c r="M396" s="73" t="inlineStr">
         <is>
-          <t>Consulting;Modernization / Migration;Platform Implementation (ERP, CRMs);Managed Services (MSP)</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="N396" s="73" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O396" s="73" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="P396" s="73" t="inlineStr"/>
@@ -34119,12 +34119,12 @@
       <c r="X396" s="73" t="inlineStr"/>
       <c r="Y396" s="73" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z396" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/259789462223</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/264972738293</t>
         </is>
       </c>
       <c r="AA396" s="73" t="inlineStr"/>
@@ -55163,23 +55163,27 @@
       </c>
       <c r="B2" s="73" t="inlineStr">
         <is>
-          <t>127690112742</t>
-        </is>
-      </c>
-      <c r="C2" s="73" t="inlineStr"/>
+          <t>116977709771</t>
+        </is>
+      </c>
+      <c r="C2" s="73" t="inlineStr">
+        <is>
+          <t>RFP-25-0005</t>
+        </is>
+      </c>
       <c r="D2" s="73" t="inlineStr">
         <is>
-          <t>Illinois Department of Public Health- Data Literacy Training</t>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
         </is>
       </c>
       <c r="E2" s="73" t="inlineStr">
         <is>
-          <t>Illinois Department of Public Health</t>
+          <t>NeighborWorks America</t>
         </is>
       </c>
       <c r="F2" s="73" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="G2" s="73" t="inlineStr">
@@ -55191,18 +55195,16 @@
       <c r="I2" s="73" t="inlineStr"/>
       <c r="J2" s="73" t="inlineStr"/>
       <c r="K2" s="73" t="inlineStr"/>
-      <c r="L2" s="75" t="n">
-        <v>18499</v>
-      </c>
+      <c r="L2" s="73" t="n"/>
       <c r="M2" s="73" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="N2" s="73" t="inlineStr"/>
       <c r="O2" s="73" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="P2" s="73" t="inlineStr"/>
@@ -55210,35 +55212,31 @@
       <c r="R2" s="73" t="inlineStr"/>
       <c r="S2" s="73" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="T2" s="73" t="inlineStr"/>
       <c r="U2" s="73" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="V2" s="73" t="inlineStr">
-        <is>
-          <t>In Process</t>
-        </is>
-      </c>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="V2" s="73" t="inlineStr"/>
       <c r="W2" s="73" t="inlineStr"/>
       <c r="X2" s="73" t="inlineStr"/>
       <c r="Y2" s="73" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z2" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/127690112742</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
         </is>
       </c>
       <c r="AA2" s="73" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -55248,27 +55246,27 @@
       </c>
       <c r="B3" s="73" t="inlineStr">
         <is>
-          <t>116977709771</t>
+          <t>116977709757</t>
         </is>
       </c>
       <c r="C3" s="73" t="inlineStr">
         <is>
-          <t>RFP-25-0005</t>
+          <t>RCA-017-25010066</t>
         </is>
       </c>
       <c r="D3" s="73" t="inlineStr">
         <is>
-          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
+          <t>ON-LINE MARKETPLACE FOR CLOUD SERVICES AND SOFTWARE</t>
         </is>
       </c>
       <c r="E3" s="73" t="inlineStr">
         <is>
-          <t>NeighborWorks America</t>
+          <t>Orange County</t>
         </is>
       </c>
       <c r="F3" s="73" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G3" s="73" t="inlineStr">
@@ -55283,7 +55281,7 @@
       <c r="L3" s="73" t="n"/>
       <c r="M3" s="73" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting;Reseller</t>
         </is>
       </c>
       <c r="N3" s="73" t="inlineStr"/>
@@ -55297,15 +55295,11 @@
       <c r="R3" s="73" t="inlineStr"/>
       <c r="S3" s="73" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="T3" s="73" t="inlineStr"/>
-      <c r="U3" s="73" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+      <c r="U3" s="73" t="inlineStr"/>
       <c r="V3" s="73" t="inlineStr"/>
       <c r="W3" s="73" t="inlineStr"/>
       <c r="X3" s="73" t="inlineStr"/>
@@ -55316,7 +55310,7 @@
       </c>
       <c r="Z3" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/116977709757</t>
         </is>
       </c>
       <c r="AA3" s="73" t="inlineStr">
@@ -55412,27 +55406,23 @@
       </c>
       <c r="B5" s="73" t="inlineStr">
         <is>
-          <t>127482767062</t>
-        </is>
-      </c>
-      <c r="C5" s="73" t="inlineStr">
-        <is>
-          <t>2024-013</t>
-        </is>
-      </c>
+          <t>127690112742</t>
+        </is>
+      </c>
+      <c r="C5" s="73" t="inlineStr"/>
       <c r="D5" s="73" t="inlineStr">
         <is>
-          <t>Marin Housing Authority- Managed IT Services, CIO and Cybersecurity Services</t>
+          <t>Illinois Department of Public Health- Data Literacy Training</t>
         </is>
       </c>
       <c r="E5" s="73" t="inlineStr">
         <is>
-          <t>Marin Housing Authority</t>
+          <t>Illinois Department of Public Health</t>
         </is>
       </c>
       <c r="F5" s="73" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="G5" s="73" t="inlineStr">
@@ -55445,11 +55435,11 @@
       <c r="J5" s="73" t="inlineStr"/>
       <c r="K5" s="73" t="inlineStr"/>
       <c r="L5" s="75" t="n">
-        <v>1200000</v>
+        <v>18499</v>
       </c>
       <c r="M5" s="73" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="N5" s="73" t="inlineStr"/>
@@ -55463,16 +55453,20 @@
       <c r="R5" s="73" t="inlineStr"/>
       <c r="S5" s="73" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="T5" s="73" t="inlineStr"/>
       <c r="U5" s="73" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="V5" s="73" t="inlineStr"/>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="V5" s="73" t="inlineStr">
+        <is>
+          <t>In Process</t>
+        </is>
+      </c>
       <c r="W5" s="73" t="inlineStr"/>
       <c r="X5" s="73" t="inlineStr"/>
       <c r="Y5" s="73" t="inlineStr">
@@ -55482,7 +55476,7 @@
       </c>
       <c r="Z5" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/127482767062</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/127690112742</t>
         </is>
       </c>
       <c r="AA5" s="73" t="inlineStr">
@@ -55665,22 +55659,22 @@
       </c>
       <c r="B8" s="73" t="inlineStr">
         <is>
-          <t>116977709757</t>
+          <t>127482767062</t>
         </is>
       </c>
       <c r="C8" s="73" t="inlineStr">
         <is>
-          <t>RCA-017-25010066</t>
+          <t>2024-013</t>
         </is>
       </c>
       <c r="D8" s="73" t="inlineStr">
         <is>
-          <t>ON-LINE MARKETPLACE FOR CLOUD SERVICES AND SOFTWARE</t>
+          <t>Marin Housing Authority- Managed IT Services, CIO and Cybersecurity Services</t>
         </is>
       </c>
       <c r="E8" s="73" t="inlineStr">
         <is>
-          <t>Orange County</t>
+          <t>Marin Housing Authority</t>
         </is>
       </c>
       <c r="F8" s="73" t="inlineStr">
@@ -55697,16 +55691,18 @@
       <c r="I8" s="73" t="inlineStr"/>
       <c r="J8" s="73" t="inlineStr"/>
       <c r="K8" s="73" t="inlineStr"/>
-      <c r="L8" s="73" t="n"/>
+      <c r="L8" s="75" t="n">
+        <v>1200000</v>
+      </c>
       <c r="M8" s="73" t="inlineStr">
         <is>
-          <t>Consulting;Reseller</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N8" s="73" t="inlineStr"/>
       <c r="O8" s="73" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="P8" s="73" t="inlineStr"/>
@@ -55714,27 +55710,31 @@
       <c r="R8" s="73" t="inlineStr"/>
       <c r="S8" s="73" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="T8" s="73" t="inlineStr"/>
-      <c r="U8" s="73" t="inlineStr"/>
+      <c r="U8" s="73" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
       <c r="V8" s="73" t="inlineStr"/>
       <c r="W8" s="73" t="inlineStr"/>
       <c r="X8" s="73" t="inlineStr"/>
       <c r="Y8" s="73" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z8" s="73" t="inlineStr">
         <is>
-          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/116977709757</t>
+          <t>https://app-na2.hubspot.com/contacts/243046792/record/0-3/127482767062</t>
         </is>
       </c>
       <c r="AA8" s="73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-05-01 13:28 EDT</t>
+          <t>2026-05-03 03:25 EDT</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA691"/>
+  <dimension ref="A1:AA694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -6158,12 +6158,17 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>BAFO</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -6179,9 +6184,24 @@
           <t>Audits and Assessment</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr">
         <is>
           <t>Arshdeep Kaur</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>BAFO</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6992,27 +7012,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>161660341982</t>
+          <t>126595998432</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>RFP-554-2025-0052-0-2025/AH</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>PROFESSIONAL CONSULTANT SERVICES</t>
+          <t>SharePoint Consultant</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Greene County</t>
+          <t>Raleigh Durham Airport Authority [NC]</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7022,7 +7047,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -7030,34 +7055,37 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="L66" s="65" t="n">
+        <v>18830</v>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/161660341982</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/126595998432</t>
         </is>
       </c>
     </row>
@@ -7067,27 +7095,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>126595998432</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>RFP-554-2025-0052-0-2025/AH</t>
+          <t>161660341982</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SharePoint Consultant</t>
+          <t>PROFESSIONAL CONSULTANT SERVICES</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Raleigh Durham Airport Authority [NC]</t>
+          <t>Greene County</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -7102,7 +7125,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -7110,37 +7133,44 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="L67" s="65" t="n">
-        <v>18830</v>
-      </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Arshdeep Kaur</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/126595998432</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/161660341982</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8566,17 +8596,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>240974373562</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Consolidated IT Services Bench</t>
+          <t>182109882089</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consolidated IT Services Bench </t>
+          <t>Enterprise Software Application Services Bench</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8626,7 +8651,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -8636,7 +8661,12 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/240974373562</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182109882089</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8646,27 +8676,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>182109882089</t>
+          <t>181172764371</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Enterprise Software Application Services Bench</t>
+          <t xml:space="preserve">INFORMATION TECHNOLOGY CONSULTANT SERVICES	</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Los Angeles Unified School District (LAUSD)</t>
+          <t xml:space="preserve">Township of Bloomfield </t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -8676,47 +8706,40 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>2025-10-13</t>
-        </is>
+      <c r="L88" s="65" t="n">
+        <v>179860</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182109882089</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/181172764371</t>
         </is>
       </c>
     </row>
@@ -8726,22 +8749,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>181172764371</t>
+          <t>175110074066</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>26-008</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">INFORMATION TECHNOLOGY CONSULTANT SERVICES	</t>
+          <t>Business Analyst Consulting Services</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Township of Bloomfield </t>
+          <t>Northeast Wisconsin Technical College (NWTC)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -8756,7 +8784,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -8764,17 +8792,14 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="L89" s="65" t="n">
-        <v>179860</v>
-      </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -8784,12 +8809,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/181172764371</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/175110074066</t>
         </is>
       </c>
     </row>
@@ -8799,42 +8824,47 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>175110074066</t>
+          <t>162089211630</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>26-008</t>
+          <t>2025-122</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Business Analyst Consulting Services</t>
+          <t>Auto-Update Oracle System Integration Testing Environment</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Northeast Wisconsin Technical College (NWTC)</t>
+          <t>Greater Cleveland Regional Transit Authority</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8844,27 +8874,37 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/175110074066</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/162089211630</t>
         </is>
       </c>
     </row>
@@ -8874,32 +8914,32 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>162089211630</t>
+          <t>240974373562</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2025-122</t>
+          <t>Consolidated IT Services Bench</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Auto-Update Oracle System Integration Testing Environment</t>
+          <t xml:space="preserve">Consolidated IT Services Bench </t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Greater Cleveland Regional Transit Authority</t>
+          <t>Los Angeles Unified School District (LAUSD)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Interview</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8909,12 +8949,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Interview</t>
+          <t>BAFO</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8924,37 +8964,42 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
+          <t>BAFO</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/162089211630</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/240974373562</t>
         </is>
       </c>
     </row>
@@ -15216,6 +15261,11 @@
           <t>Staff Augmentation</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
       <c r="O176" t="inlineStr">
         <is>
           <t>Abhishek Zalani</t>
@@ -21607,7 +21657,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Mexico Finance Authority ("NMFA") </t>
+          <t xml:space="preserve">New Mexico Finance Authority (“NMFA”) </t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -35951,6 +36001,11 @@
           <t>Consulting</t>
         </is>
       </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
       <c r="O465" t="inlineStr">
         <is>
           <t>Abhishek Zalani</t>
@@ -39903,9 +39958,17 @@
           <t>2026-02-27</t>
         </is>
       </c>
+      <c r="L520" s="65" t="n">
+        <v>7825</v>
+      </c>
       <c r="M520" t="inlineStr">
         <is>
           <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O520" t="inlineStr">
@@ -41565,7 +41628,12 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J544" t="inlineStr">
@@ -41578,16 +41646,34 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="L544" s="65" t="n">
+        <v>47775</v>
+      </c>
       <c r="M544" t="inlineStr">
         <is>
           <t>Consulting;Staff Augmentation</t>
         </is>
       </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O544" t="inlineStr">
         <is>
           <t>Savya Atrey</t>
         </is>
       </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q544" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
       <c r="S544" t="inlineStr">
         <is>
           <t>2026-04-22</t>
@@ -41601,6 +41687,11 @@
       <c r="Z544" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/305108054745</t>
+        </is>
+      </c>
+      <c r="AA544" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -50232,22 +50323,22 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>145081112265</t>
+          <t>320835245763</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>Technology Strategic Management Consulting</t>
+          <t>SECURITY OPERATIONS CENTER SOLUTION</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>State of Colorado, the Office of Information Technology (OIT)</t>
+          <t>NEW YORK eHEALTH COLLABORATIVE</t>
         </is>
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
@@ -50262,27 +50353,40 @@
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="L668" s="65" t="n">
+        <v>528000</v>
       </c>
       <c r="M668" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Audits and Assessment;Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N668" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O668" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y668" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z668" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320835245763</t>
         </is>
       </c>
     </row>
@@ -50292,27 +50396,17 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>175110048474</t>
+          <t>322527283932</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>Agile ITQ Development</t>
-        </is>
-      </c>
-      <c r="E669" t="inlineStr">
-        <is>
-          <t>Commonwealth of Pennsylvania</t>
-        </is>
-      </c>
-      <c r="F669" t="inlineStr">
-        <is>
-          <t>Pennsylvania</t>
+          <t>Test RFX (please ignore)</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H669" t="inlineStr">
@@ -50320,44 +50414,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J669" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
       <c r="M669" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O669" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Akshat Tripathi</t>
         </is>
       </c>
       <c r="S669" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="U669" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y669" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z669" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/175110048474</t>
-        </is>
-      </c>
-      <c r="AA669" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
         </is>
       </c>
     </row>
@@ -50367,27 +50446,32 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>166098266830</t>
+          <t>116977709771</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>RFP-25-0005</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>Mecklenburg County</t>
+          <t>NeighborWorks America</t>
         </is>
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
@@ -50395,29 +50479,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J670" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
       <c r="M670" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O670" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="S670" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="U670" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Y670" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z670" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+        </is>
+      </c>
+      <c r="AA670" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -50427,27 +50521,27 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>180166400720</t>
+          <t>145081112265</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
+          <t>Technology Strategic Management Consulting</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>Central Ohio Transit Authority</t>
+          <t>State of Colorado, the Office of Information Technology (OIT)</t>
         </is>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
@@ -50457,7 +50551,12 @@
       </c>
       <c r="J671" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M671" t="inlineStr">
+        <is>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O671" t="inlineStr">
@@ -50467,12 +50566,12 @@
       </c>
       <c r="Y671" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z671" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
         </is>
       </c>
     </row>
@@ -50482,32 +50581,27 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>164634446543</t>
-        </is>
-      </c>
-      <c r="C672" t="inlineStr">
-        <is>
-          <t>RFP26007KAB</t>
+          <t>175110048474</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>Enterprise Resource Planning System and Services</t>
+          <t>Agile ITQ Development</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>Clark County School District</t>
+          <t>Commonwealth of Pennsylvania</t>
         </is>
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H672" t="inlineStr">
@@ -50517,30 +50611,42 @@
       </c>
       <c r="J672" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="L672" s="65" t="n">
-        <v>180988276.8</v>
+          <t>2025-10-02</t>
+        </is>
       </c>
       <c r="M672" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
-        </is>
-      </c>
-      <c r="N672" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="O672" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S672" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="U672" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Y672" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z672" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/164634446543</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/175110048474</t>
+        </is>
+      </c>
+      <c r="AA672" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -50550,32 +50656,27 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>182404957915</t>
-        </is>
-      </c>
-      <c r="C673" t="inlineStr">
-        <is>
-          <t>PWE-10.08.2025</t>
+          <t>166098266830</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>PWE Power BI Dashboard</t>
+          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>City of Issaquah</t>
+          <t>Mecklenburg County</t>
         </is>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
@@ -50585,27 +50686,27 @@
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="M673" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O673" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y673" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z673" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
         </is>
       </c>
     </row>
@@ -50615,27 +50716,22 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>108771177151</t>
-        </is>
-      </c>
-      <c r="C674" t="inlineStr">
-        <is>
-          <t>791202505005</t>
+          <t>180166400720</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>Government Consulting Services</t>
+          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>North Central Texas Council of Governments</t>
+          <t>Central Ohio Transit Authority</t>
         </is>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>TEXAS</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
@@ -50650,12 +50746,7 @@
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="N674" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="O674" t="inlineStr">
@@ -50665,12 +50756,12 @@
       </c>
       <c r="Y674" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="Z674" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
         </is>
       </c>
     </row>
@@ -50680,32 +50771,32 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>120893940416</t>
+          <t>164634446543</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>DQ SAAA #2026000004</t>
+          <t>RFP26007KAB</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Online Content Learning</t>
+          <t>Enterprise Resource Planning System and Services</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>State of Colorado Department of Regulatory Agencies</t>
+          <t>Clark County School District</t>
         </is>
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
@@ -50715,30 +50806,30 @@
       </c>
       <c r="J675" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="L675" s="65" t="n">
-        <v>67300</v>
+        <v>180988276.8</v>
       </c>
       <c r="M675" t="inlineStr">
         <is>
-          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
-        </is>
-      </c>
-      <c r="O675" t="inlineStr">
-        <is>
-          <t>Madhav Mitruka</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="N675" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="Y675" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z675" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/164634446543</t>
         </is>
       </c>
     </row>
@@ -50748,27 +50839,32 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>199601365715</t>
+          <t>182404957915</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>PWE-10.08.2025</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Contracted IT Support Services</t>
+          <t>PWE Power BI Dashboard</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>ECS4Kids</t>
+          <t>City of Issaquah</t>
         </is>
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H676" t="inlineStr">
@@ -50778,20 +50874,12 @@
       </c>
       <c r="J676" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="L676" s="65" t="n">
-        <v>291141</v>
+          <t>2025-10-29</t>
+        </is>
       </c>
       <c r="M676" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N676" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O676" t="inlineStr">
@@ -50801,12 +50889,12 @@
       </c>
       <c r="Y676" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Z676" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
         </is>
       </c>
     </row>
@@ -50816,55 +50904,47 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>140123456196</t>
+          <t>108771177151</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>24-RFP-10</t>
+          <t>791202505005</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+          <t>Government Consulting Services</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+          <t>North Central Texas Council of Governments</t>
         </is>
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>TEXAS</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I677" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J677" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L677" s="65" t="n">
-        <v>18620</v>
-      </c>
-      <c r="M677" t="inlineStr">
-        <is>
-          <t>Training</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="N677" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O677" t="inlineStr">
@@ -50872,44 +50952,14 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="P677" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q677" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="S677" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="U677" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="V677" t="inlineStr">
-        <is>
-          <t>In Process</t>
-        </is>
-      </c>
       <c r="Y677" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="Z677" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
-        </is>
-      </c>
-      <c r="AA677" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
         </is>
       </c>
     </row>
@@ -50919,27 +50969,32 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>261982669555</t>
+          <t>120893940416</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>DQ SAAA #2026000004</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT Backfill for ERP Configuration </t>
+          <t>Online Content Learning</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>Madison Metropolitan Sewerage District</t>
+          <t>State of Colorado Department of Regulatory Agencies</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
@@ -50949,15 +51004,15 @@
       </c>
       <c r="J678" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="L678" s="65" t="n">
-        <v>157000</v>
+        <v>67300</v>
       </c>
       <c r="M678" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O678" t="inlineStr">
@@ -50965,34 +51020,14 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="S678" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="U678" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="V678" t="inlineStr">
-        <is>
-          <t>In Process</t>
-        </is>
-      </c>
       <c r="Y678" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z678" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
-        </is>
-      </c>
-      <c r="AA678" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
         </is>
       </c>
     </row>
@@ -51002,22 +51037,22 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>278519751386</t>
+          <t>199601365715</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>Data Warehousing Services</t>
+          <t>Contracted IT Support Services</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allen Town School District </t>
+          <t>ECS4Kids</t>
         </is>
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
@@ -51032,32 +51067,35 @@
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="L679" s="65" t="n">
+        <v>291141</v>
       </c>
       <c r="M679" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N679" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O679" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y679" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z679" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
         </is>
       </c>
     </row>
@@ -51067,62 +51105,100 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>259790359234</t>
+          <t>140123456196</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>601440000049523</t>
+          <t>24-RFP-10</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>Managed Application Services: Application Development and Maintenance Services</t>
+          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>Texas Department of Transportation</t>
+          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J680" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
-        </is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L680" s="65" t="n">
+        <v>18620</v>
       </c>
       <c r="M680" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O680" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P680" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q680" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="S680" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="U680" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="V680" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y680" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z680" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
+        </is>
+      </c>
+      <c r="AA680" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -51132,27 +51208,27 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>277652547262</t>
+          <t>261982669555</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
+          <t xml:space="preserve">IT Backfill for ERP Configuration </t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>District of Columbia Housing Finance Agency</t>
+          <t>Madison Metropolitan Sewerage District</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
@@ -51162,32 +51238,50 @@
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
-        </is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="L681" s="65" t="n">
+        <v>157000</v>
       </c>
       <c r="M681" t="inlineStr">
         <is>
-          <t>Consulting;Training</t>
-        </is>
-      </c>
-      <c r="N681" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O681" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S681" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="U681" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="V681" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y681" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z681" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
+        </is>
+      </c>
+      <c r="AA681" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -51197,22 +51291,22 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>269507522240</t>
+          <t>278519751386</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
+          <t>Data Warehousing Services</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>Central Midlands Regional Transit Authority</t>
+          <t xml:space="preserve">Allen Town School District </t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
@@ -51227,27 +51321,32 @@
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="M682" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N682" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O682" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y682" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Z682" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
         </is>
       </c>
     </row>
@@ -51257,27 +51356,32 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>294055526085</t>
+          <t>259790359234</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>601440000049523</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Oracle Managed Services and Testing as a Service Support</t>
+          <t>Managed Application Services: Application Development and Maintenance Services</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>CITY OF DURHAM</t>
+          <t>Texas Department of Transportation</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
@@ -51287,7 +51391,7 @@
       </c>
       <c r="J683" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="M683" t="inlineStr">
@@ -51297,17 +51401,17 @@
       </c>
       <c r="O683" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y683" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z683" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
         </is>
       </c>
     </row>
@@ -51317,22 +51421,22 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>305430641393</t>
+          <t>277652547262</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>OFF - Information Technology Managed Services</t>
+          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>County of Montcalm</t>
+          <t>District of Columbia Housing Finance Agency</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
@@ -51347,27 +51451,32 @@
       </c>
       <c r="J684" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="M684" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting;Training</t>
+        </is>
+      </c>
+      <c r="N684" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O684" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y684" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Z684" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
         </is>
       </c>
     </row>
@@ -51377,32 +51486,27 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>135161266908</t>
-        </is>
-      </c>
-      <c r="C685" t="inlineStr">
-        <is>
-          <t>RFQ1757840</t>
+          <t>269507522240</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>25-51-A-PMO-ES-SSN</t>
+          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>U.S. Department of the Treasury</t>
+          <t>Central Midlands Regional Transit Authority</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
@@ -51412,27 +51516,27 @@
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="N685" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O685" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y685" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z685" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
         </is>
       </c>
     </row>
@@ -51442,17 +51546,27 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>110691507903</t>
+          <t>294055526085</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
+          <t>Oracle Managed Services and Testing as a Service Support</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>CITY OF DURHAM</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
@@ -51462,25 +51576,27 @@
       </c>
       <c r="J686" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="L686" s="65" t="n">
-        <v>96200</v>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance</t>
+        </is>
       </c>
       <c r="O686" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y686" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Z686" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
         </is>
       </c>
     </row>
@@ -51490,17 +51606,27 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>110691507909</t>
+          <t>305430641393</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
+          <t>OFF - Information Technology Managed Services</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>County of Montcalm</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
@@ -51510,22 +51636,27 @@
       </c>
       <c r="J687" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O687" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y687" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="Z687" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
         </is>
       </c>
     </row>
@@ -51535,12 +51666,27 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>108771377911</t>
+          <t>135161266908</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>RFQ1757840</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>Facilities and Information Technology Infrastructure Assessment</t>
+          <t>25-51-A-PMO-ES-SSN</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>U.S. Department of the Treasury</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
@@ -51555,7 +51701,12 @@
       </c>
       <c r="J688" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="N688" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O688" t="inlineStr">
@@ -51565,12 +51716,12 @@
       </c>
       <c r="Y688" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z688" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
         </is>
       </c>
     </row>
@@ -51580,17 +51731,12 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>120893940419</t>
-        </is>
-      </c>
-      <c r="C689" t="inlineStr">
-        <is>
-          <t>#25-038-RFP)</t>
+          <t>110691507903</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>HUMAN RESOURCES INFORMATION SYSTEM ("HRIS") &amp; LEARNING MANAGEMENT SYSTEM ("LMS") REPLACEMENT</t>
+          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
@@ -51608,24 +51754,22 @@
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="M689" t="inlineStr">
-        <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
-        </is>
+      <c r="L689" s="65" t="n">
+        <v>96200</v>
       </c>
       <c r="O689" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y689" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z689" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
         </is>
       </c>
     </row>
@@ -51635,12 +51779,12 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>114864654049</t>
+          <t>110691507909</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>M365 Tenant backup</t>
+          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
@@ -51660,17 +51804,17 @@
       </c>
       <c r="O690" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y690" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z690" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
         </is>
       </c>
     </row>
@@ -51680,50 +51824,195 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
+          <t>108771377911</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Facilities and Information Technology Infrastructure Assessment</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O691" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y691" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z691" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="n">
+        <v>691</v>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>120893940419</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>#25-038-RFP)</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>HUMAN RESOURCES INFORMATION SYSTEM ("HRIS") &amp; LEARNING MANAGEMENT SYSTEM ("LMS") REPLACEMENT</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="O692" t="inlineStr">
+        <is>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="Y692" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="Z692" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="n">
+        <v>692</v>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>114864654049</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>M365 Tenant backup</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O693" t="inlineStr">
+        <is>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="Y693" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z693" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="n">
+        <v>693</v>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
           <t>317945474767</t>
         </is>
       </c>
-      <c r="D691" t="inlineStr">
+      <c r="D694" t="inlineStr">
         <is>
           <t>ServiceNow Technical Services</t>
         </is>
       </c>
-      <c r="E691" t="inlineStr">
+      <c r="E694" t="inlineStr">
         <is>
           <t>City of Sacramento</t>
         </is>
       </c>
-      <c r="F691" t="inlineStr">
+      <c r="F694" t="inlineStr">
         <is>
           <t>California</t>
         </is>
       </c>
-      <c r="G691" t="inlineStr">
+      <c r="G694" t="inlineStr">
         <is>
           <t>RFx Cancelled</t>
         </is>
       </c>
-      <c r="H691" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J691" t="inlineStr">
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="O691" t="inlineStr">
+      <c r="O694" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
-      <c r="Y691" t="inlineStr">
+      <c r="Y694" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="Z691" t="inlineStr">
+      <c r="Z694" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
         </is>
@@ -52483,22 +52772,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>127690112742</t>
+          <t>127482766020</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Illinois Department of Public Health- Data Literacy Training</t>
+          <t>Contingency Health IT Staffing - San Mateo County</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Illinois Department of Public Health</t>
+          <t>County of San Mateo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Illinios</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -52513,20 +52802,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="L8" s="65" t="n">
-        <v>18499</v>
+          <t>2025-02-28</t>
+        </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -52536,22 +52822,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Arshdeep Kaur</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -52561,12 +52842,12 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127690112742</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127482766020</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -52576,22 +52857,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>127482769082</t>
+          <t>127685792505</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EVT00010112</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ohio Department of Natural Resources- H2O PROJECT MANAGEMENTTASK TACKING TOOLENHANCEMENTS-SALESFORCE DEVELOPER</t>
+          <t>Temporary Staffing Services - State of Kansas</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ohio Department of Natural Resources</t>
+          <t xml:space="preserve">Kansas Department of Administration </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -52606,45 +52892,32 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="L9" s="65" t="n">
-        <v>11275</v>
+          <t>2025-03-21</t>
+        </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Arshdeep Kaur</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Completed</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -52654,12 +52927,12 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127482769082</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127685792505</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -52669,27 +52942,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>114864632563</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>IT1638-25</t>
+          <t>127690112742</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Marion County - Oracle Support Services</t>
+          <t>Illinois Department of Public Health- Data Literacy Training</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marion County</t>
+          <t>Illinois Department of Public Health</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>Illinios</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -52704,20 +52972,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="L10" s="65" t="n">
-        <v>100000</v>
+        <v>18499</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -52732,12 +53000,12 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -52747,12 +53015,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864632563</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127690112742</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -52767,22 +53035,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>127482750660</t>
+          <t>127482769082</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ON-CALL INFORMATION TECHNOLOGY (IT) QUALITY ASSURANCE AND CONTROL, PROJECT MANAGEMENT, AND BUSINESS ANALYSIS SUPPORT SERVICES (RFQ-MN-1395)</t>
+          <t>Ohio Department of Natural Resources- H2O PROJECT MANAGEMENTTASK TACKING TOOLENHANCEMENTS-SALESFORCE DEVELOPER</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Metropolitan Water District of Southern California</t>
+          <t>Ohio Department of Natural Resources</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -52797,17 +53065,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
-        </is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="L11" s="65" t="n">
+        <v>11275</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -52817,17 +53088,22 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -52837,12 +53113,12 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127482750660</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127482769082</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -52852,27 +53128,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>126600317675</t>
+          <t>114864632563</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RFP S24262</t>
+          <t>IT1638-25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Employee Application</t>
+          <t>Marion County - Oracle Support Services</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Santa Clara Valley Transportation Authority</t>
+          <t>Marion County</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -52882,30 +53158,25 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="L12" s="65" t="n">
-        <v>212000</v>
+        <v>100000</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Modernization / Migration;Support &amp; Maintenance;Platform Implementation (ERP, CRMs)</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -52918,24 +53189,14 @@
           <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>2025-05-08</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -52945,12 +53206,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/126600317675</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864632563</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -52965,27 +53226,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>126595998395</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>DOR RFP 24/25-59</t>
+          <t>127482750660</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FLDOR - SAP License Analysis</t>
+          <t>ON-CALL INFORMATION TECHNOLOGY (IT) QUALITY ASSURANCE AND CONTROL, PROJECT MANAGEMENT, AND BUSINESS ANALYSIS SUPPORT SERVICES (RFQ-MN-1395)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Florida Department of Revenue</t>
+          <t>Metropolitan Water District of Southern California</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -53000,60 +53256,52 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="L13" s="65" t="n">
-        <v>58800</v>
+          <t>2025-04-08</t>
+        </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/126595998395</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127482750660</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -53063,22 +53311,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>235860602564</t>
+          <t>126600317675</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RFQ-AR-1398</t>
+          <t>RFP S24262</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">On-Call Information Technology Cybersecurity Services </t>
+          <t>Employee Application</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Metropolitan Water District of Southern California</t>
+          <t>Santa Clara Valley Transportation Authority</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -53093,42 +53341,80 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="L14" s="65" t="n">
+        <v>212000</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Modernization / Migration;Support &amp; Maintenance;Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/235860602564</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/126600317675</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -53138,22 +53424,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>108072562388</t>
+          <t>126595998395</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DOR RFP 24/25-59</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>IT Augmentation Partner (SOW 1)</t>
+          <t>FLDOR - SAP License Analysis</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Madison Metropolitan Sewerage District</t>
+          <t>Florida Department of Revenue</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -53163,55 +53454,45 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="L15" s="65" t="n">
-        <v>1450000</v>
+        <v>58800</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Audits and Assessment</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -53221,12 +53502,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108072562388</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/126595998395</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -53241,22 +53522,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>127743477490</t>
+          <t>235860602564</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>RFQ-AR-1398</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EPIC 6- RFP 21.25 Technology Solutions &amp; Services</t>
+          <t xml:space="preserve">On-Call Information Technology Cybersecurity Services </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EPIC 6</t>
+          <t>Metropolitan Water District of Southern California</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -53271,52 +53557,37 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Staff Augmentation</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127743477490</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/235860602564</t>
         </is>
       </c>
     </row>
@@ -53326,22 +53597,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>135608301264</t>
+          <t>186570653428</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RFP-3578</t>
+          <t>405 24R0019168C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Managed Network Operations Center Services</t>
+          <t>Cherwell Professional Services</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Port Houston</t>
+          <t>Texas Department of Public Safety</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -53356,70 +53627,55 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="L17" s="65" t="n">
-        <v>1200000</v>
+        <v>148500</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>Managed Services (MSP)</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>2025-07-23</t>
+          <t>Satvik Chaudhary</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135608301264</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/186570653428</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -53434,22 +53690,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>181172764367</t>
+          <t>108072562388</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Temporary Personnel Services for Information Technology</t>
+          <t>IT Augmentation Partner (SOW 1)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Monroe County</t>
+          <t>Madison Metropolitan Sewerage District</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -53459,52 +53715,70 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="L18" s="65" t="n">
+        <v>1450000</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>In Process</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>2025-06-25</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Jyothsna Nanda kishore</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/181172764367</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108072562388</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -53519,22 +53793,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>127677476588</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>23-030</t>
+          <t>127743477490</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Miscellaneous Consultant Services</t>
+          <t>EPIC 6- RFP 21.25 Technology Solutions &amp; Services</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Antonio Independent School District</t>
+          <t>EPIC 6</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -53554,12 +53823,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -53579,17 +53848,12 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -53599,7 +53863,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127677476588</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127743477490</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -53614,22 +53878,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>110712028891</t>
+          <t>135608301264</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>RFP-3578</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>STAFFING SERVICES WITH RELATED SERVICES AND SOLUTIONS</t>
+          <t>Managed Network Operations Center Services</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oregon League of Cities</t>
+          <t>Port Houston</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -53639,27 +53908,30 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
-        </is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="L20" s="65" t="n">
+        <v>1200000</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -53667,24 +53939,39 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110712028891</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135608301264</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -53699,27 +53986,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>127424133880</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>5400028271</t>
+          <t>181172764367</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>STC Dynamics Managed Service Provider</t>
+          <t>Temporary Personnel Services for Information Technology</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>State of South Carolina</t>
+          <t>Monroe County</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -53734,17 +54016,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Managed Services (MSP);Staff Augmentation</t>
+          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -53759,22 +54041,22 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127424133880</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/181172764367</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -53789,22 +54071,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>114864544502</t>
+          <t>127677476588</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>23-030</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Workday Related Staff Augmentation and Project Work</t>
+          <t>Miscellaneous Consultant Services</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>University System of New Hampshire</t>
+          <t>San Antonio Independent School District</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>New Hampshire</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -53819,42 +54106,57 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>In Process</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025-07-08</t>
-        </is>
-      </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864544502</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127677476588</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -53864,22 +54166,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>134329484998</t>
+          <t>110712028891</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>OPENCollier MPO WordPress Website Maintenance &amp; Hosting</t>
+          <t>STAFFING SERVICES WITH RELATED SERVICES AND SOLUTIONS</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Collier County</t>
+          <t>Oregon League of Cities</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -53894,16 +54196,18 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="L23" s="65" t="n">
-        <v>2640</v>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Staff Augmentation</t>
+        </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -53917,22 +54221,27 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/134329484998</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110712028891</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -53942,27 +54251,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>110968802000</t>
+          <t>127424133880</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>201-2025-1000-1</t>
+          <t>5400028271</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>School Data Migration</t>
+          <t>STC Dynamics Managed Service Provider</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>North Dakota Department of Public Instruction</t>
+          <t>State of South Carolina</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>North Dakota</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -53977,50 +54286,47 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="L24" s="65" t="n">
-        <v>193000</v>
+          <t>2025-07-22</t>
+        </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Managed Services (MSP);Staff Augmentation</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110968802000</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127424133880</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -54035,27 +54341,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>120592685811</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>RFQ-1001295</t>
+          <t>114864544502</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cybersecurity Services for Iowa Political Subdivisions</t>
+          <t>Workday Related Staff Augmentation and Project Work</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Iowa State University</t>
+          <t>University System of New Hampshire</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>New Hampshire</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -54075,12 +54376,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Audits and Assessment</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -54090,32 +54386,27 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120592685811</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864544502</t>
         </is>
       </c>
     </row>
@@ -54125,22 +54416,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>121105455846</t>
+          <t>134329484998</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>IT Services - Palo Verde Valley Transit Agency</t>
+          <t>OPENCollier MPO WordPress Website Maintenance &amp; Hosting</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Palo Verde Valley Transit Agency</t>
+          <t>Collier County</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -54150,35 +54441,25 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="L26" s="65" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Managed Services (MSP)</t>
-        </is>
+        <v>2640</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -54186,39 +54467,24 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/121105455846</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/134329484998</t>
         </is>
       </c>
     </row>
@@ -54228,95 +54494,85 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>129524913852</t>
+          <t>110968802000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2124952</t>
+          <t>201-2025-1000-1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Broadcom CA ESP dSeries Workload Automation Migration</t>
+          <t>School Data Migration</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>New York State Office of the State Comptroller</t>
+          <t>North Dakota Department of Public Instruction</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>North Dakota</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="L27" s="65" t="n">
+        <v>193000</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Modernization / Migration</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Arshdeep Kaur</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="L27" s="65" t="n">
-        <v>126200</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Modernization / Migration</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>2026-01-06</t>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/129524913852</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110968802000</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -54331,22 +54587,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>126587718330</t>
+          <t>120592685811</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>RFQ-1001295</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>E-Rate Cybersecurity Pilot Program - Next Generation Firewall</t>
+          <t>Cybersecurity Services for Iowa Political Subdivisions</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Alachua County Library District</t>
+          <t>Iowa State University</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -54361,20 +54622,17 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="L28" s="65" t="n">
-        <v>125000</v>
+          <t>2025-08-08</t>
+        </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -54384,22 +54642,32 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/126587718330</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120592685811</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -54409,27 +54677,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>144659629780</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>02805095</t>
+          <t>121105455846</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Veeam VBR Enterprise Basic Maintenance License Renew</t>
+          <t>IT Services - Palo Verde Valley Transit Agency</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>St. Johns County</t>
+          <t>Palo Verde Valley Transit Agency</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -54439,25 +54702,30 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="L29" s="65" t="n">
-        <v>15712</v>
+        <v>24000</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Reseller</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -54470,24 +54738,39 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/144659629780</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/121105455846</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -54497,32 +54780,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>137815198453</t>
+          <t>129524913852</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>RFP No. FIN0825-001</t>
+          <t>2124952</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Enterprise Planning Resource (ERP) System Architecture and Configuration (RFP No. FIN0825-001)</t>
+          <t>Broadcom CA ESP dSeries Workload Automation Migration</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Municipal Water District of Orange County (MWDOC)</t>
+          <t>New York State Office of the State Comptroller</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -54537,20 +54820,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="L30" s="65" t="n">
-        <v>81000</v>
+        <v>126200</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -54570,32 +54853,22 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/137815198453</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/129524913852</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -54610,22 +54883,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>145845264086</t>
+          <t>126587718330</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Information Technology Services</t>
+          <t>E-Rate Cybersecurity Pilot Program - Next Generation Firewall</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>City of Olmos Park</t>
+          <t>Alachua County Library District</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -54640,55 +54913,45 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="L31" s="65" t="n">
-        <v>308576</v>
+        <v>125000</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145845264086</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/126587718330</t>
         </is>
       </c>
     </row>
@@ -54698,17 +54961,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>134489494217</t>
+          <t>144659629780</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>02805095</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Prequalification for Information Technology Staff Augmentation Services (Supplemental) 2025</t>
+          <t>Veeam VBR Enterprise Basic Maintenance License Renew</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Florida Department of Management Services</t>
+          <t>St. Johns County</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -54728,22 +54996,25 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
-        </is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="L32" s="65" t="n">
+        <v>15712</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Reseller</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -54753,27 +55024,22 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/134489494217</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/144659629780</t>
         </is>
       </c>
     </row>
@@ -54783,17 +55049,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>144653136611</t>
+          <t>137815198453</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>RFP No. FIN0825-001</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Data Solution Design, Build &amp; Implementation, Western Municipal Water District (Western Water)</t>
+          <t>Enterprise Planning Resource (ERP) System Architecture and Configuration (RFP No. FIN0825-001)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Western Municipal Water District </t>
+          <t>Municipal Water District of Orange County (MWDOC)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -54808,45 +55079,60 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="L33" s="65" t="n">
-        <v>143460</v>
+        <v>81000</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -54856,12 +55142,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/144653136611</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/137815198453</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -54876,27 +55162,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>159541459657</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>WSD001</t>
+          <t>145845264086</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Microsoft Power Platform Training</t>
+          <t>Information Technology Services</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>County of Los Angeles Department of Public Works</t>
+          <t>City of Olmos Park</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -54911,50 +55192,55 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="L34" s="65" t="n">
-        <v>12000</v>
+        <v>308576</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Arshdeep Kaur</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/159541459657</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145845264086</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -54969,22 +55255,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>158113558258</t>
+          <t>134489494217</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Data Center Assessment and Risk Mitigation Strategy</t>
+          <t>Prequalification for Information Technology Staff Augmentation Services (Supplemental) 2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tri-County Metropolitan Transportation District of Oregon</t>
+          <t>Florida Department of Management Services</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -54999,50 +55285,52 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="L35" s="65" t="n">
-        <v>20893</v>
+          <t>2025-09-16</t>
+        </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/158113558258</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/134489494217</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -55052,27 +55340,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>161660341982</t>
+          <t>144653136611</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PROFESSIONAL CONSULTANT SERVICES</t>
+          <t>Data Solution Design, Build &amp; Implementation, Western Municipal Water District (Western Water)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Greene County</t>
+          <t xml:space="preserve">Western Municipal Water District </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -55082,42 +55370,60 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="L36" s="65" t="n">
+        <v>143460</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/161660341982</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/144653136611</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -55127,27 +55433,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>126595998432</t>
+          <t>159541459657</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RFP-554-2025-0052-0-2025/AH</t>
+          <t>WSD001</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SharePoint Consultant</t>
+          <t>Microsoft Power Platform Training</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Raleigh Durham Airport Authority [NC]</t>
+          <t>County of Los Angeles Department of Public Works</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -55162,45 +55468,55 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="L37" s="65" t="n">
-        <v>18830</v>
+        <v>12000</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/126595998432</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/159541459657</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -55210,27 +55526,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>158113559231</t>
+          <t>158113558258</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Legacy File Server Migration to SharePoint Modernization</t>
+          <t>Data Center Assessment and Risk Mitigation Strategy</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>City of San Carlos</t>
+          <t>Tri-County Metropolitan Transportation District of Oregon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -55240,50 +55556,55 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Interview</t>
+          <t>BAFO</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="L38" s="65" t="n">
-        <v>98000</v>
+        <v>20893</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Arshdeep Kaur</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
+          <t>BAFO</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -55293,7 +55614,12 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/158113559231</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/158113558258</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -55303,32 +55629,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>240974373562</t>
+          <t>126595998432</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Consolidated IT Services Bench</t>
+          <t>RFP-554-2025-0052-0-2025/AH</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consolidated IT Services Bench </t>
+          <t>SharePoint Consultant</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Los Angeles Unified School District (LAUSD)</t>
+          <t>Raleigh Durham Airport Authority [NC]</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -55338,17 +55664,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="L39" s="65" t="n">
+        <v>18830</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -55358,22 +55687,22 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/240974373562</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/126595998432</t>
         </is>
       </c>
     </row>
@@ -55383,27 +55712,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>182109882089</t>
+          <t>161660341982</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Enterprise Software Application Services Bench</t>
+          <t>PROFESSIONAL CONSULTANT SERVICES</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Los Angeles Unified School District (LAUSD)</t>
+          <t>Greene County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -55413,12 +55742,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -55428,27 +55757,32 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Arshdeep Kaur</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182109882089</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/161660341982</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -55463,50 +55797,55 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>241471982294</t>
+          <t>158113559231</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>IT SERVICES FOR THE TOWN OF ST MICHAELS</t>
+          <t>Legacy File Server Migration to SharePoint Modernization</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Town of St Michaels </t>
+          <t>City of San Carlos</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="L41" s="65" t="n">
-        <v>74000</v>
+        <v>98000</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -55519,34 +55858,29 @@
           <t>Abhishek Zalani</t>
         </is>
       </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/241471982294</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/158113559231</t>
         </is>
       </c>
     </row>
@@ -55556,60 +55890,47 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>159501546182</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>25-082</t>
+          <t>182109882089</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Amazon Web Services Website Managed ServicesID: 25-082</t>
+          <t>Enterprise Software Application Services Bench</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>El Paso County</t>
+          <t>Los Angeles Unified School District (LAUSD)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="L42" s="65" t="n">
-        <v>769752</v>
+          <t>2025-10-13</t>
+        </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -55619,42 +55940,27 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/159501546182</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182109882089</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -55664,27 +55970,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>169109642951</t>
+          <t>240974373562</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>242-25-00022</t>
+          <t>Consolidated IT Services Bench</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consulting &amp; Training Support - Workday Adaptive Planning </t>
+          <t xml:space="preserve">Consolidated IT Services Bench </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Christopher Newport University</t>
+          <t>Los Angeles Unified School District (LAUSD)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -55704,75 +56010,52 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="L43" s="65" t="n">
-        <v>30000</v>
+          <t>2025-10-13</t>
+        </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Consulting;Training</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
+          <t>BAFO</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Awarded</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/169109642951</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/240974373562</t>
         </is>
       </c>
     </row>
@@ -55782,32 +56065,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>145845271269</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>PI25-0148F</t>
+          <t>241471982294</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Computerized Maintenance Management System</t>
+          <t>IT SERVICES FOR THE TOWN OF ST MICHAELS</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>City of Tacoma</t>
+          <t xml:space="preserve">Town of St Michaels </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -55817,20 +56095,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="L44" s="65" t="n">
-        <v>83098</v>
+        <v>74000</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -55845,17 +56123,27 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145845271269</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/241471982294</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -55870,22 +56158,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>200821843683</t>
+          <t>159501546182</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>25-082</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Veeam Data Platform Renewal</t>
+          <t>Amazon Web Services Website Managed ServicesID: 25-082</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cuyahoga County Board of Elections</t>
+          <t>El Paso County</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -55895,25 +56188,30 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="L45" s="65" t="n">
-        <v>6078.19</v>
+        <v>769752</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Reseller</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -55923,32 +56221,42 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/200821843683</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/159501546182</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -55958,22 +56266,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>182109882068</t>
+          <t>169109642951</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>242-25-00022</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Professional Consultant Services (Rebid)</t>
+          <t xml:space="preserve">Consulting &amp; Training Support - Workday Adaptive Planning </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Greene County</t>
+          <t>Christopher Newport University</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -55983,52 +56296,85 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>BAFO</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="L46" s="65" t="n">
+        <v>30000</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting;Training</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Awarded</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182109882068</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/169109642951</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -56038,85 +56384,80 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>209641964265</t>
+          <t>145845271269</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PI25-0148F</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Professional and Technical IT Contracting Services for SharePoint Migration</t>
+          <t>Computerized Maintenance Management System</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>City of Sunnyvale</t>
+          <t>City of Tacoma</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="L47" s="65" t="n">
-        <v>45800</v>
+        <v>83098</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/209641964265</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145845271269</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -56131,55 +56472,55 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>202061536982</t>
+          <t>200821843683</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY (IT)MANAGED SERVICE PROVIDER AND NETWORK OPERATIONS CENTER (NOC)</t>
+          <t>Veeam Data Platform Renewal</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Mexico Finance Authority ('NMFA') </t>
+          <t>Cuyahoga County Board of Elections</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>BAFO</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="L48" s="65" t="n">
-        <v>84000</v>
+        <v>6078.19</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Reseller</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -56187,44 +56528,29 @@
           <t>Ashutosh Chauhan</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/202061536982</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/200821843683</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -56234,22 +56560,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>231581420260</t>
+          <t>182109882068</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Information Technology Services</t>
+          <t>Professional Consultant Services (Rebid)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>New Castle County</t>
+          <t>Greene County</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -56264,12 +56590,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -56284,27 +56610,27 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/231581420260</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182109882068</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -56319,17 +56645,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>225906283257</t>
+          <t>209641964265</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Information Systems Consultant</t>
+          <t>Professional and Technical IT Contracting Services for SharePoint Migration</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Community Action Partnership of Kern</t>
+          <t>City of Sunnyvale</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -56344,57 +56670,60 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
-        </is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="L50" s="65" t="n">
+        <v>45800</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Consulting</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Awarded</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/225906283257</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/209641964265</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -56409,80 +56738,100 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>235886616288</t>
+          <t>202061536982</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Rebid- Information Technology Services</t>
+          <t>INFORMATION TECHNOLOGY (IT)MANAGED SERVICE PROVIDER AND NETWORK OPERATIONS CENTER (NOC)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>LEAD CHARTER SCHOOL</t>
+          <t xml:space="preserve">New Mexico Finance Authority (“NMFA”) </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>BAFO</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="L51" s="65" t="n">
+        <v>84000</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="L51" s="65" t="n">
-        <v>24750</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Jyothsna Nanda kishore</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/235886616288</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/202061536982</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -56497,22 +56846,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>235964612297</t>
+          <t>231581420260</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>AI Governance, Compliance, and Enablement Platform</t>
+          <t>Information Technology Services</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>North Central Texas Council of Governments</t>
+          <t>New Castle County</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TEXAS</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -56527,52 +56876,47 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Awarded</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/235964612297</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/231581420260</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -56587,27 +56931,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>225906287352</t>
+          <t>225906283257</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Small Software Application Development</t>
+          <t>Information Systems Consultant</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Insurance Reserve Fund </t>
+          <t>Community Action Partnership of Kern</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -56617,22 +56961,22 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -56642,12 +56986,17 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Awarded</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -56657,7 +57006,12 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/225906287352</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/225906283257</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -56667,27 +57021,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>275926212329</t>
+          <t>235886616288</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>MICROSOFT OFFICE 365 LICENSING</t>
+          <t>Rebid- Information Technology Services</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Village of Tinley Park</t>
+          <t>LEAD CHARTER SCHOOL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -56697,20 +57051,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="L54" s="65" t="n">
-        <v>114400</v>
+        <v>24750</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Reseller</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -56735,17 +57089,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/275926212329</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/235886616288</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -56755,22 +57109,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>267386743501</t>
+          <t>235964612297</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>FPB – Direct Placement Staffing Services for IT Positions</t>
+          <t>AI Governance, Compliance, and Enablement Platform</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>University of South Carolina</t>
+          <t>North Central Texas Council of Governments</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>TEXAS</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -56785,17 +57139,17 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -56805,27 +57159,32 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Awarded</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/267386743501</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/235964612297</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -56840,27 +57199,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>277951244006</t>
+          <t>225906287352</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>offline + online IT Disaster Response Plan</t>
+          <t>Small Software Application Development</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>City of Kenai</t>
+          <t xml:space="preserve">Insurance Reserve Fund </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -56870,55 +57229,47 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="L56" s="65" t="n">
-        <v>16800</v>
+          <t>2026-01-26</t>
+        </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Awarded</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277951244006</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/225906287352</t>
         </is>
       </c>
     </row>
@@ -56928,22 +57279,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>285814477558</t>
+          <t>275926212329</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>RFQ - 1400 Long Beach Cybersecurity Grant Program</t>
+          <t>MICROSOFT OFFICE 365 LICENSING</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>City of Long Beach</t>
+          <t>Village of Tinley Park</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mississippi</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -56963,20 +57314,20 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="L57" s="65" t="n">
-        <v>123785</v>
+        <v>114400</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Reseller</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -56986,27 +57337,27 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/285814477558</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/275926212329</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -57016,22 +57367,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>290824554187</t>
+          <t>267386743501</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cybersecurity Policy and Protocol Consultant Services</t>
+          <t>FPB – Direct Placement Staffing Services for IT Positions</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Navojo Housing Authority</t>
+          <t>University of South Carolina</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -57046,52 +57397,52 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Awarded</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/290824554187</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/267386743501</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -57101,22 +57452,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>305108054745</t>
+          <t>277951244006</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Technology Data Architect Services</t>
+          <t>offline + online IT Disaster Response Plan</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>City of Stamford</t>
+          <t>City of Kenai</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>Alaska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -57131,37 +57482,60 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="L59" s="65" t="n">
+        <v>16800</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Consulting;Staff Augmentation</t>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Awarded</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305108054745</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277951244006</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -57171,22 +57545,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>320213008064</t>
+          <t>285814477558</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ONLINE WEB-BASED TRAINING</t>
+          <t>RFQ - 1400 Long Beach Cybersecurity Grant Program</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Alaska Department of Administration</t>
+          <t>City of Long Beach</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>Mississippi</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -57201,20 +57575,25 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="L60" s="65" t="n">
-        <v>37800</v>
+        <v>123785</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Audits and Assessment</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -57224,22 +57603,22 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320213008064</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/285814477558</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -57254,27 +57633,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>116977709771</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>RFP-25-0005</t>
+          <t>290824554187</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
+          <t>Cybersecurity Policy and Protocol Consultant Services</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>NeighborWorks America</t>
+          <t>Navojo Housing Authority</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -57287,39 +57661,62 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="L61" s="65" t="n">
+        <v>7825</v>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Awarded</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/290824554187</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -57329,27 +57726,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>269389012723</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>COVB-25-101486</t>
+          <t>305108054745</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Technology Data Architect Services</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">City of Virginia Beach </t>
+          <t>City of Stamford</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Connecticut</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -57359,42 +57751,70 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="L62" s="65" t="n">
+        <v>47775</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting;Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Savya Atrey</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269389012723</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305108054745</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -57404,22 +57824,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>116977709756</t>
+          <t>320213008064</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Hazelwood Information Technology Audit Services</t>
+          <t>ONLINE WEB-BASED TRAINING</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hazelwood School District</t>
+          <t>Alaska Department of Administration</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Alaska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -57432,37 +57852,42 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
       <c r="L63" s="65" t="n">
-        <v>48500</v>
+        <v>37800</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709756</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320213008064</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -57477,22 +57902,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>116977709757</t>
+          <t>127482765035</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>RCA-017-25010066</t>
+          <t>RFP NO. NC- 2025-14</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ON-LINE MARKETPLACE FOR CLOUD SERVICES AND SOFTWARE</t>
+          <t>Computer Maintenance &amp; Technology Support Services - FCSS Fresno County Superintendent of Schools</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Orange County</t>
+          <t>FRESNO COUNTY SUPERINTENDENT OF SCHOOLS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -57510,29 +57935,54 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Consulting;Reseller</t>
+          <t>Consulting;Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Arshdeep Kaur</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709757</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127482765035</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -57547,17 +57997,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>322527283932</t>
+          <t>116977709757</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>RCA-017-25010066</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Test RFX (please ignore)</t>
+          <t>ON-LINE MARKETPLACE FOR CLOUD SERVICES AND SOFTWARE</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Orange County</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>California</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -57567,27 +58032,32 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Consulting;Reseller</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>159334547664</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709757</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -57597,22 +58067,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>127590445803</t>
+          <t>116977709771</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>RFP-25-0005</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>IT Staffing and Professional Services</t>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Roswell Park Comprehensive Cancer Centre</t>
+          <t>NeighborWorks America</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -57625,39 +58100,34 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Consulting;Staff Augmentation</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445803</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -57672,27 +58142,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>123670192881</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>24-31</t>
+          <t>116977709756</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Arapahoe County - IT RECRUITMENT AND STAFFING</t>
+          <t>Hazelwood Information Technology Audit Services</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Arapahoe County</t>
+          <t>Hazelwood School District</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -57705,44 +58170,42 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>2024-11-13</t>
-        </is>
+      <c r="L67" s="65" t="n">
+        <v>48500</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
           <t>2025-04-28</t>
         </is>
       </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>In Process</t>
+        </is>
+      </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/123670192881</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709756</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -57752,27 +58215,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>114864632551</t>
+          <t>269389012723</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>F25-077</t>
+          <t>COVB-25-101486</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>City of Sunnyvale - Group 4, Software/Application/Database Development, Business Requirements Analysis, and Integration Services</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>City of Sunnyvale</t>
+          <t xml:space="preserve">City of Virginia Beach </t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -57785,44 +58248,34 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t>Staff Augmentation</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864632551</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269389012723</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -57837,32 +58290,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>127678196421</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>RFQ 24 - 00332</t>
+          <t>322527283932</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>HRT - Workday HCM Staffing Services</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Hampton Roads Transit</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Virginia</t>
+          <t>Test RFX (please ignore)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -57870,52 +58308,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="L69" s="65" t="n">
-        <v>10000</v>
-      </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
+          <t>Akshat Tripathi</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127678196421</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
         </is>
       </c>
     </row>
@@ -57925,22 +58340,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>127482766020</t>
+          <t>127590445803</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Contingency Health IT Staffing - San Mateo County</t>
+          <t>IT Staffing and Professional Services</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>County of San Mateo</t>
+          <t>Roswell Park Comprehensive Cancer Centre</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -57955,32 +58370,27 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Consulting;Staff Augmentation</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -57990,7 +58400,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127482766020</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445803</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -58005,22 +58415,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>127590445777</t>
+          <t>123670192881</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>24-31</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Temporary Professional Staff Services 2</t>
+          <t>Arapahoe County - IT RECRUITMENT AND STAFFING</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>State of South Dakota Department of Social Services</t>
+          <t>Arapahoe County</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>South Dakota</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -58035,7 +58450,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -58045,27 +58460,27 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445777</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/123670192881</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -58080,27 +58495,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>127685792505</t>
+          <t>114864632551</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>EVT00010112</t>
+          <t>F25-077</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Temporary Staffing Services - State of Kansas</t>
+          <t>City of Sunnyvale - Group 4, Software/Application/Database Development, Business Requirements Analysis, and Integration Services</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas Department of Administration </t>
+          <t>City of Sunnyvale</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -58115,7 +58530,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -58123,29 +58538,34 @@
           <t>Staff Augmentation</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127685792505</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864632551</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -58160,27 +58580,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>142851074788</t>
+          <t>127678196421</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>RFQ-DH-1394</t>
+          <t>RFQ 24 - 00332</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ON-CALL INFORMATION TECHNOLOGY INFRASTRUCTURE SERVICES</t>
+          <t>HRT - Workday HCM Staffing Services</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Metropolitan Water District of Southern California</t>
+          <t>Hampton Roads Transit</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -58190,52 +58610,70 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
-        </is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="L73" s="65" t="n">
+        <v>10000</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
           <t>Staff Augmentation</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Arshdeep Kaur</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/142851074788</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127678196421</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -58245,22 +58683,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>132776626904</t>
+          <t>127590445777</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ON-CALL INFORMATION TECHNOLOGY (IT) APPLICATION SUPPORT SERVICES (RFQ-DS-1397)</t>
+          <t>Temporary Professional Staff Services 2</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Metropolitan Water District of Southern California</t>
+          <t>State of South Dakota Department of Social Services</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>South Dakota</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -58275,7 +58713,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -58290,22 +58728,22 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/132776626904</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445777</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -58320,22 +58758,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>127678196440</t>
+          <t>142851074788</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>RFQ-DH-1394</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>MINNESOTA JUDICIAL BRANCH - IT Technical/infrastructure Services, Information Technology Application Development And Support Services &amp; Data Science And Machine Learning Services</t>
+          <t>ON-CALL INFORMATION TECHNOLOGY INFRASTRUCTURE SERVICES</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Minnesota Judicial Branch</t>
+          <t>Metropolitan Water District of Southern California</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -58350,7 +58793,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -58358,29 +58801,34 @@
           <t>Staff Augmentation</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127678196440</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/142851074788</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -58395,27 +58843,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>186570653428</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>405 24R0019168C</t>
+          <t>132776626904</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Cherwell Professional Services</t>
+          <t>ON-CALL INFORMATION TECHNOLOGY (IT) APPLICATION SUPPORT SERVICES (RFQ-DS-1397)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Texas Department of Public Safety</t>
+          <t>Metropolitan Water District of Southern California</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -58430,50 +58873,42 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="L76" s="65" t="n">
-        <v>148500</v>
+          <t>2025-04-10</t>
+        </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Satvik Chaudhary</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/186570653428</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/132776626904</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -58483,27 +58918,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>127482765035</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>RFP NO. NC- 2025-14</t>
+          <t>127678196440</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Computer Maintenance &amp; Technology Support Services - FCSS Fresno County Superintendent of Schools</t>
+          <t>MINNESOTA JUDICIAL BRANCH - IT Technical/infrastructure Services, Information Technology Application Development And Support Services &amp; Data Science And Machine Learning Services</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>FRESNO COUNTY SUPERINTENDENT OF SCHOOLS</t>
+          <t>Minnesota Judicial Branch</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -58518,12 +58948,12 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Consulting;Support &amp; Maintenance</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -58533,17 +58963,12 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -58553,7 +58978,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127482765035</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127678196440</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-05-04 03:38 EDT</t>
+          <t>2026-05-04 09:09 EDT</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>609</v>
+        <v>614</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA697"/>
+  <dimension ref="A1:AA702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -42632,12 +42632,17 @@
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J558" t="inlineStr">
@@ -42663,6 +42668,16 @@
       <c r="O558" t="inlineStr">
         <is>
           <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q558" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Y558" t="inlineStr">
@@ -45529,17 +45544,17 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>316973421242</t>
+          <t>323517591239</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t xml:space="preserve">As-Needed Cybersecurity Services </t>
+          <t>CAPK SOW 1</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>Inland Empire Utilities Agency</t>
+          <t>Community Action Partnership of Kern</t>
         </is>
       </c>
       <c r="F599" t="inlineStr">
@@ -45549,7 +45564,7 @@
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
@@ -45559,37 +45574,37 @@
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="K599" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M599" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N599" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Consulting;Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O599" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="U599" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Y599" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Z599" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316973421242</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323517591239</t>
         </is>
       </c>
     </row>
@@ -45599,22 +45614,22 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>316925843186</t>
+          <t>316973421242</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>IT SERVICES</t>
+          <t xml:space="preserve">As-Needed Cybersecurity Services </t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>BUTLER COUNTY REGIONAL TRANSIT AUTHORITY</t>
+          <t>Inland Empire Utilities Agency</t>
         </is>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
@@ -45642,19 +45657,24 @@
           <t>Managed Services (MSP)</t>
         </is>
       </c>
+      <c r="N600" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O600" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y600" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="Z600" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316925843186</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316973421242</t>
         </is>
       </c>
     </row>
@@ -45664,22 +45684,22 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>317195360975</t>
+          <t>316925843186</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t xml:space="preserve">Information Technology Support Services </t>
+          <t>IT SERVICES</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>Early Learning Coalition of Northwest Florida, Inc.</t>
+          <t>BUTLER COUNTY REGIONAL TRANSIT AUTHORITY</t>
         </is>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
@@ -45694,7 +45714,7 @@
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="K601" t="inlineStr">
@@ -45704,7 +45724,7 @@
       </c>
       <c r="M601" t="inlineStr">
         <is>
-          <t>Managed Services (MSP);Support &amp; Maintenance</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O601" t="inlineStr">
@@ -45714,12 +45734,12 @@
       </c>
       <c r="Y601" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Z601" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317195360975</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316925843186</t>
         </is>
       </c>
     </row>
@@ -45729,22 +45749,22 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>316930256598</t>
+          <t>317195360975</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>Information Technology Support and Managed IT Services</t>
+          <t xml:space="preserve">Information Technology Support Services </t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>Macon County</t>
+          <t>Early Learning Coalition of Northwest Florida, Inc.</t>
         </is>
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
@@ -45759,7 +45779,7 @@
       </c>
       <c r="J602" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="K602" t="inlineStr">
@@ -45767,32 +45787,24 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="L602" s="65" t="n">
-        <v>16200</v>
-      </c>
       <c r="M602" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N602" t="inlineStr">
-        <is>
-          <t>Offline</t>
+          <t>Managed Services (MSP);Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O602" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y602" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="Z602" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316930256598</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317195360975</t>
         </is>
       </c>
     </row>
@@ -45802,22 +45814,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>316199248583</t>
+          <t>316930256598</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>RFP for IT Services Provider</t>
+          <t>Information Technology Support and Managed IT Services</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>Port of Newport</t>
+          <t>Macon County</t>
         </is>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
@@ -45832,16 +45844,16 @@
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="K603" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="L603" s="65" t="n">
-        <v>53900</v>
+        <v>16200</v>
       </c>
       <c r="M603" t="inlineStr">
         <is>
@@ -45850,22 +45862,22 @@
       </c>
       <c r="N603" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O603" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y603" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="Z603" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316199248583</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316930256598</t>
         </is>
       </c>
     </row>
@@ -45875,27 +45887,22 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>302579423962</t>
-        </is>
-      </c>
-      <c r="C604" t="inlineStr">
-        <is>
-          <t>26-165591</t>
+          <t>316199248583</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>Logging and NERC Compliance Automation Solution</t>
+          <t>RFP for IT Services Provider</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>City of Farmington</t>
+          <t>Port of Newport</t>
         </is>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
@@ -45919,16 +45926,16 @@
         </is>
       </c>
       <c r="L604" s="65" t="n">
-        <v>389700</v>
+        <v>53900</v>
       </c>
       <c r="M604" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N604" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O604" t="inlineStr">
@@ -45938,12 +45945,12 @@
       </c>
       <c r="Y604" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="Z604" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/302579423962</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316199248583</t>
         </is>
       </c>
     </row>
@@ -45953,22 +45960,27 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>316932382432</t>
+          <t>302579423962</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>26-165591</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t xml:space="preserve">Information Technology Services </t>
+          <t>Logging and NERC Compliance Automation Solution</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>North Bergen Housing Authority</t>
+          <t>City of Farmington</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
@@ -45983,7 +45995,7 @@
       </c>
       <c r="J605" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="K605" t="inlineStr">
@@ -45992,31 +46004,31 @@
         </is>
       </c>
       <c r="L605" s="65" t="n">
-        <v>76800</v>
+        <v>389700</v>
       </c>
       <c r="M605" t="inlineStr">
         <is>
-          <t>Consulting;Managed Services (MSP)</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="N605" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O605" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y605" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="Z605" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316932382432</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/302579423962</t>
         </is>
       </c>
     </row>
@@ -46026,22 +46038,22 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>317791592158</t>
+          <t>316932382432</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>Vermont Education Data Visualizations Dashboard</t>
+          <t xml:space="preserve">Information Technology Services </t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>Vermont Agency of Education</t>
+          <t>North Bergen Housing Authority</t>
         </is>
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>Vermont</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
@@ -46056,32 +46068,40 @@
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="K606" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="L606" s="65" t="n">
+        <v>76800</v>
       </c>
       <c r="M606" t="inlineStr">
         <is>
-          <t>Modernization / Migration;Platform Implementation (ERP, CRMs);Support &amp; Maintenance;Consulting</t>
+          <t>Consulting;Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N606" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O606" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y606" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="Z606" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317791592158</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316932382432</t>
         </is>
       </c>
     </row>
@@ -46091,27 +46111,22 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>304628097754</t>
-        </is>
-      </c>
-      <c r="C607" t="inlineStr">
-        <is>
-          <t>WS5568983661</t>
+          <t>317791592158</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>151_Managed Detection and Response RFP</t>
+          <t>Vermont Education Data Visualizations Dashboard</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>Amtrak</t>
+          <t>Vermont Agency of Education</t>
         </is>
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Vermont</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
@@ -46136,7 +46151,7 @@
       </c>
       <c r="M607" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Modernization / Migration;Platform Implementation (ERP, CRMs);Support &amp; Maintenance;Consulting</t>
         </is>
       </c>
       <c r="O607" t="inlineStr">
@@ -46146,12 +46161,12 @@
       </c>
       <c r="Y607" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z607" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/304628097754</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317791592158</t>
         </is>
       </c>
     </row>
@@ -46161,22 +46176,27 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>316837417711</t>
+          <t>304628097754</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>WS5568983661</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>FY 25 Sun Cloud Statewide Implementation and Innovations AID Grant RFP</t>
+          <t>151_Managed Detection and Response RFP</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>Maricopa Association of Governments</t>
+          <t>Amtrak</t>
         </is>
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
@@ -46199,12 +46219,9 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="L608" s="65" t="n">
-        <v>649998</v>
-      </c>
       <c r="M608" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O608" t="inlineStr">
@@ -46214,12 +46231,12 @@
       </c>
       <c r="Y608" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="Z608" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316837417711</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/304628097754</t>
         </is>
       </c>
     </row>
@@ -46229,22 +46246,22 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>316972747502</t>
+          <t>316837417711</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADVISORY SERVICES FOR ENTERPRISE RESOURCE PLANNING (ERP) SYSTEM SELECTION AND IMPLEMENTATION </t>
+          <t>FY 25 Sun Cloud Statewide Implementation and Innovations AID Grant RFP</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>City of Pacific Grove</t>
+          <t>Maricopa Association of Governments</t>
         </is>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
@@ -46259,7 +46276,7 @@
       </c>
       <c r="J609" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="K609" t="inlineStr">
@@ -46268,31 +46285,26 @@
         </is>
       </c>
       <c r="L609" s="65" t="n">
-        <v>134400</v>
+        <v>649998</v>
       </c>
       <c r="M609" t="inlineStr">
         <is>
           <t>Consulting</t>
         </is>
       </c>
-      <c r="N609" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
       <c r="O609" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y609" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Z609" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316972747502</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316837417711</t>
         </is>
       </c>
     </row>
@@ -46302,22 +46314,22 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>318907181813</t>
+          <t>316972747502</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>OFFLINE - Comprehensive Cyber Security Managed Services &amp; Equipment</t>
+          <t xml:space="preserve">ADVISORY SERVICES FOR ENTERPRISE RESOURCE PLANNING (ERP) SYSTEM SELECTION AND IMPLEMENTATION </t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>City of Dexter</t>
+          <t>City of Pacific Grove</t>
         </is>
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
@@ -46341,11 +46353,11 @@
         </is>
       </c>
       <c r="L610" s="65" t="n">
-        <v>162200</v>
+        <v>134400</v>
       </c>
       <c r="M610" t="inlineStr">
         <is>
-          <t>Managed Services (MSP);Reseller</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N610" t="inlineStr">
@@ -46355,17 +46367,17 @@
       </c>
       <c r="O610" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y610" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="Z610" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318907181813</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316972747502</t>
         </is>
       </c>
     </row>
@@ -46375,22 +46387,22 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>305111030499</t>
+          <t>318907181813</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>ITS Salesforce Center of Excellence (COE) Stand-up</t>
+          <t>OFFLINE - Comprehensive Cyber Security Managed Services &amp; Equipment</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>NYS Office of Information Technology Services</t>
+          <t>City of Dexter</t>
         </is>
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
@@ -46405,32 +46417,40 @@
       </c>
       <c r="J611" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="K611" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
-        </is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="L611" s="65" t="n">
+        <v>162200</v>
       </c>
       <c r="M611" t="inlineStr">
         <is>
-          <t>Consulting;Platform Implementation (ERP, CRMs)</t>
+          <t>Managed Services (MSP);Reseller</t>
+        </is>
+      </c>
+      <c r="N611" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O611" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y611" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z611" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305111030499</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318907181813</t>
         </is>
       </c>
     </row>
@@ -46440,22 +46460,22 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>311299158740</t>
+          <t>305111030499</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and Maintenance of Information Technology Systems for Virginia Outdoors Foundation (VOF)  </t>
+          <t>ITS Salesforce Center of Excellence (COE) Stand-up</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>Virginia Outdoors Foundation (VOF)</t>
+          <t>NYS Office of Information Technology Services</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
@@ -46480,22 +46500,22 @@
       </c>
       <c r="M612" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting;Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O612" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y612" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="Z612" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311299158740</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305111030499</t>
         </is>
       </c>
     </row>
@@ -46505,22 +46525,22 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>319105688274</t>
+          <t>311299158740</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>On-Premises AI Analytics Implementation Project</t>
+          <t xml:space="preserve">Support and Maintenance of Information Technology Systems for Virginia Outdoors Foundation (VOF)  </t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>Ferris State University</t>
+          <t>Virginia Outdoors Foundation (VOF)</t>
         </is>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
@@ -46535,17 +46555,17 @@
       </c>
       <c r="J613" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="K613" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="M613" t="inlineStr">
         <is>
-          <t>Custom development</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O613" t="inlineStr">
@@ -46555,12 +46575,12 @@
       </c>
       <c r="Y613" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Z613" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319105688274</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311299158740</t>
         </is>
       </c>
     </row>
@@ -46570,27 +46590,22 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>316631239404</t>
-        </is>
-      </c>
-      <c r="C614" t="inlineStr">
-        <is>
-          <t>21260206151206</t>
+          <t>319105688274</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>Technical Support and Process Development for Collector Systems Units</t>
+          <t>On-Premises AI Analytics Implementation Project</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>Philadelphia Water Department</t>
+          <t>Ferris State University</t>
         </is>
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
@@ -46613,32 +46628,24 @@
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="L614" s="65" t="n">
-        <v>441600</v>
-      </c>
       <c r="M614" t="inlineStr">
         <is>
-          <t>Consulting;Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N614" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Custom development</t>
         </is>
       </c>
       <c r="O614" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y614" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z614" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316631239404</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319105688274</t>
         </is>
       </c>
     </row>
@@ -46648,22 +46655,27 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>316929505981</t>
+          <t>316631239404</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>21260206151206</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>Salesforce Professional Services</t>
+          <t>Technical Support and Process Development for Collector Systems Units</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>City and County of San Francisco</t>
+          <t>Philadelphia Water Department</t>
         </is>
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
@@ -46678,32 +46690,40 @@
       </c>
       <c r="J615" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="K615" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="L615" s="65" t="n">
+        <v>441600</v>
       </c>
       <c r="M615" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting;Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O615" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y615" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="Z615" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316929505981</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316631239404</t>
         </is>
       </c>
     </row>
@@ -46713,22 +46733,22 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>318902876904</t>
+          <t>316929505981</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>Managed Infrastructure Support Services</t>
+          <t>Salesforce Professional Services</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>City of Upper Arlington</t>
+          <t>City and County of San Francisco</t>
         </is>
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
@@ -46753,12 +46773,7 @@
       </c>
       <c r="M616" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N616" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O616" t="inlineStr">
@@ -46768,12 +46783,12 @@
       </c>
       <c r="Y616" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="Z616" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318902876904</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316929505981</t>
         </is>
       </c>
     </row>
@@ -46783,22 +46798,22 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>316633497326</t>
+          <t>318902876904</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>Information Technology Support Services</t>
+          <t>Managed Infrastructure Support Services</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>CITY OF PIEDMONT</t>
+          <t>City of Upper Arlington</t>
         </is>
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
@@ -46821,27 +46836,29 @@
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="L617" s="65" t="n">
-        <v>350500</v>
-      </c>
       <c r="M617" t="inlineStr">
         <is>
-          <t>Managed Services (MSP);Support &amp; Maintenance</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N617" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O617" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y617" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="Z617" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316633497326</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318902876904</t>
         </is>
       </c>
     </row>
@@ -46851,22 +46868,22 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>318902162116</t>
+          <t>316633497326</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>Information Technology (IT) Managed Services</t>
+          <t>Information Technology Support Services</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>Town of Prospect</t>
+          <t>CITY OF PIEDMONT</t>
         </is>
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
@@ -46890,31 +46907,26 @@
         </is>
       </c>
       <c r="L618" s="65" t="n">
-        <v>104400</v>
+        <v>350500</v>
       </c>
       <c r="M618" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N618" t="inlineStr">
-        <is>
-          <t>Offline;Email</t>
+          <t>Managed Services (MSP);Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O618" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y618" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Z618" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318902162116</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316633497326</t>
         </is>
       </c>
     </row>
@@ -46924,22 +46936,22 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>316199247586</t>
+          <t>318902162116</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>ITS Discretionary Procurement Salesforce</t>
+          <t>Information Technology (IT) Managed Services</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>NYS Office of Information Technology Services</t>
+          <t>Town of Prospect</t>
         </is>
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Connecticut</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
@@ -46954,32 +46966,40 @@
       </c>
       <c r="J619" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="K619" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="L619" s="65" t="n">
+        <v>104400</v>
       </c>
       <c r="M619" t="inlineStr">
         <is>
-          <t>Staff Augmentation;Consulting</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N619" t="inlineStr">
+        <is>
+          <t>Offline;Email</t>
         </is>
       </c>
       <c r="O619" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y619" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="Z619" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316199247586</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318902162116</t>
         </is>
       </c>
     </row>
@@ -46989,22 +47009,22 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>317943306990</t>
+          <t>316199247586</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>Website Hosting and Support Services</t>
+          <t>ITS Discretionary Procurement Salesforce</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>Shasta Regional Transportation Agency</t>
+          <t>NYS Office of Information Technology Services</t>
         </is>
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
@@ -47029,7 +47049,7 @@
       </c>
       <c r="M620" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Staff Augmentation;Consulting</t>
         </is>
       </c>
       <c r="O620" t="inlineStr">
@@ -47039,12 +47059,12 @@
       </c>
       <c r="Y620" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="Z620" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317943306990</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316199247586</t>
         </is>
       </c>
     </row>
@@ -47054,22 +47074,22 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>320490435282</t>
+          <t>317943306990</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>Microsoft Office 365</t>
+          <t>Website Hosting and Support Services</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>City of Morristown</t>
+          <t>Shasta Regional Transportation Agency</t>
         </is>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
@@ -47084,7 +47104,7 @@
       </c>
       <c r="J621" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="K621" t="inlineStr">
@@ -47092,32 +47112,24 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="L621" s="65" t="n">
-        <v>75000</v>
-      </c>
       <c r="M621" t="inlineStr">
         <is>
-          <t>Reseller</t>
-        </is>
-      </c>
-      <c r="N621" t="inlineStr">
-        <is>
-          <t>Offline</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O621" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y621" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z621" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320490435282</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317943306990</t>
         </is>
       </c>
     </row>
@@ -47127,22 +47139,22 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>316928723643</t>
+          <t>320490435282</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>OFF - Information Technology Managed Services</t>
+          <t>Microsoft Office 365</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>City of Leominster</t>
+          <t>City of Morristown</t>
         </is>
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>Masssachusetts</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
@@ -47165,24 +47177,32 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="L622" s="65" t="n">
+        <v>75000</v>
+      </c>
       <c r="M622" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Reseller</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O622" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y622" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="Z622" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316928723643</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320490435282</t>
         </is>
       </c>
     </row>
@@ -47192,22 +47212,22 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>317997728482</t>
+          <t>316928723643</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>Veeam Software Subscription Renewal</t>
+          <t>OFF - Information Technology Managed Services</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>County of Riverside Purchasing &amp; Fleet Services Department</t>
+          <t>City of Leominster</t>
         </is>
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Masssachusetts</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
@@ -47227,35 +47247,27 @@
       </c>
       <c r="K623" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="L623" s="65" t="n">
-        <v>992387.88</v>
+          <t>2026-04-14</t>
+        </is>
       </c>
       <c r="M623" t="inlineStr">
         <is>
-          <t>Reseller</t>
-        </is>
-      </c>
-      <c r="N623" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O623" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y623" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Z623" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317997728482</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316928723643</t>
         </is>
       </c>
     </row>
@@ -47265,22 +47277,22 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>318930498283</t>
+          <t>317997728482</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>OFF - Data Strategy Project</t>
+          <t>Veeam Software Subscription Renewal</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>Region 16 Education Service Center</t>
+          <t>County of Riverside Purchasing &amp; Fleet Services Department</t>
         </is>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
@@ -47295,7 +47307,7 @@
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="K624" t="inlineStr">
@@ -47304,31 +47316,31 @@
         </is>
       </c>
       <c r="L624" s="65" t="n">
-        <v>45760</v>
+        <v>992387.88</v>
       </c>
       <c r="M624" t="inlineStr">
         <is>
-          <t>Managed Services (MSP);Consulting;Audits and Assessment;Modernization / Migration</t>
+          <t>Reseller</t>
         </is>
       </c>
       <c r="N624" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O624" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y624" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="Z624" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318930498283</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317997728482</t>
         </is>
       </c>
     </row>
@@ -47338,22 +47350,22 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>318905093818</t>
+          <t>318930498283</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t xml:space="preserve">Information Technology Security Audit </t>
+          <t>OFF - Data Strategy Project</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>Northwestern Michigan College</t>
+          <t>Region 16 Education Service Center</t>
         </is>
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
@@ -47373,25 +47385,25 @@
       </c>
       <c r="K625" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="L625" s="65" t="n">
-        <v>32070</v>
+        <v>45760</v>
       </c>
       <c r="M625" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Managed Services (MSP);Consulting;Audits and Assessment;Modernization / Migration</t>
         </is>
       </c>
       <c r="N625" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O625" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y625" t="inlineStr">
@@ -47401,7 +47413,7 @@
       </c>
       <c r="Z625" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318905093818</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318930498283</t>
         </is>
       </c>
     </row>
@@ -47411,22 +47423,22 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>318929810149</t>
+          <t>318905093818</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>Outsourced IT Services</t>
+          <t xml:space="preserve">Information Technology Security Audit </t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>First 5 Kids Santa Clara County</t>
+          <t>Northwestern Michigan College</t>
         </is>
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
@@ -47450,16 +47462,21 @@
         </is>
       </c>
       <c r="L626" s="65" t="n">
-        <v>133800</v>
+        <v>32070</v>
       </c>
       <c r="M626" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Audits and Assessment</t>
+        </is>
+      </c>
+      <c r="N626" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O626" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y626" t="inlineStr">
@@ -47469,7 +47486,7 @@
       </c>
       <c r="Z626" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318929810149</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318905093818</t>
         </is>
       </c>
     </row>
@@ -47479,22 +47496,22 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>319926000360</t>
+          <t>318929810149</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>Organizational File System Assessment &amp; Restructuring Services</t>
+          <t>Outsourced IT Services</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>Dutchess County Workforce Investment Board (DCWIB)</t>
+          <t>First 5 Kids Santa Clara County</t>
         </is>
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
@@ -47509,25 +47526,20 @@
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="K627" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="L627" s="65" t="n">
-        <v>3990</v>
+        <v>133800</v>
       </c>
       <c r="M627" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
-        </is>
-      </c>
-      <c r="N627" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O627" t="inlineStr">
@@ -47537,12 +47549,12 @@
       </c>
       <c r="Y627" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z627" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319926000360</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318929810149</t>
         </is>
       </c>
     </row>
@@ -47552,22 +47564,22 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>317994793688</t>
+          <t>319926000360</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>Education Cloud Implementation</t>
+          <t>Organizational File System Assessment &amp; Restructuring Services</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Dutchess County Workforce Investment Board (DCWIB)</t>
         </is>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
@@ -47591,16 +47603,16 @@
         </is>
       </c>
       <c r="L628" s="65" t="n">
-        <v>237000</v>
+        <v>3990</v>
       </c>
       <c r="M628" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="N628" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O628" t="inlineStr">
@@ -47610,12 +47622,12 @@
       </c>
       <c r="Y628" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z628" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317994793688</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319926000360</t>
         </is>
       </c>
     </row>
@@ -47625,27 +47637,22 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>316125286091</t>
-        </is>
-      </c>
-      <c r="C629" t="inlineStr">
-        <is>
-          <t>2026-09</t>
+          <t>317994793688</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>Website and Mobile App Replacement Services</t>
+          <t>Education Cloud Implementation</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>City of Menifee</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
@@ -47669,11 +47676,11 @@
         </is>
       </c>
       <c r="L629" s="65" t="n">
-        <v>618820</v>
+        <v>237000</v>
       </c>
       <c r="M629" t="inlineStr">
         <is>
-          <t>Custom development</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="N629" t="inlineStr">
@@ -47688,12 +47695,12 @@
       </c>
       <c r="Y629" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z629" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316125286091</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317994793688</t>
         </is>
       </c>
     </row>
@@ -47703,17 +47710,22 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>320536008422</t>
+          <t>316125286091</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>RFP NO. 150684 - Outsourced Tier 1 Help Desk Services - Information Technology Department</t>
+          <t>Website and Mobile App Replacement Services</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>Superior Court of California - San Francisco County</t>
+          <t>City of Menifee</t>
         </is>
       </c>
       <c r="F630" t="inlineStr">
@@ -47741,24 +47753,32 @@
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="L630" s="65" t="n">
+        <v>618820</v>
+      </c>
       <c r="M630" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Custom development</t>
+        </is>
+      </c>
+      <c r="N630" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O630" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y630" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Z630" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320536008422</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316125286091</t>
         </is>
       </c>
     </row>
@@ -47768,22 +47788,22 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>316198616795</t>
+          <t>320536008422</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>[Offline] Low-Code Application Development Services</t>
+          <t>RFP NO. 150684 - Outsourced Tier 1 Help Desk Services - Information Technology Department</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>Florida Department of Citrus (CIT) [FL]</t>
+          <t>Superior Court of California - San Francisco County</t>
         </is>
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
@@ -47798,37 +47818,32 @@
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="K631" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="M631" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance;Custom development</t>
-        </is>
-      </c>
-      <c r="N631" t="inlineStr">
-        <is>
-          <t>Offline</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O631" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y631" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z631" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316198616795</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320536008422</t>
         </is>
       </c>
     </row>
@@ -47838,22 +47853,22 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>317997672181</t>
+          <t>316198616795</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>SAP S/4 HANA SUPPORT SERVICES</t>
+          <t>[Offline] Low-Code Application Development Services</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>Charlottesville</t>
+          <t>Florida Department of Citrus (CIT) [FL]</t>
         </is>
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
@@ -47878,27 +47893,27 @@
       </c>
       <c r="M632" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Support &amp; Maintenance;Custom development</t>
         </is>
       </c>
       <c r="N632" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O632" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y632" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="Z632" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317997672181</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316198616795</t>
         </is>
       </c>
     </row>
@@ -47908,22 +47923,22 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>317793033939</t>
+          <t>317997672181</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t xml:space="preserve">OFF - Computer Services </t>
+          <t>SAP S/4 HANA SUPPORT SERVICES</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>Town of Islip Affordable Housing Corp (TOIAHC)</t>
+          <t>Charlottesville</t>
         </is>
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
@@ -47938,27 +47953,27 @@
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="K633" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M633" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N633" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O633" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y633" t="inlineStr">
@@ -47968,7 +47983,7 @@
       </c>
       <c r="Z633" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317793033939</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317997672181</t>
         </is>
       </c>
     </row>
@@ -47978,22 +47993,22 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>316123953854</t>
+          <t>317793033939</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>Executive Search and General Staffing Services</t>
+          <t xml:space="preserve">OFF - Computer Services </t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>Santa Clara Valley Transportation Authority</t>
+          <t>Town of Islip Affordable Housing Corp (TOIAHC)</t>
         </is>
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
@@ -48008,22 +48023,22 @@
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="K634" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M634" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N634" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O634" t="inlineStr">
@@ -48033,12 +48048,12 @@
       </c>
       <c r="Y634" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z634" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316123953854</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317793033939</t>
         </is>
       </c>
     </row>
@@ -48048,27 +48063,27 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>316972808892</t>
+          <t>323528390341</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>Bridges Library System Mobile App</t>
+          <t>IT MSP &amp; NOC NMFA Additional SOW</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>Waukesha County</t>
+          <t xml:space="preserve">New Mexico Finance Authority (“NMFA”) </t>
         </is>
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -48078,40 +48093,37 @@
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="K635" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="L635" s="65" t="n">
-        <v>360200</v>
+          <t>2026-04-22</t>
+        </is>
       </c>
       <c r="M635" t="inlineStr">
         <is>
-          <t>Custom development</t>
-        </is>
-      </c>
-      <c r="N635" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O635" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="S635" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="Y635" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Z635" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316972808892</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323528390341</t>
         </is>
       </c>
     </row>
@@ -48121,27 +48133,22 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>317946904258</t>
-        </is>
-      </c>
-      <c r="C636" t="inlineStr">
-        <is>
-          <t>25-0245-IT</t>
+          <t>316123953854</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>Information Security Governance &amp; Policy Framework Development</t>
+          <t>Executive Search and General Staffing Services</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>City of Florissant</t>
+          <t>Santa Clara Valley Transportation Authority</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
@@ -48164,8 +48171,10 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="L636" s="65" t="n">
-        <v>52560</v>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>Staff Augmentation</t>
+        </is>
       </c>
       <c r="N636" t="inlineStr">
         <is>
@@ -48174,22 +48183,17 @@
       </c>
       <c r="O636" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y636" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="Z636" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317946904258</t>
-        </is>
-      </c>
-      <c r="AA636" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316123953854</t>
         </is>
       </c>
     </row>
@@ -48199,22 +48203,22 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>320043417335</t>
+          <t>316972808892</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>MICROSOFT OFFICE COMPUTER TRAININGS</t>
+          <t>Bridges Library System Mobile App</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>COUNTY OF LOS ANGELES DEPARTMENT OF HUMAN RESOURCES</t>
+          <t>Waukesha County</t>
         </is>
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
@@ -48237,9 +48241,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="L637" s="65" t="n">
+        <v>360200</v>
+      </c>
       <c r="M637" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Custom development</t>
         </is>
       </c>
       <c r="N637" t="inlineStr">
@@ -48254,12 +48261,12 @@
       </c>
       <c r="Y637" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="Z637" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320043417335</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316972808892</t>
         </is>
       </c>
     </row>
@@ -48269,22 +48276,27 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>316626212560</t>
+          <t>317946904258</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>25-0245-IT</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SERVICES</t>
+          <t>Information Security Governance &amp; Policy Framework Development</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>Town of Irmo</t>
+          <t>City of Florissant</t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
@@ -48299,7 +48311,7 @@
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="K638" t="inlineStr">
@@ -48307,14 +48319,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="M638" t="inlineStr">
-        <is>
-          <t>Managed Services (MSP)</t>
-        </is>
+      <c r="L638" s="65" t="n">
+        <v>52560</v>
       </c>
       <c r="N638" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O638" t="inlineStr">
@@ -48324,12 +48334,17 @@
       </c>
       <c r="Y638" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z638" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316626212560</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317946904258</t>
+        </is>
+      </c>
+      <c r="AA638" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -48339,27 +48354,22 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>320489741047</t>
-        </is>
-      </c>
-      <c r="C639" t="inlineStr">
-        <is>
-          <t>RFQ #: 26-026-TK</t>
+          <t>320043417335</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>Community Health Assessment &amp; Improvements Plan for Data Dashboard</t>
+          <t>MICROSOFT OFFICE COMPUTER TRAININGS</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>Kane County Health Department</t>
+          <t>COUNTY OF LOS ANGELES DEPARTMENT OF HUMAN RESOURCES</t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
@@ -48374,20 +48384,17 @@
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="K639" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="L639" s="65" t="n">
-        <v>121930</v>
+          <t>2026-04-23</t>
+        </is>
       </c>
       <c r="M639" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="N639" t="inlineStr">
@@ -48402,12 +48409,12 @@
       </c>
       <c r="Y639" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z639" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320489741047</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320043417335</t>
         </is>
       </c>
     </row>
@@ -48417,22 +48424,22 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>321691657937</t>
+          <t>316626212560</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>Technology Support Services</t>
+          <t>INFORMATION TECHNOLOGY SERVICES</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkway Schools </t>
+          <t>Town of Irmo</t>
         </is>
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
@@ -48452,27 +48459,35 @@
       </c>
       <c r="K640" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="L640" s="65" t="n">
+        <v>405880</v>
       </c>
       <c r="M640" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N640" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O640" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y640" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="Z640" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321691657937</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316626212560</t>
         </is>
       </c>
     </row>
@@ -48482,22 +48497,27 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>319181385439</t>
+          <t>320489741047</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>RFQ #: 26-026-TK</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>IT Managed Services</t>
+          <t>Community Health Assessment &amp; Improvements Plan for Data Dashboard</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>Emerald Coast Regional Council</t>
+          <t>Kane County Health Department</t>
         </is>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="G641" t="inlineStr">
@@ -48520,24 +48540,32 @@
           <t>2026-04-24</t>
         </is>
       </c>
+      <c r="L641" s="65" t="n">
+        <v>121930</v>
+      </c>
       <c r="M641" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N641" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O641" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y641" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="Z641" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319181385439</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320489741047</t>
         </is>
       </c>
     </row>
@@ -48547,22 +48575,22 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>317828186810</t>
+          <t>321691657937</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>Cybersecurity Risk Assessment for Information Security</t>
+          <t>Technology Support Services</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>The Administrative Office of the Courts (AOC)</t>
+          <t xml:space="preserve">Parkway Schools </t>
         </is>
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
@@ -48585,32 +48613,24 @@
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="L642" s="65" t="n">
-        <v>85000</v>
-      </c>
       <c r="M642" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
-        </is>
-      </c>
-      <c r="N642" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O642" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y642" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z642" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317828186810</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321691657937</t>
         </is>
       </c>
     </row>
@@ -48620,22 +48640,22 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>317166061283</t>
+          <t>319181385439</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t xml:space="preserve">Request for Proposals Cybersecurity Assessment and Plan </t>
+          <t>IT Managed Services</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>Pueblo of Laguna</t>
+          <t>Emerald Coast Regional Council</t>
         </is>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
@@ -48660,7 +48680,7 @@
       </c>
       <c r="M643" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O643" t="inlineStr">
@@ -48670,12 +48690,12 @@
       </c>
       <c r="Y643" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="Z643" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317166061283</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319181385439</t>
         </is>
       </c>
     </row>
@@ -48685,22 +48705,22 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>317793033962</t>
+          <t>317828186810</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>PeopleSoft Update Manager</t>
+          <t>Cybersecurity Risk Assessment for Information Security</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>City and County of San Francisco</t>
+          <t>The Administrative Office of the Courts (AOC)</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
@@ -48723,9 +48743,12 @@
           <t>2026-04-24</t>
         </is>
       </c>
+      <c r="L644" s="65" t="n">
+        <v>85000</v>
+      </c>
       <c r="M644" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="N644" t="inlineStr">
@@ -48745,7 +48768,7 @@
       </c>
       <c r="Z644" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317793033962</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317828186810</t>
         </is>
       </c>
     </row>
@@ -48755,22 +48778,22 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>294210815704</t>
+          <t>317166061283</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>offline Information Technology Services</t>
+          <t xml:space="preserve">Request for Proposals Cybersecurity Assessment and Plan </t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Danville Redevelopment and Housing Authority</t>
+          <t>Pueblo of Laguna</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
@@ -48785,7 +48808,7 @@
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="K645" t="inlineStr">
@@ -48795,22 +48818,22 @@
       </c>
       <c r="M645" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O645" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y645" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="Z645" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294210815704</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317166061283</t>
         </is>
       </c>
     </row>
@@ -48820,22 +48843,22 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>323231785701</t>
+          <t>317793033962</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t xml:space="preserve">FMLA Case Management System </t>
+          <t>PeopleSoft Update Manager</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>Tennessee Department of Human Resources</t>
+          <t>City and County of San Francisco</t>
         </is>
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
@@ -48850,7 +48873,7 @@
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="K646" t="inlineStr">
@@ -48860,22 +48883,27 @@
       </c>
       <c r="M646" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs);Consulting;Training</t>
+          <t>Modernization / Migration</t>
+        </is>
+      </c>
+      <c r="N646" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O646" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y646" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z646" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323231785701</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317793033962</t>
         </is>
       </c>
     </row>
@@ -48885,22 +48913,22 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>319924556489</t>
+          <t>294210815704</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>Network Security Audit and Vulnerability Assessment</t>
+          <t>offline Information Technology Services</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Regional Commission </t>
+          <t>Danville Redevelopment and Housing Authority</t>
         </is>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
@@ -48920,27 +48948,27 @@
       </c>
       <c r="K647" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="M647" t="inlineStr">
         <is>
-          <t>Consulting;Audits and Assessment</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O647" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y647" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="Z647" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319924556489</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294210815704</t>
         </is>
       </c>
     </row>
@@ -48950,22 +48978,22 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>318902943445</t>
+          <t>323231785701</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>Technology Consultant for the Production Tracking System (PTS)</t>
+          <t xml:space="preserve">FMLA Case Management System </t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>Massachusetts Clean Energy Center (MassCEC)</t>
+          <t>Tennessee Department of Human Resources</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
@@ -48980,25 +49008,17 @@
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="K648" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="L648" s="65" t="n">
-        <v>732660</v>
+          <t>2026-04-24</t>
+        </is>
       </c>
       <c r="M648" t="inlineStr">
         <is>
-          <t>Consulting</t>
-        </is>
-      </c>
-      <c r="N648" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Platform Implementation (ERP, CRMs);Consulting;Training</t>
         </is>
       </c>
       <c r="O648" t="inlineStr">
@@ -49008,12 +49028,12 @@
       </c>
       <c r="Y648" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z648" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318902943445</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323231785701</t>
         </is>
       </c>
     </row>
@@ -49023,22 +49043,22 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>321924670199</t>
+          <t>319924556489</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>Management. Applications Development</t>
+          <t>Network Security Audit and Vulnerability Assessment</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Florida Department of Health</t>
+          <t xml:space="preserve">Atlanta Regional Commission </t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
@@ -49063,27 +49083,22 @@
       </c>
       <c r="M649" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting;Audits and Assessment</t>
         </is>
       </c>
       <c r="O649" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y649" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z649" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321924670199</t>
-        </is>
-      </c>
-      <c r="AA649" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319924556489</t>
         </is>
       </c>
     </row>
@@ -49093,22 +49108,22 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>314835484352</t>
+          <t>318902943445</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professional Managed Services </t>
+          <t>Technology Consultant for the Production Tracking System (PTS)</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t xml:space="preserve">City of Virginia Beach </t>
+          <t>Massachusetts Clean Energy Center (MassCEC)</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
@@ -49123,7 +49138,7 @@
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="K650" t="inlineStr">
@@ -49131,24 +49146,32 @@
           <t>2026-04-27</t>
         </is>
       </c>
+      <c r="L650" s="65" t="n">
+        <v>732660</v>
+      </c>
       <c r="M650" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N650" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O650" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y650" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z650" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/314835484352</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318902943445</t>
         </is>
       </c>
     </row>
@@ -49158,22 +49181,22 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>318654617301</t>
+          <t>321924670199</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>GRANT: Artificial Intelligence (AI) to Accelerate Charitable Giving</t>
+          <t>Management. Applications Development</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Florida Department of Health</t>
         </is>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
@@ -49188,7 +49211,7 @@
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="K651" t="inlineStr">
@@ -49198,22 +49221,27 @@
       </c>
       <c r="M651" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O651" t="inlineStr">
         <is>
-          <t>Srikrishnadeva D</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y651" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Z651" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318654617301</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321924670199</t>
+        </is>
+      </c>
+      <c r="AA651" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -49223,27 +49251,27 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>320213008064</t>
+          <t>314835484352</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>ONLINE WEB-BASED TRAINING</t>
+          <t xml:space="preserve">Professional Managed Services </t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>Alaska Department of Administration</t>
+          <t xml:space="preserve">City of Virginia Beach </t>
         </is>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
@@ -49253,7 +49281,7 @@
       </c>
       <c r="J652" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="K652" t="inlineStr">
@@ -49261,37 +49289,24 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="L652" s="65" t="n">
-        <v>37800</v>
-      </c>
       <c r="M652" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O652" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
-        </is>
-      </c>
-      <c r="S652" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y652" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="Z652" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320213008064</t>
-        </is>
-      </c>
-      <c r="AA652" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/314835484352</t>
         </is>
       </c>
     </row>
@@ -49301,22 +49316,22 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>318905090784</t>
+          <t>318654617301</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>Information Technology Consulting Services</t>
+          <t>GRANT: Artificial Intelligence (AI) to Accelerate Charitable Giving</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>City of Coronado</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
@@ -49336,22 +49351,27 @@
       </c>
       <c r="K653" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M653" t="inlineStr">
+        <is>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O653" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Srikrishnadeva D</t>
         </is>
       </c>
       <c r="Y653" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="Z653" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318905090784</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318654617301</t>
         </is>
       </c>
     </row>
@@ -49361,27 +49381,27 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>318930494184</t>
+          <t>320213008064</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>OFF - ERP Consultant</t>
+          <t>ONLINE WEB-BASED TRAINING</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>City of Westfield Gas and Electrics</t>
+          <t>Alaska Department of Administration</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>Massachussets</t>
+          <t>Alaska</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -49391,32 +49411,45 @@
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="K654" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="L654" s="65" t="n">
+        <v>37800</v>
       </c>
       <c r="M654" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O654" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="S654" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Y654" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="Z654" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318930494184</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320213008064</t>
+        </is>
+      </c>
+      <c r="AA654" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -49426,22 +49459,22 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>319925999318</t>
+          <t>318905090784</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>OFFLINE Information Technology Services, Including Cybersecurity</t>
+          <t>Information Technology Consulting Services</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>Haddon Heights Borough</t>
+          <t>City of Coronado</t>
         </is>
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
@@ -49456,32 +49489,27 @@
       </c>
       <c r="J655" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="K655" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="M655" t="inlineStr">
-        <is>
-          <t>Managed Services (MSP);Consulting</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="O655" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y655" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z655" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319925999318</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318905090784</t>
         </is>
       </c>
     </row>
@@ -49491,22 +49519,22 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>320536008419</t>
+          <t>318930494184</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY AND COMPUTER CONSULTING SERVICES FOR COMPUTERS, PROGRAMS AND PERIPHERAL COMPUTER EQUIPMENT THROUGHOUT THE DEPARTMENTS OF THE BOROUGH OF MIDDLESEX</t>
+          <t>OFF - ERP Consultant</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>Borough of Middlesex</t>
+          <t>City of Westfield Gas and Electrics</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>Massachussets</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
@@ -49521,35 +49549,32 @@
       </c>
       <c r="J656" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="K656" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="L656" s="65" t="n">
-        <v>135360</v>
+          <t>2026-04-28</t>
+        </is>
       </c>
       <c r="M656" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O656" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y656" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z656" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320536008419</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318930494184</t>
         </is>
       </c>
     </row>
@@ -49559,22 +49584,22 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>319104964317</t>
+          <t>319925999318</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration from On-Premises Microsoft CRM to Microsoft Dynamics 365 Cloud </t>
+          <t>OFFLINE Information Technology Services, Including Cybersecurity</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>Energy Trust of Oregon</t>
+          <t>Haddon Heights Borough</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
@@ -49597,37 +49622,24 @@
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="L657" s="65" t="n">
-        <v>1189350</v>
-      </c>
       <c r="M657" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
-        </is>
-      </c>
-      <c r="N657" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Managed Services (MSP);Consulting</t>
         </is>
       </c>
       <c r="O657" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y657" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z657" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319104964317</t>
-        </is>
-      </c>
-      <c r="AA657" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319925999318</t>
         </is>
       </c>
     </row>
@@ -49637,22 +49649,22 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>319925999345</t>
+          <t>320536008419</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>REQUEST FOR QUALIFICATIONS FOR INFORMATION TECHNOLOGY STRATEGIC CONSULTING SERVICES</t>
+          <t>INFORMATION TECHNOLOGY AND COMPUTER CONSULTING SERVICES FOR COMPUTERS, PROGRAMS AND PERIPHERAL COMPUTER EQUIPMENT THROUGHOUT THE DEPARTMENTS OF THE BOROUGH OF MIDDLESEX</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>Susquehanna River Basin Commission (SRBC)</t>
+          <t>Borough of Middlesex</t>
         </is>
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>Pennsylvania, New York, Maryland</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
@@ -49675,24 +49687,27 @@
           <t>2026-04-29</t>
         </is>
       </c>
+      <c r="L658" s="65" t="n">
+        <v>135360</v>
+      </c>
       <c r="M658" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O658" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y658" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z658" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319925999345</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320536008419</t>
         </is>
       </c>
     </row>
@@ -49702,22 +49717,22 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>320623193837</t>
+          <t>319104964317</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>offline RFP IT SUPPORT SERVICES FOR SCCDA</t>
+          <t xml:space="preserve">Migration from On-Premises Microsoft CRM to Microsoft Dynamics 365 Cloud </t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>City of Quincy</t>
+          <t>Energy Trust of Oregon</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
@@ -49732,7 +49747,7 @@
       </c>
       <c r="J659" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="K659" t="inlineStr">
@@ -49740,24 +49755,37 @@
           <t>2026-04-29</t>
         </is>
       </c>
+      <c r="L659" s="65" t="n">
+        <v>1189350</v>
+      </c>
       <c r="M659" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Modernization / Migration</t>
+        </is>
+      </c>
+      <c r="N659" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O659" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y659" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z659" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320623193837</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319104964317</t>
+        </is>
+      </c>
+      <c r="AA659" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -49767,22 +49795,22 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>322269405882</t>
+          <t>319925999345</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>2026 Veeam License Renewal</t>
+          <t>REQUEST FOR QUALIFICATIONS FOR INFORMATION TECHNOLOGY STRATEGIC CONSULTING SERVICES</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>Village of Schaumburg</t>
+          <t>Susquehanna River Basin Commission (SRBC)</t>
         </is>
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Pennsylvania, New York, Maryland</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
@@ -49797,7 +49825,7 @@
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="K660" t="inlineStr">
@@ -49805,27 +49833,24 @@
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="L660" s="65" t="n">
-        <v>54186.88</v>
-      </c>
-      <c r="N660" t="inlineStr">
-        <is>
-          <t>Portal</t>
+      <c r="M660" t="inlineStr">
+        <is>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O660" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y660" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z660" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322269405882</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319925999345</t>
         </is>
       </c>
     </row>
@@ -49835,27 +49860,22 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>319926717149</t>
-        </is>
-      </c>
-      <c r="C661" t="inlineStr">
-        <is>
-          <t>COW2026-02</t>
+          <t>320623193837</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>Information Technology and GIS Support Services</t>
+          <t>offline RFP IT SUPPORT SERVICES FOR SCCDA</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>City of Wildomar</t>
+          <t>City of Quincy</t>
         </is>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
@@ -49875,35 +49895,27 @@
       </c>
       <c r="K661" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L661" s="65" t="n">
-        <v>210000</v>
+          <t>2026-04-29</t>
+        </is>
       </c>
       <c r="M661" t="inlineStr">
         <is>
-          <t>Consulting;Staff Augmentation;Audits and Assessment</t>
-        </is>
-      </c>
-      <c r="N661" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O661" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y661" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z661" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319926717149</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320623193837</t>
         </is>
       </c>
     </row>
@@ -49913,27 +49925,22 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>320834566889</t>
-        </is>
-      </c>
-      <c r="C662" t="inlineStr">
-        <is>
-          <t>2026-002 REBID</t>
+          <t>322269405882</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>MICROSOFT DYNAMICS GP MIGRATION TO BUSINESS CENTRAL 365</t>
+          <t>2026 Veeam License Renewal</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>Detroit Wayne Integrated Health Network</t>
+          <t>Village of Schaumburg</t>
         </is>
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
@@ -49948,21 +49955,16 @@
       </c>
       <c r="J662" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="K662" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L662" s="65" t="n">
-        <v>135830</v>
-      </c>
-      <c r="M662" t="inlineStr">
-        <is>
-          <t>Modernization / Migration</t>
-        </is>
+        <v>54186.88</v>
       </c>
       <c r="N662" t="inlineStr">
         <is>
@@ -49971,17 +49973,17 @@
       </c>
       <c r="O662" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y662" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z662" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320834566889</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322269405882</t>
         </is>
       </c>
     </row>
@@ -49991,17 +49993,22 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>323231105770</t>
+          <t>319926717149</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>COW2026-02</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>Consulting and Professional Services Master Agreement (CAPSMA)</t>
+          <t>Information Technology and GIS Support Services</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>Los Angeles County - Board of Supervisors</t>
+          <t>City of Wildomar</t>
         </is>
       </c>
       <c r="F663" t="inlineStr">
@@ -50029,29 +50036,32 @@
           <t>2026-04-30</t>
         </is>
       </c>
+      <c r="L663" s="65" t="n">
+        <v>210000</v>
+      </c>
       <c r="M663" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Consulting;Staff Augmentation;Audits and Assessment</t>
         </is>
       </c>
       <c r="N663" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O663" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y663" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z663" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323231105770</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319926717149</t>
         </is>
       </c>
     </row>
@@ -50061,22 +50071,27 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>318930495177</t>
+          <t>320834566889</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>2026-002 REBID</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>Request for Services (RFS) for Consulting Services to Enhance Education Information Sharing Processes and Data Systems for Systems-Involved Youth</t>
+          <t>MICROSOFT DYNAMICS GP MIGRATION TO BUSINESS CENTRAL 365</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>Los Angeles County - Board of Supervisors</t>
+          <t>Detroit Wayne Integrated Health Network</t>
         </is>
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
@@ -50099,29 +50114,32 @@
           <t>2026-04-30</t>
         </is>
       </c>
+      <c r="L664" s="65" t="n">
+        <v>135830</v>
+      </c>
       <c r="M664" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="N664" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O664" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y664" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z664" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318930495177</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320834566889</t>
         </is>
       </c>
     </row>
@@ -50131,22 +50149,22 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>319925282512</t>
+          <t>323231105770</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>MANAGED SERVICE PROVIDER (MSP)</t>
+          <t>Consulting and Professional Services Master Agreement (CAPSMA)</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>Freire Schools</t>
+          <t>Los Angeles County - Board of Supervisors</t>
         </is>
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
@@ -50161,35 +50179,37 @@
       </c>
       <c r="J665" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="M665" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N665" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O665" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y665" t="inlineStr">
+        <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L665" s="65" t="n">
-        <v>199960</v>
-      </c>
-      <c r="M665" t="inlineStr">
-        <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="O665" t="inlineStr">
-        <is>
-          <t>Jyothsna Nanda kishore</t>
-        </is>
-      </c>
-      <c r="Y665" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
       <c r="Z665" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319925282512</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323231105770</t>
         </is>
       </c>
     </row>
@@ -50199,22 +50219,22 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>321688802026</t>
+          <t>318930495177</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>(Offline) RFP ACCOUNTING &amp; HUMAN RESOURCES ERP SYSTEM</t>
+          <t>Request for Services (RFS) for Consulting Services to Enhance Education Information Sharing Processes and Data Systems for Systems-Involved Youth</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>NORMANDY SCHOOLS COLLABORATIVE</t>
+          <t>Los Angeles County - Board of Supervisors</t>
         </is>
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
@@ -50229,7 +50249,7 @@
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="K666" t="inlineStr">
@@ -50239,22 +50259,27 @@
       </c>
       <c r="M666" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N666" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O666" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y666" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z666" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321688802026</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318930495177</t>
         </is>
       </c>
     </row>
@@ -50264,22 +50289,22 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>318905084658</t>
+          <t>319925282512</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>On-Call As-Needed Temporary Information Technology Staffing Services</t>
+          <t>MANAGED SERVICE PROVIDER (MSP)</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>East Bay Municipal Utility District</t>
+          <t>Freire Schools</t>
         </is>
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
@@ -50302,24 +50327,27 @@
           <t>2026-04-30</t>
         </is>
       </c>
+      <c r="L667" s="65" t="n">
+        <v>199960</v>
+      </c>
       <c r="M667" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O667" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y667" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z667" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318905084658</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319925282512</t>
         </is>
       </c>
     </row>
@@ -50329,22 +50357,22 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>323230348993</t>
+          <t>321688802026</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>Computerized Maintenance Management System</t>
+          <t>(Offline) RFP ACCOUNTING &amp; HUMAN RESOURCES ERP SYSTEM</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>University of California</t>
+          <t>NORMANDY SCHOOLS COLLABORATIVE</t>
         </is>
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
@@ -50359,7 +50387,7 @@
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="K668" t="inlineStr">
@@ -50379,12 +50407,12 @@
       </c>
       <c r="Y668" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z668" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323230348993</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321688802026</t>
         </is>
       </c>
     </row>
@@ -50394,22 +50422,22 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>321190312662</t>
+          <t>318905084658</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t xml:space="preserve">On-Call Data Modernization and Analytics Consulting Services </t>
+          <t>On-Call As-Needed Temporary Information Technology Staffing Services</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>Seattle Public Utilities (SPU)</t>
+          <t>East Bay Municipal Utility District</t>
         </is>
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
@@ -50424,7 +50452,7 @@
       </c>
       <c r="J669" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="K669" t="inlineStr">
@@ -50444,12 +50472,12 @@
       </c>
       <c r="Y669" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z669" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321190312662</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318905084658</t>
         </is>
       </c>
     </row>
@@ -50459,22 +50487,22 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>320835245763</t>
+          <t>323230348993</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>SECURITY OPERATIONS CENTER SOLUTION</t>
+          <t>Computerized Maintenance Management System</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>NEW YORK eHEALTH COLLABORATIVE</t>
+          <t>University of California</t>
         </is>
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
@@ -50489,40 +50517,32 @@
       </c>
       <c r="J670" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="K670" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="L670" s="65" t="n">
-        <v>528000</v>
+          <t>2026-04-30</t>
+        </is>
       </c>
       <c r="M670" t="inlineStr">
         <is>
-          <t>Audits and Assessment;Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N670" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O670" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y670" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z670" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320835245763</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323230348993</t>
         </is>
       </c>
     </row>
@@ -50532,17 +50552,22 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>321688803002</t>
+          <t>321190312662</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>IMRF IFB - 2026 Penetration Testing and Red Teaming Services</t>
+          <t xml:space="preserve">On-Call Data Modernization and Analytics Consulting Services </t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>ILLINOIS MUNICIPAL RETIREMENT FUND</t>
+          <t>Seattle Public Utilities (SPU)</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
@@ -50557,40 +50582,32 @@
       </c>
       <c r="J671" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="K671" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="L671" s="65" t="n">
-        <v>142500</v>
+          <t>2026-04-30</t>
+        </is>
       </c>
       <c r="M671" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
-        </is>
-      </c>
-      <c r="N671" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O671" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y671" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="Z671" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321688803002</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321190312662</t>
         </is>
       </c>
     </row>
@@ -50600,17 +50617,27 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>322527283932</t>
+          <t>320835245763</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>Test RFX (please ignore)</t>
+          <t>SECURITY OPERATIONS CENTER SOLUTION</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>NEW YORK eHEALTH COLLABORATIVE</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>New York</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H672" t="inlineStr">
@@ -50618,29 +50645,42 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="L672" s="65" t="n">
+        <v>528000</v>
+      </c>
       <c r="M672" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Audits and Assessment;Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N672" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O672" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
-        </is>
-      </c>
-      <c r="S672" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y672" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z672" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320835245763</t>
         </is>
       </c>
     </row>
@@ -50650,32 +50690,22 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>116977709771</t>
-        </is>
-      </c>
-      <c r="C673" t="inlineStr">
-        <is>
-          <t>RFP-25-0005</t>
+          <t>321688803002</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
+          <t>IMRF IFB - 2026 Penetration Testing and Red Teaming Services</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>NeighborWorks America</t>
-        </is>
-      </c>
-      <c r="F673" t="inlineStr">
-        <is>
-          <t>Washington, D.C.</t>
+          <t>ILLINOIS MUNICIPAL RETIREMENT FUND</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
@@ -50683,39 +50713,42 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="L673" s="65" t="n">
+        <v>142500</v>
+      </c>
       <c r="M673" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Audits and Assessment</t>
+        </is>
+      </c>
+      <c r="N673" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O673" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
-        </is>
-      </c>
-      <c r="S673" t="inlineStr">
-        <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="U673" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y673" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z673" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
-        </is>
-      </c>
-      <c r="AA673" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321688803002</t>
         </is>
       </c>
     </row>
@@ -50725,22 +50758,27 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>145081112265</t>
+          <t>275293787895</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t># 26-10</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>Technology Strategic Management Consulting</t>
+          <t>OFF-Digital Transformation Products and Services</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>State of Colorado, the Office of Information Technology (OIT)</t>
+          <t>Upper Occoquan Service Authority</t>
         </is>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
@@ -50755,7 +50793,12 @@
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M674" t="inlineStr">
@@ -50765,17 +50808,17 @@
       </c>
       <c r="O674" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y674" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Z674" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/275293787895</t>
         </is>
       </c>
     </row>
@@ -50785,27 +50828,27 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>175110048474</t>
+          <t>316930943726</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Agile ITQ Development</t>
+          <t>OFF: INFORMATION TECHNOLOGY SERVICES</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>Commonwealth of Pennsylvania</t>
+          <t>MetroWest Regional Transit Authority</t>
         </is>
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
@@ -50815,42 +50858,37 @@
       </c>
       <c r="J675" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M675" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N675" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O675" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="S675" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="U675" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y675" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="Z675" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/175110048474</t>
-        </is>
-      </c>
-      <c r="AA675" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316930943726</t>
         </is>
       </c>
     </row>
@@ -50860,22 +50898,22 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>166098266830</t>
+          <t>320837491424</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
+          <t>Cybersecurity Assessment</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>Mecklenburg County</t>
+          <t xml:space="preserve">City of Big Rapids </t>
         </is>
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
@@ -50890,8 +50928,16 @@
       </c>
       <c r="J676" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="L676" s="65" t="n">
+        <v>10000</v>
       </c>
       <c r="M676" t="inlineStr">
         <is>
@@ -50900,17 +50946,17 @@
       </c>
       <c r="O676" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y676" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="Z676" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320837491424</t>
         </is>
       </c>
     </row>
@@ -50920,27 +50966,17 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>180166400720</t>
+          <t>322527283932</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
-        </is>
-      </c>
-      <c r="E677" t="inlineStr">
-        <is>
-          <t>Central Ohio Transit Authority</t>
-        </is>
-      </c>
-      <c r="F677" t="inlineStr">
-        <is>
-          <t>Ohio</t>
+          <t>Test RFX (please ignore)</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
@@ -50948,24 +50984,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J677" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
+      <c r="M677" t="inlineStr">
+        <is>
+          <t>Training</t>
         </is>
       </c>
       <c r="O677" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="S677" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y677" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z677" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
         </is>
       </c>
     </row>
@@ -50975,32 +51016,32 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>164634446543</t>
+          <t>116977709771</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>RFP26007KAB</t>
+          <t>RFP-25-0005</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>Enterprise Resource Planning System and Services</t>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>Clark County School District</t>
+          <t>NeighborWorks America</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
@@ -51008,32 +51049,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J678" t="inlineStr">
-        <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="L678" s="65" t="n">
-        <v>180988276.8</v>
-      </c>
       <c r="M678" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
-        </is>
-      </c>
-      <c r="N678" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="O678" t="inlineStr">
+        <is>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="S678" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="U678" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Y678" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z678" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/164634446543</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+        </is>
+      </c>
+      <c r="AA678" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -51043,32 +51091,27 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>182404957915</t>
-        </is>
-      </c>
-      <c r="C679" t="inlineStr">
-        <is>
-          <t>PWE-10.08.2025</t>
+          <t>145081112265</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>PWE Power BI Dashboard</t>
+          <t>Technology Strategic Management Consulting</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>City of Issaquah</t>
+          <t>State of Colorado, the Office of Information Technology (OIT)</t>
         </is>
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H679" t="inlineStr">
@@ -51078,27 +51121,27 @@
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="M679" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O679" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y679" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z679" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
         </is>
       </c>
     </row>
@@ -51108,32 +51151,27 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>108771177151</t>
-        </is>
-      </c>
-      <c r="C680" t="inlineStr">
-        <is>
-          <t>791202505005</t>
+          <t>175110048474</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>Government Consulting Services</t>
+          <t>Agile ITQ Development</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>North Central Texas Council of Governments</t>
+          <t>Commonwealth of Pennsylvania</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>TEXAS</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
@@ -51143,12 +51181,12 @@
       </c>
       <c r="J680" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="N680" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="M680" t="inlineStr">
+        <is>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O680" t="inlineStr">
@@ -51156,14 +51194,29 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
+      <c r="S680" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="U680" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
       <c r="Y680" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z680" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/175110048474</t>
+        </is>
+      </c>
+      <c r="AA680" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -51173,32 +51226,27 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>120893940416</t>
-        </is>
-      </c>
-      <c r="C681" t="inlineStr">
-        <is>
-          <t>DQ SAAA #2026000004</t>
+          <t>166098266830</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>Online Content Learning</t>
+          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>State of Colorado Department of Regulatory Agencies</t>
+          <t>Mecklenburg County</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
@@ -51208,30 +51256,27 @@
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L681" s="65" t="n">
-        <v>67300</v>
+          <t>2025-10-07</t>
+        </is>
       </c>
       <c r="M681" t="inlineStr">
         <is>
-          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O681" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y681" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z681" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
         </is>
       </c>
     </row>
@@ -51241,27 +51286,27 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>199601365715</t>
+          <t>180166400720</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>Contracted IT Support Services</t>
+          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>ECS4Kids</t>
+          <t>Central Ohio Transit Authority</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
@@ -51271,35 +51316,22 @@
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="L682" s="65" t="n">
-        <v>291141</v>
-      </c>
-      <c r="M682" t="inlineStr">
-        <is>
-          <t>Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N682" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="O682" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y682" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="Z682" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
         </is>
       </c>
     </row>
@@ -51309,100 +51341,65 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>140123456196</t>
+          <t>164634446543</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>24-RFP-10</t>
+          <t>RFP26007KAB</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+          <t>Enterprise Resource Planning System and Services</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+          <t>Clark County School District</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I683" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J683" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="L683" s="65" t="n">
-        <v>18620</v>
+        <v>180988276.8</v>
       </c>
       <c r="M683" t="inlineStr">
         <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="O683" t="inlineStr">
-        <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="P683" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q683" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="S683" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="U683" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="V683" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="N683" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="Y683" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z683" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
-        </is>
-      </c>
-      <c r="AA683" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/164634446543</t>
         </is>
       </c>
     </row>
@@ -51412,27 +51409,32 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>261982669555</t>
+          <t>182404957915</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>PWE-10.08.2025</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT Backfill for ERP Configuration </t>
+          <t>PWE Power BI Dashboard</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>Madison Metropolitan Sewerage District</t>
+          <t>City of Issaquah</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
@@ -51442,50 +51444,27 @@
       </c>
       <c r="J684" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="L684" s="65" t="n">
-        <v>157000</v>
+          <t>2025-10-29</t>
+        </is>
       </c>
       <c r="M684" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O684" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="S684" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="U684" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="V684" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y684" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Z684" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
-        </is>
-      </c>
-      <c r="AA684" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
         </is>
       </c>
     </row>
@@ -51495,27 +51474,32 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>278519751386</t>
+          <t>108771177151</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>791202505005</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>Data Warehousing Services</t>
+          <t>Government Consulting Services</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allen Town School District </t>
+          <t>North Central Texas Council of Governments</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>TEXAS</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
@@ -51525,32 +51509,27 @@
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="M685" t="inlineStr">
-        <is>
-          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="N685" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O685" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y685" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="Z685" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
         </is>
       </c>
     </row>
@@ -51560,32 +51539,32 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>259790359234</t>
+          <t>120893940416</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>601440000049523</t>
+          <t>DQ SAAA #2026000004</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>Managed Application Services: Application Development and Maintenance Services</t>
+          <t>Online Content Learning</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>Texas Department of Transportation</t>
+          <t>State of Colorado Department of Regulatory Agencies</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
@@ -51595,27 +51574,30 @@
       </c>
       <c r="J686" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
-        </is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="L686" s="65" t="n">
+        <v>67300</v>
       </c>
       <c r="M686" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O686" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y686" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z686" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
         </is>
       </c>
     </row>
@@ -51625,22 +51607,22 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>277652547262</t>
+          <t>199601365715</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
+          <t>Contracted IT Support Services</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>District of Columbia Housing Finance Agency</t>
+          <t>ECS4Kids</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
@@ -51655,32 +51637,35 @@
       </c>
       <c r="J687" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
-        </is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="L687" s="65" t="n">
+        <v>291141</v>
       </c>
       <c r="M687" t="inlineStr">
         <is>
-          <t>Consulting;Training</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N687" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O687" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y687" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z687" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
         </is>
       </c>
     </row>
@@ -51690,57 +51675,100 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>269507522240</t>
+          <t>140123456196</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>24-RFP-10</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
+          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>Central Midlands Regional Transit Authority</t>
+          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J688" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
-        </is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L688" s="65" t="n">
+        <v>18620</v>
       </c>
       <c r="M688" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O688" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P688" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q688" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="S688" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="U688" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="V688" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y688" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z688" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
+        </is>
+      </c>
+      <c r="AA688" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -51750,27 +51778,27 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>294055526085</t>
+          <t>261982669555</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>Oracle Managed Services and Testing as a Service Support</t>
+          <t xml:space="preserve">IT Backfill for ERP Configuration </t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>CITY OF DURHAM</t>
+          <t>Madison Metropolitan Sewerage District</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
@@ -51780,27 +51808,50 @@
       </c>
       <c r="J689" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="L689" s="65" t="n">
+        <v>157000</v>
       </c>
       <c r="M689" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O689" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S689" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="U689" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="V689" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y689" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z689" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
+        </is>
+      </c>
+      <c r="AA689" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -51810,22 +51861,22 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>305430641393</t>
+          <t>278519751386</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>OFF - Information Technology Managed Services</t>
+          <t>Data Warehousing Services</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>County of Montcalm</t>
+          <t xml:space="preserve">Allen Town School District </t>
         </is>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
@@ -51840,27 +51891,32 @@
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="M690" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N690" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O690" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y690" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Z690" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
         </is>
       </c>
     </row>
@@ -51870,32 +51926,32 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>135161266908</t>
+          <t>259790359234</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>RFQ1757840</t>
+          <t>601440000049523</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>25-51-A-PMO-ES-SSN</t>
+          <t>Managed Application Services: Application Development and Maintenance Services</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>U.S. Department of the Treasury</t>
+          <t>Texas Department of Transportation</t>
         </is>
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
@@ -51905,27 +51961,27 @@
       </c>
       <c r="J691" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="N691" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O691" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y691" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z691" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
         </is>
       </c>
     </row>
@@ -51935,17 +51991,27 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>110691507903</t>
+          <t>277652547262</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
+          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>District of Columbia Housing Finance Agency</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
@@ -51955,25 +52021,32 @@
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="L692" s="65" t="n">
-        <v>96200</v>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>Consulting;Training</t>
+        </is>
+      </c>
+      <c r="N692" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
       </c>
       <c r="O692" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y692" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Z692" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
         </is>
       </c>
     </row>
@@ -51983,17 +52056,27 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>110691507909</t>
+          <t>269507522240</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
+          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>Central Midlands Regional Transit Authority</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -52003,22 +52086,27 @@
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O693" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y693" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z693" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
         </is>
       </c>
     </row>
@@ -52028,17 +52116,27 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>108771377911</t>
+          <t>294055526085</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>Facilities and Information Technology Infrastructure Assessment</t>
+          <t>Oracle Managed Services and Testing as a Service Support</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>CITY OF DURHAM</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
@@ -52048,22 +52146,27 @@
       </c>
       <c r="J694" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O694" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y694" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Z694" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
         </is>
       </c>
     </row>
@@ -52073,22 +52176,27 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>120893940419</t>
-        </is>
-      </c>
-      <c r="C695" t="inlineStr">
-        <is>
-          <t>#25-038-RFP)</t>
+          <t>305430641393</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>HUMAN RESOURCES INFORMATION SYSTEM ("HRIS") &amp; LEARNING MANAGEMENT SYSTEM ("LMS") REPLACEMENT</t>
+          <t>OFF - Information Technology Managed Services</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>County of Montcalm</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H695" t="inlineStr">
@@ -52098,27 +52206,27 @@
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M695" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O695" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y695" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="Z695" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
         </is>
       </c>
     </row>
@@ -52128,12 +52236,27 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>114864654049</t>
+          <t>135161266908</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>RFQ1757840</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>M365 Tenant backup</t>
+          <t>25-51-A-PMO-ES-SSN</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>U.S. Department of the Treasury</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
@@ -52148,22 +52271,27 @@
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="N696" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O696" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y696" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z696" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
         </is>
       </c>
     </row>
@@ -52173,50 +52301,288 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
+          <t>110691507903</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="L697" s="65" t="n">
+        <v>96200</v>
+      </c>
+      <c r="O697" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y697" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z697" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="n">
+        <v>697</v>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>110691507909</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O698" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y698" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z698" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="n">
+        <v>698</v>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>108771377911</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Facilities and Information Technology Infrastructure Assessment</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O699" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y699" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z699" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="n">
+        <v>699</v>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>120893940419</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>#25-038-RFP)</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>HUMAN RESOURCES INFORMATION SYSTEM ("HRIS") &amp; LEARNING MANAGEMENT SYSTEM ("LMS") REPLACEMENT</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="O700" t="inlineStr">
+        <is>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="Y700" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="Z700" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="n">
+        <v>700</v>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>114864654049</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>M365 Tenant backup</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O701" t="inlineStr">
+        <is>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="Y701" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z701" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="n">
+        <v>701</v>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
           <t>317945474767</t>
         </is>
       </c>
-      <c r="D697" t="inlineStr">
+      <c r="D702" t="inlineStr">
         <is>
           <t>ServiceNow Technical Services</t>
         </is>
       </c>
-      <c r="E697" t="inlineStr">
+      <c r="E702" t="inlineStr">
         <is>
           <t>City of Sacramento</t>
         </is>
       </c>
-      <c r="F697" t="inlineStr">
+      <c r="F702" t="inlineStr">
         <is>
           <t>California</t>
         </is>
       </c>
-      <c r="G697" t="inlineStr">
+      <c r="G702" t="inlineStr">
         <is>
           <t>RFx Cancelled</t>
         </is>
       </c>
-      <c r="H697" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J697" t="inlineStr">
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="O697" t="inlineStr">
+      <c r="O702" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
-      <c r="Y697" t="inlineStr">
+      <c r="Y702" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="Z697" t="inlineStr">
+      <c r="Z702" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
         </is>
@@ -52239,7 +52605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA85"/>
+  <dimension ref="A1:AA87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -58028,22 +58394,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>320213008064</t>
+          <t>323517591239</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ONLINE WEB-BASED TRAINING</t>
+          <t>CAPK SOW 1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Alaska Department of Administration</t>
+          <t>Community Action Partnership of Kern</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -58058,45 +58424,37 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="L63" s="65" t="n">
-        <v>37800</v>
+          <t>2026-04-03</t>
+        </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Consulting;Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320213008064</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323517591239</t>
         </is>
       </c>
     </row>
@@ -58106,32 +58464,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>127482765035</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>RFP NO. NC- 2025-14</t>
+          <t>323528390341</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Computer Maintenance &amp; Technology Support Services - FCSS Fresno County Superintendent of Schools</t>
+          <t>IT MSP &amp; NOC NMFA Additional SOW</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FRESNO COUNTY SUPERINTENDENT OF SCHOOLS</t>
+          <t xml:space="preserve">New Mexico Finance Authority (“NMFA”) </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -58141,57 +58494,37 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Consulting;Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127482765035</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323528390341</t>
         </is>
       </c>
     </row>
@@ -58201,27 +58534,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>116977709757</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>RCA-017-25010066</t>
+          <t>320213008064</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ON-LINE MARKETPLACE FOR CLOUD SERVICES AND SOFTWARE</t>
+          <t>ONLINE WEB-BASED TRAINING</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Orange County</t>
+          <t>Alaska Department of Administration</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Alaska</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -58234,34 +58562,47 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="L65" s="65" t="n">
+        <v>37800</v>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Consulting;Reseller</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709757</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320213008064</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -58271,27 +58612,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>116977709771</t>
+          <t>127482765035</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>RFP-25-0005</t>
+          <t>RFP NO. NC- 2025-14</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
+          <t>Computer Maintenance &amp; Technology Support Services - FCSS Fresno County Superintendent of Schools</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>NeighborWorks America</t>
+          <t>FRESNO COUNTY SUPERINTENDENT OF SCHOOLS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -58304,34 +58645,54 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting;Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Arshdeep Kaur</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127482765035</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -58346,22 +58707,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>116977709756</t>
+          <t>116977709757</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>RCA-017-25010066</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Hazelwood Information Technology Audit Services</t>
+          <t>ON-LINE MARKETPLACE FOR CLOUD SERVICES AND SOFTWARE</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hazelwood School District</t>
+          <t>Orange County</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -58374,12 +58740,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L67" s="65" t="n">
-        <v>48500</v>
-      </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Consulting;Reseller</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -58389,12 +58752,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -58404,12 +58762,12 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709756</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709757</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -58419,27 +58777,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>269389012723</t>
+          <t>116977709771</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>COVB-25-101486</t>
+          <t>RFP-25-0005</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">City of Virginia Beach </t>
+          <t>NeighborWorks America</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -58464,22 +58822,22 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269389012723</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -58494,17 +58852,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>322527283932</t>
+          <t>116977709756</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Test RFX (please ignore)</t>
+          <t>Hazelwood Information Technology Audit Services</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Hazelwood School District</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -58512,29 +58880,42 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L69" s="65" t="n">
+        <v>48500</v>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709756</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -58544,22 +58925,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>127590445803</t>
+          <t>269389012723</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>COVB-25-101486</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>IT Staffing and Professional Services</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Roswell Park Comprehensive Cancer Centre</t>
+          <t xml:space="preserve">City of Virginia Beach </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -58572,39 +58958,34 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Consulting;Staff Augmentation</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445803</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269389012723</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -58619,32 +59000,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>123670192881</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>24-31</t>
+          <t>322527283932</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Arapahoe County - IT RECRUITMENT AND STAFFING</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Arapahoe County</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Colorado</t>
+          <t>Test RFX (please ignore)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -58652,44 +59018,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Akshat Tripathi</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>2025-04-28</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/123670192881</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
         </is>
       </c>
     </row>
@@ -58699,27 +59050,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>114864632551</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>F25-077</t>
+          <t>127590445803</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>City of Sunnyvale - Group 4, Software/Application/Database Development, Business Requirements Analysis, and Integration Services</t>
+          <t>IT Staffing and Professional Services</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>City of Sunnyvale</t>
+          <t>Roswell Park Comprehensive Cancer Centre</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -58734,42 +59080,37 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Consulting;Staff Augmentation</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864632551</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445803</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -58784,27 +59125,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>127678196421</t>
+          <t>123670192881</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>RFQ 24 - 00332</t>
+          <t>24-31</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>HRT - Workday HCM Staffing Services</t>
+          <t>Arapahoe County - IT RECRUITMENT AND STAFFING</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hampton Roads Transit</t>
+          <t>Arapahoe County</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -58814,21 +59155,13 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="L73" s="65" t="n">
-        <v>10000</v>
+          <t>2024-11-13</t>
+        </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -58837,47 +59170,32 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>2025-02-07</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127678196421</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/123670192881</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -58887,22 +59205,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>127590445777</t>
+          <t>114864632551</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>F25-077</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Temporary Professional Staff Services 2</t>
+          <t>City of Sunnyvale - Group 4, Software/Application/Database Development, Business Requirements Analysis, and Integration Services</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>State of South Dakota Department of Social Services</t>
+          <t>City of Sunnyvale</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>South Dakota</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -58917,7 +59240,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -58925,29 +59248,34 @@
           <t>Staff Augmentation</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445777</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864632551</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -58962,27 +59290,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>142851074788</t>
+          <t>127678196421</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>RFQ-DH-1394</t>
+          <t>RFQ 24 - 00332</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ON-CALL INFORMATION TECHNOLOGY INFRASTRUCTURE SERVICES</t>
+          <t>HRT - Workday HCM Staffing Services</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Metropolitan Water District of Southern California</t>
+          <t>Hampton Roads Transit</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -58992,52 +59320,70 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
-        </is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="L75" s="65" t="n">
+        <v>10000</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
           <t>Staff Augmentation</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Arshdeep Kaur</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/142851074788</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127678196421</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -59047,22 +59393,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>132776626904</t>
+          <t>127590445777</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ON-CALL INFORMATION TECHNOLOGY (IT) APPLICATION SUPPORT SERVICES (RFQ-DS-1397)</t>
+          <t>Temporary Professional Staff Services 2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Metropolitan Water District of Southern California</t>
+          <t>State of South Dakota Department of Social Services</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>South Dakota</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -59077,7 +59423,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -59092,22 +59438,22 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/132776626904</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445777</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -59122,22 +59468,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>127678196440</t>
+          <t>142851074788</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>RFQ-DH-1394</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>MINNESOTA JUDICIAL BRANCH - IT Technical/infrastructure Services, Information Technology Application Development And Support Services &amp; Data Science And Machine Learning Services</t>
+          <t>ON-CALL INFORMATION TECHNOLOGY INFRASTRUCTURE SERVICES</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Minnesota Judicial Branch</t>
+          <t>Metropolitan Water District of Southern California</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -59152,7 +59503,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -59160,29 +59511,34 @@
           <t>Staff Augmentation</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127678196440</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/142851074788</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -59197,22 +59553,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>127590445789</t>
+          <t>132776626904</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Retainer Contract Opportunity for Information Technology (IT) Services</t>
+          <t>ON-CALL INFORMATION TECHNOLOGY (IT) APPLICATION SUPPORT SERVICES (RFQ-DS-1397)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>State of Vermont (Department of Buildings and General Services)</t>
+          <t>Metropolitan Water District of Southern California</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vermont</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -59227,7 +59583,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -59242,22 +59598,22 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445789</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/132776626904</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -59272,27 +59628,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>135198825206</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>24-25-78</t>
+          <t>127678196440</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>IT Project Management &amp; Consulting Services</t>
+          <t>MINNESOTA JUDICIAL BRANCH - IT Technical/infrastructure Services, Information Technology Application Development And Support Services &amp; Data Science And Machine Learning Services</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>City of Santa Clara</t>
+          <t>Minnesota Judicial Branch</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -59302,57 +59653,42 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
+          <t>Arshdeep Kaur</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135198825206</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127678196440</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -59367,27 +59703,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>168988159693</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>6000002323</t>
+          <t>127590445789</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Performance of Expert Professional Airport Data Analysis and Business Intelligence Consulting Services during 2025 through 2029</t>
+          <t>Retainer Contract Opportunity for Information Technology (IT) Services</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Port Authority of New York New Jersey</t>
+          <t>State of Vermont (Department of Buildings and General Services)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Vermont</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -59402,7 +59733,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -59412,22 +59743,32 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/168988159693</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445789</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -59437,27 +59778,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>169111068380</t>
+          <t>135198825206</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6000002328</t>
+          <t>24-25-78</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Performance of Expert Professional Airport Information Technology and Innovation Consulting Services</t>
+          <t>IT Project Management &amp; Consulting Services</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Port Authority of New York New Jersey</t>
+          <t>City of Santa Clara</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -59467,37 +59808,57 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/169111068380</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135198825206</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -59512,27 +59873,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>169108930291</t>
+          <t>168988159693</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>RFQ-AR-1399</t>
+          <t>6000002323</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ON-CALL INFORMATION TECHNOLOGY SOFTWARE ASSET MANAGEMENT SERVICES</t>
+          <t>Performance of Expert Professional Airport Data Analysis and Business Intelligence Consulting Services during 2025 through 2029</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Metropolitan Water District of Southern California</t>
+          <t>Port Authority of New York New Jersey</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -59552,37 +59913,27 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/169108930291</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/168988159693</t>
         </is>
       </c>
     </row>
@@ -59592,22 +59943,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>175110048474</t>
+          <t>169111068380</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>6000002328</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Agile ITQ Development</t>
+          <t>Performance of Expert Professional Airport Information Technology and Innovation Consulting Services</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Commonwealth of Pennsylvania</t>
+          <t>Port Authority of New York New Jersey</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -59622,7 +59978,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -59632,27 +59988,22 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/175110048474</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/169111068380</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -59667,55 +60018,47 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>140123456196</t>
+          <t>169108930291</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>24-RFP-10</t>
+          <t>RFQ-AR-1399</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+          <t>ON-CALL INFORMATION TECHNOLOGY SOFTWARE ASSET MANAGEMENT SERVICES</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+          <t>Metropolitan Water District of Southern California</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L84" s="65" t="n">
-        <v>18620</v>
+          <t>2025-09-24</t>
+        </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -59723,39 +60066,24 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/169108930291</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -59770,78 +60098,256 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t>175110048474</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Agile ITQ Development</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Commonwealth of Pennsylvania</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/175110048474</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>140123456196</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>24-RFP-10</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Intent to Award</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L86" s="65" t="n">
+        <v>18620</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>In Process</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>261982669555</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t xml:space="preserve">IT Backfill for ERP Configuration </t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>Madison Metropolitan Sewerage District</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Wisconsin</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>Closed Won</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
         <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="L85" s="65" t="n">
+      <c r="L87" s="65" t="n">
         <v>157000</v>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>Staff Augmentation</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>2025-10-24</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="U87" t="inlineStr">
         <is>
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr">
+      <c r="V87" t="inlineStr">
         <is>
           <t>In Process</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Y87" t="inlineStr">
         <is>
           <t>2026-01-14</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
+      <c r="Z87" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
         </is>
       </c>
-      <c r="AA85" t="inlineStr">
+      <c r="AA87" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-05-06 11:06 EDT</t>
+          <t>2026-05-07 02:32 EDT</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA708"/>
+  <dimension ref="A1:AA711"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -23591,6 +23591,9 @@
           <t>2025-12-15</t>
         </is>
       </c>
+      <c r="L292" s="65" t="n">
+        <v>37960</v>
+      </c>
       <c r="M292" t="inlineStr">
         <is>
           <t>Managed Services (MSP)</t>
@@ -25095,6 +25098,9 @@
           <t>2025-12-18</t>
         </is>
       </c>
+      <c r="L314" s="65" t="n">
+        <v>100</v>
+      </c>
       <c r="M314" t="inlineStr">
         <is>
           <t>Consulting</t>
@@ -42260,7 +42266,7 @@
         </is>
       </c>
       <c r="L552" s="65" t="n">
-        <v>39360</v>
+        <v>49440</v>
       </c>
       <c r="M552" t="inlineStr">
         <is>
@@ -48208,7 +48214,7 @@
       </c>
       <c r="S636" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y636" t="inlineStr">
@@ -49592,6 +49598,11 @@
           <t>2026-04-28</t>
         </is>
       </c>
+      <c r="M656" t="inlineStr">
+        <is>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
       <c r="O656" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
@@ -49790,6 +49801,11 @@
           <t>Managed Services (MSP)</t>
         </is>
       </c>
+      <c r="N659" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
       <c r="O659" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
@@ -51400,17 +51416,27 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>322527283932</t>
+          <t>321905742529</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Test RFX (please ignore)</t>
+          <t>Dynamics CRM Migration Support, Portal Development, &amp; Train-the-Trainer</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>Governor's Office of Business and Economic Development (GO-Biz)</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>California</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
@@ -51418,29 +51444,42 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="L683" s="65" t="n">
+        <v>173290</v>
+      </c>
       <c r="M683" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Platform Implementation (ERP, CRMs);Training</t>
+        </is>
+      </c>
+      <c r="N683" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O683" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
-        </is>
-      </c>
-      <c r="S683" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y683" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Z683" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321905742529</t>
         </is>
       </c>
     </row>
@@ -51450,32 +51489,27 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>116977709771</t>
-        </is>
-      </c>
-      <c r="C684" t="inlineStr">
-        <is>
-          <t>RFP-25-0005</t>
+          <t>320114224858</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
+          <t>Information Technology Strategic Plan</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>NeighborWorks America</t>
+          <t>City of Richmond</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
@@ -51483,39 +51517,39 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
       <c r="M684" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N684" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O684" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
-        </is>
-      </c>
-      <c r="S684" t="inlineStr">
-        <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="U684" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y684" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="Z684" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
-        </is>
-      </c>
-      <c r="AA684" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320114224858</t>
         </is>
       </c>
     </row>
@@ -51525,22 +51559,27 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>145081112265</t>
+          <t>319866591968</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>RFP260304</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>Technology Strategic Management Consulting</t>
+          <t>Full Stack WordPress Developer (part-time)</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>State of Colorado, the Office of Information Technology (OIT)</t>
+          <t>Seattle Public Schools</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
@@ -51555,27 +51594,40 @@
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="L685" s="65" t="n">
+        <v>65000</v>
       </c>
       <c r="M685" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="N685" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O685" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y685" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z685" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319866591968</t>
         </is>
       </c>
     </row>
@@ -51585,27 +51637,17 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>175110048474</t>
+          <t>322527283932</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>Agile ITQ Development</t>
-        </is>
-      </c>
-      <c r="E686" t="inlineStr">
-        <is>
-          <t>Commonwealth of Pennsylvania</t>
-        </is>
-      </c>
-      <c r="F686" t="inlineStr">
-        <is>
-          <t>Pennsylvania</t>
+          <t>Test RFX (please ignore)</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
@@ -51613,44 +51655,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J686" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
       <c r="M686" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O686" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Akshat Tripathi</t>
         </is>
       </c>
       <c r="S686" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="U686" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y686" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z686" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/175110048474</t>
-        </is>
-      </c>
-      <c r="AA686" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
         </is>
       </c>
     </row>
@@ -51660,27 +51687,32 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>166098266830</t>
+          <t>116977709771</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>RFP-25-0005</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>Mecklenburg County</t>
+          <t>NeighborWorks America</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
@@ -51688,29 +51720,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J687" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
       <c r="M687" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O687" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="S687" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="U687" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Y687" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z687" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+        </is>
+      </c>
+      <c r="AA687" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -51720,27 +51762,27 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>180166400720</t>
+          <t>145081112265</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
+          <t>Technology Strategic Management Consulting</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>Central Ohio Transit Authority</t>
+          <t>State of Colorado, the Office of Information Technology (OIT)</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
@@ -51750,7 +51792,12 @@
       </c>
       <c r="J688" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O688" t="inlineStr">
@@ -51760,12 +51807,12 @@
       </c>
       <c r="Y688" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z688" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
         </is>
       </c>
     </row>
@@ -51775,32 +51822,27 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>164634446543</t>
-        </is>
-      </c>
-      <c r="C689" t="inlineStr">
-        <is>
-          <t>RFP26007KAB</t>
+          <t>175110048474</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>Enterprise Resource Planning System and Services</t>
+          <t>Agile ITQ Development</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>Clark County School District</t>
+          <t>Commonwealth of Pennsylvania</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
@@ -51810,30 +51852,42 @@
       </c>
       <c r="J689" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="L689" s="65" t="n">
-        <v>180988276.8</v>
+          <t>2025-10-02</t>
+        </is>
       </c>
       <c r="M689" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
-        </is>
-      </c>
-      <c r="N689" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="O689" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S689" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="U689" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Y689" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z689" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/164634446543</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/175110048474</t>
+        </is>
+      </c>
+      <c r="AA689" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -51843,32 +51897,27 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>182404957915</t>
-        </is>
-      </c>
-      <c r="C690" t="inlineStr">
-        <is>
-          <t>PWE-10.08.2025</t>
+          <t>166098266830</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>PWE Power BI Dashboard</t>
+          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>City of Issaquah</t>
+          <t>Mecklenburg County</t>
         </is>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
@@ -51878,27 +51927,27 @@
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="M690" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O690" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y690" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z690" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
         </is>
       </c>
     </row>
@@ -51908,27 +51957,22 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>108771177151</t>
-        </is>
-      </c>
-      <c r="C691" t="inlineStr">
-        <is>
-          <t>791202505005</t>
+          <t>180166400720</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>Government Consulting Services</t>
+          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>North Central Texas Council of Governments</t>
+          <t>Central Ohio Transit Authority</t>
         </is>
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>TEXAS</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
@@ -51943,12 +51987,7 @@
       </c>
       <c r="J691" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="N691" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="O691" t="inlineStr">
@@ -51958,12 +51997,12 @@
       </c>
       <c r="Y691" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="Z691" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
         </is>
       </c>
     </row>
@@ -51973,32 +52012,32 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>120893940416</t>
+          <t>164634446543</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>DQ SAAA #2026000004</t>
+          <t>RFP26007KAB</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>Online Content Learning</t>
+          <t>Enterprise Resource Planning System and Services</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>State of Colorado Department of Regulatory Agencies</t>
+          <t>Clark County School District</t>
         </is>
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
@@ -52008,30 +52047,30 @@
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="L692" s="65" t="n">
-        <v>67300</v>
+        <v>180988276.8</v>
       </c>
       <c r="M692" t="inlineStr">
         <is>
-          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
-        </is>
-      </c>
-      <c r="O692" t="inlineStr">
-        <is>
-          <t>Madhav Mitruka</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="N692" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="Y692" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z692" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/164634446543</t>
         </is>
       </c>
     </row>
@@ -52041,27 +52080,32 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>199601365715</t>
+          <t>182404957915</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>PWE-10.08.2025</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>Contracted IT Support Services</t>
+          <t>PWE Power BI Dashboard</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>ECS4Kids</t>
+          <t>City of Issaquah</t>
         </is>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -52071,20 +52115,12 @@
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="L693" s="65" t="n">
-        <v>291141</v>
+          <t>2025-10-29</t>
+        </is>
       </c>
       <c r="M693" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N693" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O693" t="inlineStr">
@@ -52094,12 +52130,12 @@
       </c>
       <c r="Y693" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Z693" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
         </is>
       </c>
     </row>
@@ -52109,55 +52145,47 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>140123456196</t>
+          <t>108771177151</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>24-RFP-10</t>
+          <t>791202505005</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+          <t>Government Consulting Services</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+          <t>North Central Texas Council of Governments</t>
         </is>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>TEXAS</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I694" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J694" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L694" s="65" t="n">
-        <v>18620</v>
-      </c>
-      <c r="M694" t="inlineStr">
-        <is>
-          <t>Training</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="N694" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O694" t="inlineStr">
@@ -52165,44 +52193,14 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="P694" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q694" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="S694" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="U694" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="V694" t="inlineStr">
-        <is>
-          <t>In Process</t>
-        </is>
-      </c>
       <c r="Y694" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="Z694" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
-        </is>
-      </c>
-      <c r="AA694" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
         </is>
       </c>
     </row>
@@ -52212,27 +52210,32 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>261982669555</t>
+          <t>120893940416</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>DQ SAAA #2026000004</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT Backfill for ERP Configuration </t>
+          <t>Online Content Learning</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>Madison Metropolitan Sewerage District</t>
+          <t>State of Colorado Department of Regulatory Agencies</t>
         </is>
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H695" t="inlineStr">
@@ -52242,15 +52245,15 @@
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="L695" s="65" t="n">
-        <v>157000</v>
+        <v>67300</v>
       </c>
       <c r="M695" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O695" t="inlineStr">
@@ -52258,34 +52261,14 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="S695" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="U695" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="V695" t="inlineStr">
-        <is>
-          <t>In Process</t>
-        </is>
-      </c>
       <c r="Y695" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z695" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
-        </is>
-      </c>
-      <c r="AA695" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
         </is>
       </c>
     </row>
@@ -52295,22 +52278,22 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>278519751386</t>
+          <t>199601365715</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>Data Warehousing Services</t>
+          <t>Contracted IT Support Services</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allen Town School District </t>
+          <t>ECS4Kids</t>
         </is>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
@@ -52325,32 +52308,35 @@
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="L696" s="65" t="n">
+        <v>291141</v>
       </c>
       <c r="M696" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N696" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O696" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y696" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z696" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
         </is>
       </c>
     </row>
@@ -52360,62 +52346,100 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>259790359234</t>
+          <t>140123456196</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>601440000049523</t>
+          <t>24-RFP-10</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>Managed Application Services: Application Development and Maintenance Services</t>
+          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>Texas Department of Transportation</t>
+          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
         </is>
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
-        </is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L697" s="65" t="n">
+        <v>18620</v>
       </c>
       <c r="M697" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O697" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P697" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q697" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="S697" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="U697" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="V697" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y697" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z697" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
+        </is>
+      </c>
+      <c r="AA697" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -52425,27 +52449,27 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>277652547262</t>
+          <t>261982669555</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
+          <t xml:space="preserve">IT Backfill for ERP Configuration </t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>District of Columbia Housing Finance Agency</t>
+          <t>Madison Metropolitan Sewerage District</t>
         </is>
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
@@ -52455,32 +52479,50 @@
       </c>
       <c r="J698" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
-        </is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="L698" s="65" t="n">
+        <v>157000</v>
       </c>
       <c r="M698" t="inlineStr">
         <is>
-          <t>Consulting;Training</t>
-        </is>
-      </c>
-      <c r="N698" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O698" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S698" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="U698" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="V698" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y698" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z698" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
+        </is>
+      </c>
+      <c r="AA698" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -52490,22 +52532,22 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>269507522240</t>
+          <t>278519751386</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
+          <t>Data Warehousing Services</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>Central Midlands Regional Transit Authority</t>
+          <t xml:space="preserve">Allen Town School District </t>
         </is>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
@@ -52520,27 +52562,32 @@
       </c>
       <c r="J699" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="M699" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N699" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O699" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y699" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Z699" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
         </is>
       </c>
     </row>
@@ -52550,27 +52597,32 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>294055526085</t>
+          <t>259790359234</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>601440000049523</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Oracle Managed Services and Testing as a Service Support</t>
+          <t>Managed Application Services: Application Development and Maintenance Services</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>CITY OF DURHAM</t>
+          <t>Texas Department of Transportation</t>
         </is>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
@@ -52580,7 +52632,7 @@
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="M700" t="inlineStr">
@@ -52590,17 +52642,17 @@
       </c>
       <c r="O700" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y700" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z700" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
         </is>
       </c>
     </row>
@@ -52610,22 +52662,22 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>305430641393</t>
+          <t>277652547262</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>OFF - Information Technology Managed Services</t>
+          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>County of Montcalm</t>
+          <t>District of Columbia Housing Finance Agency</t>
         </is>
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
@@ -52640,27 +52692,32 @@
       </c>
       <c r="J701" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="M701" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting;Training</t>
+        </is>
+      </c>
+      <c r="N701" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O701" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y701" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Z701" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
         </is>
       </c>
     </row>
@@ -52670,32 +52727,27 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>135161266908</t>
-        </is>
-      </c>
-      <c r="C702" t="inlineStr">
-        <is>
-          <t>RFQ1757840</t>
+          <t>269507522240</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>25-51-A-PMO-ES-SSN</t>
+          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>U.S. Department of the Treasury</t>
+          <t>Central Midlands Regional Transit Authority</t>
         </is>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
@@ -52705,27 +52757,27 @@
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="N702" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O702" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y702" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z702" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
         </is>
       </c>
     </row>
@@ -52735,17 +52787,27 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>110691507903</t>
+          <t>294055526085</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
+          <t>Oracle Managed Services and Testing as a Service Support</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>CITY OF DURHAM</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
@@ -52755,25 +52817,27 @@
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="L703" s="65" t="n">
-        <v>96200</v>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance</t>
+        </is>
       </c>
       <c r="O703" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y703" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Z703" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
         </is>
       </c>
     </row>
@@ -52783,17 +52847,27 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>110691507909</t>
+          <t>305430641393</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
+          <t>OFF - Information Technology Managed Services</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>County of Montcalm</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
@@ -52803,22 +52877,27 @@
       </c>
       <c r="J704" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O704" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y704" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="Z704" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
         </is>
       </c>
     </row>
@@ -52828,12 +52907,27 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>108771377911</t>
+          <t>135161266908</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>RFQ1757840</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>Facilities and Information Technology Infrastructure Assessment</t>
+          <t>25-51-A-PMO-ES-SSN</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>U.S. Department of the Treasury</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
@@ -52848,7 +52942,12 @@
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="N705" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O705" t="inlineStr">
@@ -52858,12 +52957,12 @@
       </c>
       <c r="Y705" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z705" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
         </is>
       </c>
     </row>
@@ -52873,17 +52972,12 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>120893940419</t>
-        </is>
-      </c>
-      <c r="C706" t="inlineStr">
-        <is>
-          <t>#25-038-RFP)</t>
+          <t>110691507903</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>HUMAN RESOURCES INFORMATION SYSTEM ("HRIS") &amp; LEARNING MANAGEMENT SYSTEM ("LMS") REPLACEMENT</t>
+          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
@@ -52901,24 +52995,22 @@
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="M706" t="inlineStr">
-        <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
-        </is>
+      <c r="L706" s="65" t="n">
+        <v>96200</v>
       </c>
       <c r="O706" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y706" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z706" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
         </is>
       </c>
     </row>
@@ -52928,12 +53020,12 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>114864654049</t>
+          <t>110691507909</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>M365 Tenant backup</t>
+          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
@@ -52953,17 +53045,17 @@
       </c>
       <c r="O707" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y707" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z707" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
         </is>
       </c>
     </row>
@@ -52973,50 +53065,195 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
+          <t>108771377911</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Facilities and Information Technology Infrastructure Assessment</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O708" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y708" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z708" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="n">
+        <v>708</v>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>120893940419</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>#25-038-RFP)</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>HUMAN RESOURCES INFORMATION SYSTEM ("HRIS") &amp; LEARNING MANAGEMENT SYSTEM ("LMS") REPLACEMENT</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="O709" t="inlineStr">
+        <is>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="Y709" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="Z709" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="n">
+        <v>709</v>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>114864654049</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>M365 Tenant backup</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O710" t="inlineStr">
+        <is>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="Y710" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z710" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="n">
+        <v>710</v>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
           <t>317945474767</t>
         </is>
       </c>
-      <c r="D708" t="inlineStr">
+      <c r="D711" t="inlineStr">
         <is>
           <t>ServiceNow Technical Services</t>
         </is>
       </c>
-      <c r="E708" t="inlineStr">
+      <c r="E711" t="inlineStr">
         <is>
           <t>City of Sacramento</t>
         </is>
       </c>
-      <c r="F708" t="inlineStr">
+      <c r="F711" t="inlineStr">
         <is>
           <t>California</t>
         </is>
       </c>
-      <c r="G708" t="inlineStr">
+      <c r="G711" t="inlineStr">
         <is>
           <t>RFx Cancelled</t>
         </is>
       </c>
-      <c r="H708" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J708" t="inlineStr">
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J711" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="O708" t="inlineStr">
+      <c r="O711" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
-      <c r="Y708" t="inlineStr">
+      <c r="Y711" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="Z708" t="inlineStr">
+      <c r="Z711" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
         </is>
@@ -55651,7 +55888,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -57983,6 +58220,9 @@
           <t>2025-12-18</t>
         </is>
       </c>
+      <c r="L53" s="65" t="n">
+        <v>100</v>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>Consulting</t>
@@ -58958,7 +59198,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-05-10 14:24 EDT</t>
+          <t>2026-05-12 06:32 EDT</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA717"/>
+  <dimension ref="A1:AA719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -44768,42 +44768,32 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>314639183583</t>
-        </is>
-      </c>
-      <c r="C587" t="inlineStr">
-        <is>
-          <t>RFP No.: _001</t>
+          <t>291136345846</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>Information Technology Services</t>
+          <t>2025 Citywide Information Technology (IT) Professionals RFQ</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>Clear Creek School District No. RE-1</t>
+          <t>City of Los Angeles (City) Information Technology Agency (ITA)</t>
         </is>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Interview</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I587" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J587" t="inlineStr">
@@ -44816,9 +44806,6 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="L587" s="65" t="n">
-        <v>212330</v>
-      </c>
       <c r="M587" t="inlineStr">
         <is>
           <t>Managed Services (MSP)</t>
@@ -44831,27 +44818,17 @@
       </c>
       <c r="O587" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
-        </is>
-      </c>
-      <c r="P587" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q587" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y587" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="Z587" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/314639183583</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/291136345846</t>
         </is>
       </c>
     </row>
@@ -44861,43 +44838,56 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>291136345846</t>
+          <t>314639183583</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>RFP No.: _001</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>2025 Citywide Information Technology (IT) Professionals RFQ</t>
+          <t>Information Technology Services</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>City of Los Angeles (City) Information Technology Agency (ITA)</t>
+          <t>Clear Creek School District No. RE-1</t>
         </is>
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J588" t="inlineStr">
         <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+      <c r="L588" s="65" t="n">
+        <v>212330</v>
       </c>
       <c r="M588" t="inlineStr">
         <is>
@@ -44911,17 +44901,27 @@
       </c>
       <c r="O588" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="P588" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q588" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Y588" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="Z588" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/291136345846</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/314639183583</t>
         </is>
       </c>
     </row>
@@ -51973,17 +51973,17 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>321711121139</t>
+          <t>321010534088</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>Information Technology Managed Services: IT Service Desk</t>
+          <t>IT MANAGED SERVICES PROVIDER</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>Brunswick County</t>
+          <t>City of Ferndale</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
@@ -51998,7 +51998,7 @@
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="K690" t="inlineStr">
@@ -52007,7 +52007,7 @@
         </is>
       </c>
       <c r="L690" s="65" t="n">
-        <v>92560</v>
+        <v>373572</v>
       </c>
       <c r="M690" t="inlineStr">
         <is>
@@ -52016,22 +52016,22 @@
       </c>
       <c r="N690" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O690" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y690" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="Z690" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321711121139</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321010534088</t>
         </is>
       </c>
     </row>
@@ -52041,27 +52041,27 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>320489731795</t>
-        </is>
-      </c>
-      <c r="C691" t="inlineStr">
-        <is>
-          <t>CR#: 2133336</t>
+          <t>324699843267</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>Technical Consultant</t>
+          <t>Microsoft 365 GCC Licensing Quote</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>NYS Division of Criminal Justice Services</t>
+          <t xml:space="preserve">New Mexico Finance Authority (“NMFA”) </t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
@@ -52071,20 +52071,20 @@
       </c>
       <c r="J691" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="K691" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="L691" s="65" t="n">
-        <v>49500</v>
+        <v>57658.61</v>
       </c>
       <c r="M691" t="inlineStr">
         <is>
-          <t>Consulting;Staff Augmentation</t>
+          <t>Reseller</t>
         </is>
       </c>
       <c r="N691" t="inlineStr">
@@ -52099,12 +52099,12 @@
       </c>
       <c r="Y691" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Z691" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320489731795</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/324699843267</t>
         </is>
       </c>
     </row>
@@ -52114,17 +52114,22 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>322527283932</t>
+          <t>321711121139</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>Test RFX (please ignore)</t>
+          <t>Information Technology Managed Services: IT Service Desk</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>Brunswick County</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
@@ -52132,29 +52137,42 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="L692" s="65" t="n">
+        <v>92560</v>
+      </c>
       <c r="M692" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N692" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O692" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
-        </is>
-      </c>
-      <c r="S692" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y692" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z692" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321711121139</t>
         </is>
       </c>
     </row>
@@ -52164,32 +52182,27 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>116977709771</t>
+          <t>320489731795</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>RFP-25-0005</t>
+          <t>CR#: 2133336</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
+          <t>Technical Consultant</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>NeighborWorks America</t>
-        </is>
-      </c>
-      <c r="F693" t="inlineStr">
-        <is>
-          <t>Washington, D.C.</t>
+          <t>NYS Division of Criminal Justice Services</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -52197,39 +52210,42 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="L693" s="65" t="n">
+        <v>49500</v>
+      </c>
       <c r="M693" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting;Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="N693" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O693" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
-        </is>
-      </c>
-      <c r="S693" t="inlineStr">
-        <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="U693" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y693" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="Z693" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
-        </is>
-      </c>
-      <c r="AA693" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320489731795</t>
         </is>
       </c>
     </row>
@@ -52239,27 +52255,17 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>145081112265</t>
+          <t>322527283932</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>Technology Strategic Management Consulting</t>
-        </is>
-      </c>
-      <c r="E694" t="inlineStr">
-        <is>
-          <t>State of Colorado, the Office of Information Technology (OIT)</t>
-        </is>
-      </c>
-      <c r="F694" t="inlineStr">
-        <is>
-          <t>Colorado</t>
+          <t>Test RFX (please ignore)</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
@@ -52267,29 +52273,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J694" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
       <c r="M694" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O694" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="S694" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y694" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z694" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
         </is>
       </c>
     </row>
@@ -52299,27 +52305,32 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>166098266830</t>
+          <t>116977709771</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>RFP-25-0005</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>Mecklenburg County</t>
+          <t>NeighborWorks America</t>
         </is>
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H695" t="inlineStr">
@@ -52327,29 +52338,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J695" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
       <c r="M695" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O695" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="S695" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="U695" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Y695" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z695" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+        </is>
+      </c>
+      <c r="AA695" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -52359,27 +52380,27 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>180166400720</t>
+          <t>145081112265</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
+          <t>Technology Strategic Management Consulting</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>Central Ohio Transit Authority</t>
+          <t>State of Colorado, the Office of Information Technology (OIT)</t>
         </is>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
@@ -52389,7 +52410,12 @@
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O696" t="inlineStr">
@@ -52399,12 +52425,12 @@
       </c>
       <c r="Y696" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z696" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
         </is>
       </c>
     </row>
@@ -52414,32 +52440,27 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>182404957915</t>
-        </is>
-      </c>
-      <c r="C697" t="inlineStr">
-        <is>
-          <t>PWE-10.08.2025</t>
+          <t>166098266830</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>PWE Power BI Dashboard</t>
+          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>City of Issaquah</t>
+          <t>Mecklenburg County</t>
         </is>
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
@@ -52449,27 +52470,27 @@
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="M697" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O697" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y697" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z697" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
         </is>
       </c>
     </row>
@@ -52479,27 +52500,22 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>108771177151</t>
-        </is>
-      </c>
-      <c r="C698" t="inlineStr">
-        <is>
-          <t>791202505005</t>
+          <t>180166400720</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>Government Consulting Services</t>
+          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>North Central Texas Council of Governments</t>
+          <t>Central Ohio Transit Authority</t>
         </is>
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>TEXAS</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
@@ -52514,12 +52530,7 @@
       </c>
       <c r="J698" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="N698" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="O698" t="inlineStr">
@@ -52529,12 +52540,12 @@
       </c>
       <c r="Y698" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="Z698" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
         </is>
       </c>
     </row>
@@ -52544,27 +52555,27 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>120893940416</t>
+          <t>182404957915</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>DQ SAAA #2026000004</t>
+          <t>PWE-10.08.2025</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>Online Content Learning</t>
+          <t>PWE Power BI Dashboard</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>State of Colorado Department of Regulatory Agencies</t>
+          <t>City of Issaquah</t>
         </is>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
@@ -52579,30 +52590,27 @@
       </c>
       <c r="J699" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L699" s="65" t="n">
-        <v>67300</v>
+          <t>2025-10-29</t>
+        </is>
       </c>
       <c r="M699" t="inlineStr">
         <is>
-          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O699" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y699" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Z699" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
         </is>
       </c>
     </row>
@@ -52612,27 +52620,32 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>199601365715</t>
+          <t>108771177151</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>791202505005</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Contracted IT Support Services</t>
+          <t>Government Consulting Services</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>ECS4Kids</t>
+          <t>North Central Texas Council of Governments</t>
         </is>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>TEXAS</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
@@ -52642,15 +52655,7 @@
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="L700" s="65" t="n">
-        <v>291141</v>
-      </c>
-      <c r="M700" t="inlineStr">
-        <is>
-          <t>Support &amp; Maintenance</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="N700" t="inlineStr">
@@ -52660,17 +52665,17 @@
       </c>
       <c r="O700" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y700" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="Z700" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
         </is>
       </c>
     </row>
@@ -52680,55 +52685,50 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>140123456196</t>
+          <t>120893940416</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>24-RFP-10</t>
+          <t>DQ SAAA #2026000004</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+          <t>Online Content Learning</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+          <t>State of Colorado Department of Regulatory Agencies</t>
         </is>
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I701" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J701" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="L701" s="65" t="n">
-        <v>18620</v>
+        <v>67300</v>
       </c>
       <c r="M701" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O701" t="inlineStr">
@@ -52736,44 +52736,14 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="P701" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q701" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="S701" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="U701" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="V701" t="inlineStr">
-        <is>
-          <t>In Process</t>
-        </is>
-      </c>
       <c r="Y701" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z701" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
-        </is>
-      </c>
-      <c r="AA701" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
         </is>
       </c>
     </row>
@@ -52783,27 +52753,27 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>261982669555</t>
+          <t>199601365715</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>IT Backfill for ERP Configuration (SOW 2)</t>
+          <t>Contracted IT Support Services</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>Madison Metropolitan Sewerage District</t>
+          <t>ECS4Kids</t>
         </is>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
@@ -52813,50 +52783,35 @@
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="L702" s="65" t="n">
-        <v>157000</v>
+        <v>291141</v>
       </c>
       <c r="M702" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N702" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O702" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="S702" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="U702" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="V702" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y702" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z702" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
-        </is>
-      </c>
-      <c r="AA702" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
         </is>
       </c>
     </row>
@@ -52866,62 +52821,100 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>278519751386</t>
+          <t>140123456196</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>24-RFP-10</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>Data Warehousing Services</t>
+          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allen Town School District </t>
+          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L703" s="65" t="n">
+        <v>18620</v>
       </c>
       <c r="M703" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N703" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O703" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P703" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q703" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="S703" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="U703" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="V703" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y703" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z703" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
+        </is>
+      </c>
+      <c r="AA703" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -52931,32 +52924,27 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>259790359234</t>
-        </is>
-      </c>
-      <c r="C704" t="inlineStr">
-        <is>
-          <t>601440000049523</t>
+          <t>261982669555</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>Managed Application Services: Application Development and Maintenance Services</t>
+          <t>IT Backfill for ERP Configuration (SOW 2)</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>Texas Department of Transportation</t>
+          <t>Madison Metropolitan Sewerage District</t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
@@ -52966,17 +52954,35 @@
       </c>
       <c r="J704" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
-        </is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="L704" s="65" t="n">
+        <v>157000</v>
       </c>
       <c r="M704" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O704" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S704" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="U704" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="V704" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y704" t="inlineStr">
@@ -52986,7 +52992,12 @@
       </c>
       <c r="Z704" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
+        </is>
+      </c>
+      <c r="AA704" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -52996,22 +53007,22 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>277652547262</t>
+          <t>278519751386</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
+          <t>Data Warehousing Services</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>District of Columbia Housing Finance Agency</t>
+          <t xml:space="preserve">Allen Town School District </t>
         </is>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
@@ -53026,12 +53037,12 @@
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="M705" t="inlineStr">
         <is>
-          <t>Consulting;Training</t>
+          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N705" t="inlineStr">
@@ -53046,12 +53057,12 @@
       </c>
       <c r="Y705" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Z705" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
         </is>
       </c>
     </row>
@@ -53061,27 +53072,32 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>269507522240</t>
+          <t>259790359234</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>601440000049523</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
+          <t>Managed Application Services: Application Development and Maintenance Services</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>Central Midlands Regional Transit Authority</t>
+          <t>Texas Department of Transportation</t>
         </is>
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
@@ -53091,27 +53107,27 @@
       </c>
       <c r="J706" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="M706" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O706" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y706" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z706" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
         </is>
       </c>
     </row>
@@ -53121,22 +53137,22 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>294055526085</t>
+          <t>277652547262</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>Oracle Managed Services and Testing as a Service Support</t>
+          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>CITY OF DURHAM</t>
+          <t>District of Columbia Housing Finance Agency</t>
         </is>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
@@ -53151,12 +53167,17 @@
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="M707" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Consulting;Training</t>
+        </is>
+      </c>
+      <c r="N707" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O707" t="inlineStr">
@@ -53166,12 +53187,12 @@
       </c>
       <c r="Y707" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Z707" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
         </is>
       </c>
     </row>
@@ -53181,22 +53202,22 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>305430641393</t>
+          <t>269507522240</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>OFF - Information Technology Managed Services</t>
+          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>County of Montcalm</t>
+          <t>Central Midlands Regional Transit Authority</t>
         </is>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
@@ -53211,7 +53232,7 @@
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="M708" t="inlineStr">
@@ -53221,17 +53242,17 @@
       </c>
       <c r="O708" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y708" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z708" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
         </is>
       </c>
     </row>
@@ -53241,17 +53262,22 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>311307032268</t>
+          <t>294055526085</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+          <t>Oracle Managed Services and Testing as a Service Support</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>Housing Authority of the City of Passaic</t>
+          <t>CITY OF DURHAM</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
@@ -53266,27 +53292,27 @@
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M709" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O709" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y709" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Z709" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
         </is>
       </c>
     </row>
@@ -53296,32 +53322,27 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>135161266908</t>
-        </is>
-      </c>
-      <c r="C710" t="inlineStr">
-        <is>
-          <t>RFQ1757840</t>
+          <t>305430641393</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>25-51-A-PMO-ES-SSN</t>
+          <t>OFF - Information Technology Managed Services</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>U.S. Department of the Treasury</t>
+          <t>County of Montcalm</t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
@@ -53331,27 +53352,27 @@
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="N710" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O710" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y710" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="Z710" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
         </is>
       </c>
     </row>
@@ -53361,17 +53382,22 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>110691507903</t>
+          <t>311307032268</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
+          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>Housing Authority of the City of Passaic</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
@@ -53381,25 +53407,27 @@
       </c>
       <c r="J711" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="L711" s="65" t="n">
-        <v>96200</v>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
       </c>
       <c r="O711" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y711" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Z711" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
         </is>
       </c>
     </row>
@@ -53409,12 +53437,27 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>110691507909</t>
+          <t>135161266908</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>RFQ1757840</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
+          <t>25-51-A-PMO-ES-SSN</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>U.S. Department of the Treasury</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -53429,7 +53472,12 @@
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="N712" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O712" t="inlineStr">
@@ -53439,12 +53487,12 @@
       </c>
       <c r="Y712" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z712" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
         </is>
       </c>
     </row>
@@ -53454,12 +53502,12 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>108771377911</t>
+          <t>110691507903</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>Facilities and Information Technology Infrastructure Assessment</t>
+          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -53477,6 +53525,9 @@
           <t>2026-03-31</t>
         </is>
       </c>
+      <c r="L713" s="65" t="n">
+        <v>96200</v>
+      </c>
       <c r="O713" t="inlineStr">
         <is>
           <t>Madhav Mitruka</t>
@@ -53489,7 +53540,7 @@
       </c>
       <c r="Z713" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
         </is>
       </c>
     </row>
@@ -53499,17 +53550,12 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>120893940419</t>
-        </is>
-      </c>
-      <c r="C714" t="inlineStr">
-        <is>
-          <t>#25-038-RFP)</t>
+          <t>110691507909</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
+          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -53527,24 +53573,19 @@
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="M714" t="inlineStr">
-        <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
-        </is>
-      </c>
       <c r="O714" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y714" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z714" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
         </is>
       </c>
     </row>
@@ -53554,12 +53595,12 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>114864654049</t>
+          <t>108771377911</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>M365 Tenant backup</t>
+          <t>Facilities and Information Technology Infrastructure Assessment</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -53579,17 +53620,17 @@
       </c>
       <c r="O715" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y715" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z715" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
         </is>
       </c>
     </row>
@@ -53599,27 +53640,22 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>317945474767</t>
+          <t>120893940419</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>#25-038-RFP)</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>ServiceNow Technical Services</t>
-        </is>
-      </c>
-      <c r="E716" t="inlineStr">
-        <is>
-          <t>City of Sacramento</t>
-        </is>
-      </c>
-      <c r="F716" t="inlineStr">
-        <is>
-          <t>California</t>
+          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
@@ -53629,22 +53665,27 @@
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O716" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="Y716" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z716" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
         </is>
       </c>
     </row>
@@ -53654,45 +53695,145 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
+          <t>114864654049</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>M365 Tenant backup</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O717" t="inlineStr">
+        <is>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="Y717" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z717" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="n">
+        <v>717</v>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>317945474767</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>ServiceNow Technical Services</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>City of Sacramento</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O718" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y718" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z718" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="n">
+        <v>718</v>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
           <t>317911067336</t>
         </is>
       </c>
-      <c r="D717" t="inlineStr">
+      <c r="D719" t="inlineStr">
         <is>
           <t>Enterprise Data Warehouse</t>
         </is>
       </c>
-      <c r="E717" t="inlineStr">
+      <c r="E719" t="inlineStr">
         <is>
           <t>Michigan Department of Technology Management and Budget</t>
         </is>
       </c>
-      <c r="G717" t="inlineStr">
+      <c r="G719" t="inlineStr">
         <is>
           <t>RFx Cancelled</t>
         </is>
       </c>
-      <c r="H717" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J717" t="inlineStr">
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J719" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="O717" t="inlineStr">
+      <c r="O719" t="inlineStr">
         <is>
           <t>Ashutosh Chauhan</t>
         </is>
       </c>
-      <c r="Y717" t="inlineStr">
+      <c r="Y719" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="Z717" t="inlineStr">
+      <c r="Z719" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
         </is>

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-05-12 06:32 EDT</t>
+          <t>2026-05-13 09:29 EDT</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA719"/>
+  <dimension ref="A1:AA724"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Colorado Avalanche Information Center ("CAIC")  (Department of Natural Resources)</t>
+          <t>Colorado Avalanche Information Center (“CAIC”)  (Department of Natural Resources)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -13674,12 +13674,17 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -13700,6 +13705,11 @@
       <c r="O153" t="inlineStr">
         <is>
           <t>Abhishek Zalani</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Y153" t="inlineStr">
@@ -25261,32 +25271,27 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>212696339180</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>AI02-26</t>
+          <t>225906283257</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>AI Consulting Services</t>
+          <t>Information Systems Consultant</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Houston-Galveston Area Council</t>
+          <t>Community Action Partnership of Kern</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -25296,22 +25301,25 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
           <t>2025-12-18</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
+      <c r="L316" s="65" t="n">
+        <v>100</v>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Consulting;Staff Augmentation</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O316" t="inlineStr">
@@ -25319,14 +25327,34 @@
           <t>Ashutosh Chauhan</t>
         </is>
       </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>Awarded</t>
+        </is>
+      </c>
       <c r="Y316" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/212696339180</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/225906283257</t>
+        </is>
+      </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -25336,27 +25364,27 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>225906283257</t>
+          <t>232557362897</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Information Systems Consultant</t>
+          <t>Incident Response Plan, Disaster Recovery Plan, and Business Continuity Plan</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Community Action Partnership of Kern</t>
+          <t>North Texas Municipal Water District (NTMWD)</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -25366,7 +25394,7 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -25374,52 +25402,29 @@
           <t>2025-12-18</t>
         </is>
       </c>
-      <c r="L317" s="65" t="n">
-        <v>100</v>
-      </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Consulting;Audits and Assessment</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal;Offline</t>
         </is>
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
-        </is>
-      </c>
-      <c r="S317" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
-      <c r="U317" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
-      <c r="V317" t="inlineStr">
-        <is>
-          <t>Awarded</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y317" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/225906283257</t>
-        </is>
-      </c>
-      <c r="AA317" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/232557362897</t>
         </is>
       </c>
     </row>
@@ -25429,17 +25434,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>232557362897</t>
+          <t>212696339180</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>AI02-26</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Incident Response Plan, Disaster Recovery Plan, and Business Continuity Plan</t>
+          <t>AI Consulting Services</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>North Texas Municipal Water District (NTMWD)</t>
+          <t>Houston-Galveston Area Council</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -25449,7 +25459,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -25459,7 +25469,7 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -25469,27 +25479,42 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Consulting;Audits and Assessment</t>
+          <t>Consulting;Staff Augmentation</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>Portal;Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="Y318" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/232557362897</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/212696339180</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -40731,7 +40756,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>ADMINISTRATION FOR CHILDREN'S SERVICES (ACS)</t>
+          <t>ADMINISTRATION FOR CHILDREN’S SERVICES (ACS)</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
@@ -44337,22 +44362,22 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>316973419240</t>
+          <t>292902372057</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>.Net Core Modernization</t>
+          <t>CMS Project Assistant 2026</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>California Housing Finance Agency (CalHFA)</t>
+          <t>NYS Office of Children &amp; Family Services [NY]</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
@@ -44375,12 +44400,9 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="L581" s="65" t="n">
-        <v>218800</v>
-      </c>
       <c r="M581" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="N581" t="inlineStr">
@@ -44390,17 +44412,17 @@
       </c>
       <c r="O581" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y581" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="Z581" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316973419240</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/292902372057</t>
         </is>
       </c>
     </row>
@@ -44410,27 +44432,27 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>292902372057</t>
+          <t>316973419240</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>CMS Project Assistant 2026</t>
+          <t>.Net Core Modernization</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>NYS Office of Children &amp; Family Services [NY]</t>
+          <t>California Housing Finance Agency (CalHFA)</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
@@ -44440,17 +44462,20 @@
       </c>
       <c r="J582" t="inlineStr">
         <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
+      <c r="L582" s="65" t="n">
+        <v>218800</v>
       </c>
       <c r="M582" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N582" t="inlineStr">
@@ -44460,17 +44485,17 @@
       </c>
       <c r="O582" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y582" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="Z582" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/292902372057</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316973419240</t>
         </is>
       </c>
     </row>
@@ -48230,22 +48255,22 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>317997672181</t>
+          <t>320115663606</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>SAP S/4 HANA SUPPORT SERVICES</t>
+          <t>1083617 SOFTWARE - SUBSCRIPTION - DISASTER RECOVERY</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>Charlottesville</t>
+          <t>LA County- Internal Services Department</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
@@ -48260,17 +48285,20 @@
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="K636" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="L636" s="65" t="n">
+        <v>744000</v>
       </c>
       <c r="M636" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Reseller</t>
         </is>
       </c>
       <c r="N636" t="inlineStr">
@@ -48280,17 +48308,17 @@
       </c>
       <c r="O636" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y636" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="Z636" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317997672181</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320115663606</t>
         </is>
       </c>
     </row>
@@ -48300,27 +48328,27 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>316198616795</t>
+          <t>317997672181</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>[Offline] Low-Code Application Development Services</t>
+          <t>SAP S/4 HANA SUPPORT SERVICES</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>Florida Department of Citrus (CIT) [FL]</t>
+          <t>Charlottesville</t>
         </is>
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -48330,7 +48358,7 @@
       </c>
       <c r="J637" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="K637" t="inlineStr">
@@ -48340,27 +48368,27 @@
       </c>
       <c r="M637" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance;Custom development</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N637" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O637" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y637" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z637" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316198616795</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317997672181</t>
         </is>
       </c>
     </row>
@@ -48370,27 +48398,27 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>317793033939</t>
+          <t>316198616795</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t xml:space="preserve">OFF - Computer Services </t>
+          <t>[Offline] Low-Code Application Development Services</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>Town of Islip Affordable Housing Corp (TOIAHC)</t>
+          <t>Florida Department of Citrus (CIT) [FL]</t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
@@ -48400,17 +48428,17 @@
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="K638" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="M638" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Support &amp; Maintenance;Custom development</t>
         </is>
       </c>
       <c r="N638" t="inlineStr">
@@ -48420,17 +48448,17 @@
       </c>
       <c r="O638" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y638" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="Z638" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317793033939</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316198616795</t>
         </is>
       </c>
     </row>
@@ -48440,27 +48468,27 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>323528390341</t>
+          <t>317793033939</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>IT MSP &amp; NOC NMFA Additional SOW</t>
+          <t xml:space="preserve">OFF - Computer Services </t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Mexico Finance Authority (“NMFA”) </t>
+          <t>Town of Islip Affordable Housing Corp (TOIAHC)</t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H639" t="inlineStr">
@@ -48470,7 +48498,7 @@
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="K639" t="inlineStr">
@@ -48483,24 +48511,24 @@
           <t>Managed Services (MSP)</t>
         </is>
       </c>
+      <c r="N639" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
       <c r="O639" t="inlineStr">
         <is>
           <t>Ashutosh Chauhan</t>
         </is>
       </c>
-      <c r="S639" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
       <c r="Y639" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z639" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323528390341</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317793033939</t>
         </is>
       </c>
     </row>
@@ -48510,27 +48538,27 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>316123953854</t>
+          <t>323528390341</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>Executive Search and General Staffing Services</t>
+          <t>IT MSP &amp; NOC NMFA Additional SOW</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>Santa Clara Valley Transportation Authority</t>
+          <t xml:space="preserve">New Mexico Finance Authority (“NMFA”) </t>
         </is>
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H640" t="inlineStr">
@@ -48540,22 +48568,17 @@
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="K640" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="M640" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
-        </is>
-      </c>
-      <c r="N640" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O640" t="inlineStr">
@@ -48563,14 +48586,19 @@
           <t>Ashutosh Chauhan</t>
         </is>
       </c>
+      <c r="S640" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
       <c r="Y640" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Z640" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316123953854</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323528390341</t>
         </is>
       </c>
     </row>
@@ -48580,22 +48608,22 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>316972808892</t>
+          <t>316123953854</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>Bridges Library System Mobile App</t>
+          <t>Executive Search and General Staffing Services</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>Waukesha County</t>
+          <t>Santa Clara Valley Transportation Authority</t>
         </is>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G641" t="inlineStr">
@@ -48618,12 +48646,9 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="L641" s="65" t="n">
-        <v>360200</v>
-      </c>
       <c r="M641" t="inlineStr">
         <is>
-          <t>Custom development</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="N641" t="inlineStr">
@@ -48633,17 +48658,17 @@
       </c>
       <c r="O641" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y641" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="Z641" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316972808892</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316123953854</t>
         </is>
       </c>
     </row>
@@ -48653,27 +48678,22 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>317946904258</t>
-        </is>
-      </c>
-      <c r="C642" t="inlineStr">
-        <is>
-          <t>25-0245-IT</t>
+          <t>316972808892</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>Information Security Governance &amp; Policy Framework Development</t>
+          <t>Bridges Library System Mobile App</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>City of Florissant</t>
+          <t>Waukesha County</t>
         </is>
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
@@ -48697,7 +48717,12 @@
         </is>
       </c>
       <c r="L642" s="65" t="n">
-        <v>52560</v>
+        <v>360200</v>
+      </c>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>Custom development</t>
+        </is>
       </c>
       <c r="N642" t="inlineStr">
         <is>
@@ -48706,22 +48731,17 @@
       </c>
       <c r="O642" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y642" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="Z642" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317946904258</t>
-        </is>
-      </c>
-      <c r="AA642" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316972808892</t>
         </is>
       </c>
     </row>
@@ -48731,22 +48751,27 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>320043417335</t>
+          <t>317946904258</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>25-0245-IT</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>MICROSOFT OFFICE COMPUTER TRAININGS</t>
+          <t>Information Security Governance &amp; Policy Framework Development</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>COUNTY OF LOS ANGELES DEPARTMENT OF HUMAN RESOURCES</t>
+          <t>City of Florissant</t>
         </is>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
@@ -48769,10 +48794,8 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="M643" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
+      <c r="L643" s="65" t="n">
+        <v>52560</v>
       </c>
       <c r="N643" t="inlineStr">
         <is>
@@ -48781,17 +48804,22 @@
       </c>
       <c r="O643" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y643" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z643" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320043417335</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317946904258</t>
+        </is>
+      </c>
+      <c r="AA643" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -48801,22 +48829,22 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>316626212560</t>
+          <t>320043417335</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SERVICES</t>
+          <t>MICROSOFT OFFICE COMPUTER TRAININGS</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Town of Irmo</t>
+          <t>COUNTY OF LOS ANGELES DEPARTMENT OF HUMAN RESOURCES</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
@@ -48831,7 +48859,7 @@
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="K644" t="inlineStr">
@@ -48839,32 +48867,29 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="L644" s="65" t="n">
-        <v>405880</v>
-      </c>
       <c r="M644" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="N644" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O644" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y644" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z644" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316626212560</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320043417335</t>
         </is>
       </c>
     </row>
@@ -48874,27 +48899,22 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>320489741047</t>
-        </is>
-      </c>
-      <c r="C645" t="inlineStr">
-        <is>
-          <t>RFQ #: 26-026-TK</t>
+          <t>316626212560</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>Community Health Assessment &amp; Improvements Plan for Data Dashboard</t>
+          <t>INFORMATION TECHNOLOGY SERVICES</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Kane County Health Department</t>
+          <t>Town of Irmo</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
@@ -48914,35 +48934,35 @@
       </c>
       <c r="K645" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="L645" s="65" t="n">
-        <v>121930</v>
+        <v>405880</v>
       </c>
       <c r="M645" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N645" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O645" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y645" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="Z645" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320489741047</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316626212560</t>
         </is>
       </c>
     </row>
@@ -48952,22 +48972,27 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>319181385439</t>
+          <t>320489741047</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>RFQ #: 26-026-TK</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>IT Managed Services</t>
+          <t>Community Health Assessment &amp; Improvements Plan for Data Dashboard</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>Emerald Coast Regional Council</t>
+          <t>Kane County Health Department</t>
         </is>
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
@@ -48990,24 +49015,32 @@
           <t>2026-04-24</t>
         </is>
       </c>
+      <c r="L646" s="65" t="n">
+        <v>121930</v>
+      </c>
       <c r="M646" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N646" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O646" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y646" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="Z646" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319181385439</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320489741047</t>
         </is>
       </c>
     </row>
@@ -49017,22 +49050,22 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>317828186810</t>
+          <t>319181385439</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>Cybersecurity Risk Assessment for Information Security</t>
+          <t>IT Managed Services</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>The Administrative Office of the Courts (AOC)</t>
+          <t>Emerald Coast Regional Council</t>
         </is>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
@@ -49055,17 +49088,9 @@
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="L647" s="65" t="n">
-        <v>85000</v>
-      </c>
       <c r="M647" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
-        </is>
-      </c>
-      <c r="N647" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O647" t="inlineStr">
@@ -49075,12 +49100,12 @@
       </c>
       <c r="Y647" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="Z647" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317828186810</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319181385439</t>
         </is>
       </c>
     </row>
@@ -49090,22 +49115,22 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>317166061283</t>
+          <t>317828186810</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t xml:space="preserve">Request for Proposals Cybersecurity Assessment and Plan </t>
+          <t>Cybersecurity Risk Assessment for Information Security</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>Pueblo of Laguna</t>
+          <t>The Administrative Office of the Courts (AOC)</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
@@ -49128,9 +49153,17 @@
           <t>2026-04-24</t>
         </is>
       </c>
+      <c r="L648" s="65" t="n">
+        <v>85000</v>
+      </c>
       <c r="M648" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Audits and Assessment</t>
+        </is>
+      </c>
+      <c r="N648" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O648" t="inlineStr">
@@ -49140,12 +49173,12 @@
       </c>
       <c r="Y648" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z648" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317166061283</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317828186810</t>
         </is>
       </c>
     </row>
@@ -49155,22 +49188,22 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>317793033962</t>
+          <t>317166061283</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>PeopleSoft Update Manager</t>
+          <t xml:space="preserve">Request for Proposals Cybersecurity Assessment and Plan </t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>City and County of San Francisco</t>
+          <t>Pueblo of Laguna</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
@@ -49195,12 +49228,7 @@
       </c>
       <c r="M649" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
-        </is>
-      </c>
-      <c r="N649" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O649" t="inlineStr">
@@ -49210,12 +49238,12 @@
       </c>
       <c r="Y649" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="Z649" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317793033962</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317166061283</t>
         </is>
       </c>
     </row>
@@ -49225,22 +49253,22 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>294210815704</t>
+          <t>317793033962</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>offline Information Technology Services</t>
+          <t>PeopleSoft Update Manager</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>Danville Redevelopment and Housing Authority</t>
+          <t>City and County of San Francisco</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
@@ -49255,7 +49283,7 @@
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="K650" t="inlineStr">
@@ -49265,22 +49293,27 @@
       </c>
       <c r="M650" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Modernization / Migration</t>
+        </is>
+      </c>
+      <c r="N650" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O650" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y650" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z650" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294210815704</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317793033962</t>
         </is>
       </c>
     </row>
@@ -49290,22 +49323,22 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>323231785701</t>
+          <t>294210815704</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t xml:space="preserve">FMLA Case Management System </t>
+          <t>offline Information Technology Services</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>Tennessee Department of Human Resources</t>
+          <t>Danville Redevelopment and Housing Authority</t>
         </is>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
@@ -49320,7 +49353,7 @@
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="K651" t="inlineStr">
@@ -49330,7 +49363,7 @@
       </c>
       <c r="M651" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs);Consulting;Training</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O651" t="inlineStr">
@@ -49340,12 +49373,12 @@
       </c>
       <c r="Y651" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="Z651" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323231785701</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294210815704</t>
         </is>
       </c>
     </row>
@@ -49355,27 +49388,27 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>321691657937</t>
+          <t>323231785701</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>Technology Support Services</t>
+          <t xml:space="preserve">FMLA Case Management System </t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkway Schools </t>
+          <t>Tennessee Department of Human Resources</t>
         </is>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
@@ -49385,7 +49418,7 @@
       </c>
       <c r="J652" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="K652" t="inlineStr">
@@ -49395,7 +49428,7 @@
       </c>
       <c r="M652" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Platform Implementation (ERP, CRMs);Consulting;Training</t>
         </is>
       </c>
       <c r="O652" t="inlineStr">
@@ -49405,12 +49438,12 @@
       </c>
       <c r="Y652" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z652" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321691657937</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323231785701</t>
         </is>
       </c>
     </row>
@@ -49420,27 +49453,27 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>319924556489</t>
+          <t>321691657937</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>Network Security Audit and Vulnerability Assessment</t>
+          <t>Technology Support Services</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Regional Commission </t>
+          <t xml:space="preserve">Parkway Schools </t>
         </is>
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
@@ -49450,32 +49483,32 @@
       </c>
       <c r="J653" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="K653" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="M653" t="inlineStr">
         <is>
-          <t>Consulting;Audits and Assessment</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O653" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y653" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z653" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319924556489</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321691657937</t>
         </is>
       </c>
     </row>
@@ -49485,22 +49518,22 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>318902943445</t>
+          <t>319924556489</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>Technology Consultant for the Production Tracking System (PTS)</t>
+          <t>Network Security Audit and Vulnerability Assessment</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>Massachusetts Clean Energy Center (MassCEC)</t>
+          <t xml:space="preserve">Atlanta Regional Commission </t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
@@ -49523,32 +49556,24 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="L654" s="65" t="n">
-        <v>732660</v>
-      </c>
       <c r="M654" t="inlineStr">
         <is>
-          <t>Consulting</t>
-        </is>
-      </c>
-      <c r="N654" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Consulting;Audits and Assessment</t>
         </is>
       </c>
       <c r="O654" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y654" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z654" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318902943445</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319924556489</t>
         </is>
       </c>
     </row>
@@ -49558,22 +49583,22 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>321924670199</t>
+          <t>318902943445</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>Management. Applications Development</t>
+          <t>Technology Consultant for the Production Tracking System (PTS)</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>Florida Department of Health</t>
+          <t>Massachusetts Clean Energy Center (MassCEC)</t>
         </is>
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
@@ -49596,9 +49621,17 @@
           <t>2026-04-27</t>
         </is>
       </c>
+      <c r="L655" s="65" t="n">
+        <v>732660</v>
+      </c>
       <c r="M655" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N655" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O655" t="inlineStr">
@@ -49608,17 +49641,12 @@
       </c>
       <c r="Y655" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z655" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321924670199</t>
-        </is>
-      </c>
-      <c r="AA655" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318902943445</t>
         </is>
       </c>
     </row>
@@ -49628,22 +49656,22 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>314835484352</t>
+          <t>321924670199</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professional Managed Services </t>
+          <t>Management. Applications Development</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t xml:space="preserve">City of Virginia Beach </t>
+          <t>Florida Department of Health</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
@@ -49658,7 +49686,7 @@
       </c>
       <c r="J656" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="K656" t="inlineStr">
@@ -49668,22 +49696,27 @@
       </c>
       <c r="M656" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O656" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y656" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Z656" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/314835484352</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321924670199</t>
+        </is>
+      </c>
+      <c r="AA656" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -49693,22 +49726,22 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>318654617301</t>
+          <t>314835484352</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>GRANT: Artificial Intelligence (AI) to Accelerate Charitable Giving</t>
+          <t xml:space="preserve">Professional Managed Services </t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t xml:space="preserve">City of Virginia Beach </t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
@@ -49733,22 +49766,22 @@
       </c>
       <c r="M657" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O657" t="inlineStr">
         <is>
-          <t>Srikrishnadeva D</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y657" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="Z657" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318654617301</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/314835484352</t>
         </is>
       </c>
     </row>
@@ -49758,27 +49791,27 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>320213008064</t>
+          <t>318654617301</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>ONLINE WEB-BASED TRAINING</t>
+          <t>GRANT: Artificial Intelligence (AI) to Accelerate Charitable Giving</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>Alaska Department of Administration</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -49788,7 +49821,7 @@
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="K658" t="inlineStr">
@@ -49796,37 +49829,24 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="L658" s="65" t="n">
-        <v>37800</v>
-      </c>
       <c r="M658" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O658" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
-        </is>
-      </c>
-      <c r="S658" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
+          <t>Srikrishnadeva D</t>
         </is>
       </c>
       <c r="Y658" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="Z658" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320213008064</t>
-        </is>
-      </c>
-      <c r="AA658" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318654617301</t>
         </is>
       </c>
     </row>
@@ -49836,27 +49856,27 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>318905090784</t>
+          <t>320213008064</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>Information Technology Consulting Services</t>
+          <t>ONLINE WEB-BASED TRAINING</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>City of Coronado</t>
+          <t>Alaska Department of Administration</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Alaska</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -49866,17 +49886,20 @@
       </c>
       <c r="J659" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="K659" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="L659" s="65" t="n">
+        <v>37800</v>
       </c>
       <c r="M659" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O659" t="inlineStr">
@@ -49884,14 +49907,24 @@
           <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
+      <c r="S659" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
       <c r="Y659" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="Z659" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318905090784</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320213008064</t>
+        </is>
+      </c>
+      <c r="AA659" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -49901,22 +49934,22 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>318930494184</t>
+          <t>318905090784</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>OFF - ERP Consultant</t>
+          <t>Information Technology Consulting Services</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>City of Westfield Gas and Electrics</t>
+          <t>City of Coronado</t>
         </is>
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>Massachussets</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
@@ -49941,12 +49974,12 @@
       </c>
       <c r="M660" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O660" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y660" t="inlineStr">
@@ -49956,7 +49989,7 @@
       </c>
       <c r="Z660" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318930494184</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318905090784</t>
         </is>
       </c>
     </row>
@@ -49966,22 +49999,22 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>319925999318</t>
+          <t>318930494184</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>OFFLINE Information Technology Services, Including Cybersecurity</t>
+          <t>OFF - ERP Consultant</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>Haddon Heights Borough</t>
+          <t>City of Westfield Gas and Electrics</t>
         </is>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>Massachussets</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
@@ -49996,32 +50029,32 @@
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="K661" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="M661" t="inlineStr">
         <is>
-          <t>Managed Services (MSP);Consulting</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O661" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y661" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z661" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319925999318</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318930494184</t>
         </is>
       </c>
     </row>
@@ -50031,17 +50064,17 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>320536008419</t>
+          <t>319925999318</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY AND COMPUTER CONSULTING SERVICES FOR COMPUTERS, PROGRAMS AND PERIPHERAL COMPUTER EQUIPMENT THROUGHOUT THE DEPARTMENTS OF THE BOROUGH OF MIDDLESEX</t>
+          <t>OFFLINE Information Technology Services, Including Cybersecurity</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>Borough of Middlesex</t>
+          <t>Haddon Heights Borough</t>
         </is>
       </c>
       <c r="F662" t="inlineStr">
@@ -50069,32 +50102,24 @@
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="L662" s="65" t="n">
-        <v>135360</v>
-      </c>
       <c r="M662" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N662" t="inlineStr">
-        <is>
-          <t>Offline</t>
+          <t>Managed Services (MSP);Consulting</t>
         </is>
       </c>
       <c r="O662" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y662" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z662" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320536008419</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319925999318</t>
         </is>
       </c>
     </row>
@@ -50104,22 +50129,22 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>319104964317</t>
+          <t>320536008419</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration from On-Premises Microsoft CRM to Microsoft Dynamics 365 Cloud </t>
+          <t>INFORMATION TECHNOLOGY AND COMPUTER CONSULTING SERVICES FOR COMPUTERS, PROGRAMS AND PERIPHERAL COMPUTER EQUIPMENT THROUGHOUT THE DEPARTMENTS OF THE BOROUGH OF MIDDLESEX</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>Energy Trust of Oregon</t>
+          <t>Borough of Middlesex</t>
         </is>
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
@@ -50143,16 +50168,16 @@
         </is>
       </c>
       <c r="L663" s="65" t="n">
-        <v>1189350</v>
+        <v>135360</v>
       </c>
       <c r="M663" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N663" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O663" t="inlineStr">
@@ -50162,17 +50187,12 @@
       </c>
       <c r="Y663" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z663" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319104964317</t>
-        </is>
-      </c>
-      <c r="AA663" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320536008419</t>
         </is>
       </c>
     </row>
@@ -50182,22 +50202,22 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>319925999345</t>
+          <t>319104964317</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>REQUEST FOR QUALIFICATIONS FOR INFORMATION TECHNOLOGY STRATEGIC CONSULTING SERVICES</t>
+          <t xml:space="preserve">Migration from On-Premises Microsoft CRM to Microsoft Dynamics 365 Cloud </t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>Susquehanna River Basin Commission (SRBC)</t>
+          <t>Energy Trust of Oregon</t>
         </is>
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>Pennsylvania, New York, Maryland</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
@@ -50220,24 +50240,37 @@
           <t>2026-04-29</t>
         </is>
       </c>
+      <c r="L664" s="65" t="n">
+        <v>1189350</v>
+      </c>
       <c r="M664" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Modernization / Migration</t>
+        </is>
+      </c>
+      <c r="N664" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O664" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y664" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z664" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319925999345</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319104964317</t>
+        </is>
+      </c>
+      <c r="AA664" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -50247,22 +50280,22 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>320623193837</t>
+          <t>319925999345</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>offline RFP IT SUPPORT SERVICES FOR SCCDA</t>
+          <t>REQUEST FOR QUALIFICATIONS FOR INFORMATION TECHNOLOGY STRATEGIC CONSULTING SERVICES</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>City of Quincy</t>
+          <t>Susquehanna River Basin Commission (SRBC)</t>
         </is>
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Pennsylvania, New York, Maryland</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
@@ -50277,7 +50310,7 @@
       </c>
       <c r="J665" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="K665" t="inlineStr">
@@ -50287,7 +50320,7 @@
       </c>
       <c r="M665" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O665" t="inlineStr">
@@ -50297,12 +50330,12 @@
       </c>
       <c r="Y665" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z665" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320623193837</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319925999345</t>
         </is>
       </c>
     </row>
@@ -50312,22 +50345,22 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>322269405882</t>
+          <t>320623193837</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>2026 Veeam License Renewal</t>
+          <t>offline RFP IT SUPPORT SERVICES FOR SCCDA</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>Village of Schaumburg</t>
+          <t>City of Quincy</t>
         </is>
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
@@ -50342,7 +50375,7 @@
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="K666" t="inlineStr">
@@ -50350,27 +50383,24 @@
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="L666" s="65" t="n">
-        <v>54186.88</v>
-      </c>
-      <c r="N666" t="inlineStr">
-        <is>
-          <t>Portal</t>
+      <c r="M666" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O666" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y666" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z666" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322269405882</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320623193837</t>
         </is>
       </c>
     </row>
@@ -50380,27 +50410,22 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>319926717149</t>
-        </is>
-      </c>
-      <c r="C667" t="inlineStr">
-        <is>
-          <t>COW2026-02</t>
+          <t>322269405882</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>Information Technology and GIS Support Services</t>
+          <t>2026 Veeam License Renewal</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>City of Wildomar</t>
+          <t>Village of Schaumburg</t>
         </is>
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
@@ -50415,21 +50440,16 @@
       </c>
       <c r="J667" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="K667" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L667" s="65" t="n">
-        <v>210000</v>
-      </c>
-      <c r="M667" t="inlineStr">
-        <is>
-          <t>Consulting;Staff Augmentation;Audits and Assessment</t>
-        </is>
+        <v>54186.88</v>
       </c>
       <c r="N667" t="inlineStr">
         <is>
@@ -50438,17 +50458,17 @@
       </c>
       <c r="O667" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y667" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z667" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319926717149</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322269405882</t>
         </is>
       </c>
     </row>
@@ -50458,27 +50478,27 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>320834566889</t>
+          <t>319926717149</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>2026-002 REBID</t>
+          <t>COW2026-02</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>MICROSOFT DYNAMICS GP MIGRATION TO BUSINESS CENTRAL 365</t>
+          <t>Information Technology and GIS Support Services</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>Detroit Wayne Integrated Health Network</t>
+          <t>City of Wildomar</t>
         </is>
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
@@ -50502,11 +50522,11 @@
         </is>
       </c>
       <c r="L668" s="65" t="n">
-        <v>135830</v>
+        <v>210000</v>
       </c>
       <c r="M668" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Consulting;Staff Augmentation;Audits and Assessment</t>
         </is>
       </c>
       <c r="N668" t="inlineStr">
@@ -50521,12 +50541,12 @@
       </c>
       <c r="Y668" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z668" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320834566889</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319926717149</t>
         </is>
       </c>
     </row>
@@ -50536,22 +50556,27 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>323231105770</t>
+          <t>320834566889</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>2026-002 REBID</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>Consulting and Professional Services Master Agreement (CAPSMA)</t>
+          <t>MICROSOFT DYNAMICS GP MIGRATION TO BUSINESS CENTRAL 365</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>Los Angeles County - Board of Supervisors</t>
+          <t>Detroit Wayne Integrated Health Network</t>
         </is>
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
@@ -50574,29 +50599,32 @@
           <t>2026-04-30</t>
         </is>
       </c>
+      <c r="L669" s="65" t="n">
+        <v>135830</v>
+      </c>
       <c r="M669" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="N669" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O669" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y669" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z669" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323231105770</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320834566889</t>
         </is>
       </c>
     </row>
@@ -50606,12 +50634,12 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>318930495177</t>
+          <t>323231105770</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>Request for Services (RFS) for Consulting Services to Enhance Education Information Sharing Processes and Data Systems for Systems-Involved Youth</t>
+          <t>Consulting and Professional Services Master Agreement (CAPSMA)</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
@@ -50661,12 +50689,12 @@
       </c>
       <c r="Y670" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z670" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318930495177</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323231105770</t>
         </is>
       </c>
     </row>
@@ -50676,22 +50704,22 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>319925282512</t>
+          <t>318930495177</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>MANAGED SERVICE PROVIDER (MSP)</t>
+          <t>Request for Services (RFS) for Consulting Services to Enhance Education Information Sharing Processes and Data Systems for Systems-Involved Youth</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>Freire Schools</t>
+          <t>Los Angeles County - Board of Supervisors</t>
         </is>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
@@ -50706,7 +50734,7 @@
       </c>
       <c r="J671" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="K671" t="inlineStr">
@@ -50714,12 +50742,14 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="L671" s="65" t="n">
-        <v>199960</v>
-      </c>
       <c r="M671" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N671" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O671" t="inlineStr">
@@ -50729,12 +50759,12 @@
       </c>
       <c r="Y671" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z671" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319925282512</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318930495177</t>
         </is>
       </c>
     </row>
@@ -50744,22 +50774,22 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>321688802026</t>
+          <t>319925282512</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>(Offline) RFP ACCOUNTING &amp; HUMAN RESOURCES ERP SYSTEM</t>
+          <t>MANAGED SERVICE PROVIDER (MSP)</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>NORMANDY SCHOOLS COLLABORATIVE</t>
+          <t>Freire Schools</t>
         </is>
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
@@ -50782,24 +50812,27 @@
           <t>2026-04-30</t>
         </is>
       </c>
+      <c r="L672" s="65" t="n">
+        <v>199960</v>
+      </c>
       <c r="M672" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O672" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y672" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z672" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321688802026</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319925282512</t>
         </is>
       </c>
     </row>
@@ -50809,22 +50842,22 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>318905084658</t>
+          <t>321688802026</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>On-Call As-Needed Temporary Information Technology Staffing Services</t>
+          <t>(Offline) RFP ACCOUNTING &amp; HUMAN RESOURCES ERP SYSTEM</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>East Bay Municipal Utility District</t>
+          <t>NORMANDY SCHOOLS COLLABORATIVE</t>
         </is>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
@@ -50849,7 +50882,7 @@
       </c>
       <c r="M673" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O673" t="inlineStr">
@@ -50859,12 +50892,12 @@
       </c>
       <c r="Y673" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z673" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318905084658</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321688802026</t>
         </is>
       </c>
     </row>
@@ -50874,17 +50907,17 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>323230348993</t>
+          <t>318905084658</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>Computerized Maintenance Management System</t>
+          <t>On-Call As-Needed Temporary Information Technology Staffing Services</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>University of California</t>
+          <t>East Bay Municipal Utility District</t>
         </is>
       </c>
       <c r="F674" t="inlineStr">
@@ -50904,7 +50937,7 @@
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="K674" t="inlineStr">
@@ -50914,7 +50947,7 @@
       </c>
       <c r="M674" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O674" t="inlineStr">
@@ -50924,12 +50957,12 @@
       </c>
       <c r="Y674" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z674" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323230348993</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318905084658</t>
         </is>
       </c>
     </row>
@@ -50939,22 +50972,22 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>321190312662</t>
+          <t>323230348993</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t xml:space="preserve">On-Call Data Modernization and Analytics Consulting Services </t>
+          <t>Computerized Maintenance Management System</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>Seattle Public Utilities (SPU)</t>
+          <t>University of California</t>
         </is>
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
@@ -50969,7 +51002,7 @@
       </c>
       <c r="J675" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="K675" t="inlineStr">
@@ -50979,7 +51012,7 @@
       </c>
       <c r="M675" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O675" t="inlineStr">
@@ -50989,12 +51022,12 @@
       </c>
       <c r="Y675" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z675" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321190312662</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323230348993</t>
         </is>
       </c>
     </row>
@@ -51004,22 +51037,22 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>320835245763</t>
+          <t>321190312662</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>SECURITY OPERATIONS CENTER SOLUTION</t>
+          <t xml:space="preserve">On-Call Data Modernization and Analytics Consulting Services </t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>NEW YORK eHEALTH COLLABORATIVE</t>
+          <t>Seattle Public Utilities (SPU)</t>
         </is>
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
@@ -51034,40 +51067,32 @@
       </c>
       <c r="J676" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="K676" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="L676" s="65" t="n">
-        <v>528000</v>
+          <t>2026-04-30</t>
+        </is>
       </c>
       <c r="M676" t="inlineStr">
         <is>
-          <t>Audits and Assessment;Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N676" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O676" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y676" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="Z676" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320835245763</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321190312662</t>
         </is>
       </c>
     </row>
@@ -51077,17 +51102,22 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>321688803002</t>
+          <t>320835245763</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>IMRF IFB - 2026 Penetration Testing and Red Teaming Services</t>
+          <t>SECURITY OPERATIONS CENTER SOLUTION</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>ILLINOIS MUNICIPAL RETIREMENT FUND</t>
+          <t>NEW YORK eHEALTH COLLABORATIVE</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>New York</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
@@ -51111,11 +51141,11 @@
         </is>
       </c>
       <c r="L677" s="65" t="n">
-        <v>142500</v>
+        <v>528000</v>
       </c>
       <c r="M677" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Audits and Assessment;Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N677" t="inlineStr">
@@ -51130,12 +51160,12 @@
       </c>
       <c r="Y677" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z677" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321688803002</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320835245763</t>
         </is>
       </c>
     </row>
@@ -51145,27 +51175,17 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>275293787895</t>
-        </is>
-      </c>
-      <c r="C678" t="inlineStr">
-        <is>
-          <t># 26-10</t>
+          <t>321688803002</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>OFF-Digital Transformation Products and Services</t>
+          <t>IMRF IFB - 2026 Penetration Testing and Red Teaming Services</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>Upper Occoquan Service Authority</t>
-        </is>
-      </c>
-      <c r="F678" t="inlineStr">
-        <is>
-          <t>Virginia</t>
+          <t>ILLINOIS MUNICIPAL RETIREMENT FUND</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
@@ -51188,9 +51208,17 @@
           <t>2026-05-01</t>
         </is>
       </c>
+      <c r="L678" s="65" t="n">
+        <v>142500</v>
+      </c>
       <c r="M678" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Audits and Assessment</t>
+        </is>
+      </c>
+      <c r="N678" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O678" t="inlineStr">
@@ -51200,12 +51228,12 @@
       </c>
       <c r="Y678" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z678" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/275293787895</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321688803002</t>
         </is>
       </c>
     </row>
@@ -51215,22 +51243,27 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>316930943726</t>
+          <t>275293787895</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t># 26-10</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>OFF: INFORMATION TECHNOLOGY SERVICES</t>
+          <t>OFF-Digital Transformation Products and Services</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>MetroWest Regional Transit Authority</t>
+          <t>Upper Occoquan Service Authority</t>
         </is>
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
@@ -51255,12 +51288,7 @@
       </c>
       <c r="M679" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N679" t="inlineStr">
-        <is>
-          <t>Offline</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O679" t="inlineStr">
@@ -51270,12 +51298,12 @@
       </c>
       <c r="Y679" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Z679" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316930943726</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/275293787895</t>
         </is>
       </c>
     </row>
@@ -51285,22 +51313,22 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>320837491424</t>
+          <t>316930943726</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>Cybersecurity Assessment</t>
+          <t>OFF: INFORMATION TECHNOLOGY SERVICES</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t xml:space="preserve">City of Big Rapids </t>
+          <t>MetroWest Regional Transit Authority</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
@@ -51315,20 +51343,22 @@
       </c>
       <c r="J680" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="K680" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="L680" s="65" t="n">
-        <v>10000</v>
+          <t>2026-05-01</t>
+        </is>
       </c>
       <c r="M680" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N680" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O680" t="inlineStr">
@@ -51338,12 +51368,12 @@
       </c>
       <c r="Y680" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="Z680" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320837491424</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316930943726</t>
         </is>
       </c>
     </row>
@@ -51353,22 +51383,22 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>321691656932</t>
+          <t>320837491424</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>IT Services' Contract</t>
+          <t>Cybersecurity Assessment</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holt County- Sheriffs Office </t>
+          <t xml:space="preserve">City of Big Rapids </t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
@@ -51392,26 +51422,26 @@
         </is>
       </c>
       <c r="L681" s="65" t="n">
-        <v>87900</v>
+        <v>10000</v>
       </c>
       <c r="M681" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O681" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y681" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="Z681" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321691656932</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320837491424</t>
         </is>
       </c>
     </row>
@@ -51421,17 +51451,17 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>319177778875</t>
+          <t>321691656932</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>SAP BTP &amp; Integration Suite Implementation</t>
+          <t>IT Services' Contract</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>Lincoln Electric System</t>
+          <t xml:space="preserve">Holt County- Sheriffs Office </t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
@@ -51451,7 +51481,7 @@
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="K682" t="inlineStr">
@@ -51460,16 +51490,11 @@
         </is>
       </c>
       <c r="L682" s="65" t="n">
-        <v>124320</v>
+        <v>87900</v>
       </c>
       <c r="M682" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
-        </is>
-      </c>
-      <c r="N682" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O682" t="inlineStr">
@@ -51479,12 +51504,12 @@
       </c>
       <c r="Y682" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z682" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319177778875</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321691656932</t>
         </is>
       </c>
     </row>
@@ -51494,22 +51519,22 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>321911416540</t>
+          <t>319177778875</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>IT Infrastructure and Related Services</t>
+          <t>SAP BTP &amp; Integration Suite Implementation</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>City of Odonnell</t>
+          <t>Lincoln Electric System</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
@@ -51529,27 +51554,35 @@
       </c>
       <c r="K683" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
-        </is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="L683" s="65" t="n">
+        <v>124320</v>
       </c>
       <c r="M683" t="inlineStr">
         <is>
-          <t>Consulting;Staff Augmentation</t>
+          <t>Modernization / Migration</t>
+        </is>
+      </c>
+      <c r="N683" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O683" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y683" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="Z683" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321911416540</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319177778875</t>
         </is>
       </c>
     </row>
@@ -51559,22 +51592,22 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>321765371610</t>
+          <t>321911416540</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>ServiceNow Professional Services</t>
+          <t>IT Infrastructure and Related Services</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>City of Sacramento</t>
+          <t>City of Odonnell</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
@@ -51589,37 +51622,32 @@
       </c>
       <c r="J684" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="K684" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="M684" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
-        </is>
-      </c>
-      <c r="N684" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Consulting;Staff Augmentation</t>
         </is>
       </c>
       <c r="O684" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y684" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Z684" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765371610</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321911416540</t>
         </is>
       </c>
     </row>
@@ -51629,22 +51657,22 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>320114224857</t>
+          <t>321765371610</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>Microsoft 365/Azure Security Policiies</t>
+          <t>ServiceNow Professional Services</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>Stark Metropolitan Housing Authority</t>
+          <t>City of Sacramento</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
@@ -51667,8 +51695,15 @@
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="L685" s="65" t="n">
-        <v>14000</v>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="N685" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
       </c>
       <c r="O685" t="inlineStr">
         <is>
@@ -51677,12 +51712,12 @@
       </c>
       <c r="Y685" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z685" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320114224857</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765371610</t>
         </is>
       </c>
     </row>
@@ -51692,22 +51727,22 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>321905742529</t>
+          <t>320114224857</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>Dynamics CRM Migration Support, Portal Development, &amp; Train-the-Trainer</t>
+          <t>Microsoft 365/Azure Security Policiies</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>Governor's Office of Business and Economic Development (GO-Biz)</t>
+          <t>Stark Metropolitan Housing Authority</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
@@ -51731,31 +51766,21 @@
         </is>
       </c>
       <c r="L686" s="65" t="n">
-        <v>173290</v>
-      </c>
-      <c r="M686" t="inlineStr">
-        <is>
-          <t>Platform Implementation (ERP, CRMs);Training</t>
-        </is>
-      </c>
-      <c r="N686" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
+        <v>14000</v>
       </c>
       <c r="O686" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y686" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="Z686" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321905742529</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320114224857</t>
         </is>
       </c>
     </row>
@@ -51765,17 +51790,17 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>320114224858</t>
+          <t>321905742529</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>Information Technology Strategic Plan</t>
+          <t>Dynamics CRM Migration Support, Portal Development, &amp; Train-the-Trainer</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>City of Richmond</t>
+          <t>Governor's Office of Business and Economic Development (GO-Biz)</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
@@ -51803,14 +51828,17 @@
           <t>2026-05-06</t>
         </is>
       </c>
+      <c r="L687" s="65" t="n">
+        <v>173290</v>
+      </c>
       <c r="M687" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Platform Implementation (ERP, CRMs);Training</t>
         </is>
       </c>
       <c r="N687" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O687" t="inlineStr">
@@ -51820,12 +51848,12 @@
       </c>
       <c r="Y687" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Z687" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320114224858</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321905742529</t>
         </is>
       </c>
     </row>
@@ -51835,27 +51863,22 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>319866591968</t>
-        </is>
-      </c>
-      <c r="C688" t="inlineStr">
-        <is>
-          <t>RFP260304</t>
+          <t>320114224858</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>Full Stack WordPress Developer (part-time)</t>
+          <t>Information Technology Strategic Plan</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>Seattle Public Schools</t>
+          <t>City of Richmond</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
@@ -51878,12 +51901,9 @@
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="L688" s="65" t="n">
-        <v>65000</v>
-      </c>
       <c r="M688" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N688" t="inlineStr">
@@ -51898,12 +51918,12 @@
       </c>
       <c r="Y688" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="Z688" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319866591968</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320114224858</t>
         </is>
       </c>
     </row>
@@ -51913,17 +51933,27 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>319311117011</t>
+          <t>319866591968</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>RFP260304</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>IT SECURITY ASSESSMENT</t>
+          <t>Full Stack WordPress Developer (part-time)</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>City of Rockville</t>
+          <t>Seattle Public Schools</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
@@ -51938,32 +51968,40 @@
       </c>
       <c r="J689" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="K689" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="L689" s="65" t="n">
+        <v>65000</v>
       </c>
       <c r="M689" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="N689" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O689" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y689" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z689" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319311117011</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319866591968</t>
         </is>
       </c>
     </row>
@@ -51973,17 +52011,17 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>321010534088</t>
+          <t>319311117011</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>IT MANAGED SERVICES PROVIDER</t>
+          <t>IT SECURITY ASSESSMENT</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>City of Ferndale</t>
+          <t>City of Rockville</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
@@ -52006,17 +52044,9 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="L690" s="65" t="n">
-        <v>373572</v>
-      </c>
       <c r="M690" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N690" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O690" t="inlineStr">
@@ -52026,12 +52056,12 @@
       </c>
       <c r="Y690" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="Z690" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321010534088</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319311117011</t>
         </is>
       </c>
     </row>
@@ -52041,27 +52071,22 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>324699843267</t>
+          <t>321010534088</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>Microsoft 365 GCC Licensing Quote</t>
+          <t>IT MANAGED SERVICES PROVIDER</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Mexico Finance Authority (“NMFA”) </t>
-        </is>
-      </c>
-      <c r="F691" t="inlineStr">
-        <is>
-          <t>New Mexico</t>
+          <t>City of Ferndale</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
@@ -52071,7 +52096,7 @@
       </c>
       <c r="J691" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="K691" t="inlineStr">
@@ -52080,11 +52105,11 @@
         </is>
       </c>
       <c r="L691" s="65" t="n">
-        <v>57658.61</v>
+        <v>373572</v>
       </c>
       <c r="M691" t="inlineStr">
         <is>
-          <t>Reseller</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N691" t="inlineStr">
@@ -52094,17 +52119,17 @@
       </c>
       <c r="O691" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y691" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="Z691" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/324699843267</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321010534088</t>
         </is>
       </c>
     </row>
@@ -52114,17 +52139,22 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>321711121139</t>
+          <t>322911466218</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>6100015191</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>Information Technology Managed Services: IT Service Desk</t>
+          <t>Security and Infrastructure Support Work Order Services</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>Brunswick County</t>
+          <t>Pennsylvania Turnpike Commission</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
@@ -52139,7 +52169,7 @@
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="K692" t="inlineStr">
@@ -52147,17 +52177,14 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="L692" s="65" t="n">
-        <v>92560</v>
-      </c>
       <c r="M692" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Staff Augmentation;Consulting</t>
         </is>
       </c>
       <c r="N692" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O692" t="inlineStr">
@@ -52167,12 +52194,12 @@
       </c>
       <c r="Y692" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="Z692" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321711121139</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322911466218</t>
         </is>
       </c>
     </row>
@@ -52182,27 +52209,27 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>320489731795</t>
-        </is>
-      </c>
-      <c r="C693" t="inlineStr">
-        <is>
-          <t>CR#: 2133336</t>
+          <t>324699843267</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>Technical Consultant</t>
+          <t>Microsoft 365 GCC Licensing Quote</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>NYS Division of Criminal Justice Services</t>
+          <t xml:space="preserve">New Mexico Finance Authority (“NMFA”) </t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -52212,20 +52239,20 @@
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="K693" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="L693" s="65" t="n">
-        <v>49500</v>
+        <v>57658.61</v>
       </c>
       <c r="M693" t="inlineStr">
         <is>
-          <t>Consulting;Staff Augmentation</t>
+          <t>Reseller</t>
         </is>
       </c>
       <c r="N693" t="inlineStr">
@@ -52240,12 +52267,12 @@
       </c>
       <c r="Y693" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Z693" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320489731795</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/324699843267</t>
         </is>
       </c>
     </row>
@@ -52255,17 +52282,22 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>322527283932</t>
+          <t>321711121139</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>Test RFX (please ignore)</t>
+          <t>Information Technology Managed Services: IT Service Desk</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>Brunswick County</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
@@ -52273,29 +52305,42 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="L694" s="65" t="n">
+        <v>92560</v>
+      </c>
       <c r="M694" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N694" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O694" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
-        </is>
-      </c>
-      <c r="S694" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y694" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z694" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321711121139</t>
         </is>
       </c>
     </row>
@@ -52305,32 +52350,27 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>116977709771</t>
+          <t>320489731795</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>RFP-25-0005</t>
+          <t>CR#: 2133336</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
+          <t>Technical Consultant</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>NeighborWorks America</t>
-        </is>
-      </c>
-      <c r="F695" t="inlineStr">
-        <is>
-          <t>Washington, D.C.</t>
+          <t>NYS Division of Criminal Justice Services</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H695" t="inlineStr">
@@ -52338,39 +52378,42 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="L695" s="65" t="n">
+        <v>49500</v>
+      </c>
       <c r="M695" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting;Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="N695" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O695" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
-        </is>
-      </c>
-      <c r="S695" t="inlineStr">
-        <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="U695" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y695" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="Z695" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
-        </is>
-      </c>
-      <c r="AA695" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320489731795</t>
         </is>
       </c>
     </row>
@@ -52380,27 +52423,27 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>145081112265</t>
+          <t>319309140723</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>RFP 019-0-2026/HM</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>Technology Strategic Management Consulting</t>
+          <t>Cybersecurity Penetration &amp; Vulnerability Testing Services</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>State of Colorado, the Office of Information Technology (OIT)</t>
-        </is>
-      </c>
-      <c r="F696" t="inlineStr">
-        <is>
-          <t>Colorado</t>
+          <t>Newport News Public Schools [VA]</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
@@ -52410,27 +52453,40 @@
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="L696" s="65" t="n">
+        <v>66096</v>
       </c>
       <c r="M696" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Audits and Assessment</t>
+        </is>
+      </c>
+      <c r="N696" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O696" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y696" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="Z696" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319309140723</t>
         </is>
       </c>
     </row>
@@ -52440,22 +52496,22 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>166098266830</t>
+          <t>320623193832</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>213924802</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
+          <t>Clemson LIFE Program Management System</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>Mecklenburg County</t>
-        </is>
-      </c>
-      <c r="F697" t="inlineStr">
-        <is>
-          <t>North Carolina</t>
+          <t>Clemson University</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
@@ -52470,27 +52526,35 @@
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="M697" t="inlineStr">
-        <is>
-          <t>Audits and Assessment</t>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="L697" s="65" t="n">
+        <v>572000</v>
+      </c>
+      <c r="N697" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O697" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y697" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z697" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320623193832</t>
         </is>
       </c>
     </row>
@@ -52500,27 +52564,17 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>180166400720</t>
+          <t>322527283932</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
-        </is>
-      </c>
-      <c r="E698" t="inlineStr">
-        <is>
-          <t>Central Ohio Transit Authority</t>
-        </is>
-      </c>
-      <c r="F698" t="inlineStr">
-        <is>
-          <t>Ohio</t>
+          <t>Test RFX (please ignore)</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
@@ -52528,24 +52582,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J698" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>Training</t>
         </is>
       </c>
       <c r="O698" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="S698" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y698" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z698" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
         </is>
       </c>
     </row>
@@ -52555,32 +52614,32 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>182404957915</t>
+          <t>116977709771</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>PWE-10.08.2025</t>
+          <t>RFP-25-0005</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>PWE Power BI Dashboard</t>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>City of Issaquah</t>
+          <t>NeighborWorks America</t>
         </is>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
@@ -52588,29 +52647,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J699" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
       <c r="M699" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O699" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="S699" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="U699" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Y699" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z699" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+        </is>
+      </c>
+      <c r="AA699" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -52620,32 +52689,27 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>108771177151</t>
-        </is>
-      </c>
-      <c r="C700" t="inlineStr">
-        <is>
-          <t>791202505005</t>
+          <t>145081112265</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Government Consulting Services</t>
+          <t>Technology Strategic Management Consulting</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>North Central Texas Council of Governments</t>
+          <t>State of Colorado, the Office of Information Technology (OIT)</t>
         </is>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>TEXAS</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
@@ -52655,12 +52719,12 @@
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="N700" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O700" t="inlineStr">
@@ -52670,12 +52734,12 @@
       </c>
       <c r="Y700" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z700" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
         </is>
       </c>
     </row>
@@ -52685,32 +52749,27 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>120893940416</t>
-        </is>
-      </c>
-      <c r="C701" t="inlineStr">
-        <is>
-          <t>DQ SAAA #2026000004</t>
+          <t>166098266830</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>Online Content Learning</t>
+          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>State of Colorado Department of Regulatory Agencies</t>
+          <t>Mecklenburg County</t>
         </is>
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
@@ -52720,30 +52779,27 @@
       </c>
       <c r="J701" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L701" s="65" t="n">
-        <v>67300</v>
+          <t>2025-10-07</t>
+        </is>
       </c>
       <c r="M701" t="inlineStr">
         <is>
-          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O701" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y701" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z701" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
         </is>
       </c>
     </row>
@@ -52753,27 +52809,27 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>199601365715</t>
+          <t>180166400720</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>Contracted IT Support Services</t>
+          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>ECS4Kids</t>
+          <t>Central Ohio Transit Authority</t>
         </is>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
@@ -52783,35 +52839,22 @@
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="L702" s="65" t="n">
-        <v>291141</v>
-      </c>
-      <c r="M702" t="inlineStr">
-        <is>
-          <t>Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N702" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="O702" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y702" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="Z702" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
         </is>
       </c>
     </row>
@@ -52821,100 +52864,62 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>140123456196</t>
+          <t>182404957915</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>24-RFP-10</t>
+          <t>PWE-10.08.2025</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+          <t>PWE Power BI Dashboard</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+          <t>City of Issaquah</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I703" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L703" s="65" t="n">
-        <v>18620</v>
+          <t>2025-10-29</t>
+        </is>
       </c>
       <c r="M703" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O703" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="P703" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q703" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="S703" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="U703" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="V703" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y703" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Z703" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
-        </is>
-      </c>
-      <c r="AA703" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
         </is>
       </c>
     </row>
@@ -52924,27 +52929,32 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>261982669555</t>
+          <t>108771177151</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>791202505005</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>IT Backfill for ERP Configuration (SOW 2)</t>
+          <t>Government Consulting Services</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>Madison Metropolitan Sewerage District</t>
+          <t>North Central Texas Council of Governments</t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>TEXAS</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
@@ -52954,15 +52964,12 @@
       </c>
       <c r="J704" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="L704" s="65" t="n">
-        <v>157000</v>
-      </c>
-      <c r="M704" t="inlineStr">
-        <is>
-          <t>Staff Augmentation</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="N704" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O704" t="inlineStr">
@@ -52970,34 +52977,14 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="S704" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="U704" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="V704" t="inlineStr">
-        <is>
-          <t>In Process</t>
-        </is>
-      </c>
       <c r="Y704" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="Z704" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
-        </is>
-      </c>
-      <c r="AA704" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
         </is>
       </c>
     </row>
@@ -53007,27 +52994,32 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>278519751386</t>
+          <t>120893940416</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>DQ SAAA #2026000004</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>Data Warehousing Services</t>
+          <t>Online Content Learning</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allen Town School District </t>
+          <t>State of Colorado Department of Regulatory Agencies</t>
         </is>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
@@ -53037,32 +53029,30 @@
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="L705" s="65" t="n">
+        <v>67300</v>
       </c>
       <c r="M705" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N705" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O705" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y705" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z705" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
         </is>
       </c>
     </row>
@@ -53072,32 +53062,27 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>259790359234</t>
-        </is>
-      </c>
-      <c r="C706" t="inlineStr">
-        <is>
-          <t>601440000049523</t>
+          <t>199601365715</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>Managed Application Services: Application Development and Maintenance Services</t>
+          <t>Contracted IT Support Services</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>Texas Department of Transportation</t>
+          <t>ECS4Kids</t>
         </is>
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
@@ -53107,14 +53092,22 @@
       </c>
       <c r="J706" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
-        </is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="L706" s="65" t="n">
+        <v>291141</v>
       </c>
       <c r="M706" t="inlineStr">
         <is>
           <t>Support &amp; Maintenance</t>
         </is>
       </c>
+      <c r="N706" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O706" t="inlineStr">
         <is>
           <t>Ashutosh Chauhan</t>
@@ -53122,12 +53115,12 @@
       </c>
       <c r="Y706" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z706" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
         </is>
       </c>
     </row>
@@ -53137,62 +53130,100 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>277652547262</t>
+          <t>140123456196</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>24-RFP-10</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
+          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>District of Columbia Housing Finance Agency</t>
+          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
         </is>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
-        </is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L707" s="65" t="n">
+        <v>18620</v>
       </c>
       <c r="M707" t="inlineStr">
         <is>
-          <t>Consulting;Training</t>
-        </is>
-      </c>
-      <c r="N707" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O707" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P707" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q707" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="S707" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="U707" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="V707" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y707" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z707" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
+        </is>
+      </c>
+      <c r="AA707" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -53202,27 +53233,27 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>269507522240</t>
+          <t>261982669555</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
+          <t>IT Backfill for ERP Configuration (SOW 2)</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>Central Midlands Regional Transit Authority</t>
+          <t>Madison Metropolitan Sewerage District</t>
         </is>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
@@ -53232,27 +53263,50 @@
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
-        </is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="L708" s="65" t="n">
+        <v>157000</v>
       </c>
       <c r="M708" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O708" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S708" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="U708" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="V708" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y708" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z708" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
+        </is>
+      </c>
+      <c r="AA708" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -53262,22 +53316,22 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>294055526085</t>
+          <t>278519751386</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>Oracle Managed Services and Testing as a Service Support</t>
+          <t>Data Warehousing Services</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>CITY OF DURHAM</t>
+          <t xml:space="preserve">Allen Town School District </t>
         </is>
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
@@ -53292,12 +53346,17 @@
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="M709" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N709" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O709" t="inlineStr">
@@ -53307,12 +53366,12 @@
       </c>
       <c r="Y709" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Z709" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
         </is>
       </c>
     </row>
@@ -53322,27 +53381,32 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>305430641393</t>
+          <t>259790359234</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>601440000049523</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>OFF - Information Technology Managed Services</t>
+          <t>Managed Application Services: Application Development and Maintenance Services</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>County of Montcalm</t>
+          <t>Texas Department of Transportation</t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
@@ -53352,12 +53416,12 @@
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="M710" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O710" t="inlineStr">
@@ -53367,12 +53431,12 @@
       </c>
       <c r="Y710" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z710" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
         </is>
       </c>
     </row>
@@ -53382,17 +53446,22 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>311307032268</t>
+          <t>277652547262</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>Housing Authority of the City of Passaic</t>
+          <t>District of Columbia Housing Finance Agency</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
@@ -53407,27 +53476,32 @@
       </c>
       <c r="J711" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="M711" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting;Training</t>
+        </is>
+      </c>
+      <c r="N711" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O711" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y711" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Z711" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
         </is>
       </c>
     </row>
@@ -53437,32 +53511,27 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>135161266908</t>
-        </is>
-      </c>
-      <c r="C712" t="inlineStr">
-        <is>
-          <t>RFQ1757840</t>
+          <t>269507522240</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>25-51-A-PMO-ES-SSN</t>
+          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>U.S. Department of the Treasury</t>
+          <t>Central Midlands Regional Transit Authority</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
@@ -53472,27 +53541,27 @@
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="N712" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O712" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y712" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z712" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
         </is>
       </c>
     </row>
@@ -53502,17 +53571,27 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>110691507903</t>
+          <t>294055526085</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
+          <t>Oracle Managed Services and Testing as a Service Support</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>CITY OF DURHAM</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
@@ -53522,25 +53601,27 @@
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="L713" s="65" t="n">
-        <v>96200</v>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance</t>
+        </is>
       </c>
       <c r="O713" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y713" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Z713" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
         </is>
       </c>
     </row>
@@ -53550,17 +53631,27 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>110691507909</t>
+          <t>305430641393</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
+          <t>OFF - Information Technology Managed Services</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>County of Montcalm</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
@@ -53570,22 +53661,27 @@
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O714" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y714" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="Z714" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
         </is>
       </c>
     </row>
@@ -53595,17 +53691,22 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>108771377911</t>
+          <t>311307032268</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Facilities and Information Technology Infrastructure Assessment</t>
+          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>Housing Authority of the City of Passaic</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
@@ -53615,22 +53716,27 @@
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O715" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y715" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Z715" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
         </is>
       </c>
     </row>
@@ -53640,17 +53746,27 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>120893940419</t>
+          <t>135161266908</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>#25-038-RFP)</t>
+          <t>RFQ1757840</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
+          <t>25-51-A-PMO-ES-SSN</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>U.S. Department of the Treasury</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -53665,27 +53781,27 @@
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="M716" t="inlineStr">
-        <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="N716" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O716" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y716" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z716" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
         </is>
       </c>
     </row>
@@ -53695,12 +53811,12 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>114864654049</t>
+          <t>110691507903</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>M365 Tenant backup</t>
+          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -53718,19 +53834,22 @@
           <t>2026-03-31</t>
         </is>
       </c>
+      <c r="L717" s="65" t="n">
+        <v>96200</v>
+      </c>
       <c r="O717" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y717" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z717" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
         </is>
       </c>
     </row>
@@ -53740,27 +53859,17 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>317945474767</t>
+          <t>110691507909</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>ServiceNow Technical Services</t>
-        </is>
-      </c>
-      <c r="E718" t="inlineStr">
-        <is>
-          <t>City of Sacramento</t>
-        </is>
-      </c>
-      <c r="F718" t="inlineStr">
-        <is>
-          <t>California</t>
+          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
@@ -53770,22 +53879,22 @@
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="O718" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y718" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z718" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
         </is>
       </c>
     </row>
@@ -53795,45 +53904,305 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
+          <t>108771377911</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Facilities and Information Technology Infrastructure Assessment</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O719" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y719" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z719" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="n">
+        <v>719</v>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>120893940419</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>#25-038-RFP)</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="O720" t="inlineStr">
+        <is>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="Y720" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="Z720" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="n">
+        <v>720</v>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>114864654049</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>M365 Tenant backup</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O721" t="inlineStr">
+        <is>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="Y721" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z721" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="n">
+        <v>721</v>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>317194645231</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>BCH-C25-008</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Data Migration (CMAS RFP)</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>Business, Consumer Services and Housing Agency</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>Modernization / Migration</t>
+        </is>
+      </c>
+      <c r="O722" t="inlineStr">
+        <is>
+          <t>Darshan Tiwari</t>
+        </is>
+      </c>
+      <c r="Y722" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z722" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="n">
+        <v>722</v>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>317945474767</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>ServiceNow Technical Services</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>City of Sacramento</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O723" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y723" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z723" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="n">
+        <v>723</v>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
           <t>317911067336</t>
         </is>
       </c>
-      <c r="D719" t="inlineStr">
+      <c r="D724" t="inlineStr">
         <is>
           <t>Enterprise Data Warehouse</t>
         </is>
       </c>
-      <c r="E719" t="inlineStr">
+      <c r="E724" t="inlineStr">
         <is>
           <t>Michigan Department of Technology Management and Budget</t>
         </is>
       </c>
-      <c r="G719" t="inlineStr">
+      <c r="G724" t="inlineStr">
         <is>
           <t>RFx Cancelled</t>
         </is>
       </c>
-      <c r="H719" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J719" t="inlineStr">
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="O719" t="inlineStr">
+      <c r="O724" t="inlineStr">
         <is>
           <t>Ashutosh Chauhan</t>
         </is>
       </c>
-      <c r="Y719" t="inlineStr">
+      <c r="Y724" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="Z719" t="inlineStr">
+      <c r="Z724" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
         </is>
@@ -53856,7 +54225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA87"/>
+  <dimension ref="A1:AA88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -58960,27 +59329,32 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>235886616288</t>
+          <t>212696339180</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AI02-26</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Rebid- Information Technology Services</t>
+          <t>AI Consulting Services</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>LEAD CHARTER SCHOOL</t>
+          <t>Houston-Galveston Area Council</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -58990,55 +59364,52 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="L55" s="65" t="n">
-        <v>24750</v>
+          <t>2025-12-18</t>
+        </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting;Staff Augmentation</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/235886616288</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/212696339180</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -59048,27 +59419,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>235964612297</t>
+          <t>235886616288</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>AI Governance, Compliance, and Enablement Platform</t>
+          <t>Rebid- Information Technology Services</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>North Central Texas Council of Governments</t>
+          <t>LEAD CHARTER SCHOOL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>TEXAS</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -59078,42 +59449,40 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="L56" s="65" t="n">
+        <v>24750</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Awarded</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -59123,12 +59492,12 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/235964612297</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/235886616288</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -59138,27 +59507,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>225906287352</t>
+          <t>235964612297</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Small Software Application Development</t>
+          <t>AI Governance, Compliance, and Enablement Platform</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Insurance Reserve Fund </t>
+          <t>North Central Texas Council of Governments</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>TEXAS</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -59168,17 +59537,17 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -59193,22 +59562,32 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Awarded</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/225906287352</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/235964612297</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -59218,27 +59597,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>275926212329</t>
+          <t>225906287352</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>MICROSOFT OFFICE 365 LICENSING</t>
+          <t>Small Software Application Development</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Village of Tinley Park</t>
+          <t xml:space="preserve">Insurance Reserve Fund </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -59248,55 +59627,47 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="L58" s="65" t="n">
-        <v>114400</v>
+          <t>2026-01-26</t>
+        </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Reseller</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/275926212329</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/225906287352</t>
         </is>
       </c>
     </row>
@@ -59306,22 +59677,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>267386743501</t>
+          <t>275926212329</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>FPB – Direct Placement Staffing Services for IT Positions</t>
+          <t>MICROSOFT OFFICE 365 LICENSING</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>University of South Carolina</t>
+          <t>Village of Tinley Park</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -59336,7 +59707,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -59344,14 +59715,17 @@
           <t>2026-02-06</t>
         </is>
       </c>
+      <c r="L59" s="65" t="n">
+        <v>114400</v>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Reseller</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -59361,22 +59735,22 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/267386743501</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/275926212329</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -59391,22 +59765,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>277951244006</t>
+          <t>267386743501</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>offline + online IT Disaster Response Plan</t>
+          <t>FPB – Direct Placement Staffing Services for IT Positions</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>City of Kenai</t>
+          <t>University of South Carolina</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -59421,60 +59795,52 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="L60" s="65" t="n">
-        <v>16800</v>
+          <t>2026-02-06</t>
+        </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Awarded</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277951244006</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/267386743501</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -59484,22 +59850,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>285814477558</t>
+          <t>277951244006</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>RFQ - 1400 Long Beach Cybersecurity Grant Program</t>
+          <t>offline + online IT Disaster Response Plan</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>City of Long Beach</t>
+          <t>City of Kenai</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mississippi</t>
+          <t>Alaska</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -59514,50 +59880,55 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="L61" s="65" t="n">
-        <v>123785</v>
+        <v>16800</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Awarded</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/285814477558</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277951244006</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -59572,22 +59943,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>290824554187</t>
+          <t>285814477558</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cybersecurity Policy and Protocol Consultant Services</t>
+          <t>RFQ - 1400 Long Beach Cybersecurity Grant Program</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Navojo Housing Authority</t>
+          <t>City of Long Beach</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>Mississippi</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -59602,55 +59973,50 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="L62" s="65" t="n">
-        <v>7825</v>
+        <v>123785</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Awarded</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/290824554187</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/285814477558</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -59665,22 +60031,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>305108054745</t>
+          <t>290824554187</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Technology Data Architect Services</t>
+          <t>Cybersecurity Policy and Protocol Consultant Services</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>City of Stamford</t>
+          <t>Navojo Housing Authority</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -59690,35 +60056,30 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="L63" s="65" t="n">
-        <v>47775</v>
+        <v>7825</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Consulting;Staff Augmentation</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -59726,29 +60087,29 @@
           <t>Savya Atrey</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Awarded</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305108054745</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/290824554187</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -59763,22 +60124,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>323517591239</t>
+          <t>305108054745</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>CAPK SOW 1</t>
+          <t>Technology Data Architect Services</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Community Action Partnership of Kern</t>
+          <t>City of Stamford</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Connecticut</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -59788,42 +60149,70 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="L64" s="65" t="n">
+        <v>47775</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Consulting;Managed Services (MSP)</t>
+          <t>Consulting;Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
+          <t>Savya Atrey</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323517591239</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305108054745</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -59833,27 +60222,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>323528390341</t>
+          <t>323517591239</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>IT MSP &amp; NOC NMFA Additional SOW</t>
+          <t>CAPK SOW 1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Mexico Finance Authority (“NMFA”) </t>
+          <t>Community Action Partnership of Kern</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -59863,17 +60252,17 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting;Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -59881,19 +60270,19 @@
           <t>Ashutosh Chauhan</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323528390341</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323517591239</t>
         </is>
       </c>
     </row>
@@ -59903,27 +60292,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>320213008064</t>
+          <t>323528390341</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ONLINE WEB-BASED TRAINING</t>
+          <t>IT MSP &amp; NOC NMFA Additional SOW</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Alaska Department of Administration</t>
+          <t xml:space="preserve">New Mexico Finance Authority (“NMFA”) </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -59938,40 +60327,32 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="L66" s="65" t="n">
-        <v>37800</v>
+          <t>2026-04-22</t>
+        </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320213008064</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323528390341</t>
         </is>
       </c>
     </row>
@@ -59981,27 +60362,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>127482765035</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>RFP NO. NC- 2025-14</t>
+          <t>320213008064</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Computer Maintenance &amp; Technology Support Services - FCSS Fresno County Superintendent of Schools</t>
+          <t>ONLINE WEB-BASED TRAINING</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FRESNO COUNTY SUPERINTENDENT OF SCHOOLS</t>
+          <t>Alaska Department of Administration</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Alaska</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -60016,57 +60392,45 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="L67" s="65" t="n">
+        <v>37800</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Consulting;Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127482765035</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320213008064</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -60076,22 +60440,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>116977709757</t>
+          <t>127482765035</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>RCA-017-25010066</t>
+          <t>RFP NO. NC- 2025-14</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ON-LINE MARKETPLACE FOR CLOUD SERVICES AND SOFTWARE</t>
+          <t>Computer Maintenance &amp; Technology Support Services - FCSS Fresno County Superintendent of Schools</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Orange County</t>
+          <t>FRESNO COUNTY SUPERINTENDENT OF SCHOOLS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -60109,29 +60473,54 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Consulting;Reseller</t>
+          <t>Consulting;Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Arshdeep Kaur</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709757</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127482765035</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -60146,27 +60535,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>116977709771</t>
+          <t>116977709757</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>RFP-25-0005</t>
+          <t>RCA-017-25010066</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
+          <t>ON-LINE MARKETPLACE FOR CLOUD SERVICES AND SOFTWARE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>NeighborWorks America</t>
+          <t>Orange County</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -60181,7 +60570,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting;Reseller</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -60191,12 +60580,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -60206,7 +60590,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709757</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -60221,22 +60605,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>116977709756</t>
+          <t>116977709771</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>RFP-25-0005</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Hazelwood Information Technology Audit Services</t>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hazelwood School District</t>
+          <t>NeighborWorks America</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -60249,12 +60638,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L70" s="65" t="n">
-        <v>48500</v>
-      </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -60264,12 +60650,12 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -60279,12 +60665,12 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709756</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -60294,27 +60680,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>269389012723</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>COVB-25-101486</t>
+          <t>116977709756</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Hazelwood Information Technology Audit Services</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">City of Virginia Beach </t>
+          <t>Hazelwood School District</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -60327,9 +60708,12 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L71" s="65" t="n">
+        <v>48500</v>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -60339,27 +60723,27 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269389012723</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709756</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -60369,17 +60753,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>322527283932</t>
+          <t>269389012723</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>COVB-25-101486</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Test RFX (please ignore)</t>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">City of Virginia Beach </t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -60389,27 +60788,37 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269389012723</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -60419,27 +60828,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>127590445803</t>
+          <t>322527283932</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>IT Staffing and Professional Services</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Roswell Park Comprehensive Cancer Centre</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>New York</t>
+          <t>Test RFX (please ignore)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -60447,44 +60846,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Consulting;Staff Augmentation</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Akshat Tripathi</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>2025-02-18</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445803</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
         </is>
       </c>
     </row>
@@ -60494,27 +60878,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>123670192881</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>24-31</t>
+          <t>127590445803</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Arapahoe County - IT RECRUITMENT AND STAFFING</t>
+          <t>IT Staffing and Professional Services</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Arapahoe County</t>
+          <t>Roswell Park Comprehensive Cancer Centre</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -60529,37 +60908,37 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting;Staff Augmentation</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/123670192881</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445803</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -60574,27 +60953,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>114864632551</t>
+          <t>123670192881</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>F25-077</t>
+          <t>24-31</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>City of Sunnyvale - Group 4, Software/Application/Database Development, Business Requirements Analysis, and Integration Services</t>
+          <t>Arapahoe County - IT RECRUITMENT AND STAFFING</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>City of Sunnyvale</t>
+          <t>Arapahoe County</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -60609,7 +60988,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -60617,11 +60996,6 @@
           <t>Staff Augmentation</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
       <c r="O75" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
@@ -60629,22 +61003,22 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864632551</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/123670192881</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -60659,27 +61033,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>127678196421</t>
+          <t>114864632551</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>RFQ 24 - 00332</t>
+          <t>F25-077</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>HRT - Workday HCM Staffing Services</t>
+          <t>City of Sunnyvale - Group 4, Software/Application/Database Development, Business Requirements Analysis, and Integration Services</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hampton Roads Transit</t>
+          <t>City of Sunnyvale</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -60689,70 +61063,52 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="L76" s="65" t="n">
-        <v>10000</v>
+          <t>2024-11-14</t>
+        </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
           <t>Staff Augmentation</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>2025-02-07</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127678196421</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864632551</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -60762,22 +61118,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>127590445777</t>
+          <t>127678196421</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>RFQ 24 - 00332</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Temporary Professional Staff Services 2</t>
+          <t>HRT - Workday HCM Staffing Services</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>State of South Dakota Department of Social Services</t>
+          <t>Hampton Roads Transit</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>South Dakota</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -60787,13 +61148,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
-        </is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="L77" s="65" t="n">
+        <v>10000</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -60802,17 +61171,32 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Arshdeep Kaur</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -60822,12 +61206,12 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445777</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127678196421</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -60837,27 +61221,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>142851074788</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>RFQ-DH-1394</t>
+          <t>127590445777</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ON-CALL INFORMATION TECHNOLOGY INFRASTRUCTURE SERVICES</t>
+          <t>Temporary Professional Staff Services 2</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Metropolitan Water District of Southern California</t>
+          <t>State of South Dakota Department of Social Services</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>South Dakota</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -60872,7 +61251,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -60880,34 +61259,29 @@
           <t>Staff Augmentation</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/142851074788</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445777</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -60922,12 +61296,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>132776626904</t>
+          <t>142851074788</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>RFQ-DH-1394</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ON-CALL INFORMATION TECHNOLOGY (IT) APPLICATION SUPPORT SERVICES (RFQ-DS-1397)</t>
+          <t>ON-CALL INFORMATION TECHNOLOGY INFRASTRUCTURE SERVICES</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -60952,7 +61331,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -60960,29 +61339,34 @@
           <t>Staff Augmentation</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/132776626904</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/142851074788</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -60997,22 +61381,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>127678196440</t>
+          <t>132776626904</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>MINNESOTA JUDICIAL BRANCH - IT Technical/infrastructure Services, Information Technology Application Development And Support Services &amp; Data Science And Machine Learning Services</t>
+          <t>ON-CALL INFORMATION TECHNOLOGY (IT) APPLICATION SUPPORT SERVICES (RFQ-DS-1397)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Minnesota Judicial Branch</t>
+          <t>Metropolitan Water District of Southern California</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -61027,7 +61411,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -61037,27 +61421,27 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127678196440</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/132776626904</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -61072,22 +61456,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>127590445789</t>
+          <t>127678196440</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Retainer Contract Opportunity for Information Technology (IT) Services</t>
+          <t>MINNESOTA JUDICIAL BRANCH - IT Technical/infrastructure Services, Information Technology Application Development And Support Services &amp; Data Science And Machine Learning Services</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>State of Vermont (Department of Buildings and General Services)</t>
+          <t>Minnesota Judicial Branch</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vermont</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -61102,7 +61486,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -61112,17 +61496,17 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Arshdeep Kaur</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
@@ -61132,7 +61516,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445789</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127678196440</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -61147,27 +61531,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>135198825206</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>24-25-78</t>
+          <t>127590445789</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>IT Project Management &amp; Consulting Services</t>
+          <t>Retainer Contract Opportunity for Information Technology (IT) Services</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>City of Santa Clara</t>
+          <t>State of Vermont (Department of Buildings and General Services)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Vermont</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -61177,22 +61556,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -61200,34 +61574,24 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135198825206</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445789</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -61242,27 +61606,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>168988159693</t>
+          <t>135198825206</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6000002323</t>
+          <t>24-25-78</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Performance of Expert Professional Airport Data Analysis and Business Intelligence Consulting Services during 2025 through 2029</t>
+          <t>IT Project Management &amp; Consulting Services</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Port Authority of New York New Jersey</t>
+          <t>City of Santa Clara</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -61272,37 +61636,62 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/168988159693</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135198825206</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -61312,17 +61701,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>169111068380</t>
+          <t>168988159693</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>6000002328</t>
+          <t>6000002323</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Performance of Expert Professional Airport Information Technology and Innovation Consulting Services</t>
+          <t>Performance of Expert Professional Airport Data Analysis and Business Intelligence Consulting Services during 2025 through 2029</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -61372,12 +61761,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/169111068380</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/168988159693</t>
         </is>
       </c>
     </row>
@@ -61387,27 +61771,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>169108930291</t>
+          <t>169111068380</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>RFQ-AR-1399</t>
+          <t>6000002328</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ON-CALL INFORMATION TECHNOLOGY SOFTWARE ASSET MANAGEMENT SERVICES</t>
+          <t>Performance of Expert Professional Airport Information Technology and Innovation Consulting Services</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Metropolitan Water District of Southern California</t>
+          <t>Port Authority of New York New Jersey</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -61427,37 +61811,32 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/169108930291</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/169111068380</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -61467,55 +61846,47 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>140123456196</t>
+          <t>169108930291</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>24-RFP-10</t>
+          <t>RFQ-AR-1399</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+          <t>ON-CALL INFORMATION TECHNOLOGY SOFTWARE ASSET MANAGEMENT SERVICES</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+          <t>Metropolitan Water District of Southern California</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L86" s="65" t="n">
-        <v>18620</v>
+          <t>2025-09-24</t>
+        </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -61523,39 +61894,24 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/169108930291</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -61570,78 +61926,181 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
+          <t>140123456196</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>24-RFP-10</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Intent to Award</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L87" s="65" t="n">
+        <v>18620</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>In Process</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>261982669555</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>IT Backfill for ERP Configuration (SOW 2)</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Madison Metropolitan Sewerage District</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Wisconsin</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>Closed Won</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
         <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="L87" s="65" t="n">
+      <c r="L88" s="65" t="n">
         <v>157000</v>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>Staff Augmentation</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>2025-10-24</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="U88" t="inlineStr">
         <is>
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="V87" t="inlineStr">
+      <c r="V88" t="inlineStr">
         <is>
           <t>In Process</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="Y88" t="inlineStr">
         <is>
           <t>2026-01-14</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
         </is>
       </c>
-      <c r="AA87" t="inlineStr">
+      <c r="AA88" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-05-13 09:29 EDT</t>
+          <t>2026-05-14 12:31 EDT</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA724"/>
+  <dimension ref="A1:AA730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -14719,7 +14719,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -16174,22 +16174,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>202093180646</t>
+          <t>202091740908</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>OFFLINE Information Technology Management Services</t>
+          <t>OFFLINE Exchange Migration Services</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>City of Eagle Pass</t>
+          <t>City of Warwick</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -16204,7 +16204,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/202093180646</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/202091740908</t>
         </is>
       </c>
     </row>
@@ -16239,27 +16239,27 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>202091740908</t>
+          <t>202093180646</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>OFFLINE Exchange Migration Services</t>
+          <t>OFFLINE Information Technology Management Services</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>City of Warwick</t>
+          <t>City of Eagle Pass</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -16279,7 +16279,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -16294,7 +16294,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/202091740908</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/202093180646</t>
         </is>
       </c>
     </row>
@@ -26909,7 +26909,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -44362,27 +44362,27 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>292902372057</t>
+          <t>316973419240</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>CMS Project Assistant 2026</t>
+          <t>.Net Core Modernization</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>NYS Office of Children &amp; Family Services [NY]</t>
+          <t>California Housing Finance Agency (CalHFA)</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
@@ -44392,17 +44392,20 @@
       </c>
       <c r="J581" t="inlineStr">
         <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
+      <c r="L581" s="65" t="n">
+        <v>218800</v>
       </c>
       <c r="M581" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N581" t="inlineStr">
@@ -44412,17 +44415,17 @@
       </c>
       <c r="O581" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y581" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="Z581" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/292902372057</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316973419240</t>
         </is>
       </c>
     </row>
@@ -44432,22 +44435,22 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>316973419240</t>
+          <t>292902372057</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>.Net Core Modernization</t>
+          <t>CMS Project Assistant 2026</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>California Housing Finance Agency (CalHFA)</t>
+          <t>NYS Office of Children &amp; Family Services [NY]</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
@@ -44462,7 +44465,7 @@
       </c>
       <c r="J582" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="K582" t="inlineStr">
@@ -44470,12 +44473,9 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="L582" s="65" t="n">
-        <v>218800</v>
-      </c>
       <c r="M582" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="N582" t="inlineStr">
@@ -44485,17 +44485,17 @@
       </c>
       <c r="O582" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y582" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="Z582" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316973419240</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/292902372057</t>
         </is>
       </c>
     </row>
@@ -52496,22 +52496,17 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>320623193832</t>
-        </is>
-      </c>
-      <c r="C697" t="inlineStr">
-        <is>
-          <t>213924802</t>
+          <t>322356230853</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>Clemson LIFE Program Management System</t>
+          <t>AI Professional Development for Administration,Staff, and Training for Students</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>Clemson University</t>
+          <t>GROSSMONT UNION HIGH SCHOOL DISTRICT</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
@@ -52531,30 +52526,35 @@
       </c>
       <c r="K697" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="L697" s="65" t="n">
-        <v>572000</v>
+        <v>225400</v>
+      </c>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
       </c>
       <c r="N697" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O697" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y697" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z697" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320623193832</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322356230853</t>
         </is>
       </c>
     </row>
@@ -52564,17 +52564,27 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>322527283932</t>
+          <t>320623193832</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>213924802</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>Test RFX (please ignore)</t>
+          <t>Clemson LIFE Program Management System</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>Clemson University</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
@@ -52582,29 +52592,37 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M698" t="inlineStr">
-        <is>
-          <t>Training</t>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="L698" s="65" t="n">
+        <v>572000</v>
+      </c>
+      <c r="N698" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O698" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
-        </is>
-      </c>
-      <c r="S698" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y698" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z698" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320623193832</t>
         </is>
       </c>
     </row>
@@ -52614,32 +52632,22 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>116977709771</t>
-        </is>
-      </c>
-      <c r="C699" t="inlineStr">
-        <is>
-          <t>RFP-25-0005</t>
+          <t>321691658976</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
+          <t>OFF - Managed Service Provider (MSP) – IT &amp; Microsoft Cloud Services</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>NeighborWorks America</t>
-        </is>
-      </c>
-      <c r="F699" t="inlineStr">
-        <is>
-          <t>Washington, D.C.</t>
+          <t>Phelps County Sheriff’s Department (PCSD)</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
@@ -52647,39 +52655,42 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L699" s="65" t="n">
+        <v>173400</v>
+      </c>
       <c r="M699" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N699" t="inlineStr">
+        <is>
+          <t>Offline;Email</t>
         </is>
       </c>
       <c r="O699" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
-        </is>
-      </c>
-      <c r="S699" t="inlineStr">
-        <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="U699" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y699" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z699" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
-        </is>
-      </c>
-      <c r="AA699" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321691658976</t>
         </is>
       </c>
     </row>
@@ -52689,22 +52700,17 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>145081112265</t>
+          <t>320137093859</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Technology Strategic Management Consulting</t>
+          <t>OFFLINE Annual Contract For Managed It Services For Youth Lab</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>State of Colorado, the Office of Information Technology (OIT)</t>
-        </is>
-      </c>
-      <c r="F700" t="inlineStr">
-        <is>
-          <t>Colorado</t>
+          <t>City of Visalia</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
@@ -52719,27 +52725,32 @@
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M700" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O700" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y700" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="Z700" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320137093859</t>
         </is>
       </c>
     </row>
@@ -52749,22 +52760,17 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>166098266830</t>
+          <t>321010642622</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>Mecklenburg County</t>
-        </is>
-      </c>
-      <c r="F701" t="inlineStr">
-        <is>
-          <t>North Carolina</t>
+          <t>I-195 Redevelopment District</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
@@ -52779,12 +52785,25 @@
       </c>
       <c r="J701" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L701" s="65" t="n">
+        <v>78900</v>
       </c>
       <c r="M701" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N701" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O701" t="inlineStr">
@@ -52794,12 +52813,12 @@
       </c>
       <c r="Y701" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="Z701" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321010642622</t>
         </is>
       </c>
     </row>
@@ -52809,27 +52828,17 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>180166400720</t>
+          <t>322527283932</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
-        </is>
-      </c>
-      <c r="E702" t="inlineStr">
-        <is>
-          <t>Central Ohio Transit Authority</t>
-        </is>
-      </c>
-      <c r="F702" t="inlineStr">
-        <is>
-          <t>Ohio</t>
+          <t>Test RFX (please ignore)</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
@@ -52837,24 +52846,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J702" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>Training</t>
         </is>
       </c>
       <c r="O702" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="S702" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y702" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z702" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
         </is>
       </c>
     </row>
@@ -52864,32 +52878,32 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>182404957915</t>
+          <t>116977709771</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>PWE-10.08.2025</t>
+          <t>RFP-25-0005</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>PWE Power BI Dashboard</t>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>City of Issaquah</t>
+          <t>NeighborWorks America</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
@@ -52897,29 +52911,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J703" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
       <c r="M703" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O703" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="S703" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="U703" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Y703" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z703" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+        </is>
+      </c>
+      <c r="AA703" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -52929,32 +52953,27 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>108771177151</t>
-        </is>
-      </c>
-      <c r="C704" t="inlineStr">
-        <is>
-          <t>791202505005</t>
+          <t>145081112265</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>Government Consulting Services</t>
+          <t>Technology Strategic Management Consulting</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>North Central Texas Council of Governments</t>
+          <t>State of Colorado, the Office of Information Technology (OIT)</t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>TEXAS</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
@@ -52964,12 +52983,12 @@
       </c>
       <c r="J704" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="N704" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O704" t="inlineStr">
@@ -52979,12 +52998,12 @@
       </c>
       <c r="Y704" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z704" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
         </is>
       </c>
     </row>
@@ -52994,32 +53013,27 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>120893940416</t>
-        </is>
-      </c>
-      <c r="C705" t="inlineStr">
-        <is>
-          <t>DQ SAAA #2026000004</t>
+          <t>166098266830</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>Online Content Learning</t>
+          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>State of Colorado Department of Regulatory Agencies</t>
+          <t>Mecklenburg County</t>
         </is>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
@@ -53029,30 +53043,27 @@
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L705" s="65" t="n">
-        <v>67300</v>
+          <t>2025-10-07</t>
+        </is>
       </c>
       <c r="M705" t="inlineStr">
         <is>
-          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O705" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y705" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z705" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
         </is>
       </c>
     </row>
@@ -53062,27 +53073,27 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>199601365715</t>
+          <t>180166400720</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>Contracted IT Support Services</t>
+          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>ECS4Kids</t>
+          <t>Central Ohio Transit Authority</t>
         </is>
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
@@ -53092,35 +53103,22 @@
       </c>
       <c r="J706" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="L706" s="65" t="n">
-        <v>291141</v>
-      </c>
-      <c r="M706" t="inlineStr">
-        <is>
-          <t>Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N706" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="O706" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y706" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="Z706" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
         </is>
       </c>
     </row>
@@ -53130,100 +53128,62 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>140123456196</t>
+          <t>182404957915</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>24-RFP-10</t>
+          <t>PWE-10.08.2025</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+          <t>PWE Power BI Dashboard</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+          <t>City of Issaquah</t>
         </is>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I707" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L707" s="65" t="n">
-        <v>18620</v>
+          <t>2025-10-29</t>
+        </is>
       </c>
       <c r="M707" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O707" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="P707" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q707" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="S707" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="U707" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="V707" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y707" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Z707" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
-        </is>
-      </c>
-      <c r="AA707" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
         </is>
       </c>
     </row>
@@ -53233,27 +53193,32 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>261982669555</t>
+          <t>108771177151</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>791202505005</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>IT Backfill for ERP Configuration (SOW 2)</t>
+          <t>Government Consulting Services</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>Madison Metropolitan Sewerage District</t>
+          <t>North Central Texas Council of Governments</t>
         </is>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>TEXAS</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
@@ -53263,15 +53228,12 @@
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="L708" s="65" t="n">
-        <v>157000</v>
-      </c>
-      <c r="M708" t="inlineStr">
-        <is>
-          <t>Staff Augmentation</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="N708" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O708" t="inlineStr">
@@ -53279,34 +53241,14 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="S708" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="U708" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="V708" t="inlineStr">
-        <is>
-          <t>In Process</t>
-        </is>
-      </c>
       <c r="Y708" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="Z708" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
-        </is>
-      </c>
-      <c r="AA708" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
         </is>
       </c>
     </row>
@@ -53316,27 +53258,32 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>278519751386</t>
+          <t>120893940416</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>DQ SAAA #2026000004</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>Data Warehousing Services</t>
+          <t>Online Content Learning</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allen Town School District </t>
+          <t>State of Colorado Department of Regulatory Agencies</t>
         </is>
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H709" t="inlineStr">
@@ -53346,32 +53293,30 @@
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="L709" s="65" t="n">
+        <v>67300</v>
       </c>
       <c r="M709" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N709" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O709" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y709" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z709" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
         </is>
       </c>
     </row>
@@ -53381,32 +53326,27 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>259790359234</t>
-        </is>
-      </c>
-      <c r="C710" t="inlineStr">
-        <is>
-          <t>601440000049523</t>
+          <t>199601365715</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>Managed Application Services: Application Development and Maintenance Services</t>
+          <t>Contracted IT Support Services</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>Texas Department of Transportation</t>
+          <t>ECS4Kids</t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
@@ -53416,14 +53356,22 @@
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
-        </is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="L710" s="65" t="n">
+        <v>291141</v>
       </c>
       <c r="M710" t="inlineStr">
         <is>
           <t>Support &amp; Maintenance</t>
         </is>
       </c>
+      <c r="N710" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O710" t="inlineStr">
         <is>
           <t>Ashutosh Chauhan</t>
@@ -53431,12 +53379,12 @@
       </c>
       <c r="Y710" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z710" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
         </is>
       </c>
     </row>
@@ -53446,62 +53394,100 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>277652547262</t>
+          <t>140123456196</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>24-RFP-10</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
+          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>District of Columbia Housing Finance Agency</t>
+          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J711" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
-        </is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L711" s="65" t="n">
+        <v>18620</v>
       </c>
       <c r="M711" t="inlineStr">
         <is>
-          <t>Consulting;Training</t>
-        </is>
-      </c>
-      <c r="N711" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O711" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P711" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q711" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="S711" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="U711" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="V711" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y711" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z711" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
+        </is>
+      </c>
+      <c r="AA711" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -53511,27 +53497,27 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>269507522240</t>
+          <t>261982669555</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
+          <t>IT Backfill for ERP Configuration (SOW 2)</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>Central Midlands Regional Transit Authority</t>
+          <t>Madison Metropolitan Sewerage District</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
@@ -53541,27 +53527,50 @@
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
-        </is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="L712" s="65" t="n">
+        <v>157000</v>
       </c>
       <c r="M712" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O712" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S712" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="U712" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="V712" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y712" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z712" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
+        </is>
+      </c>
+      <c r="AA712" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -53571,22 +53580,22 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>294055526085</t>
+          <t>278519751386</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>Oracle Managed Services and Testing as a Service Support</t>
+          <t>Data Warehousing Services</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>CITY OF DURHAM</t>
+          <t xml:space="preserve">Allen Town School District </t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -53601,12 +53610,17 @@
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="M713" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N713" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O713" t="inlineStr">
@@ -53616,12 +53630,12 @@
       </c>
       <c r="Y713" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Z713" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
         </is>
       </c>
     </row>
@@ -53631,27 +53645,32 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>305430641393</t>
+          <t>259790359234</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>601440000049523</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>OFF - Information Technology Managed Services</t>
+          <t>Managed Application Services: Application Development and Maintenance Services</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>County of Montcalm</t>
+          <t>Texas Department of Transportation</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
@@ -53661,12 +53680,12 @@
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="M714" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O714" t="inlineStr">
@@ -53676,12 +53695,12 @@
       </c>
       <c r="Y714" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z714" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
         </is>
       </c>
     </row>
@@ -53691,17 +53710,22 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>311307032268</t>
+          <t>277652547262</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Housing Authority of the City of Passaic</t>
+          <t>District of Columbia Housing Finance Agency</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -53716,27 +53740,32 @@
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="M715" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting;Training</t>
+        </is>
+      </c>
+      <c r="N715" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O715" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y715" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Z715" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
         </is>
       </c>
     </row>
@@ -53746,32 +53775,27 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>135161266908</t>
-        </is>
-      </c>
-      <c r="C716" t="inlineStr">
-        <is>
-          <t>RFQ1757840</t>
+          <t>269507522240</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>25-51-A-PMO-ES-SSN</t>
+          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>U.S. Department of the Treasury</t>
+          <t>Central Midlands Regional Transit Authority</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
@@ -53781,27 +53805,27 @@
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="N716" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O716" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y716" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z716" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
         </is>
       </c>
     </row>
@@ -53811,17 +53835,27 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>110691507903</t>
+          <t>294055526085</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
+          <t>Oracle Managed Services and Testing as a Service Support</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>CITY OF DURHAM</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
@@ -53831,25 +53865,27 @@
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="L717" s="65" t="n">
-        <v>96200</v>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance</t>
+        </is>
       </c>
       <c r="O717" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y717" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Z717" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
         </is>
       </c>
     </row>
@@ -53859,17 +53895,27 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>110691507909</t>
+          <t>305430641393</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
+          <t>OFF - Information Technology Managed Services</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>County of Montcalm</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
@@ -53879,22 +53925,27 @@
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O718" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y718" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="Z718" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
         </is>
       </c>
     </row>
@@ -53904,17 +53955,22 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>108771377911</t>
+          <t>311307032268</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Facilities and Information Technology Infrastructure Assessment</t>
+          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>Housing Authority of the City of Passaic</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H719" t="inlineStr">
@@ -53924,22 +53980,27 @@
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O719" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y719" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Z719" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
         </is>
       </c>
     </row>
@@ -53949,17 +54010,27 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>120893940419</t>
+          <t>135161266908</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>#25-038-RFP)</t>
+          <t>RFQ1757840</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
+          <t>25-51-A-PMO-ES-SSN</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>U.S. Department of the Treasury</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -53974,27 +54045,27 @@
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="M720" t="inlineStr">
-        <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="N720" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O720" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y720" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z720" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
         </is>
       </c>
     </row>
@@ -54004,12 +54075,12 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>114864654049</t>
+          <t>110691507903</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>M365 Tenant backup</t>
+          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -54027,19 +54098,22 @@
           <t>2026-03-31</t>
         </is>
       </c>
+      <c r="L721" s="65" t="n">
+        <v>96200</v>
+      </c>
       <c r="O721" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y721" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z721" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
         </is>
       </c>
     </row>
@@ -54049,27 +54123,17 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>317194645231</t>
-        </is>
-      </c>
-      <c r="C722" t="inlineStr">
-        <is>
-          <t>BCH-C25-008</t>
+          <t>110691507909</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Data Migration (CMAS RFP)</t>
-        </is>
-      </c>
-      <c r="E722" t="inlineStr">
-        <is>
-          <t>Business, Consumer Services and Housing Agency</t>
+          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
@@ -54079,27 +54143,22 @@
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="M722" t="inlineStr">
-        <is>
-          <t>Modernization / Migration</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="O722" t="inlineStr">
         <is>
-          <t>Darshan Tiwari</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y722" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z722" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
         </is>
       </c>
     </row>
@@ -54109,27 +54168,17 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>317945474767</t>
+          <t>108771377911</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>ServiceNow Technical Services</t>
-        </is>
-      </c>
-      <c r="E723" t="inlineStr">
-        <is>
-          <t>City of Sacramento</t>
-        </is>
-      </c>
-      <c r="F723" t="inlineStr">
-        <is>
-          <t>California</t>
+          <t>Facilities and Information Technology Infrastructure Assessment</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
@@ -54139,22 +54188,22 @@
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="O723" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y723" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z723" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
         </is>
       </c>
     </row>
@@ -54164,47 +54213,372 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
+          <t>120893940419</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>#25-038-RFP)</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="O724" t="inlineStr">
+        <is>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="Y724" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="Z724" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="n">
+        <v>724</v>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>114864654049</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>M365 Tenant backup</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O725" t="inlineStr">
+        <is>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="Y725" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z725" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="n">
+        <v>725</v>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>317194645231</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>BCH-C25-008</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Data Migration (CMAS RFP)</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>Business, Consumer Services and Housing Agency</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>Modernization / Migration</t>
+        </is>
+      </c>
+      <c r="O726" t="inlineStr">
+        <is>
+          <t>Darshan Tiwari</t>
+        </is>
+      </c>
+      <c r="Y726" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z726" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="n">
+        <v>726</v>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>317945474767</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>ServiceNow Technical Services</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>City of Sacramento</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O727" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y727" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z727" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="n">
+        <v>727</v>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>325178884841</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Test RFX (Please Ignore)</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>Test associated agency for trello</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="O728" t="inlineStr">
+        <is>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="Y728" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z728" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="n">
+        <v>728</v>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
           <t>317911067336</t>
         </is>
       </c>
-      <c r="D724" t="inlineStr">
+      <c r="D729" t="inlineStr">
         <is>
           <t>Enterprise Data Warehouse</t>
         </is>
       </c>
-      <c r="E724" t="inlineStr">
+      <c r="E729" t="inlineStr">
         <is>
           <t>Michigan Department of Technology Management and Budget</t>
         </is>
       </c>
-      <c r="G724" t="inlineStr">
+      <c r="G729" t="inlineStr">
         <is>
           <t>RFx Cancelled</t>
         </is>
       </c>
-      <c r="H724" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J724" t="inlineStr">
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="O724" t="inlineStr">
+      <c r="O729" t="inlineStr">
         <is>
           <t>Ashutosh Chauhan</t>
         </is>
       </c>
-      <c r="Y724" t="inlineStr">
+      <c r="Y729" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="Z724" t="inlineStr">
+      <c r="Z729" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="n">
+        <v>729</v>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>321765371626</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>207-26</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Professional and Consulting Services for Strategy and Technology Division</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>Fulton County Schools</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="O730" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y730" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="Z730" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765371626</t>
         </is>
       </c>
     </row>
@@ -54225,7 +54599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA88"/>
+  <dimension ref="A1:AA89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -62106,6 +62480,61 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>325178884841</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Test RFX (Please Ignore)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Test associated agency for trello</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AA85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-05-14 12:31 EDT</t>
+          <t>2026-05-15 11:07 EDT</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA730"/>
+  <dimension ref="A1:AA733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -52632,17 +52632,22 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>321691658976</t>
+          <t>317946186441</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>6483</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>OFF - Managed Service Provider (MSP) – IT &amp; Microsoft Cloud Services</t>
+          <t>Network Penetration Testing Services</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>Phelps County Sheriff’s Department (PCSD)</t>
+          <t>Kent County</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
@@ -52657,40 +52662,40 @@
       </c>
       <c r="J699" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="K699" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="L699" s="65" t="n">
-        <v>173400</v>
+        <v>29390</v>
       </c>
       <c r="M699" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N699" t="inlineStr">
         <is>
-          <t>Offline;Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O699" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y699" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z699" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321691658976</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317946186441</t>
         </is>
       </c>
     </row>
@@ -52700,17 +52705,17 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>320137093859</t>
+          <t>321691658976</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>OFFLINE Annual Contract For Managed It Services For Youth Lab</t>
+          <t>OFF - Managed Service Provider (MSP) – IT &amp; Microsoft Cloud Services</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>City of Visalia</t>
+          <t>Phelps County Sheriff’s Department (PCSD)</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
@@ -52725,7 +52730,7 @@
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="K700" t="inlineStr">
@@ -52733,24 +52738,32 @@
           <t>2026-05-13</t>
         </is>
       </c>
+      <c r="L700" s="65" t="n">
+        <v>173400</v>
+      </c>
       <c r="M700" t="inlineStr">
         <is>
           <t>Managed Services (MSP)</t>
         </is>
       </c>
+      <c r="N700" t="inlineStr">
+        <is>
+          <t>Offline;Email</t>
+        </is>
+      </c>
       <c r="O700" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y700" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z700" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320137093859</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321691658976</t>
         </is>
       </c>
     </row>
@@ -52760,17 +52773,17 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>321010642622</t>
+          <t>320137093859</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>OFFLINE Annual Contract For Managed It Services For Youth Lab</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>I-195 Redevelopment District</t>
+          <t>City of Visalia</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
@@ -52785,7 +52798,7 @@
       </c>
       <c r="J701" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="K701" t="inlineStr">
@@ -52793,32 +52806,24 @@
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="L701" s="65" t="n">
-        <v>78900</v>
-      </c>
       <c r="M701" t="inlineStr">
         <is>
           <t>Managed Services (MSP)</t>
         </is>
       </c>
-      <c r="N701" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
       <c r="O701" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y701" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="Z701" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321010642622</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320137093859</t>
         </is>
       </c>
     </row>
@@ -52828,17 +52833,22 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>322527283932</t>
+          <t>321010642622</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>Test RFX (please ignore)</t>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>I-195 Redevelopment District</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
@@ -52846,29 +52856,42 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L702" s="65" t="n">
+        <v>78900</v>
+      </c>
       <c r="M702" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N702" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O702" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
-        </is>
-      </c>
-      <c r="S702" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y702" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="Z702" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321010642622</t>
         </is>
       </c>
     </row>
@@ -52878,32 +52901,22 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>116977709771</t>
-        </is>
-      </c>
-      <c r="C703" t="inlineStr">
-        <is>
-          <t>RFP-25-0005</t>
+          <t>321765372642</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
+          <t>Unified Endpoint Management (UEM) Managed Services Program</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>NeighborWorks America</t>
-        </is>
-      </c>
-      <c r="F703" t="inlineStr">
-        <is>
-          <t>Washington, D.C.</t>
+          <t>Southeastern Pennsylvania Transportation Authority</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
@@ -52911,39 +52924,39 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="M703" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N703" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O703" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
-        </is>
-      </c>
-      <c r="S703" t="inlineStr">
-        <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="U703" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y703" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z703" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
-        </is>
-      </c>
-      <c r="AA703" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765372642</t>
         </is>
       </c>
     </row>
@@ -52953,22 +52966,17 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>145081112265</t>
+          <t>323237511900</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>Technology Strategic Management Consulting</t>
+          <t>Workday On-Demand Support Services  &amp; Workday Managed Services - RFI</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>State of Colorado, the Office of Information Technology (OIT)</t>
-        </is>
-      </c>
-      <c r="F704" t="inlineStr">
-        <is>
-          <t>Colorado</t>
+          <t>Bexar County</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
@@ -52983,7 +52991,12 @@
       </c>
       <c r="J704" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="M704" t="inlineStr">
@@ -52993,17 +53006,17 @@
       </c>
       <c r="O704" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Srikrishnadeva D</t>
         </is>
       </c>
       <c r="Y704" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z704" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323237511900</t>
         </is>
       </c>
     </row>
@@ -53013,27 +53026,17 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>166098266830</t>
+          <t>322527283932</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
-        </is>
-      </c>
-      <c r="E705" t="inlineStr">
-        <is>
-          <t>Mecklenburg County</t>
-        </is>
-      </c>
-      <c r="F705" t="inlineStr">
-        <is>
-          <t>North Carolina</t>
+          <t>Test RFX (please ignore)</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
@@ -53041,29 +53044,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J705" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
       <c r="M705" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O705" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="S705" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y705" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z705" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
         </is>
       </c>
     </row>
@@ -53073,27 +53076,32 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>180166400720</t>
+          <t>116977709771</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>RFP-25-0005</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>Central Ohio Transit Authority</t>
+          <t>NeighborWorks America</t>
         </is>
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
@@ -53101,24 +53109,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J706" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O706" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="S706" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="U706" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Y706" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z706" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+        </is>
+      </c>
+      <c r="AA706" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -53128,32 +53151,27 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>182404957915</t>
-        </is>
-      </c>
-      <c r="C707" t="inlineStr">
-        <is>
-          <t>PWE-10.08.2025</t>
+          <t>145081112265</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>PWE Power BI Dashboard</t>
+          <t>Technology Strategic Management Consulting</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>City of Issaquah</t>
+          <t>State of Colorado, the Office of Information Technology (OIT)</t>
         </is>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
@@ -53163,27 +53181,27 @@
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="M707" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O707" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y707" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z707" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
         </is>
       </c>
     </row>
@@ -53193,32 +53211,27 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>108771177151</t>
-        </is>
-      </c>
-      <c r="C708" t="inlineStr">
-        <is>
-          <t>791202505005</t>
+          <t>166098266830</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>Government Consulting Services</t>
+          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>North Central Texas Council of Governments</t>
+          <t>Mecklenburg County</t>
         </is>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>TEXAS</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
@@ -53228,27 +53241,27 @@
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="N708" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O708" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y708" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z708" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
         </is>
       </c>
     </row>
@@ -53258,27 +53271,22 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>120893940416</t>
-        </is>
-      </c>
-      <c r="C709" t="inlineStr">
-        <is>
-          <t>DQ SAAA #2026000004</t>
+          <t>180166400720</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>Online Content Learning</t>
+          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>State of Colorado Department of Regulatory Agencies</t>
+          <t>Central Ohio Transit Authority</t>
         </is>
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
@@ -53293,15 +53301,7 @@
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L709" s="65" t="n">
-        <v>67300</v>
-      </c>
-      <c r="M709" t="inlineStr">
-        <is>
-          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="O709" t="inlineStr">
@@ -53311,12 +53311,12 @@
       </c>
       <c r="Y709" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="Z709" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
         </is>
       </c>
     </row>
@@ -53326,27 +53326,32 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>199601365715</t>
+          <t>182404957915</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>PWE-10.08.2025</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>Contracted IT Support Services</t>
+          <t>PWE Power BI Dashboard</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>ECS4Kids</t>
+          <t>City of Issaquah</t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
@@ -53356,20 +53361,12 @@
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="L710" s="65" t="n">
-        <v>291141</v>
+          <t>2025-10-29</t>
+        </is>
       </c>
       <c r="M710" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N710" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O710" t="inlineStr">
@@ -53379,12 +53376,12 @@
       </c>
       <c r="Y710" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Z710" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
         </is>
       </c>
     </row>
@@ -53394,55 +53391,47 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>140123456196</t>
+          <t>108771177151</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>24-RFP-10</t>
+          <t>791202505005</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+          <t>Government Consulting Services</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+          <t>North Central Texas Council of Governments</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>TEXAS</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I711" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J711" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L711" s="65" t="n">
-        <v>18620</v>
-      </c>
-      <c r="M711" t="inlineStr">
-        <is>
-          <t>Training</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="N711" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O711" t="inlineStr">
@@ -53450,44 +53439,14 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="P711" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q711" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="S711" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="U711" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="V711" t="inlineStr">
-        <is>
-          <t>In Process</t>
-        </is>
-      </c>
       <c r="Y711" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="Z711" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
-        </is>
-      </c>
-      <c r="AA711" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
         </is>
       </c>
     </row>
@@ -53497,27 +53456,32 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>261982669555</t>
+          <t>120893940416</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>DQ SAAA #2026000004</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>IT Backfill for ERP Configuration (SOW 2)</t>
+          <t>Online Content Learning</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>Madison Metropolitan Sewerage District</t>
+          <t>State of Colorado Department of Regulatory Agencies</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
@@ -53527,15 +53491,15 @@
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="L712" s="65" t="n">
-        <v>157000</v>
+        <v>67300</v>
       </c>
       <c r="M712" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O712" t="inlineStr">
@@ -53543,34 +53507,14 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="S712" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="U712" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="V712" t="inlineStr">
-        <is>
-          <t>In Process</t>
-        </is>
-      </c>
       <c r="Y712" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z712" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
-        </is>
-      </c>
-      <c r="AA712" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
         </is>
       </c>
     </row>
@@ -53580,22 +53524,22 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>278519751386</t>
+          <t>199601365715</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>Data Warehousing Services</t>
+          <t>Contracted IT Support Services</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allen Town School District </t>
+          <t>ECS4Kids</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -53610,32 +53554,35 @@
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="L713" s="65" t="n">
+        <v>291141</v>
       </c>
       <c r="M713" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N713" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O713" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y713" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z713" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
         </is>
       </c>
     </row>
@@ -53645,62 +53592,100 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>259790359234</t>
+          <t>140123456196</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>601440000049523</t>
+          <t>24-RFP-10</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>Managed Application Services: Application Development and Maintenance Services</t>
+          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Texas Department of Transportation</t>
+          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
-        </is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L714" s="65" t="n">
+        <v>18620</v>
       </c>
       <c r="M714" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O714" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P714" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q714" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="S714" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="U714" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="V714" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y714" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z714" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
+        </is>
+      </c>
+      <c r="AA714" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -53710,27 +53695,27 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>277652547262</t>
+          <t>261982669555</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
+          <t>IT Backfill for ERP Configuration (SOW 2)</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>District of Columbia Housing Finance Agency</t>
+          <t>Madison Metropolitan Sewerage District</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
@@ -53740,32 +53725,50 @@
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
-        </is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="L715" s="65" t="n">
+        <v>157000</v>
       </c>
       <c r="M715" t="inlineStr">
         <is>
-          <t>Consulting;Training</t>
-        </is>
-      </c>
-      <c r="N715" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O715" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S715" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="U715" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="V715" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y715" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z715" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
+        </is>
+      </c>
+      <c r="AA715" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -53775,22 +53778,22 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>269507522240</t>
+          <t>278519751386</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
+          <t>Data Warehousing Services</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Central Midlands Regional Transit Authority</t>
+          <t xml:space="preserve">Allen Town School District </t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -53805,27 +53808,32 @@
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="M716" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N716" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O716" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y716" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Z716" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
         </is>
       </c>
     </row>
@@ -53835,27 +53843,32 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>294055526085</t>
+          <t>259790359234</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>601440000049523</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Oracle Managed Services and Testing as a Service Support</t>
+          <t>Managed Application Services: Application Development and Maintenance Services</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>CITY OF DURHAM</t>
+          <t>Texas Department of Transportation</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
@@ -53865,7 +53878,7 @@
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="M717" t="inlineStr">
@@ -53875,17 +53888,17 @@
       </c>
       <c r="O717" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y717" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z717" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
         </is>
       </c>
     </row>
@@ -53895,22 +53908,22 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>305430641393</t>
+          <t>277652547262</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>OFF - Information Technology Managed Services</t>
+          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>County of Montcalm</t>
+          <t>District of Columbia Housing Finance Agency</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -53925,27 +53938,32 @@
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="M718" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting;Training</t>
+        </is>
+      </c>
+      <c r="N718" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O718" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y718" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Z718" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
         </is>
       </c>
     </row>
@@ -53955,17 +53973,22 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>311307032268</t>
+          <t>269507522240</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>Housing Authority of the City of Passaic</t>
+          <t>Central Midlands Regional Transit Authority</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -53980,7 +54003,7 @@
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="M719" t="inlineStr">
@@ -53995,12 +54018,12 @@
       </c>
       <c r="Y719" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z719" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
         </is>
       </c>
     </row>
@@ -54010,32 +54033,27 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>135161266908</t>
-        </is>
-      </c>
-      <c r="C720" t="inlineStr">
-        <is>
-          <t>RFQ1757840</t>
+          <t>294055526085</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>25-51-A-PMO-ES-SSN</t>
+          <t>Oracle Managed Services and Testing as a Service Support</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>U.S. Department of the Treasury</t>
+          <t>CITY OF DURHAM</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
@@ -54045,27 +54063,27 @@
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="N720" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O720" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y720" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Z720" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
         </is>
       </c>
     </row>
@@ -54075,17 +54093,27 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>110691507903</t>
+          <t>305430641393</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
+          <t>OFF - Information Technology Managed Services</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>County of Montcalm</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
@@ -54095,25 +54123,27 @@
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="L721" s="65" t="n">
-        <v>96200</v>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
       </c>
       <c r="O721" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y721" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="Z721" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
         </is>
       </c>
     </row>
@@ -54123,17 +54153,22 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>110691507909</t>
+          <t>311307032268</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
+          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>Housing Authority of the City of Passaic</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
@@ -54143,22 +54178,27 @@
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O722" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y722" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Z722" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
         </is>
       </c>
     </row>
@@ -54168,12 +54208,27 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>108771377911</t>
+          <t>135161266908</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>RFQ1757840</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>Facilities and Information Technology Infrastructure Assessment</t>
+          <t>25-51-A-PMO-ES-SSN</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>U.S. Department of the Treasury</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -54188,7 +54243,12 @@
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="N723" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O723" t="inlineStr">
@@ -54198,12 +54258,12 @@
       </c>
       <c r="Y723" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z723" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
         </is>
       </c>
     </row>
@@ -54213,17 +54273,12 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>120893940419</t>
-        </is>
-      </c>
-      <c r="C724" t="inlineStr">
-        <is>
-          <t>#25-038-RFP)</t>
+          <t>110691507903</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
+          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -54241,24 +54296,22 @@
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="M724" t="inlineStr">
-        <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
-        </is>
+      <c r="L724" s="65" t="n">
+        <v>96200</v>
       </c>
       <c r="O724" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y724" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z724" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
         </is>
       </c>
     </row>
@@ -54268,12 +54321,12 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>114864654049</t>
+          <t>110691507909</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>M365 Tenant backup</t>
+          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
@@ -54293,17 +54346,17 @@
       </c>
       <c r="O725" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y725" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z725" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
         </is>
       </c>
     </row>
@@ -54313,27 +54366,17 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>317194645231</t>
-        </is>
-      </c>
-      <c r="C726" t="inlineStr">
-        <is>
-          <t>BCH-C25-008</t>
+          <t>108771377911</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>Data Migration (CMAS RFP)</t>
-        </is>
-      </c>
-      <c r="E726" t="inlineStr">
-        <is>
-          <t>Business, Consumer Services and Housing Agency</t>
+          <t>Facilities and Information Technology Infrastructure Assessment</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
@@ -54343,27 +54386,22 @@
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="M726" t="inlineStr">
-        <is>
-          <t>Modernization / Migration</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="O726" t="inlineStr">
         <is>
-          <t>Darshan Tiwari</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y726" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z726" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
         </is>
       </c>
     </row>
@@ -54373,27 +54411,22 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>317945474767</t>
+          <t>120893940419</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>#25-038-RFP)</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>ServiceNow Technical Services</t>
-        </is>
-      </c>
-      <c r="E727" t="inlineStr">
-        <is>
-          <t>City of Sacramento</t>
-        </is>
-      </c>
-      <c r="F727" t="inlineStr">
-        <is>
-          <t>California</t>
+          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
@@ -54403,22 +54436,27 @@
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="M727" t="inlineStr">
+        <is>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O727" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="Y727" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z727" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
         </is>
       </c>
     </row>
@@ -54428,22 +54466,17 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>325178884841</t>
+          <t>114864654049</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>Test RFX (Please Ignore)</t>
-        </is>
-      </c>
-      <c r="E728" t="inlineStr">
-        <is>
-          <t>Test associated agency for trello</t>
+          <t>M365 Tenant backup</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
@@ -54453,27 +54486,22 @@
       </c>
       <c r="J728" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="M728" t="inlineStr">
-        <is>
-          <t>Training</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="O728" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="Y728" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Z728" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
         </is>
       </c>
     </row>
@@ -54483,17 +54511,22 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>317911067336</t>
+          <t>317194645231</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>BCH-C25-008</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse</t>
+          <t>Data Migration (CMAS RFP)</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>Michigan Department of Technology Management and Budget</t>
+          <t>Business, Consumer Services and Housing Agency</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
@@ -54508,22 +54541,27 @@
       </c>
       <c r="J729" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O729" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Darshan Tiwari</t>
         </is>
       </c>
       <c r="Y729" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="Z729" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
         </is>
       </c>
     </row>
@@ -54533,50 +54571,210 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
+          <t>317945474767</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>ServiceNow Technical Services</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>City of Sacramento</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O730" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y730" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z730" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="n">
+        <v>730</v>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>325178884841</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Test RFX (Please Ignore)</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>Test associated agency for trello</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="O731" t="inlineStr">
+        <is>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="Y731" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z731" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="n">
+        <v>731</v>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>317911067336</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Enterprise Data Warehouse</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>Michigan Department of Technology Management and Budget</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O732" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y732" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z732" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="n">
+        <v>732</v>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
           <t>321765371626</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr">
+      <c r="C733" t="inlineStr">
         <is>
           <t>207-26</t>
         </is>
       </c>
-      <c r="D730" t="inlineStr">
+      <c r="D733" t="inlineStr">
         <is>
           <t>Professional and Consulting Services for Strategy and Technology Division</t>
         </is>
       </c>
-      <c r="E730" t="inlineStr">
+      <c r="E733" t="inlineStr">
         <is>
           <t>Fulton County Schools</t>
         </is>
       </c>
-      <c r="G730" t="inlineStr">
+      <c r="G733" t="inlineStr">
         <is>
           <t>RFx Cancelled</t>
         </is>
       </c>
-      <c r="H730" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J730" t="inlineStr">
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="O730" t="inlineStr">
+      <c r="O733" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
-      <c r="Y730" t="inlineStr">
+      <c r="Y733" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="Z730" t="inlineStr">
+      <c r="Z733" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765371626</t>
         </is>

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-05-15 11:07 EDT</t>
+          <t>2026-05-15 14:51 EDT</t>
         </is>
       </c>
     </row>
@@ -52511,12 +52511,17 @@
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
@@ -52545,6 +52550,16 @@
       <c r="O697" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="P697" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q697" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Y697" t="inlineStr">

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-05-15 14:51 EDT</t>
+          <t>2026-05-19 08:40 EDT</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>640</v>
+        <v>645</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA733"/>
+  <dimension ref="A1:AA738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -44006,22 +44006,27 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>316123950830</t>
+          <t>316626904813</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>26-004</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>AI Readiness Training</t>
+          <t>ManageEngine Endpoint Central Cloud UEM Subscription</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>Cincinnati Metropolitan Housing Authority</t>
+          <t>City of Dania Beach</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
@@ -44036,7 +44041,7 @@
       </c>
       <c r="J576" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="K576" t="inlineStr">
@@ -44044,24 +44049,32 @@
           <t>2026-03-24</t>
         </is>
       </c>
+      <c r="L576" s="65" t="n">
+        <v>9175</v>
+      </c>
       <c r="M576" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Reseller</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O576" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y576" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="Z576" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316123950830</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316626904813</t>
         </is>
       </c>
     </row>
@@ -44071,27 +44084,22 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>316626904813</t>
-        </is>
-      </c>
-      <c r="C577" t="inlineStr">
-        <is>
-          <t>26-004</t>
+          <t>316971216590</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>ManageEngine Endpoint Central Cloud UEM Subscription</t>
+          <t>Airport Technology Consulting Services</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>City of Dania Beach</t>
+          <t>Metropolitan Washington Airports Authority</t>
         </is>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
@@ -44114,17 +44122,9 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="L577" s="65" t="n">
-        <v>9175</v>
-      </c>
       <c r="M577" t="inlineStr">
         <is>
-          <t>Reseller</t>
-        </is>
-      </c>
-      <c r="N577" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O577" t="inlineStr">
@@ -44134,12 +44134,12 @@
       </c>
       <c r="Y577" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Z577" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316626904813</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316971216590</t>
         </is>
       </c>
     </row>
@@ -44149,22 +44149,27 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>316971216590</t>
+          <t>310413135583</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RFP NO. 4-2026 </t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>Airport Technology Consulting Services</t>
+          <t xml:space="preserve">TO SELECT A CONSULTANT TO DEVELOP A TECHNOLOGY STRATEGIC PLAN </t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>Metropolitan Washington Airports Authority</t>
+          <t xml:space="preserve">OHIO TURNPIKE AND INFRASTRUCTURE COMMISSION </t>
         </is>
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
@@ -44179,19 +44184,24 @@
       </c>
       <c r="J578" t="inlineStr">
         <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
       <c r="M578" t="inlineStr">
         <is>
           <t>Consulting</t>
         </is>
       </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="O578" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
@@ -44199,12 +44209,12 @@
       </c>
       <c r="Y578" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="Z578" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316971216590</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/310413135583</t>
         </is>
       </c>
     </row>
@@ -44214,32 +44224,27 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>310413135583</t>
-        </is>
-      </c>
-      <c r="C579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RFP NO. 4-2026 </t>
+          <t>316634162921</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t xml:space="preserve">TO SELECT A CONSULTANT TO DEVELOP A TECHNOLOGY STRATEGIC PLAN </t>
+          <t>Information Technology Consulting and Technology Support Services</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHIO TURNPIKE AND INFRASTRUCTURE COMMISSION </t>
+          <t>Seaside Heights Borough</t>
         </is>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -44249,7 +44254,7 @@
       </c>
       <c r="J579" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="K579" t="inlineStr">
@@ -44257,29 +44262,32 @@
           <t>2026-03-24</t>
         </is>
       </c>
+      <c r="L579" s="65" t="n">
+        <v>54820</v>
+      </c>
       <c r="M579" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N579" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O579" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y579" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Z579" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/310413135583</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316634162921</t>
         </is>
       </c>
     </row>
@@ -44289,22 +44297,22 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>316634162921</t>
+          <t>316123950830</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>Information Technology Consulting and Technology Support Services</t>
+          <t>AI Readiness Training</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>Seaside Heights Borough</t>
+          <t>Cincinnati Metropolitan Housing Authority</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
@@ -44319,7 +44327,7 @@
       </c>
       <c r="J580" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="K580" t="inlineStr">
@@ -44327,17 +44335,9 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="L580" s="65" t="n">
-        <v>54820</v>
-      </c>
       <c r="M580" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N580" t="inlineStr">
-        <is>
-          <t>Offline</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O580" t="inlineStr">
@@ -44347,12 +44347,12 @@
       </c>
       <c r="Y580" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="Z580" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316634162921</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316123950830</t>
         </is>
       </c>
     </row>
@@ -53041,17 +53041,22 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>322527283932</t>
+          <t>321711122109</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>Test RFX (please ignore)</t>
+          <t>Managed Information Technology Services</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>The Education Cooperative</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
@@ -53059,29 +53064,39 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
       <c r="M705" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N705" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O705" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
-        </is>
-      </c>
-      <c r="S705" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y705" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z705" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321711122109</t>
         </is>
       </c>
     </row>
@@ -53091,32 +53106,22 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>116977709771</t>
-        </is>
-      </c>
-      <c r="C706" t="inlineStr">
-        <is>
-          <t>RFP-25-0005</t>
+          <t>323518611139</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
+          <t>Request for Proposals Information Technology (IT) Managed Services &amp; Strategic Support</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>NeighborWorks America</t>
-        </is>
-      </c>
-      <c r="F706" t="inlineStr">
-        <is>
-          <t>Washington, D.C.</t>
+          <t xml:space="preserve">City of Flagler Beach </t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
@@ -53124,39 +53129,39 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
       <c r="M706" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N706" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O706" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
-        </is>
-      </c>
-      <c r="S706" t="inlineStr">
-        <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="U706" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y706" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Z706" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
-        </is>
-      </c>
-      <c r="AA706" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323518611139</t>
         </is>
       </c>
     </row>
@@ -53166,22 +53171,22 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>145081112265</t>
+          <t>323230410428</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>CC/RFP 27-01</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>Technology Strategic Management Consulting</t>
+          <t>INFORMATION TECHNOLOGY SERVICES</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>State of Colorado, the Office of Information Technology (OIT)</t>
-        </is>
-      </c>
-      <c r="F707" t="inlineStr">
-        <is>
-          <t>Colorado</t>
+          <t>Brigantine Board of Education</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
@@ -53196,27 +53201,27 @@
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="M707" t="inlineStr">
-        <is>
-          <t>Consulting</t>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="O707" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y707" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z707" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323230410428</t>
         </is>
       </c>
     </row>
@@ -53226,22 +53231,17 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>166098266830</t>
+          <t>321908570850</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
+          <t>Managed IT Services</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>Mecklenburg County</t>
-        </is>
-      </c>
-      <c r="F708" t="inlineStr">
-        <is>
-          <t>North Carolina</t>
+          <t>Town of Butner</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
@@ -53256,12 +53256,22 @@
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M708" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N708" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O708" t="inlineStr">
@@ -53271,12 +53281,12 @@
       </c>
       <c r="Y708" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Z708" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321908570850</t>
         </is>
       </c>
     </row>
@@ -53286,27 +53296,27 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>180166400720</t>
+          <t>325512086219</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
+          <t>RFQ : AI Development Tool</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>Central Ohio Transit Authority</t>
+          <t>Orange County</t>
         </is>
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H709" t="inlineStr">
@@ -53316,22 +53326,40 @@
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L709" s="65" t="n">
+        <v>1341.78</v>
+      </c>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>Reseller</t>
+        </is>
+      </c>
+      <c r="N709" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O709" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y709" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z709" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325512086219</t>
         </is>
       </c>
     </row>
@@ -53341,32 +53369,17 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>182404957915</t>
-        </is>
-      </c>
-      <c r="C710" t="inlineStr">
-        <is>
-          <t>PWE-10.08.2025</t>
+          <t>322527283932</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>PWE Power BI Dashboard</t>
-        </is>
-      </c>
-      <c r="E710" t="inlineStr">
-        <is>
-          <t>City of Issaquah</t>
-        </is>
-      </c>
-      <c r="F710" t="inlineStr">
-        <is>
-          <t>Washington</t>
+          <t>Test RFX (please ignore)</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
@@ -53374,29 +53387,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J710" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
       <c r="M710" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O710" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="S710" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y710" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z710" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
         </is>
       </c>
     </row>
@@ -53406,32 +53419,32 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>108771177151</t>
+          <t>116977709771</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>791202505005</t>
+          <t>RFP-25-0005</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>Government Consulting Services</t>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>North Central Texas Council of Governments</t>
+          <t>NeighborWorks America</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>TEXAS</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
@@ -53439,29 +53452,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J711" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="N711" t="inlineStr">
-        <is>
-          <t>Portal</t>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O711" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="S711" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="U711" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Y711" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z711" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+        </is>
+      </c>
+      <c r="AA711" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -53471,22 +53494,17 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>120893940416</t>
-        </is>
-      </c>
-      <c r="C712" t="inlineStr">
-        <is>
-          <t>DQ SAAA #2026000004</t>
+          <t>145081112265</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>Online Content Learning</t>
+          <t>Technology Strategic Management Consulting</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>State of Colorado Department of Regulatory Agencies</t>
+          <t>State of Colorado, the Office of Information Technology (OIT)</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
@@ -53496,7 +53514,7 @@
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
@@ -53506,15 +53524,12 @@
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L712" s="65" t="n">
-        <v>67300</v>
+          <t>2025-10-01</t>
+        </is>
       </c>
       <c r="M712" t="inlineStr">
         <is>
-          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O712" t="inlineStr">
@@ -53524,12 +53539,12 @@
       </c>
       <c r="Y712" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z712" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
         </is>
       </c>
     </row>
@@ -53539,22 +53554,22 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>199601365715</t>
+          <t>166098266830</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>Contracted IT Support Services</t>
+          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>ECS4Kids</t>
+          <t>Mecklenburg County</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -53569,35 +53584,27 @@
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="L713" s="65" t="n">
-        <v>291141</v>
+          <t>2025-10-07</t>
+        </is>
       </c>
       <c r="M713" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N713" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O713" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y713" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z713" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
         </is>
       </c>
     </row>
@@ -53607,55 +53614,37 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>140123456196</t>
-        </is>
-      </c>
-      <c r="C714" t="inlineStr">
-        <is>
-          <t>24-RFP-10</t>
+          <t>180166400720</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+          <t>Central Ohio Transit Authority</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I714" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L714" s="65" t="n">
-        <v>18620</v>
-      </c>
-      <c r="M714" t="inlineStr">
-        <is>
-          <t>Training</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="O714" t="inlineStr">
@@ -53663,44 +53652,14 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="P714" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q714" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="S714" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="U714" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="V714" t="inlineStr">
-        <is>
-          <t>In Process</t>
-        </is>
-      </c>
       <c r="Y714" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="Z714" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
-        </is>
-      </c>
-      <c r="AA714" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
         </is>
       </c>
     </row>
@@ -53710,27 +53669,32 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>261982669555</t>
+          <t>182404957915</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>PWE-10.08.2025</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>IT Backfill for ERP Configuration (SOW 2)</t>
+          <t>PWE Power BI Dashboard</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Madison Metropolitan Sewerage District</t>
+          <t>City of Issaquah</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
@@ -53740,50 +53704,27 @@
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="L715" s="65" t="n">
-        <v>157000</v>
+          <t>2025-10-29</t>
+        </is>
       </c>
       <c r="M715" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O715" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="S715" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="U715" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="V715" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y715" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Z715" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
-        </is>
-      </c>
-      <c r="AA715" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
         </is>
       </c>
     </row>
@@ -53793,27 +53734,32 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>278519751386</t>
+          <t>108771177151</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>791202505005</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Data Warehousing Services</t>
+          <t>Government Consulting Services</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allen Town School District </t>
+          <t>North Central Texas Council of Governments</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>TEXAS</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
@@ -53823,32 +53769,27 @@
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="M716" t="inlineStr">
-        <is>
-          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="N716" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O716" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y716" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="Z716" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
         </is>
       </c>
     </row>
@@ -53858,32 +53799,32 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>259790359234</t>
+          <t>120893940416</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>601440000049523</t>
+          <t>DQ SAAA #2026000004</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Managed Application Services: Application Development and Maintenance Services</t>
+          <t>Online Content Learning</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>Texas Department of Transportation</t>
+          <t>State of Colorado Department of Regulatory Agencies</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
@@ -53893,27 +53834,30 @@
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
-        </is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="L717" s="65" t="n">
+        <v>67300</v>
       </c>
       <c r="M717" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O717" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y717" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z717" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
         </is>
       </c>
     </row>
@@ -53923,22 +53867,22 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>277652547262</t>
+          <t>199601365715</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
+          <t>Contracted IT Support Services</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>District of Columbia Housing Finance Agency</t>
+          <t>ECS4Kids</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -53953,32 +53897,35 @@
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
-        </is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="L718" s="65" t="n">
+        <v>291141</v>
       </c>
       <c r="M718" t="inlineStr">
         <is>
-          <t>Consulting;Training</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N718" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O718" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y718" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z718" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
         </is>
       </c>
     </row>
@@ -53988,57 +53935,100 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>269507522240</t>
+          <t>140123456196</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>24-RFP-10</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
+          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>Central Midlands Regional Transit Authority</t>
+          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
-        </is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L719" s="65" t="n">
+        <v>18620</v>
       </c>
       <c r="M719" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O719" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P719" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q719" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="S719" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="U719" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="V719" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y719" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z719" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
+        </is>
+      </c>
+      <c r="AA719" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -54048,27 +54038,27 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>294055526085</t>
+          <t>261982669555</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>Oracle Managed Services and Testing as a Service Support</t>
+          <t>IT Backfill for ERP Configuration (SOW 2)</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>CITY OF DURHAM</t>
+          <t>Madison Metropolitan Sewerage District</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
@@ -54078,27 +54068,50 @@
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="L720" s="65" t="n">
+        <v>157000</v>
       </c>
       <c r="M720" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O720" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S720" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="U720" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="V720" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y720" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z720" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
+        </is>
+      </c>
+      <c r="AA720" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -54108,22 +54121,22 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>305430641393</t>
+          <t>278519751386</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>OFF - Information Technology Managed Services</t>
+          <t>Data Warehousing Services</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>County of Montcalm</t>
+          <t xml:space="preserve">Allen Town School District </t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -54138,27 +54151,32 @@
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="M721" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N721" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O721" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y721" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Z721" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
         </is>
       </c>
     </row>
@@ -54168,22 +54186,32 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>311307032268</t>
+          <t>259790359234</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>601440000049523</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+          <t>Managed Application Services: Application Development and Maintenance Services</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>Housing Authority of the City of Passaic</t>
+          <t>Texas Department of Transportation</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
@@ -54193,27 +54221,27 @@
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="M722" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O722" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y722" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z722" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
         </is>
       </c>
     </row>
@@ -54223,22 +54251,17 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>135161266908</t>
-        </is>
-      </c>
-      <c r="C723" t="inlineStr">
-        <is>
-          <t>RFQ1757840</t>
+          <t>277652547262</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>25-51-A-PMO-ES-SSN</t>
+          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>U.S. Department of the Treasury</t>
+          <t>District of Columbia Housing Finance Agency</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
@@ -54248,7 +54271,7 @@
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
@@ -54258,7 +54281,12 @@
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>Consulting;Training</t>
         </is>
       </c>
       <c r="N723" t="inlineStr">
@@ -54268,17 +54296,17 @@
       </c>
       <c r="O723" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y723" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Z723" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
         </is>
       </c>
     </row>
@@ -54288,17 +54316,27 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>110691507903</t>
+          <t>269507522240</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
+          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>Central Midlands Regional Transit Authority</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H724" t="inlineStr">
@@ -54308,25 +54346,27 @@
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="L724" s="65" t="n">
-        <v>96200</v>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
       </c>
       <c r="O724" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y724" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z724" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
         </is>
       </c>
     </row>
@@ -54336,17 +54376,27 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>110691507909</t>
+          <t>294055526085</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
+          <t>Oracle Managed Services and Testing as a Service Support</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>CITY OF DURHAM</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
@@ -54356,22 +54406,27 @@
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O725" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y725" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Z725" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
         </is>
       </c>
     </row>
@@ -54381,17 +54436,27 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>108771377911</t>
+          <t>305430641393</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>Facilities and Information Technology Infrastructure Assessment</t>
+          <t>OFF - Information Technology Managed Services</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>County of Montcalm</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
@@ -54401,22 +54466,27 @@
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O726" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y726" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="Z726" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
         </is>
       </c>
     </row>
@@ -54426,22 +54496,22 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>120893940419</t>
-        </is>
-      </c>
-      <c r="C727" t="inlineStr">
-        <is>
-          <t>#25-038-RFP)</t>
+          <t>311307032268</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
+          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>Housing Authority of the City of Passaic</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
@@ -54451,27 +54521,27 @@
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="M727" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O727" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y727" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Z727" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
         </is>
       </c>
     </row>
@@ -54481,12 +54551,27 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>114864654049</t>
+          <t>135161266908</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>RFQ1757840</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>M365 Tenant backup</t>
+          <t>25-51-A-PMO-ES-SSN</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>U.S. Department of the Treasury</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
@@ -54501,22 +54586,27 @@
       </c>
       <c r="J728" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="N728" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O728" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y728" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z728" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
         </is>
       </c>
     </row>
@@ -54526,27 +54616,17 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>317194645231</t>
-        </is>
-      </c>
-      <c r="C729" t="inlineStr">
-        <is>
-          <t>BCH-C25-008</t>
+          <t>110691507903</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>Data Migration (CMAS RFP)</t>
-        </is>
-      </c>
-      <c r="E729" t="inlineStr">
-        <is>
-          <t>Business, Consumer Services and Housing Agency</t>
+          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
@@ -54556,27 +54636,25 @@
       </c>
       <c r="J729" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="M729" t="inlineStr">
-        <is>
-          <t>Modernization / Migration</t>
-        </is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="L729" s="65" t="n">
+        <v>96200</v>
       </c>
       <c r="O729" t="inlineStr">
         <is>
-          <t>Darshan Tiwari</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y729" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z729" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
         </is>
       </c>
     </row>
@@ -54586,27 +54664,17 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>317945474767</t>
+          <t>110691507909</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>ServiceNow Technical Services</t>
-        </is>
-      </c>
-      <c r="E730" t="inlineStr">
-        <is>
-          <t>City of Sacramento</t>
-        </is>
-      </c>
-      <c r="F730" t="inlineStr">
-        <is>
-          <t>California</t>
+          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
@@ -54616,22 +54684,22 @@
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="O730" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y730" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z730" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
         </is>
       </c>
     </row>
@@ -54641,22 +54709,17 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>325178884841</t>
+          <t>108771377911</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Test RFX (Please Ignore)</t>
-        </is>
-      </c>
-      <c r="E731" t="inlineStr">
-        <is>
-          <t>Test associated agency for trello</t>
+          <t>Facilities and Information Technology Infrastructure Assessment</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
@@ -54666,27 +54729,22 @@
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="M731" t="inlineStr">
-        <is>
-          <t>Training</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="O731" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y731" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z731" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
         </is>
       </c>
     </row>
@@ -54696,22 +54754,22 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>317911067336</t>
+          <t>120893940419</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>#25-038-RFP)</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse</t>
-        </is>
-      </c>
-      <c r="E732" t="inlineStr">
-        <is>
-          <t>Michigan Department of Technology Management and Budget</t>
+          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
@@ -54721,22 +54779,27 @@
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O732" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="Y732" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z732" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
         </is>
       </c>
     </row>
@@ -54746,50 +54809,315 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
+          <t>114864654049</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>M365 Tenant backup</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O733" t="inlineStr">
+        <is>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="Y733" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z733" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="n">
+        <v>733</v>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>317194645231</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>BCH-C25-008</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Data Migration (CMAS RFP)</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>Business, Consumer Services and Housing Agency</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>Modernization / Migration</t>
+        </is>
+      </c>
+      <c r="O734" t="inlineStr">
+        <is>
+          <t>Darshan Tiwari</t>
+        </is>
+      </c>
+      <c r="Y734" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z734" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="n">
+        <v>734</v>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>317945474767</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>ServiceNow Technical Services</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>City of Sacramento</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O735" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y735" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z735" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="n">
+        <v>735</v>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>325178884841</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Test RFX (Please Ignore)</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>Test associated agency for trello</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="O736" t="inlineStr">
+        <is>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="Y736" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z736" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="n">
+        <v>736</v>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>317911067336</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Enterprise Data Warehouse</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>Michigan Department of Technology Management and Budget</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O737" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y737" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z737" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="n">
+        <v>737</v>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
           <t>321765371626</t>
         </is>
       </c>
-      <c r="C733" t="inlineStr">
+      <c r="C738" t="inlineStr">
         <is>
           <t>207-26</t>
         </is>
       </c>
-      <c r="D733" t="inlineStr">
+      <c r="D738" t="inlineStr">
         <is>
           <t>Professional and Consulting Services for Strategy and Technology Division</t>
         </is>
       </c>
-      <c r="E733" t="inlineStr">
+      <c r="E738" t="inlineStr">
         <is>
           <t>Fulton County Schools</t>
         </is>
       </c>
-      <c r="G733" t="inlineStr">
+      <c r="G738" t="inlineStr">
         <is>
           <t>RFx Cancelled</t>
         </is>
       </c>
-      <c r="H733" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J733" t="inlineStr">
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="O733" t="inlineStr">
+      <c r="O738" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
-      <c r="Y733" t="inlineStr">
+      <c r="Y738" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="Z733" t="inlineStr">
+      <c r="Z738" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765371626</t>
         </is>

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-05-19 08:40 EDT</t>
+          <t>2026-05-20 04:52 EDT</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA738"/>
+  <dimension ref="A1:AA739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -18432,22 +18432,27 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>212007532248</t>
+          <t>216534906589</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>#377-25RFP</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>System Wide CRM Alignment and Implementation Partner</t>
+          <t>Maintenance and Support of City Software</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>University System of New Hampshire</t>
+          <t xml:space="preserve">City of New Brunswick </t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>New Hampshire</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -18462,20 +18467,22 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="L220" s="65" t="n">
-        <v>69550</v>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance</t>
+        </is>
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -18485,12 +18492,12 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/212007532248</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/216534906589</t>
         </is>
       </c>
     </row>
@@ -18500,32 +18507,27 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>216534906589</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>#377-25RFP</t>
+          <t>212007532248</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Maintenance and Support of City Software</t>
+          <t>System Wide CRM Alignment and Implementation Partner</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">City of New Brunswick </t>
+          <t>University System of New Hampshire</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>New Hampshire</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -18535,7 +18537,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -18543,14 +18545,12 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>Support &amp; Maintenance</t>
-        </is>
+      <c r="L221" s="65" t="n">
+        <v>69550</v>
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -18560,12 +18560,12 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/216534906589</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/212007532248</t>
         </is>
       </c>
     </row>
@@ -37913,22 +37913,22 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>279234879202</t>
+          <t>280744452794</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Salesforce CRM Development and Consulting Services for Solid Waste &amp; Recycling</t>
+          <t>ADA Web Compliance and Remediation Service</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Washington County Solid Waste &amp; Recycling (WCSWR)</t>
+          <t>SUPERIOR COURT OF CALIFORNIA, COUNTY OF LOS ANGELES</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
@@ -37951,24 +37951,32 @@
           <t>2026-02-18</t>
         </is>
       </c>
+      <c r="L491" s="65" t="n">
+        <v>36400</v>
+      </c>
       <c r="M491" t="inlineStr">
         <is>
           <t>Consulting</t>
         </is>
       </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O491" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y491" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="Z491" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/279234879202</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/280744452794</t>
         </is>
       </c>
     </row>
@@ -37978,46 +37986,51 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>280744452794</t>
+          <t>277652548335</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>ADA Web Compliance and Remediation Service</t>
+          <t>Computerized Maintenance Management Systems (CMMS) Consulting Services</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT OF CALIFORNIA, COUNTY OF LOS ANGELES</t>
+          <t>Maryland Stadium Authority</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J492" t="inlineStr">
         <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
       <c r="L492" s="65" t="n">
-        <v>36400</v>
+        <v>196125</v>
       </c>
       <c r="M492" t="inlineStr">
         <is>
@@ -38026,22 +38039,27 @@
       </c>
       <c r="N492" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Portal;Email</t>
         </is>
       </c>
       <c r="O492" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="Y492" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Z492" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/280744452794</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652548335</t>
         </is>
       </c>
     </row>
@@ -38051,22 +38069,22 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>277652548335</t>
+          <t>279234879202</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Computerized Maintenance Management Systems (CMMS) Consulting Services</t>
+          <t>Salesforce CRM Development and Consulting Services for Solid Waste &amp; Recycling</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>Maryland Stadium Authority</t>
+          <t>Washington County Solid Waste &amp; Recycling (WCSWR)</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
@@ -38076,17 +38094,12 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I493" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="K493" t="inlineStr">
@@ -38094,37 +38107,24 @@
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="L493" s="65" t="n">
-        <v>196125</v>
-      </c>
       <c r="M493" t="inlineStr">
         <is>
           <t>Consulting</t>
         </is>
       </c>
-      <c r="N493" t="inlineStr">
-        <is>
-          <t>Portal;Email</t>
-        </is>
-      </c>
       <c r="O493" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
-        </is>
-      </c>
-      <c r="Q493" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y493" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Z493" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652548335</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/279234879202</t>
         </is>
       </c>
     </row>
@@ -53296,22 +53296,22 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>325512086219</t>
+          <t>323237509835</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>RFQ : AI Development Tool</t>
+          <t>Information Technology Services and Management (rebid)</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>Orange County</t>
-        </is>
-      </c>
-      <c r="F709" t="inlineStr">
-        <is>
-          <t>California</t>
+          <t>Palm Beach Metropolitan Planning Organization</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
@@ -53326,7 +53326,7 @@
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="K709" t="inlineStr">
@@ -53334,17 +53334,9 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="L709" s="65" t="n">
-        <v>1341.78</v>
-      </c>
       <c r="M709" t="inlineStr">
         <is>
-          <t>Reseller</t>
-        </is>
-      </c>
-      <c r="N709" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Managed Services (MSP);Consulting</t>
         </is>
       </c>
       <c r="O709" t="inlineStr">
@@ -53354,12 +53346,12 @@
       </c>
       <c r="Y709" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z709" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325512086219</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323237509835</t>
         </is>
       </c>
     </row>
@@ -53369,17 +53361,27 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>322527283932</t>
+          <t>325512086219</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>Test RFX (please ignore)</t>
+          <t>RFQ : AI Development Tool</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>Orange County</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>California</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
@@ -53387,29 +53389,42 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L710" s="65" t="n">
+        <v>1341.78</v>
+      </c>
       <c r="M710" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Reseller</t>
+        </is>
+      </c>
+      <c r="N710" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O710" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
-        </is>
-      </c>
-      <c r="S710" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y710" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z710" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325512086219</t>
         </is>
       </c>
     </row>
@@ -53419,32 +53434,17 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>116977709771</t>
-        </is>
-      </c>
-      <c r="C711" t="inlineStr">
-        <is>
-          <t>RFP-25-0005</t>
+          <t>322527283932</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
-        </is>
-      </c>
-      <c r="E711" t="inlineStr">
-        <is>
-          <t>NeighborWorks America</t>
-        </is>
-      </c>
-      <c r="F711" t="inlineStr">
-        <is>
-          <t>Washington, D.C.</t>
+          <t>Test RFX (please ignore)</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
@@ -53454,37 +53454,27 @@
       </c>
       <c r="M711" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O711" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Akshat Tripathi</t>
         </is>
       </c>
       <c r="S711" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="U711" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y711" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z711" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
-        </is>
-      </c>
-      <c r="AA711" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
         </is>
       </c>
     </row>
@@ -53494,27 +53484,32 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>145081112265</t>
+          <t>116977709771</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>RFP-25-0005</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>Technology Strategic Management Consulting</t>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>State of Colorado, the Office of Information Technology (OIT)</t>
+          <t>NeighborWorks America</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
@@ -53522,29 +53517,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J712" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
       <c r="M712" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O712" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="S712" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="U712" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Y712" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z712" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+        </is>
+      </c>
+      <c r="AA712" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -53554,22 +53559,22 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>166098266830</t>
+          <t>145081112265</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
+          <t>Technology Strategic Management Consulting</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>Mecklenburg County</t>
+          <t>State of Colorado, the Office of Information Technology (OIT)</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -53584,27 +53589,27 @@
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="M713" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O713" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y713" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z713" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
         </is>
       </c>
     </row>
@@ -53614,27 +53619,27 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>180166400720</t>
+          <t>166098266830</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
+          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Central Ohio Transit Authority</t>
+          <t>Mecklenburg County</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
@@ -53647,19 +53652,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>Audits and Assessment</t>
+        </is>
+      </c>
       <c r="O714" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y714" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z714" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
         </is>
       </c>
     </row>
@@ -53669,27 +53679,22 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>182404957915</t>
-        </is>
-      </c>
-      <c r="C715" t="inlineStr">
-        <is>
-          <t>PWE-10.08.2025</t>
+          <t>180166400720</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>PWE Power BI Dashboard</t>
+          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>City of Issaquah</t>
+          <t>Central Ohio Transit Authority</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -53704,27 +53709,22 @@
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="M715" t="inlineStr">
-        <is>
-          <t>Modernization / Migration</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="O715" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y715" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="Z715" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
         </is>
       </c>
     </row>
@@ -53734,27 +53734,27 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>108771177151</t>
+          <t>182404957915</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>791202505005</t>
+          <t>PWE-10.08.2025</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Government Consulting Services</t>
+          <t>PWE Power BI Dashboard</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>North Central Texas Council of Governments</t>
+          <t>City of Issaquah</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>TEXAS</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -53769,27 +53769,27 @@
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="N716" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O716" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y716" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Z716" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
         </is>
       </c>
     </row>
@@ -53799,27 +53799,27 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>120893940416</t>
+          <t>108771177151</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>DQ SAAA #2026000004</t>
+          <t>791202505005</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Online Content Learning</t>
+          <t>Government Consulting Services</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>State of Colorado Department of Regulatory Agencies</t>
+          <t>North Central Texas Council of Governments</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>TEXAS</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -53834,15 +53834,12 @@
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L717" s="65" t="n">
-        <v>67300</v>
-      </c>
-      <c r="M717" t="inlineStr">
-        <is>
-          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="N717" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O717" t="inlineStr">
@@ -53852,12 +53849,12 @@
       </c>
       <c r="Y717" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="Z717" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
         </is>
       </c>
     </row>
@@ -53867,27 +53864,32 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>199601365715</t>
+          <t>120893940416</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>DQ SAAA #2026000004</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Contracted IT Support Services</t>
+          <t>Online Content Learning</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>ECS4Kids</t>
+          <t>State of Colorado Department of Regulatory Agencies</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
@@ -53897,35 +53899,30 @@
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="L718" s="65" t="n">
-        <v>291141</v>
+        <v>67300</v>
       </c>
       <c r="M718" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N718" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O718" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y718" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z718" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
         </is>
       </c>
     </row>
@@ -53935,100 +53932,65 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>140123456196</t>
-        </is>
-      </c>
-      <c r="C719" t="inlineStr">
-        <is>
-          <t>24-RFP-10</t>
+          <t>199601365715</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+          <t>Contracted IT Support Services</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+          <t>ECS4Kids</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I719" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="L719" s="65" t="n">
-        <v>18620</v>
+        <v>291141</v>
       </c>
       <c r="M719" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N719" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O719" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="P719" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q719" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="S719" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="U719" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="V719" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y719" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z719" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
-        </is>
-      </c>
-      <c r="AA719" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
         </is>
       </c>
     </row>
@@ -54038,45 +54000,55 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>261982669555</t>
+          <t>140123456196</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>24-RFP-10</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>IT Backfill for ERP Configuration (SOW 2)</t>
+          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>Madison Metropolitan Sewerage District</t>
+          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L720" s="65" t="n">
-        <v>157000</v>
+        <v>18620</v>
       </c>
       <c r="M720" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O720" t="inlineStr">
@@ -54084,14 +54056,24 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
+      <c r="P720" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q720" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
       <c r="S720" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="U720" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="V720" t="inlineStr">
@@ -54101,12 +54083,12 @@
       </c>
       <c r="Y720" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z720" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
         </is>
       </c>
       <c r="AA720" t="inlineStr">
@@ -54121,27 +54103,27 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>278519751386</t>
+          <t>261982669555</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>Data Warehousing Services</t>
+          <t>IT Backfill for ERP Configuration (SOW 2)</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allen Town School District </t>
+          <t>Madison Metropolitan Sewerage District</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
@@ -54151,32 +54133,50 @@
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="L721" s="65" t="n">
+        <v>157000</v>
       </c>
       <c r="M721" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N721" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O721" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S721" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="U721" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="V721" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y721" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z721" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
+        </is>
+      </c>
+      <c r="AA721" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -54186,32 +54186,27 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>259790359234</t>
-        </is>
-      </c>
-      <c r="C722" t="inlineStr">
-        <is>
-          <t>601440000049523</t>
+          <t>278519751386</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Managed Application Services: Application Development and Maintenance Services</t>
+          <t>Data Warehousing Services</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>Texas Department of Transportation</t>
+          <t xml:space="preserve">Allen Town School District </t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
@@ -54221,27 +54216,32 @@
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="M722" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N722" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O722" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y722" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Z722" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
         </is>
       </c>
     </row>
@@ -54251,27 +54251,32 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>277652547262</t>
+          <t>259790359234</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>601440000049523</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
+          <t>Managed Application Services: Application Development and Maintenance Services</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>District of Columbia Housing Finance Agency</t>
+          <t>Texas Department of Transportation</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
@@ -54281,32 +54286,27 @@
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="M723" t="inlineStr">
         <is>
-          <t>Consulting;Training</t>
-        </is>
-      </c>
-      <c r="N723" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O723" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y723" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z723" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
         </is>
       </c>
     </row>
@@ -54316,22 +54316,22 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>269507522240</t>
+          <t>277652547262</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
+          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>Central Midlands Regional Transit Authority</t>
+          <t>District of Columbia Housing Finance Agency</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -54346,27 +54346,32 @@
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="M724" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting;Training</t>
+        </is>
+      </c>
+      <c r="N724" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O724" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y724" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Z724" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
         </is>
       </c>
     </row>
@@ -54376,22 +54381,22 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>294055526085</t>
+          <t>269507522240</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Oracle Managed Services and Testing as a Service Support</t>
+          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>CITY OF DURHAM</t>
+          <t>Central Midlands Regional Transit Authority</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
@@ -54406,27 +54411,27 @@
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="M725" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O725" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y725" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z725" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
         </is>
       </c>
     </row>
@@ -54436,22 +54441,22 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>305430641393</t>
+          <t>294055526085</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>OFF - Information Technology Managed Services</t>
+          <t>Oracle Managed Services and Testing as a Service Support</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>County of Montcalm</t>
+          <t>CITY OF DURHAM</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -54466,27 +54471,27 @@
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M726" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O726" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y726" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Z726" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
         </is>
       </c>
     </row>
@@ -54496,17 +54501,22 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>311307032268</t>
+          <t>305430641393</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+          <t>OFF - Information Technology Managed Services</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>Housing Authority of the City of Passaic</t>
+          <t>County of Montcalm</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
@@ -54521,7 +54531,7 @@
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M727" t="inlineStr">
@@ -54531,17 +54541,17 @@
       </c>
       <c r="O727" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y727" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="Z727" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
         </is>
       </c>
     </row>
@@ -54551,32 +54561,22 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>135161266908</t>
-        </is>
-      </c>
-      <c r="C728" t="inlineStr">
-        <is>
-          <t>RFQ1757840</t>
+          <t>311307032268</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>25-51-A-PMO-ES-SSN</t>
+          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>U.S. Department of the Treasury</t>
-        </is>
-      </c>
-      <c r="F728" t="inlineStr">
-        <is>
-          <t>Washington, D.C.</t>
+          <t>Housing Authority of the City of Passaic</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
@@ -54586,27 +54586,27 @@
       </c>
       <c r="J728" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="N728" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O728" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y728" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Z728" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
         </is>
       </c>
     </row>
@@ -54616,12 +54616,27 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>110691507903</t>
+          <t>135161266908</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>RFQ1757840</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
+          <t>25-51-A-PMO-ES-SSN</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>U.S. Department of the Treasury</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
@@ -54636,11 +54651,13 @@
       </c>
       <c r="J729" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="L729" s="65" t="n">
-        <v>96200</v>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="N729" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
       </c>
       <c r="O729" t="inlineStr">
         <is>
@@ -54649,12 +54666,12 @@
       </c>
       <c r="Y729" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z729" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
         </is>
       </c>
     </row>
@@ -54664,12 +54681,12 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>110691507909</t>
+          <t>110691507903</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
+          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
@@ -54687,6 +54704,9 @@
           <t>2026-03-31</t>
         </is>
       </c>
+      <c r="L730" s="65" t="n">
+        <v>96200</v>
+      </c>
       <c r="O730" t="inlineStr">
         <is>
           <t>Madhav Mitruka</t>
@@ -54699,7 +54719,7 @@
       </c>
       <c r="Z730" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
         </is>
       </c>
     </row>
@@ -54709,12 +54729,12 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>108771377911</t>
+          <t>110691507909</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Facilities and Information Technology Infrastructure Assessment</t>
+          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
@@ -54744,7 +54764,7 @@
       </c>
       <c r="Z731" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
         </is>
       </c>
     </row>
@@ -54754,17 +54774,12 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>120893940419</t>
-        </is>
-      </c>
-      <c r="C732" t="inlineStr">
-        <is>
-          <t>#25-038-RFP)</t>
+          <t>108771377911</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
+          <t>Facilities and Information Technology Infrastructure Assessment</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
@@ -54782,24 +54797,19 @@
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="M732" t="inlineStr">
-        <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
-        </is>
-      </c>
       <c r="O732" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y732" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z732" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
         </is>
       </c>
     </row>
@@ -54809,12 +54819,17 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>114864654049</t>
+          <t>120893940419</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>#25-038-RFP)</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>M365 Tenant backup</t>
+          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
@@ -54832,6 +54847,11 @@
           <t>2026-03-31</t>
         </is>
       </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
       <c r="O733" t="inlineStr">
         <is>
           <t>Yashaswini Gautam</t>
@@ -54839,12 +54859,12 @@
       </c>
       <c r="Y733" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z733" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
         </is>
       </c>
     </row>
@@ -54854,27 +54874,17 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>317194645231</t>
-        </is>
-      </c>
-      <c r="C734" t="inlineStr">
-        <is>
-          <t>BCH-C25-008</t>
+          <t>114864654049</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>Data Migration (CMAS RFP)</t>
-        </is>
-      </c>
-      <c r="E734" t="inlineStr">
-        <is>
-          <t>Business, Consumer Services and Housing Agency</t>
+          <t>M365 Tenant backup</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
@@ -54884,27 +54894,22 @@
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="M734" t="inlineStr">
-        <is>
-          <t>Modernization / Migration</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="O734" t="inlineStr">
         <is>
-          <t>Darshan Tiwari</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="Y734" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Z734" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
         </is>
       </c>
     </row>
@@ -54914,22 +54919,22 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>317945474767</t>
+          <t>317194645231</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>BCH-C25-008</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>ServiceNow Technical Services</t>
+          <t>Data Migration (CMAS RFP)</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>City of Sacramento</t>
-        </is>
-      </c>
-      <c r="F735" t="inlineStr">
-        <is>
-          <t>California</t>
+          <t>Business, Consumer Services and Housing Agency</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
@@ -54944,22 +54949,27 @@
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O735" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Darshan Tiwari</t>
         </is>
       </c>
       <c r="Y735" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="Z735" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
         </is>
       </c>
     </row>
@@ -54969,22 +54979,27 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>325178884841</t>
+          <t>317945474767</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>Test RFX (Please Ignore)</t>
+          <t>ServiceNow Technical Services</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>Test associated agency for trello</t>
+          <t>City of Sacramento</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>California</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -54994,27 +55009,22 @@
       </c>
       <c r="J736" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="M736" t="inlineStr">
-        <is>
-          <t>Training</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="O736" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y736" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z736" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
         </is>
       </c>
     </row>
@@ -55024,22 +55034,22 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>317911067336</t>
+          <t>325178884841</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse</t>
+          <t>Test RFX (Please Ignore)</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>Michigan Department of Technology Management and Budget</t>
+          <t>Test associated agency for trello</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
@@ -55049,22 +55059,27 @@
       </c>
       <c r="J737" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>Training</t>
         </is>
       </c>
       <c r="O737" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Akshat Tripathi</t>
         </is>
       </c>
       <c r="Y737" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Z737" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
         </is>
       </c>
     </row>
@@ -55074,50 +55089,100 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
+          <t>317911067336</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Enterprise Data Warehouse</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>Michigan Department of Technology Management and Budget</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O738" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y738" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z738" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="n">
+        <v>738</v>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
           <t>321765371626</t>
         </is>
       </c>
-      <c r="C738" t="inlineStr">
+      <c r="C739" t="inlineStr">
         <is>
           <t>207-26</t>
         </is>
       </c>
-      <c r="D738" t="inlineStr">
+      <c r="D739" t="inlineStr">
         <is>
           <t>Professional and Consulting Services for Strategy and Technology Division</t>
         </is>
       </c>
-      <c r="E738" t="inlineStr">
+      <c r="E739" t="inlineStr">
         <is>
           <t>Fulton County Schools</t>
         </is>
       </c>
-      <c r="G738" t="inlineStr">
+      <c r="G739" t="inlineStr">
         <is>
           <t>RFx Cancelled</t>
         </is>
       </c>
-      <c r="H738" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J738" t="inlineStr">
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="O738" t="inlineStr">
+      <c r="O739" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
-      <c r="Y738" t="inlineStr">
+      <c r="Y739" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="Z738" t="inlineStr">
+      <c r="Z739" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765371626</t>
         </is>

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-05-20 04:52 EDT</t>
+          <t>2026-05-21 07:36 EDT</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA739"/>
+  <dimension ref="A1:AA741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -38440,7 +38440,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -38450,7 +38450,7 @@
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="K498" t="inlineStr">
@@ -53361,22 +53361,17 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>325512086219</t>
+          <t>322912186063</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>RFQ : AI Development Tool</t>
+          <t>Multi-Factor Authentication Solution with Professional Services</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>Orange County</t>
-        </is>
-      </c>
-      <c r="F710" t="inlineStr">
-        <is>
-          <t>California</t>
+          <t>City of Battle Creek</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
@@ -53391,7 +53386,7 @@
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="K710" t="inlineStr">
@@ -53399,32 +53394,24 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="L710" s="65" t="n">
-        <v>1341.78</v>
-      </c>
       <c r="M710" t="inlineStr">
         <is>
-          <t>Reseller</t>
-        </is>
-      </c>
-      <c r="N710" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O710" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y710" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="Z710" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325512086219</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322912186063</t>
         </is>
       </c>
     </row>
@@ -53434,17 +53421,27 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>322527283932</t>
+          <t>325512086219</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>Test RFX (please ignore)</t>
+          <t>RFQ : AI Development Tool</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>Orange County</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>California</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
@@ -53452,29 +53449,42 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L711" s="65" t="n">
+        <v>1341.78</v>
+      </c>
       <c r="M711" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Reseller</t>
+        </is>
+      </c>
+      <c r="N711" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O711" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
-        </is>
-      </c>
-      <c r="S711" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y711" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z711" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325512086219</t>
         </is>
       </c>
     </row>
@@ -53484,32 +53494,27 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>116977709771</t>
+          <t>325817624291</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>RFP-25-0005</t>
+          <t>27-017-TUSD1</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
+          <t>TEMPORARY STAFFING SERVICES, AS NEEDED</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>NeighborWorks America</t>
-        </is>
-      </c>
-      <c r="F712" t="inlineStr">
-        <is>
-          <t>Washington, D.C.</t>
+          <t>Tucson Unified School District</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
@@ -53517,39 +53522,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M712" t="inlineStr">
-        <is>
-          <t>Staff Augmentation</t>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="O712" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
-        </is>
-      </c>
-      <c r="S712" t="inlineStr">
-        <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="U712" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y712" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="Z712" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
-        </is>
-      </c>
-      <c r="AA712" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325817624291</t>
         </is>
       </c>
     </row>
@@ -53559,27 +53554,17 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>145081112265</t>
+          <t>322527283932</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>Technology Strategic Management Consulting</t>
-        </is>
-      </c>
-      <c r="E713" t="inlineStr">
-        <is>
-          <t>State of Colorado, the Office of Information Technology (OIT)</t>
-        </is>
-      </c>
-      <c r="F713" t="inlineStr">
-        <is>
-          <t>Colorado</t>
+          <t>Test RFX (please ignore)</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
@@ -53587,29 +53572,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J713" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
       <c r="M713" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O713" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="S713" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y713" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z713" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
         </is>
       </c>
     </row>
@@ -53619,27 +53604,32 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>166098266830</t>
+          <t>116977709771</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>RFP-25-0005</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Mecklenburg County</t>
+          <t>NeighborWorks America</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
@@ -53647,29 +53637,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J714" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
       <c r="M714" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O714" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="S714" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="U714" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Y714" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z714" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+        </is>
+      </c>
+      <c r="AA714" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -53679,27 +53679,27 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>180166400720</t>
+          <t>145081112265</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
+          <t>Technology Strategic Management Consulting</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Central Ohio Transit Authority</t>
+          <t>State of Colorado, the Office of Information Technology (OIT)</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
@@ -53709,7 +53709,12 @@
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O715" t="inlineStr">
@@ -53719,12 +53724,12 @@
       </c>
       <c r="Y715" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z715" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
         </is>
       </c>
     </row>
@@ -53734,32 +53739,27 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>182404957915</t>
-        </is>
-      </c>
-      <c r="C716" t="inlineStr">
-        <is>
-          <t>PWE-10.08.2025</t>
+          <t>166098266830</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>PWE Power BI Dashboard</t>
+          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>City of Issaquah</t>
+          <t>Mecklenburg County</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
@@ -53769,27 +53769,27 @@
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="M716" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O716" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y716" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z716" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
         </is>
       </c>
     </row>
@@ -53799,27 +53799,22 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>108771177151</t>
-        </is>
-      </c>
-      <c r="C717" t="inlineStr">
-        <is>
-          <t>791202505005</t>
+          <t>180166400720</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Government Consulting Services</t>
+          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>North Central Texas Council of Governments</t>
+          <t>Central Ohio Transit Authority</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>TEXAS</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -53834,12 +53829,7 @@
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="N717" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="O717" t="inlineStr">
@@ -53849,12 +53839,12 @@
       </c>
       <c r="Y717" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="Z717" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
         </is>
       </c>
     </row>
@@ -53864,27 +53854,27 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>120893940416</t>
+          <t>182404957915</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>DQ SAAA #2026000004</t>
+          <t>PWE-10.08.2025</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Online Content Learning</t>
+          <t>PWE Power BI Dashboard</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>State of Colorado Department of Regulatory Agencies</t>
+          <t>City of Issaquah</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -53899,30 +53889,27 @@
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L718" s="65" t="n">
-        <v>67300</v>
+          <t>2025-10-29</t>
+        </is>
       </c>
       <c r="M718" t="inlineStr">
         <is>
-          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O718" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y718" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Z718" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
         </is>
       </c>
     </row>
@@ -53932,27 +53919,32 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>199601365715</t>
+          <t>108771177151</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>791202505005</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Contracted IT Support Services</t>
+          <t>Government Consulting Services</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>ECS4Kids</t>
+          <t>North Central Texas Council of Governments</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>TEXAS</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H719" t="inlineStr">
@@ -53962,15 +53954,7 @@
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="L719" s="65" t="n">
-        <v>291141</v>
-      </c>
-      <c r="M719" t="inlineStr">
-        <is>
-          <t>Support &amp; Maintenance</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="N719" t="inlineStr">
@@ -53980,17 +53964,17 @@
       </c>
       <c r="O719" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y719" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="Z719" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
         </is>
       </c>
     </row>
@@ -54000,55 +53984,50 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>140123456196</t>
+          <t>120893940416</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>24-RFP-10</t>
+          <t>DQ SAAA #2026000004</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+          <t>Online Content Learning</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+          <t>State of Colorado Department of Regulatory Agencies</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I720" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="L720" s="65" t="n">
-        <v>18620</v>
+        <v>67300</v>
       </c>
       <c r="M720" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O720" t="inlineStr">
@@ -54056,44 +54035,14 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="P720" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q720" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="S720" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="U720" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="V720" t="inlineStr">
-        <is>
-          <t>In Process</t>
-        </is>
-      </c>
       <c r="Y720" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z720" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
-        </is>
-      </c>
-      <c r="AA720" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
         </is>
       </c>
     </row>
@@ -54103,27 +54052,27 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>261982669555</t>
+          <t>199601365715</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>IT Backfill for ERP Configuration (SOW 2)</t>
+          <t>Contracted IT Support Services</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>Madison Metropolitan Sewerage District</t>
+          <t>ECS4Kids</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
@@ -54133,50 +54082,35 @@
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="L721" s="65" t="n">
-        <v>157000</v>
+        <v>291141</v>
       </c>
       <c r="M721" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N721" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O721" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="S721" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="U721" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="V721" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y721" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z721" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
-        </is>
-      </c>
-      <c r="AA721" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
         </is>
       </c>
     </row>
@@ -54186,62 +54120,100 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>278519751386</t>
+          <t>140123456196</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>24-RFP-10</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Data Warehousing Services</t>
+          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allen Town School District </t>
+          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L722" s="65" t="n">
+        <v>18620</v>
       </c>
       <c r="M722" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N722" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O722" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P722" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q722" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="S722" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="U722" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="V722" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y722" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z722" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
+        </is>
+      </c>
+      <c r="AA722" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -54251,32 +54223,27 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>259790359234</t>
-        </is>
-      </c>
-      <c r="C723" t="inlineStr">
-        <is>
-          <t>601440000049523</t>
+          <t>261982669555</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>Managed Application Services: Application Development and Maintenance Services</t>
+          <t>IT Backfill for ERP Configuration (SOW 2)</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>Texas Department of Transportation</t>
+          <t>Madison Metropolitan Sewerage District</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
@@ -54286,17 +54253,35 @@
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
-        </is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="L723" s="65" t="n">
+        <v>157000</v>
       </c>
       <c r="M723" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O723" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S723" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="U723" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="V723" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y723" t="inlineStr">
@@ -54306,7 +54291,12 @@
       </c>
       <c r="Z723" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
+        </is>
+      </c>
+      <c r="AA723" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -54316,22 +54306,22 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>277652547262</t>
+          <t>278519751386</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
+          <t>Data Warehousing Services</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>District of Columbia Housing Finance Agency</t>
+          <t xml:space="preserve">Allen Town School District </t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -54346,12 +54336,12 @@
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="M724" t="inlineStr">
         <is>
-          <t>Consulting;Training</t>
+          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N724" t="inlineStr">
@@ -54366,12 +54356,12 @@
       </c>
       <c r="Y724" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Z724" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
         </is>
       </c>
     </row>
@@ -54381,27 +54371,32 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>269507522240</t>
+          <t>259790359234</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>601440000049523</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
+          <t>Managed Application Services: Application Development and Maintenance Services</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>Central Midlands Regional Transit Authority</t>
+          <t>Texas Department of Transportation</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
@@ -54411,27 +54406,27 @@
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="M725" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O725" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y725" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z725" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
         </is>
       </c>
     </row>
@@ -54441,22 +54436,22 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>294055526085</t>
+          <t>277652547262</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>Oracle Managed Services and Testing as a Service Support</t>
+          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>CITY OF DURHAM</t>
+          <t>District of Columbia Housing Finance Agency</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -54471,12 +54466,17 @@
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="M726" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Consulting;Training</t>
+        </is>
+      </c>
+      <c r="N726" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O726" t="inlineStr">
@@ -54486,12 +54486,12 @@
       </c>
       <c r="Y726" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Z726" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
         </is>
       </c>
     </row>
@@ -54501,22 +54501,22 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>305430641393</t>
+          <t>269507522240</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>OFF - Information Technology Managed Services</t>
+          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>County of Montcalm</t>
+          <t>Central Midlands Regional Transit Authority</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
@@ -54531,7 +54531,7 @@
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="M727" t="inlineStr">
@@ -54541,17 +54541,17 @@
       </c>
       <c r="O727" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y727" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z727" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
         </is>
       </c>
     </row>
@@ -54561,17 +54561,22 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>311307032268</t>
+          <t>294055526085</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+          <t>Oracle Managed Services and Testing as a Service Support</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>Housing Authority of the City of Passaic</t>
+          <t>CITY OF DURHAM</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
@@ -54586,27 +54591,27 @@
       </c>
       <c r="J728" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M728" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O728" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y728" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Z728" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
         </is>
       </c>
     </row>
@@ -54616,32 +54621,27 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>135161266908</t>
-        </is>
-      </c>
-      <c r="C729" t="inlineStr">
-        <is>
-          <t>RFQ1757840</t>
+          <t>305430641393</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>25-51-A-PMO-ES-SSN</t>
+          <t>OFF - Information Technology Managed Services</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>U.S. Department of the Treasury</t>
+          <t>County of Montcalm</t>
         </is>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
@@ -54651,27 +54651,27 @@
       </c>
       <c r="J729" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="N729" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O729" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y729" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="Z729" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
         </is>
       </c>
     </row>
@@ -54681,17 +54681,22 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>110691507903</t>
+          <t>311307032268</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
+          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>Housing Authority of the City of Passaic</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
@@ -54701,25 +54706,27 @@
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="L730" s="65" t="n">
-        <v>96200</v>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
       </c>
       <c r="O730" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y730" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Z730" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
         </is>
       </c>
     </row>
@@ -54729,12 +54736,27 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>110691507909</t>
+          <t>135161266908</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>RFQ1757840</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
+          <t>25-51-A-PMO-ES-SSN</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>U.S. Department of the Treasury</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
@@ -54749,7 +54771,12 @@
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="N731" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O731" t="inlineStr">
@@ -54759,12 +54786,12 @@
       </c>
       <c r="Y731" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z731" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
         </is>
       </c>
     </row>
@@ -54774,12 +54801,12 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>108771377911</t>
+          <t>110691507903</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>Facilities and Information Technology Infrastructure Assessment</t>
+          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
@@ -54797,6 +54824,9 @@
           <t>2026-03-31</t>
         </is>
       </c>
+      <c r="L732" s="65" t="n">
+        <v>96200</v>
+      </c>
       <c r="O732" t="inlineStr">
         <is>
           <t>Madhav Mitruka</t>
@@ -54809,7 +54839,7 @@
       </c>
       <c r="Z732" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
         </is>
       </c>
     </row>
@@ -54819,17 +54849,12 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>120893940419</t>
-        </is>
-      </c>
-      <c r="C733" t="inlineStr">
-        <is>
-          <t>#25-038-RFP)</t>
+          <t>110691507909</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
+          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
@@ -54847,24 +54872,19 @@
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="M733" t="inlineStr">
-        <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
-        </is>
-      </c>
       <c r="O733" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y733" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z733" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
         </is>
       </c>
     </row>
@@ -54874,12 +54894,12 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>114864654049</t>
+          <t>108771377911</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>M365 Tenant backup</t>
+          <t>Facilities and Information Technology Infrastructure Assessment</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
@@ -54899,17 +54919,17 @@
       </c>
       <c r="O734" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y734" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z734" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
         </is>
       </c>
     </row>
@@ -54919,27 +54939,22 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>317194645231</t>
+          <t>120893940419</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>BCH-C25-008</t>
+          <t>#25-038-RFP)</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>Data Migration (CMAS RFP)</t>
-        </is>
-      </c>
-      <c r="E735" t="inlineStr">
-        <is>
-          <t>Business, Consumer Services and Housing Agency</t>
+          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
@@ -54949,27 +54964,27 @@
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M735" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O735" t="inlineStr">
         <is>
-          <t>Darshan Tiwari</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="Y735" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z735" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
         </is>
       </c>
     </row>
@@ -54979,27 +54994,17 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>317945474767</t>
+          <t>114864654049</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>ServiceNow Technical Services</t>
-        </is>
-      </c>
-      <c r="E736" t="inlineStr">
-        <is>
-          <t>City of Sacramento</t>
-        </is>
-      </c>
-      <c r="F736" t="inlineStr">
-        <is>
-          <t>California</t>
+          <t>M365 Tenant backup</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -55009,22 +55014,22 @@
       </c>
       <c r="J736" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="O736" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="Y736" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Z736" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
         </is>
       </c>
     </row>
@@ -55034,22 +55039,27 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>325178884841</t>
+          <t>317194645231</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>BCH-C25-008</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>Test RFX (Please Ignore)</t>
+          <t>Data Migration (CMAS RFP)</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>Test associated agency for trello</t>
+          <t>Business, Consumer Services and Housing Agency</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
@@ -55059,27 +55069,27 @@
       </c>
       <c r="J737" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M737" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O737" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
+          <t>Darshan Tiwari</t>
         </is>
       </c>
       <c r="Y737" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="Z737" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
         </is>
       </c>
     </row>
@@ -55089,17 +55099,22 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>317911067336</t>
+          <t>317945474767</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse</t>
+          <t>ServiceNow Technical Services</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>Michigan Department of Technology Management and Budget</t>
+          <t>City of Sacramento</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>California</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
@@ -55114,12 +55129,12 @@
       </c>
       <c r="J738" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="O738" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y738" t="inlineStr">
@@ -55129,7 +55144,7 @@
       </c>
       <c r="Z738" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
         </is>
       </c>
     </row>
@@ -55139,50 +55154,155 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
+          <t>325178884841</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Test RFX (Please Ignore)</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>Test associated agency for trello</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="O739" t="inlineStr">
+        <is>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="Y739" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z739" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="n">
+        <v>739</v>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>317911067336</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Enterprise Data Warehouse</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>Michigan Department of Technology Management and Budget</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O740" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y740" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z740" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="n">
+        <v>740</v>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
           <t>321765371626</t>
         </is>
       </c>
-      <c r="C739" t="inlineStr">
+      <c r="C741" t="inlineStr">
         <is>
           <t>207-26</t>
         </is>
       </c>
-      <c r="D739" t="inlineStr">
+      <c r="D741" t="inlineStr">
         <is>
           <t>Professional and Consulting Services for Strategy and Technology Division</t>
         </is>
       </c>
-      <c r="E739" t="inlineStr">
+      <c r="E741" t="inlineStr">
         <is>
           <t>Fulton County Schools</t>
         </is>
       </c>
-      <c r="G739" t="inlineStr">
+      <c r="G741" t="inlineStr">
         <is>
           <t>RFx Cancelled</t>
         </is>
       </c>
-      <c r="H739" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J739" t="inlineStr">
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="O739" t="inlineStr">
+      <c r="O741" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
-      <c r="Y739" t="inlineStr">
+      <c r="Y741" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="Z739" t="inlineStr">
+      <c r="Z741" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765371626</t>
         </is>

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-05-21 07:36 EDT</t>
+          <t>2026-05-26 02:16 EDT</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA741"/>
+  <dimension ref="A1:AA742"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -26263,7 +26263,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -26273,7 +26273,7 @@
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -55209,22 +55209,22 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>317911067336</t>
+          <t>321690935004</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse</t>
+          <t>CoManaged Managed Service Provider (MSP) Services</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>Michigan Department of Technology Management and Budget</t>
+          <t>Foothills Regional Housing</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
@@ -55234,22 +55234,27 @@
       </c>
       <c r="J740" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O740" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y740" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z740" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321690935004</t>
         </is>
       </c>
     </row>
@@ -55259,50 +55264,100 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
+          <t>317911067336</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Enterprise Data Warehouse</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>Michigan Department of Technology Management and Budget</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O741" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y741" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z741" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="n">
+        <v>741</v>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
           <t>321765371626</t>
         </is>
       </c>
-      <c r="C741" t="inlineStr">
+      <c r="C742" t="inlineStr">
         <is>
           <t>207-26</t>
         </is>
       </c>
-      <c r="D741" t="inlineStr">
+      <c r="D742" t="inlineStr">
         <is>
           <t>Professional and Consulting Services for Strategy and Technology Division</t>
         </is>
       </c>
-      <c r="E741" t="inlineStr">
+      <c r="E742" t="inlineStr">
         <is>
           <t>Fulton County Schools</t>
         </is>
       </c>
-      <c r="G741" t="inlineStr">
+      <c r="G742" t="inlineStr">
         <is>
           <t>RFx Cancelled</t>
         </is>
       </c>
-      <c r="H741" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J741" t="inlineStr">
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="O741" t="inlineStr">
+      <c r="O742" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
-      <c r="Y741" t="inlineStr">
+      <c r="Y742" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="Z741" t="inlineStr">
+      <c r="Z742" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765371626</t>
         </is>

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-05-26 02:16 EDT</t>
+          <t>2026-05-27 05:51 EDT</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA742"/>
+  <dimension ref="A1:AA745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -39588,27 +39588,27 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>288906933988</t>
+          <t>300331058928</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>#2026-017VF</t>
+          <t>2026-IFB-002</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>TO PROVIDE MIGRATION TO SAP S4/HANA</t>
+          <t>Cisco DUO subscription 2026</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>County of Erie</t>
+          <t>Village of Schaumburg</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
@@ -39632,16 +39632,16 @@
         </is>
       </c>
       <c r="L514" s="65" t="n">
-        <v>1177910</v>
+        <v>46990</v>
       </c>
       <c r="M514" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Reseller</t>
         </is>
       </c>
       <c r="N514" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O514" t="inlineStr">
@@ -39651,12 +39651,12 @@
       </c>
       <c r="Y514" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="Z514" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/288906933988</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/300331058928</t>
         </is>
       </c>
     </row>
@@ -39666,32 +39666,27 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>300331058928</t>
-        </is>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>2026-IFB-002</t>
+          <t>285814480615</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>Cisco DUO subscription 2026</t>
+          <t>INFORMATION TECHNOLOGY SERVICES</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>Village of Schaumburg</t>
+          <t>Village of Canastota</t>
         </is>
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
@@ -39701,7 +39696,7 @@
       </c>
       <c r="J515" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="K515" t="inlineStr">
@@ -39709,17 +39704,14 @@
           <t>2026-02-24</t>
         </is>
       </c>
-      <c r="L515" s="65" t="n">
-        <v>46990</v>
-      </c>
       <c r="M515" t="inlineStr">
         <is>
-          <t>Reseller</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N515" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O515" t="inlineStr">
@@ -39729,12 +39721,12 @@
       </c>
       <c r="Y515" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z515" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/300331058928</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/285814480615</t>
         </is>
       </c>
     </row>
@@ -39744,22 +39736,27 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>285814480615</t>
+          <t>288906933988</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>#2026-017VF</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SERVICES</t>
+          <t>TO PROVIDE MIGRATION TO SAP S4/HANA</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Village of Canastota</t>
+          <t>County of Erie</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
@@ -39774,7 +39771,7 @@
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="K516" t="inlineStr">
@@ -39782,14 +39779,17 @@
           <t>2026-02-24</t>
         </is>
       </c>
+      <c r="L516" s="65" t="n">
+        <v>1177910</v>
+      </c>
       <c r="M516" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="N516" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O516" t="inlineStr">
@@ -39799,12 +39799,12 @@
       </c>
       <c r="Y516" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="Z516" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/285814480615</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/288906933988</t>
         </is>
       </c>
     </row>
@@ -49876,7 +49876,7 @@
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -49908,6 +49908,11 @@
         </is>
       </c>
       <c r="S659" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="U659" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
@@ -53554,17 +53559,27 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>322527283932</t>
+          <t>322910021322</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>#2005976</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>Test RFX (please ignore)</t>
+          <t>OFF - Website Hosting Services</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>Standing Rock Housing Authority (SRHA)</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
@@ -53572,29 +53587,39 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
       <c r="M713" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N713" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O713" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
-        </is>
-      </c>
-      <c r="S713" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y713" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="Z713" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322910021322</t>
         </is>
       </c>
     </row>
@@ -53604,32 +53629,22 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>116977709771</t>
-        </is>
-      </c>
-      <c r="C714" t="inlineStr">
-        <is>
-          <t>RFP-25-0005</t>
+          <t>323641797323</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
+          <t xml:space="preserve">HOSTED INFORMATION TECHNOLOGY AND SUPPORT SERVICES </t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>NeighborWorks America</t>
-        </is>
-      </c>
-      <c r="F714" t="inlineStr">
-        <is>
-          <t>Washington, D.C.</t>
+          <t>EARLY LEARNING COALITION OF BREVARD COUNTY</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
@@ -53637,39 +53652,39 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
       <c r="M714" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N714" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O714" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
-        </is>
-      </c>
-      <c r="S714" t="inlineStr">
-        <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="U714" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y714" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Z714" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
-        </is>
-      </c>
-      <c r="AA714" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323641797323</t>
         </is>
       </c>
     </row>
@@ -53679,27 +53694,17 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>145081112265</t>
+          <t>322527283932</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Technology Strategic Management Consulting</t>
-        </is>
-      </c>
-      <c r="E715" t="inlineStr">
-        <is>
-          <t>State of Colorado, the Office of Information Technology (OIT)</t>
-        </is>
-      </c>
-      <c r="F715" t="inlineStr">
-        <is>
-          <t>Colorado</t>
+          <t>Test RFX (please ignore)</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
@@ -53707,29 +53712,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J715" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
       <c r="M715" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O715" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="S715" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y715" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z715" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
         </is>
       </c>
     </row>
@@ -53739,27 +53744,32 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>166098266830</t>
+          <t>116977709771</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>RFP-25-0005</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Mecklenburg County</t>
+          <t>NeighborWorks America</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
@@ -53767,29 +53777,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J716" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
       <c r="M716" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O716" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="S716" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="U716" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Y716" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z716" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+        </is>
+      </c>
+      <c r="AA716" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -53799,27 +53819,27 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>180166400720</t>
+          <t>145081112265</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
+          <t>Technology Strategic Management Consulting</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>Central Ohio Transit Authority</t>
+          <t>State of Colorado, the Office of Information Technology (OIT)</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
@@ -53829,7 +53849,12 @@
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O717" t="inlineStr">
@@ -53839,12 +53864,12 @@
       </c>
       <c r="Y717" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z717" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
         </is>
       </c>
     </row>
@@ -53854,32 +53879,27 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>182404957915</t>
-        </is>
-      </c>
-      <c r="C718" t="inlineStr">
-        <is>
-          <t>PWE-10.08.2025</t>
+          <t>166098266830</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>PWE Power BI Dashboard</t>
+          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>City of Issaquah</t>
+          <t>Mecklenburg County</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
@@ -53889,27 +53909,27 @@
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="M718" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O718" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y718" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z718" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
         </is>
       </c>
     </row>
@@ -53919,27 +53939,22 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>108771177151</t>
-        </is>
-      </c>
-      <c r="C719" t="inlineStr">
-        <is>
-          <t>791202505005</t>
+          <t>180166400720</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Government Consulting Services</t>
+          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>North Central Texas Council of Governments</t>
+          <t>Central Ohio Transit Authority</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>TEXAS</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -53954,12 +53969,7 @@
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="N719" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="O719" t="inlineStr">
@@ -53969,12 +53979,12 @@
       </c>
       <c r="Y719" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="Z719" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
         </is>
       </c>
     </row>
@@ -53984,27 +53994,27 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>120893940416</t>
+          <t>182404957915</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>DQ SAAA #2026000004</t>
+          <t>PWE-10.08.2025</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>Online Content Learning</t>
+          <t>PWE Power BI Dashboard</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>State of Colorado Department of Regulatory Agencies</t>
+          <t>City of Issaquah</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -54019,30 +54029,27 @@
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L720" s="65" t="n">
-        <v>67300</v>
+          <t>2025-10-29</t>
+        </is>
       </c>
       <c r="M720" t="inlineStr">
         <is>
-          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O720" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y720" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Z720" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
         </is>
       </c>
     </row>
@@ -54052,27 +54059,32 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>199601365715</t>
+          <t>108771177151</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>791202505005</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>Contracted IT Support Services</t>
+          <t>Government Consulting Services</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>ECS4Kids</t>
+          <t>North Central Texas Council of Governments</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>TEXAS</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
@@ -54082,15 +54094,7 @@
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="L721" s="65" t="n">
-        <v>291141</v>
-      </c>
-      <c r="M721" t="inlineStr">
-        <is>
-          <t>Support &amp; Maintenance</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="N721" t="inlineStr">
@@ -54100,17 +54104,17 @@
       </c>
       <c r="O721" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y721" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="Z721" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
         </is>
       </c>
     </row>
@@ -54120,55 +54124,50 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>140123456196</t>
+          <t>120893940416</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>24-RFP-10</t>
+          <t>DQ SAAA #2026000004</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+          <t>Online Content Learning</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+          <t>State of Colorado Department of Regulatory Agencies</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I722" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="L722" s="65" t="n">
-        <v>18620</v>
+        <v>67300</v>
       </c>
       <c r="M722" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O722" t="inlineStr">
@@ -54176,44 +54175,14 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="P722" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q722" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="S722" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="U722" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="V722" t="inlineStr">
-        <is>
-          <t>In Process</t>
-        </is>
-      </c>
       <c r="Y722" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z722" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
-        </is>
-      </c>
-      <c r="AA722" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
         </is>
       </c>
     </row>
@@ -54223,27 +54192,27 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>261982669555</t>
+          <t>199601365715</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>IT Backfill for ERP Configuration (SOW 2)</t>
+          <t>Contracted IT Support Services</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>Madison Metropolitan Sewerage District</t>
+          <t>ECS4Kids</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
@@ -54253,50 +54222,35 @@
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="L723" s="65" t="n">
-        <v>157000</v>
+        <v>291141</v>
       </c>
       <c r="M723" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N723" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O723" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="S723" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="U723" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="V723" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y723" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z723" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
-        </is>
-      </c>
-      <c r="AA723" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
         </is>
       </c>
     </row>
@@ -54306,62 +54260,100 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>278519751386</t>
+          <t>140123456196</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>24-RFP-10</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Data Warehousing Services</t>
+          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allen Town School District </t>
+          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L724" s="65" t="n">
+        <v>18620</v>
       </c>
       <c r="M724" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N724" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O724" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P724" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q724" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="S724" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="U724" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="V724" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y724" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z724" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
+        </is>
+      </c>
+      <c r="AA724" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -54371,32 +54363,27 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>259790359234</t>
-        </is>
-      </c>
-      <c r="C725" t="inlineStr">
-        <is>
-          <t>601440000049523</t>
+          <t>261982669555</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Managed Application Services: Application Development and Maintenance Services</t>
+          <t>IT Backfill for ERP Configuration (SOW 2)</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>Texas Department of Transportation</t>
+          <t>Madison Metropolitan Sewerage District</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
@@ -54406,17 +54393,35 @@
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
-        </is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="L725" s="65" t="n">
+        <v>157000</v>
       </c>
       <c r="M725" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O725" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S725" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="U725" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="V725" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y725" t="inlineStr">
@@ -54426,7 +54431,12 @@
       </c>
       <c r="Z725" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
+        </is>
+      </c>
+      <c r="AA725" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -54436,22 +54446,22 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>277652547262</t>
+          <t>278519751386</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
+          <t>Data Warehousing Services</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>District of Columbia Housing Finance Agency</t>
+          <t xml:space="preserve">Allen Town School District </t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -54466,12 +54476,12 @@
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="M726" t="inlineStr">
         <is>
-          <t>Consulting;Training</t>
+          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N726" t="inlineStr">
@@ -54486,12 +54496,12 @@
       </c>
       <c r="Y726" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Z726" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
         </is>
       </c>
     </row>
@@ -54501,27 +54511,32 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>269507522240</t>
+          <t>259790359234</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>601440000049523</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
+          <t>Managed Application Services: Application Development and Maintenance Services</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>Central Midlands Regional Transit Authority</t>
+          <t>Texas Department of Transportation</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
@@ -54531,27 +54546,27 @@
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="M727" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O727" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y727" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z727" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
         </is>
       </c>
     </row>
@@ -54561,22 +54576,22 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>294055526085</t>
+          <t>277652547262</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>Oracle Managed Services and Testing as a Service Support</t>
+          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>CITY OF DURHAM</t>
+          <t>District of Columbia Housing Finance Agency</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
@@ -54591,12 +54606,17 @@
       </c>
       <c r="J728" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="M728" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Consulting;Training</t>
+        </is>
+      </c>
+      <c r="N728" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O728" t="inlineStr">
@@ -54606,12 +54626,12 @@
       </c>
       <c r="Y728" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Z728" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
         </is>
       </c>
     </row>
@@ -54621,22 +54641,22 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>305430641393</t>
+          <t>269507522240</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>OFF - Information Technology Managed Services</t>
+          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>County of Montcalm</t>
+          <t>Central Midlands Regional Transit Authority</t>
         </is>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
@@ -54651,7 +54671,7 @@
       </c>
       <c r="J729" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="M729" t="inlineStr">
@@ -54661,17 +54681,17 @@
       </c>
       <c r="O729" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y729" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z729" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
         </is>
       </c>
     </row>
@@ -54681,17 +54701,22 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>311307032268</t>
+          <t>294055526085</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+          <t>Oracle Managed Services and Testing as a Service Support</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>Housing Authority of the City of Passaic</t>
+          <t>CITY OF DURHAM</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
@@ -54706,27 +54731,27 @@
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M730" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O730" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y730" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Z730" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
         </is>
       </c>
     </row>
@@ -54736,32 +54761,27 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>135161266908</t>
-        </is>
-      </c>
-      <c r="C731" t="inlineStr">
-        <is>
-          <t>RFQ1757840</t>
+          <t>305430641393</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>25-51-A-PMO-ES-SSN</t>
+          <t>OFF - Information Technology Managed Services</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>U.S. Department of the Treasury</t>
+          <t>County of Montcalm</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
@@ -54771,27 +54791,27 @@
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="N731" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O731" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y731" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="Z731" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
         </is>
       </c>
     </row>
@@ -54801,17 +54821,22 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>110691507903</t>
+          <t>311307032268</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
+          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>Housing Authority of the City of Passaic</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
@@ -54821,25 +54846,27 @@
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="L732" s="65" t="n">
-        <v>96200</v>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
       </c>
       <c r="O732" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y732" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Z732" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
         </is>
       </c>
     </row>
@@ -54849,12 +54876,27 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>110691507909</t>
+          <t>135161266908</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>RFQ1757840</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
+          <t>25-51-A-PMO-ES-SSN</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>U.S. Department of the Treasury</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
@@ -54869,7 +54911,12 @@
       </c>
       <c r="J733" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="N733" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O733" t="inlineStr">
@@ -54879,12 +54926,12 @@
       </c>
       <c r="Y733" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z733" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
         </is>
       </c>
     </row>
@@ -54894,12 +54941,12 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>108771377911</t>
+          <t>110691507903</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>Facilities and Information Technology Infrastructure Assessment</t>
+          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
@@ -54917,6 +54964,9 @@
           <t>2026-03-31</t>
         </is>
       </c>
+      <c r="L734" s="65" t="n">
+        <v>96200</v>
+      </c>
       <c r="O734" t="inlineStr">
         <is>
           <t>Madhav Mitruka</t>
@@ -54929,7 +54979,7 @@
       </c>
       <c r="Z734" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
         </is>
       </c>
     </row>
@@ -54939,17 +54989,12 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>120893940419</t>
-        </is>
-      </c>
-      <c r="C735" t="inlineStr">
-        <is>
-          <t>#25-038-RFP)</t>
+          <t>110691507909</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
+          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
@@ -54967,24 +55012,19 @@
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="M735" t="inlineStr">
-        <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
-        </is>
-      </c>
       <c r="O735" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y735" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z735" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
         </is>
       </c>
     </row>
@@ -54994,12 +55034,12 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>114864654049</t>
+          <t>108771377911</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>M365 Tenant backup</t>
+          <t>Facilities and Information Technology Infrastructure Assessment</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
@@ -55019,17 +55059,17 @@
       </c>
       <c r="O736" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y736" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z736" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
         </is>
       </c>
     </row>
@@ -55039,27 +55079,22 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>317194645231</t>
+          <t>120893940419</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>BCH-C25-008</t>
+          <t>#25-038-RFP)</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>Data Migration (CMAS RFP)</t>
-        </is>
-      </c>
-      <c r="E737" t="inlineStr">
-        <is>
-          <t>Business, Consumer Services and Housing Agency</t>
+          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
@@ -55069,27 +55104,27 @@
       </c>
       <c r="J737" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="M737" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O737" t="inlineStr">
         <is>
-          <t>Darshan Tiwari</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="Y737" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z737" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
         </is>
       </c>
     </row>
@@ -55099,27 +55134,17 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>317945474767</t>
+          <t>114864654049</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>ServiceNow Technical Services</t>
-        </is>
-      </c>
-      <c r="E738" t="inlineStr">
-        <is>
-          <t>City of Sacramento</t>
-        </is>
-      </c>
-      <c r="F738" t="inlineStr">
-        <is>
-          <t>California</t>
+          <t>M365 Tenant backup</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H738" t="inlineStr">
@@ -55129,22 +55154,22 @@
       </c>
       <c r="J738" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="O738" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="Y738" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Z738" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
         </is>
       </c>
     </row>
@@ -55154,22 +55179,27 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>325178884841</t>
+          <t>317194645231</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>BCH-C25-008</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>Test RFX (Please Ignore)</t>
+          <t>Data Migration (CMAS RFP)</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>Test associated agency for trello</t>
+          <t>Business, Consumer Services and Housing Agency</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
@@ -55179,27 +55209,27 @@
       </c>
       <c r="J739" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M739" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O739" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
+          <t>Darshan Tiwari</t>
         </is>
       </c>
       <c r="Y739" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="Z739" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
         </is>
       </c>
     </row>
@@ -55209,22 +55239,27 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>321690935004</t>
+          <t>317945474767</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>CoManaged Managed Service Provider (MSP) Services</t>
+          <t>ServiceNow Technical Services</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>Foothills Regional Housing</t>
+          <t>City of Sacramento</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>California</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
@@ -55234,27 +55269,22 @@
       </c>
       <c r="J740" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="M740" t="inlineStr">
-        <is>
-          <t>Managed Services (MSP)</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="O740" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y740" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z740" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321690935004</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
         </is>
       </c>
     </row>
@@ -55264,22 +55294,22 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>317911067336</t>
+          <t>325178884841</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse</t>
+          <t>Test RFX (Please Ignore)</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>Michigan Department of Technology Management and Budget</t>
+          <t>Test associated agency for trello</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
@@ -55289,22 +55319,27 @@
       </c>
       <c r="J741" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>Training</t>
         </is>
       </c>
       <c r="O741" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Akshat Tripathi</t>
         </is>
       </c>
       <c r="Y741" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Z741" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
         </is>
       </c>
     </row>
@@ -55314,52 +55349,212 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
+          <t>321690935004</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>CoManaged Managed Service Provider (MSP) Services</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>Foothills Regional Housing</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="O742" t="inlineStr">
+        <is>
+          <t>Savya Atrey</t>
+        </is>
+      </c>
+      <c r="Y742" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="Z742" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321690935004</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="n">
+        <v>742</v>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>317911067336</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Enterprise Data Warehouse</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Michigan Department of Technology Management and Budget</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O743" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y743" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z743" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="n">
+        <v>743</v>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
           <t>321765371626</t>
         </is>
       </c>
-      <c r="C742" t="inlineStr">
+      <c r="C744" t="inlineStr">
         <is>
           <t>207-26</t>
         </is>
       </c>
-      <c r="D742" t="inlineStr">
+      <c r="D744" t="inlineStr">
         <is>
           <t>Professional and Consulting Services for Strategy and Technology Division</t>
         </is>
       </c>
-      <c r="E742" t="inlineStr">
+      <c r="E744" t="inlineStr">
         <is>
           <t>Fulton County Schools</t>
         </is>
       </c>
-      <c r="G742" t="inlineStr">
+      <c r="G744" t="inlineStr">
         <is>
           <t>RFx Cancelled</t>
         </is>
       </c>
-      <c r="H742" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J742" t="inlineStr">
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="O742" t="inlineStr">
+      <c r="O744" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
-      <c r="Y742" t="inlineStr">
+      <c r="Y744" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="Z742" t="inlineStr">
+      <c r="Z744" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765371626</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="n">
+        <v>744</v>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>321905743581</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>ERP Needs Assessment Consulting Services</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Greater Dayton Regional Transit Authority</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="O745" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y745" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z745" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321905743581</t>
         </is>
       </c>
     </row>
@@ -58848,7 +59043,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -61537,7 +61732,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -61569,6 +61764,11 @@
         </is>
       </c>
       <c r="S67" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-05-27 05:51 EDT</t>
+          <t>2026-05-27 10:46 EDT</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>650</v>
+        <v>682</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA745"/>
+  <dimension ref="A1:AA777"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -51662,22 +51662,22 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>321765371610</t>
+          <t>318930504398</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>RFP-RC-2026-013</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>ServiceNow Professional Services</t>
+          <t>Confidential Network, Cyber Security and Technology Advisor Services</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>City of Sacramento</t>
-        </is>
-      </c>
-      <c r="F685" t="inlineStr">
-        <is>
-          <t>California</t>
+          <t>County of Rockland</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
@@ -51692,17 +51692,20 @@
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="K685" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="L685" s="65" t="n">
+        <v>297600</v>
       </c>
       <c r="M685" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting;Staff Augmentation</t>
         </is>
       </c>
       <c r="N685" t="inlineStr">
@@ -51712,17 +51715,17 @@
       </c>
       <c r="O685" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y685" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z685" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765371610</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318930504398</t>
         </is>
       </c>
     </row>
@@ -51732,22 +51735,22 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>320114224857</t>
+          <t>321765371610</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>Microsoft 365/Azure Security Policiies</t>
+          <t>ServiceNow Professional Services</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>Stark Metropolitan Housing Authority</t>
+          <t>City of Sacramento</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
@@ -51770,8 +51773,15 @@
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="L686" s="65" t="n">
-        <v>14000</v>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="N686" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
       </c>
       <c r="O686" t="inlineStr">
         <is>
@@ -51780,12 +51790,12 @@
       </c>
       <c r="Y686" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z686" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320114224857</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765371610</t>
         </is>
       </c>
     </row>
@@ -51795,22 +51805,22 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>321905742529</t>
+          <t>320114224857</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>Dynamics CRM Migration Support, Portal Development, &amp; Train-the-Trainer</t>
+          <t>Microsoft 365/Azure Security Policiies</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>Governor's Office of Business and Economic Development (GO-Biz)</t>
+          <t>Stark Metropolitan Housing Authority</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
@@ -51834,31 +51844,21 @@
         </is>
       </c>
       <c r="L687" s="65" t="n">
-        <v>173290</v>
-      </c>
-      <c r="M687" t="inlineStr">
-        <is>
-          <t>Platform Implementation (ERP, CRMs);Training</t>
-        </is>
-      </c>
-      <c r="N687" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
+        <v>14000</v>
       </c>
       <c r="O687" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y687" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="Z687" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321905742529</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320114224857</t>
         </is>
       </c>
     </row>
@@ -51868,17 +51868,17 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>320114224858</t>
+          <t>321905742529</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>Information Technology Strategic Plan</t>
+          <t>Dynamics CRM Migration Support, Portal Development, &amp; Train-the-Trainer</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>City of Richmond</t>
+          <t>Governor's Office of Business and Economic Development (GO-Biz)</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
@@ -51906,14 +51906,17 @@
           <t>2026-05-06</t>
         </is>
       </c>
+      <c r="L688" s="65" t="n">
+        <v>173290</v>
+      </c>
       <c r="M688" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Platform Implementation (ERP, CRMs);Training</t>
         </is>
       </c>
       <c r="N688" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O688" t="inlineStr">
@@ -51923,12 +51926,12 @@
       </c>
       <c r="Y688" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Z688" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320114224858</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321905742529</t>
         </is>
       </c>
     </row>
@@ -51938,27 +51941,22 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>319866591968</t>
-        </is>
-      </c>
-      <c r="C689" t="inlineStr">
-        <is>
-          <t>RFP260304</t>
+          <t>320114224858</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>Full Stack WordPress Developer (part-time)</t>
+          <t>Information Technology Strategic Plan</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>Seattle Public Schools</t>
+          <t>City of Richmond</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
@@ -51981,12 +51979,9 @@
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="L689" s="65" t="n">
-        <v>65000</v>
-      </c>
       <c r="M689" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N689" t="inlineStr">
@@ -52001,12 +51996,12 @@
       </c>
       <c r="Y689" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="Z689" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319866591968</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320114224858</t>
         </is>
       </c>
     </row>
@@ -52016,17 +52011,27 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>319311117011</t>
+          <t>319866591968</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>RFP260304</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>IT SECURITY ASSESSMENT</t>
+          <t>Full Stack WordPress Developer (part-time)</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>City of Rockville</t>
+          <t>Seattle Public Schools</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
@@ -52041,32 +52046,40 @@
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="K690" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="L690" s="65" t="n">
+        <v>65000</v>
       </c>
       <c r="M690" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="N690" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O690" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y690" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z690" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319311117011</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319866591968</t>
         </is>
       </c>
     </row>
@@ -52076,17 +52089,17 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>321010534088</t>
+          <t>319311117011</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>IT MANAGED SERVICES PROVIDER</t>
+          <t>IT SECURITY ASSESSMENT</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>City of Ferndale</t>
+          <t>City of Rockville</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
@@ -52109,17 +52122,9 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="L691" s="65" t="n">
-        <v>373572</v>
-      </c>
       <c r="M691" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N691" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O691" t="inlineStr">
@@ -52129,12 +52134,12 @@
       </c>
       <c r="Y691" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="Z691" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321010534088</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319311117011</t>
         </is>
       </c>
     </row>
@@ -52144,22 +52149,17 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>322911466218</t>
-        </is>
-      </c>
-      <c r="C692" t="inlineStr">
-        <is>
-          <t>6100015191</t>
+          <t>321010534088</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>Security and Infrastructure Support Work Order Services</t>
+          <t>IT MANAGED SERVICES PROVIDER</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>Pennsylvania Turnpike Commission</t>
+          <t>City of Ferndale</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
@@ -52182,29 +52182,32 @@
           <t>2026-05-07</t>
         </is>
       </c>
+      <c r="L692" s="65" t="n">
+        <v>373572</v>
+      </c>
       <c r="M692" t="inlineStr">
         <is>
-          <t>Staff Augmentation;Consulting</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N692" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O692" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y692" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="Z692" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322911466218</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321010534088</t>
         </is>
       </c>
     </row>
@@ -52214,27 +52217,27 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>324699843267</t>
+          <t>322911466218</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>6100015191</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>Microsoft 365 GCC Licensing Quote</t>
+          <t>Security and Infrastructure Support Work Order Services</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Mexico Finance Authority (“NMFA”) </t>
-        </is>
-      </c>
-      <c r="F693" t="inlineStr">
-        <is>
-          <t>New Mexico</t>
+          <t>Pennsylvania Turnpike Commission</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -52244,7 +52247,7 @@
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="K693" t="inlineStr">
@@ -52252,32 +52255,29 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="L693" s="65" t="n">
-        <v>57658.61</v>
-      </c>
       <c r="M693" t="inlineStr">
         <is>
-          <t>Reseller</t>
+          <t>Staff Augmentation;Consulting</t>
         </is>
       </c>
       <c r="N693" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O693" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y693" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="Z693" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/324699843267</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322911466218</t>
         </is>
       </c>
     </row>
@@ -52287,22 +52287,27 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>321711121139</t>
+          <t>324699843267</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>Information Technology Managed Services: IT Service Desk</t>
+          <t>Microsoft 365 GCC Licensing Quote</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>Brunswick County</t>
+          <t xml:space="preserve">New Mexico Finance Authority (“NMFA”) </t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
@@ -52321,31 +52326,31 @@
         </is>
       </c>
       <c r="L694" s="65" t="n">
-        <v>92560</v>
+        <v>57658.61</v>
       </c>
       <c r="M694" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Reseller</t>
         </is>
       </c>
       <c r="N694" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O694" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y694" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Z694" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321711121139</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/324699843267</t>
         </is>
       </c>
     </row>
@@ -52355,22 +52360,17 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>320489731795</t>
-        </is>
-      </c>
-      <c r="C695" t="inlineStr">
-        <is>
-          <t>CR#: 2133336</t>
+          <t>321711121139</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>Technical Consultant</t>
+          <t>Information Technology Managed Services: IT Service Desk</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>NYS Division of Criminal Justice Services</t>
+          <t>Brunswick County</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
@@ -52385,40 +52385,40 @@
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="K695" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="L695" s="65" t="n">
-        <v>49500</v>
+        <v>92560</v>
       </c>
       <c r="M695" t="inlineStr">
         <is>
-          <t>Consulting;Staff Augmentation</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N695" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O695" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y695" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z695" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320489731795</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321711121139</t>
         </is>
       </c>
     </row>
@@ -52428,27 +52428,27 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>319309140723</t>
+          <t>320489731795</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>RFP 019-0-2026/HM</t>
+          <t>CR#: 2133336</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>Cybersecurity Penetration &amp; Vulnerability Testing Services</t>
+          <t>Technical Consultant</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>Newport News Public Schools [VA]</t>
+          <t>NYS Division of Criminal Justice Services</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
@@ -52467,16 +52467,16 @@
         </is>
       </c>
       <c r="L696" s="65" t="n">
-        <v>66096</v>
+        <v>49500</v>
       </c>
       <c r="M696" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Consulting;Staff Augmentation</t>
         </is>
       </c>
       <c r="N696" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O696" t="inlineStr">
@@ -52486,12 +52486,12 @@
       </c>
       <c r="Y696" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="Z696" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319309140723</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320489731795</t>
         </is>
       </c>
     </row>
@@ -52501,37 +52501,37 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>322356230853</t>
+          <t>319309140723</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>RFP 019-0-2026/HM</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>AI Professional Development for Administration,Staff, and Training for Students</t>
+          <t>Cybersecurity Penetration &amp; Vulnerability Testing Services</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>GROSSMONT UNION HIGH SCHOOL DISTRICT</t>
+          <t>Newport News Public Schools [VA]</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>Interview</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I697" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="K697" t="inlineStr">
@@ -52540,41 +52540,31 @@
         </is>
       </c>
       <c r="L697" s="65" t="n">
-        <v>225400</v>
+        <v>66096</v>
       </c>
       <c r="M697" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="N697" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O697" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
-        </is>
-      </c>
-      <c r="P697" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q697" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y697" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="Z697" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322356230853</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319309140723</t>
         </is>
       </c>
     </row>
@@ -52584,22 +52574,17 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>320623193832</t>
-        </is>
-      </c>
-      <c r="C698" t="inlineStr">
-        <is>
-          <t>213924802</t>
+          <t>320834007772</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>Clemson LIFE Program Management System</t>
+          <t>OFF - IT Managed Services</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>Clemson University</t>
+          <t>Assabet Valley Collaborative</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
@@ -52614,20 +52599,25 @@
       </c>
       <c r="J698" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="K698" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="L698" s="65" t="n">
-        <v>572000</v>
+        <v>565800</v>
+      </c>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
       </c>
       <c r="N698" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O698" t="inlineStr">
@@ -52642,7 +52632,7 @@
       </c>
       <c r="Z698" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320623193832</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320834007772</t>
         </is>
       </c>
     </row>
@@ -52652,32 +52642,32 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>317946186441</t>
-        </is>
-      </c>
-      <c r="C699" t="inlineStr">
-        <is>
-          <t>6483</t>
+          <t>322356230853</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>Network Penetration Testing Services</t>
+          <t>AI Professional Development for Administration,Staff, and Training for Students</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>Kent County</t>
+          <t>GROSSMONT UNION HIGH SCHOOL DISTRICT</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J699" t="inlineStr">
@@ -52687,35 +52677,45 @@
       </c>
       <c r="K699" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="L699" s="65" t="n">
-        <v>29390</v>
+        <v>225400</v>
       </c>
       <c r="M699" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="N699" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O699" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="P699" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q699" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Y699" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z699" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317946186441</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322356230853</t>
         </is>
       </c>
     </row>
@@ -52725,17 +52725,22 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>321691658976</t>
+          <t>317911783129</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>PBCHA-RFP-2026-08</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>OFF - Managed Service Provider (MSP) – IT &amp; Microsoft Cloud Services</t>
+          <t>OFF - Information Technology (IT) Managed Services</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>Phelps County Sheriff’s Department (PCSD)</t>
+          <t>Palm Beach County Housing Authority</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
@@ -52750,16 +52755,16 @@
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="K700" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="L700" s="65" t="n">
-        <v>173400</v>
+        <v>493500</v>
       </c>
       <c r="M700" t="inlineStr">
         <is>
@@ -52768,7 +52773,7 @@
       </c>
       <c r="N700" t="inlineStr">
         <is>
-          <t>Offline;Email</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O700" t="inlineStr">
@@ -52778,12 +52783,12 @@
       </c>
       <c r="Y700" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z700" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321691658976</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911783129</t>
         </is>
       </c>
     </row>
@@ -52793,17 +52798,22 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>320137093859</t>
+          <t>320623193832</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>213924802</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>OFFLINE Annual Contract For Managed It Services For Youth Lab</t>
+          <t>Clemson LIFE Program Management System</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>City of Visalia</t>
+          <t>Clemson University</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
@@ -52818,32 +52828,35 @@
       </c>
       <c r="J701" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="K701" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="M701" t="inlineStr">
-        <is>
-          <t>Managed Services (MSP)</t>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="L701" s="65" t="n">
+        <v>572000</v>
+      </c>
+      <c r="N701" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O701" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y701" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z701" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320137093859</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320623193832</t>
         </is>
       </c>
     </row>
@@ -52853,17 +52866,22 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>321010642622</t>
+          <t>317946186441</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>6483</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Network Penetration Testing Services</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>I-195 Redevelopment District</t>
+          <t>Kent County</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
@@ -52878,40 +52896,40 @@
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="K702" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="L702" s="65" t="n">
-        <v>78900</v>
+        <v>29390</v>
       </c>
       <c r="M702" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N702" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O702" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y702" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z702" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321010642622</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317946186441</t>
         </is>
       </c>
     </row>
@@ -52921,17 +52939,17 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>321765372642</t>
+          <t>321691658976</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>Unified Endpoint Management (UEM) Managed Services Program</t>
+          <t>OFF - Managed Service Provider (MSP) – IT &amp; Microsoft Cloud Services</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>Southeastern Pennsylvania Transportation Authority</t>
+          <t>Phelps County Sheriff’s Department (PCSD)</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
@@ -52946,13 +52964,16 @@
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="K703" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L703" s="65" t="n">
+        <v>173400</v>
       </c>
       <c r="M703" t="inlineStr">
         <is>
@@ -52961,7 +52982,7 @@
       </c>
       <c r="N703" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Offline;Email</t>
         </is>
       </c>
       <c r="O703" t="inlineStr">
@@ -52976,7 +52997,7 @@
       </c>
       <c r="Z703" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765372642</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321691658976</t>
         </is>
       </c>
     </row>
@@ -52986,17 +53007,17 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>323237511900</t>
+          <t>320137093859</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>Workday On-Demand Support Services  &amp; Workday Managed Services - RFI</t>
+          <t>OFFLINE Annual Contract For Managed It Services For Youth Lab</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>Bexar County</t>
+          <t>City of Visalia</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
@@ -53011,32 +53032,32 @@
       </c>
       <c r="J704" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="K704" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M704" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O704" t="inlineStr">
         <is>
-          <t>Srikrishnadeva D</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y704" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="Z704" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323237511900</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320137093859</t>
         </is>
       </c>
     </row>
@@ -53046,17 +53067,17 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>321711122109</t>
+          <t>321010642622</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>Managed Information Technology Services</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>The Education Cooperative</t>
+          <t>I-195 Redevelopment District</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
@@ -53071,13 +53092,16 @@
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="K705" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
-        </is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L705" s="65" t="n">
+        <v>78900</v>
       </c>
       <c r="M705" t="inlineStr">
         <is>
@@ -53086,7 +53110,7 @@
       </c>
       <c r="N705" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O705" t="inlineStr">
@@ -53096,12 +53120,12 @@
       </c>
       <c r="Y705" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="Z705" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321711122109</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321010642622</t>
         </is>
       </c>
     </row>
@@ -53111,17 +53135,17 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>323518611139</t>
+          <t>321905741541</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>Request for Proposals Information Technology (IT) Managed Services &amp; Strategic Support</t>
+          <t>AI Powered Government Research Assistant</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t xml:space="preserve">City of Flagler Beach </t>
+          <t>Town of Coventry</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
@@ -53136,17 +53160,20 @@
       </c>
       <c r="J706" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="K706" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
-        </is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L706" s="65" t="n">
+        <v>114870</v>
       </c>
       <c r="M706" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="N706" t="inlineStr">
@@ -53161,12 +53188,12 @@
       </c>
       <c r="Y706" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Z706" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323518611139</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321905741541</t>
         </is>
       </c>
     </row>
@@ -53176,22 +53203,22 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>323230410428</t>
+          <t>321688803051</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>CC/RFP 27-01</t>
+          <t>RFP 2026-02</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SERVICES</t>
+          <t>OFF - IT Services (ReBid)</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>Brigantine Board of Education</t>
+          <t>Springfield Housing Authority</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
@@ -53206,27 +53233,37 @@
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="K707" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N707" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O707" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y707" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z707" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323230410428</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321688803051</t>
         </is>
       </c>
     </row>
@@ -53236,17 +53273,22 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>321908570850</t>
+          <t>322924493553</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>Managed IT Services</t>
+          <t>WORKDAY APPLICATION MANAGEMENT SERVICES (AMS) SUPPORT</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>Town of Butner</t>
+          <t>Orange County Transportation Authority</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>California</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
@@ -53261,22 +53303,17 @@
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="K708" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="M708" t="inlineStr">
-        <is>
-          <t>Managed Services (MSP)</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="N708" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O708" t="inlineStr">
@@ -53286,12 +53323,12 @@
       </c>
       <c r="Y708" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="Z708" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321908570850</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322924493553</t>
         </is>
       </c>
     </row>
@@ -53301,22 +53338,17 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>323237509835</t>
-        </is>
-      </c>
-      <c r="C709" t="inlineStr">
-        <is>
-          <t>2026-07</t>
+          <t>324282026710</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>Information Technology Services and Management (rebid)</t>
+          <t>IBM SOFTWARE SUBSCRIPTION AND SUPPORT RENEWAL</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>Palm Beach Metropolitan Planning Organization</t>
+          <t>City of Glendale</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
@@ -53331,32 +53363,40 @@
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="K709" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="L709" s="65" t="n">
+        <v>94846.5</v>
       </c>
       <c r="M709" t="inlineStr">
         <is>
-          <t>Managed Services (MSP);Consulting</t>
+          <t>Reseller</t>
+        </is>
+      </c>
+      <c r="N709" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O709" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y709" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="Z709" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323237509835</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/324282026710</t>
         </is>
       </c>
     </row>
@@ -53366,17 +53406,17 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>322912186063</t>
+          <t>321765372642</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>Multi-Factor Authentication Solution with Professional Services</t>
+          <t>Unified Endpoint Management (UEM) Managed Services Program</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>City of Battle Creek</t>
+          <t>Southeastern Pennsylvania Transportation Authority</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
@@ -53391,32 +53431,37 @@
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="K710" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="M710" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N710" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O710" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y710" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z710" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322912186063</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765372642</t>
         </is>
       </c>
     </row>
@@ -53426,22 +53471,22 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>325512086219</t>
+          <t>321688802039</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>RFP No. 25-R08</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>RFQ : AI Development Tool</t>
+          <t>Professional Information Technology Services</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>Orange County</t>
-        </is>
-      </c>
-      <c r="F711" t="inlineStr">
-        <is>
-          <t>California</t>
+          <t>Stanislaus Council of Governments</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
@@ -53456,25 +53501,25 @@
       </c>
       <c r="J711" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="K711" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="L711" s="65" t="n">
-        <v>1341.78</v>
+        <v>522000</v>
       </c>
       <c r="M711" t="inlineStr">
         <is>
-          <t>Reseller</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N711" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O711" t="inlineStr">
@@ -53484,12 +53529,12 @@
       </c>
       <c r="Y711" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z711" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325512086219</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321688802039</t>
         </is>
       </c>
     </row>
@@ -53499,22 +53544,22 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>325817624291</t>
+          <t>322924491505</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>27-017-TUSD1</t>
+          <t>#01526NAHAC</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>TEMPORARY STAFFING SERVICES, AS NEEDED</t>
+          <t>IT SUPPORT SERVICES</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>Tucson Unified School District</t>
+          <t>Nevada Affordable Housing Assistance Corporation</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -53529,27 +53574,37 @@
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="K712" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N712" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O712" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y712" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="Z712" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325817624291</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322924491505</t>
         </is>
       </c>
     </row>
@@ -53559,22 +53614,17 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>322910021322</t>
-        </is>
-      </c>
-      <c r="C713" t="inlineStr">
-        <is>
-          <t>#2005976</t>
+          <t>319866591986</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>OFF - Website Hosting Services</t>
+          <t>OFF - Information Technology (IT) Project Management Service For Land Management Software Implementation</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>Standing Rock Housing Authority (SRHA)</t>
+          <t>County of Palm Beach</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -53589,22 +53639,17 @@
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="M713" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N713" t="inlineStr">
-        <is>
-          <t>Offline</t>
+          <t>Consulting;Staff Augmentation</t>
         </is>
       </c>
       <c r="O713" t="inlineStr">
@@ -53614,12 +53659,12 @@
       </c>
       <c r="Y713" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z713" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322910021322</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319866591986</t>
         </is>
       </c>
     </row>
@@ -53629,17 +53674,17 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>323641797323</t>
+          <t>323237511900</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t xml:space="preserve">HOSTED INFORMATION TECHNOLOGY AND SUPPORT SERVICES </t>
+          <t>Workday On-Demand Support Services  &amp; Workday Managed Services - RFI</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>EARLY LEARNING COALITION OF BREVARD COUNTY</t>
+          <t>Bexar County</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -53654,37 +53699,32 @@
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="M714" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N714" t="inlineStr">
-        <is>
-          <t>Offline</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O714" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Srikrishnadeva D</t>
         </is>
       </c>
       <c r="Y714" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z714" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323641797323</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323237511900</t>
         </is>
       </c>
     </row>
@@ -53694,17 +53734,22 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>322527283932</t>
+          <t>321711122109</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Test RFX (please ignore)</t>
+          <t>Managed Information Technology Services</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>The Education Cooperative</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
@@ -53712,29 +53757,39 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
       <c r="M715" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N715" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O715" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
-        </is>
-      </c>
-      <c r="S715" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y715" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z715" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321711122109</t>
         </is>
       </c>
     </row>
@@ -53744,32 +53799,32 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>116977709771</t>
+          <t>321926821572</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>RFP-25-0005</t>
+          <t>2026-RFP-00380</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
+          <t xml:space="preserve">Sheriff's Office Website Hosting Services and Maintenance Support </t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>NeighborWorks America</t>
+          <t>County of San Mateo</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
@@ -53777,39 +53832,42 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="L716" s="65" t="n">
+        <v>210600</v>
+      </c>
       <c r="M716" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N716" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O716" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
-        </is>
-      </c>
-      <c r="S716" t="inlineStr">
-        <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="U716" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y716" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Z716" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
-        </is>
-      </c>
-      <c r="AA716" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321926821572</t>
         </is>
       </c>
     </row>
@@ -53819,22 +53877,17 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>145081112265</t>
+          <t>323518611139</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Technology Strategic Management Consulting</t>
+          <t>Request for Proposals Information Technology (IT) Managed Services &amp; Strategic Support</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>State of Colorado, the Office of Information Technology (OIT)</t>
-        </is>
-      </c>
-      <c r="F717" t="inlineStr">
-        <is>
-          <t>Colorado</t>
+          <t xml:space="preserve">City of Flagler Beach </t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -53849,27 +53902,37 @@
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M717" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N717" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O717" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y717" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Z717" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323518611139</t>
         </is>
       </c>
     </row>
@@ -53879,22 +53942,22 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>166098266830</t>
+          <t>323230410428</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>CC/RFP 27-01</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
+          <t>INFORMATION TECHNOLOGY SERVICES</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Mecklenburg County</t>
-        </is>
-      </c>
-      <c r="F718" t="inlineStr">
-        <is>
-          <t>North Carolina</t>
+          <t>Brigantine Board of Education</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -53909,12 +53972,12 @@
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="M718" t="inlineStr">
-        <is>
-          <t>Audits and Assessment</t>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="O718" t="inlineStr">
@@ -53924,12 +53987,12 @@
       </c>
       <c r="Y718" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z718" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323230410428</t>
         </is>
       </c>
     </row>
@@ -53939,27 +54002,32 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>180166400720</t>
+          <t>127482765035</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>RFP NO. NC- 2025-14</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
+          <t>Computer Maintenance &amp; Technology Support Services - FCSS Fresno County Superintendent of Schools</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>Central Ohio Transit Authority</t>
+          <t>FRESNO COUNTY SUPERINTENDENT OF SCHOOLS</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H719" t="inlineStr">
@@ -53969,22 +54037,57 @@
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>Consulting;Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N719" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O719" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Arshdeep Kaur</t>
+        </is>
+      </c>
+      <c r="S719" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="U719" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="V719" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y719" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z719" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127482765035</t>
+        </is>
+      </c>
+      <c r="AA719" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -53994,32 +54097,22 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>182404957915</t>
-        </is>
-      </c>
-      <c r="C720" t="inlineStr">
-        <is>
-          <t>PWE-10.08.2025</t>
+          <t>321926819566</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>PWE Power BI Dashboard</t>
+          <t xml:space="preserve">INFORMATION TECHNOLOGY (IT) MANAGED SERVICES </t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>City of Issaquah</t>
-        </is>
-      </c>
-      <c r="F720" t="inlineStr">
-        <is>
-          <t>Washington</t>
+          <t>CITY OF HIDDEN HILLS</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
@@ -54029,27 +54122,32 @@
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M720" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O720" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y720" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Z720" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321926819566</t>
         </is>
       </c>
     </row>
@@ -54059,32 +54157,22 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>108771177151</t>
-        </is>
-      </c>
-      <c r="C721" t="inlineStr">
-        <is>
-          <t>791202505005</t>
+          <t>321908570850</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>Government Consulting Services</t>
+          <t>Managed IT Services</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>North Central Texas Council of Governments</t>
-        </is>
-      </c>
-      <c r="F721" t="inlineStr">
-        <is>
-          <t>TEXAS</t>
+          <t>Town of Butner</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
@@ -54094,27 +54182,37 @@
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N721" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O721" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y721" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Z721" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321908570850</t>
         </is>
       </c>
     </row>
@@ -54124,32 +54222,27 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>120893940416</t>
+          <t>323237509835</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>DQ SAAA #2026000004</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Online Content Learning</t>
+          <t>Information Technology Services and Management (rebid)</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>State of Colorado Department of Regulatory Agencies</t>
-        </is>
-      </c>
-      <c r="F722" t="inlineStr">
-        <is>
-          <t>Colorado</t>
+          <t>Palm Beach Metropolitan Planning Organization</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
@@ -54159,30 +54252,32 @@
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L722" s="65" t="n">
-        <v>67300</v>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
       </c>
       <c r="M722" t="inlineStr">
         <is>
-          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
+          <t>Managed Services (MSP);Consulting</t>
         </is>
       </c>
       <c r="O722" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y722" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z722" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323237509835</t>
         </is>
       </c>
     </row>
@@ -54192,22 +54287,17 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>199601365715</t>
+          <t>322912186063</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>Contracted IT Support Services</t>
+          <t>Multi-Factor Authentication Solution with Professional Services</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>ECS4Kids</t>
-        </is>
-      </c>
-      <c r="F723" t="inlineStr">
-        <is>
-          <t>Florida</t>
+          <t>City of Battle Creek</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -54222,35 +54312,32 @@
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="L723" s="65" t="n">
-        <v>291141</v>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
       </c>
       <c r="M723" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N723" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O723" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y723" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="Z723" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322912186063</t>
         </is>
       </c>
     </row>
@@ -54260,100 +54347,65 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>140123456196</t>
-        </is>
-      </c>
-      <c r="C724" t="inlineStr">
-        <is>
-          <t>24-RFP-10</t>
+          <t>322356230879</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+          <t>POWER BI DEVELOPMENT SERVICES</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
-        </is>
-      </c>
-      <c r="F724" t="inlineStr">
-        <is>
-          <t>Chicago</t>
+          <t>SUPERIOR COURT OF CALIFORNIA, COUNTY OF PLACER</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I724" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="L724" s="65" t="n">
-        <v>18620</v>
+        <v>79960</v>
       </c>
       <c r="M724" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Modernization / Migration</t>
+        </is>
+      </c>
+      <c r="N724" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O724" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="P724" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q724" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="S724" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="U724" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="V724" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y724" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z724" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
-        </is>
-      </c>
-      <c r="AA724" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322356230879</t>
         </is>
       </c>
     </row>
@@ -54363,27 +54415,22 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>261982669555</t>
+          <t>322355521244</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>IT Backfill for ERP Configuration (SOW 2)</t>
+          <t>Information Technology Oversight</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>Madison Metropolitan Sewerage District</t>
-        </is>
-      </c>
-      <c r="F725" t="inlineStr">
-        <is>
-          <t>Wisconsin</t>
+          <t>Early Learning Coalition of Osceola County</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
@@ -54393,50 +54440,35 @@
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="L725" s="65" t="n">
-        <v>157000</v>
+        <v>38820</v>
       </c>
       <c r="M725" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O725" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="S725" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="U725" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="V725" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y725" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z725" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
-        </is>
-      </c>
-      <c r="AA725" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322355521244</t>
         </is>
       </c>
     </row>
@@ -54446,22 +54478,17 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>278519751386</t>
+          <t>324091329224</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>Data Warehousing Services</t>
+          <t>OFFLINE - Municipal IT Managed Services</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allen Town School District </t>
-        </is>
-      </c>
-      <c r="F726" t="inlineStr">
-        <is>
-          <t>Pennsylvania</t>
+          <t>Town of Ipswic</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -54476,32 +54503,32 @@
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M726" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N726" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Consulting;Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O726" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y726" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Z726" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/324091329224</t>
         </is>
       </c>
     </row>
@@ -54511,32 +54538,27 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>259790359234</t>
-        </is>
-      </c>
-      <c r="C727" t="inlineStr">
-        <is>
-          <t>601440000049523</t>
+          <t>325512086219</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>Managed Application Services: Application Development and Maintenance Services</t>
+          <t>RFQ : AI Development Tool</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>Texas Department of Transportation</t>
+          <t>Orange County</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
@@ -54546,12 +54568,25 @@
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
-        </is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L727" s="65" t="n">
+        <v>1341.78</v>
       </c>
       <c r="M727" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Reseller</t>
+        </is>
+      </c>
+      <c r="N727" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O727" t="inlineStr">
@@ -54561,12 +54596,12 @@
       </c>
       <c r="Y727" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z727" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325512086219</t>
         </is>
       </c>
     </row>
@@ -54576,22 +54611,22 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>277652547262</t>
+          <t>325817624291</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>27-017-TUSD1</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
+          <t>TEMPORARY STAFFING SERVICES, AS NEEDED</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>District of Columbia Housing Finance Agency</t>
-        </is>
-      </c>
-      <c r="F728" t="inlineStr">
-        <is>
-          <t>Washington, D.C.</t>
+          <t>Tucson Unified School District</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
@@ -54606,17 +54641,12 @@
       </c>
       <c r="J728" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="M728" t="inlineStr">
-        <is>
-          <t>Consulting;Training</t>
-        </is>
-      </c>
-      <c r="N728" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="O728" t="inlineStr">
@@ -54626,12 +54656,12 @@
       </c>
       <c r="Y728" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="Z728" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325817624291</t>
         </is>
       </c>
     </row>
@@ -54641,22 +54671,17 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>269507522240</t>
+          <t>320346351328</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
+          <t>Oracle eBiz Maintenance and Support Services</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>Central Midlands Regional Transit Authority</t>
-        </is>
-      </c>
-      <c r="F729" t="inlineStr">
-        <is>
-          <t>South Carolina</t>
+          <t>Jacksonville Aviation Authority</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
@@ -54671,12 +54696,17 @@
       </c>
       <c r="J729" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="M729" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O729" t="inlineStr">
@@ -54686,12 +54716,12 @@
       </c>
       <c r="Y729" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="Z729" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320346351328</t>
         </is>
       </c>
     </row>
@@ -54701,22 +54731,17 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>294055526085</t>
+          <t>324965643998</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>Oracle Managed Services and Testing as a Service Support</t>
+          <t>OFF - Computer Services Re-Bid</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>CITY OF DURHAM</t>
-        </is>
-      </c>
-      <c r="F730" t="inlineStr">
-        <is>
-          <t>North Carolina</t>
+          <t>Town of Islip Affordable Housing Corp (TOIAHC)</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
@@ -54731,27 +54756,37 @@
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="M730" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N730" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O730" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y730" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="Z730" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/324965643998</t>
         </is>
       </c>
     </row>
@@ -54761,22 +54796,27 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>305430641393</t>
+          <t>323519238874</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>RFP #251-27-92</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>OFF - Information Technology Managed Services</t>
+          <t>TECHNICAL CONTRACTED RESOURCES - IT</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>County of Montcalm</t>
+          <t>Wake County Public School System</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
@@ -54791,27 +54831,32 @@
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="M731" t="inlineStr">
-        <is>
-          <t>Managed Services (MSP)</t>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N731" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O731" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y731" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Z731" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323519238874</t>
         </is>
       </c>
     </row>
@@ -54821,17 +54866,17 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>311307032268</t>
+          <t>323642399430</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+          <t>RFQ 26-05: NETWORK PENETRATION TESTING</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>Housing Authority of the City of Passaic</t>
+          <t>Greater Dayton Premier Management</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
@@ -54846,12 +54891,17 @@
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="M732" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O732" t="inlineStr">
@@ -54861,12 +54911,12 @@
       </c>
       <c r="Y732" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Z732" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323642399430</t>
         </is>
       </c>
     </row>
@@ -54876,32 +54926,27 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>135161266908</t>
+          <t>320834567870</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>RFQ1757840</t>
+          <t>25-26-08</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>25-51-A-PMO-ES-SSN</t>
+          <t>Enterprise IT Ticketing, Asset Management, and Cost Tracking System</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>U.S. Department of the Treasury</t>
-        </is>
-      </c>
-      <c r="F733" t="inlineStr">
-        <is>
-          <t>Washington, D.C.</t>
+          <t>Las Cruces Public Schools</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
@@ -54911,27 +54956,40 @@
       </c>
       <c r="J733" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L733" s="65" t="n">
+        <v>1086140</v>
+      </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>Platform Implementation (ERP, CRMs);Modernization / Migration</t>
         </is>
       </c>
       <c r="N733" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O733" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y733" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z733" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320834567870</t>
         </is>
       </c>
     </row>
@@ -54941,17 +54999,32 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>110691507903</t>
+          <t>321924669171</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>26-8642</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
+          <t>Utility Enterprise Asset Management Consulting</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>Collier County</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
@@ -54961,25 +55034,37 @@
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="L734" s="65" t="n">
-        <v>96200</v>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N734" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
       </c>
       <c r="O734" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y734" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Z734" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321924669171</t>
         </is>
       </c>
     </row>
@@ -54989,17 +55074,22 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>110691507909</t>
+          <t>319105681092</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
+          <t>Website Chatbot Services</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>First Judicial District of Pennsylvania</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
@@ -55009,22 +55099,37 @@
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="N735" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O735" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y735" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z735" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/319105681092</t>
         </is>
       </c>
     </row>
@@ -55034,17 +55139,22 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>108771377911</t>
+          <t>323232475851</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>Facilities and Information Technology Infrastructure Assessment</t>
+          <t>Managed Services Provider for Redding Police Department</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>Town of redding</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -55054,22 +55164,37 @@
       </c>
       <c r="J736" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>Consulting;Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N736" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O736" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y736" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z736" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323232475851</t>
         </is>
       </c>
     </row>
@@ -55079,22 +55204,27 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>120893940419</t>
+          <t>324845232884</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>#25-038-RFP)</t>
+          <t>RFP 019-0-2026/HM</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
+          <t>Cybersecurity Penetration &amp; Vulnerability Testing Services (RE-POST)</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>Newport News Public Schools [VA]</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
@@ -55104,27 +55234,40 @@
       </c>
       <c r="J737" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="L737" s="65" t="n">
+        <v>66096</v>
       </c>
       <c r="M737" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Audits and Assessment</t>
+        </is>
+      </c>
+      <c r="N737" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O737" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y737" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="Z737" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/324845232884</t>
         </is>
       </c>
     </row>
@@ -55134,17 +55277,27 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>114864654049</t>
+          <t>322910021322</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>#2005976</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>M365 Tenant backup</t>
+          <t>OFF - Website Hosting Services</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>Standing Rock Housing Authority (SRHA)</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H738" t="inlineStr">
@@ -55154,22 +55307,37 @@
       </c>
       <c r="J738" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N738" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O738" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y738" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="Z738" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322910021322</t>
         </is>
       </c>
     </row>
@@ -55179,27 +55347,22 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>317194645231</t>
-        </is>
-      </c>
-      <c r="C739" t="inlineStr">
-        <is>
-          <t>BCH-C25-008</t>
+          <t>323641797323</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>Data Migration (CMAS RFP)</t>
+          <t xml:space="preserve">HOSTED INFORMATION TECHNOLOGY AND SUPPORT SERVICES </t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>Business, Consumer Services and Housing Agency</t>
+          <t>EARLY LEARNING COALITION OF BREVARD COUNTY</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
@@ -55209,27 +55372,37 @@
       </c>
       <c r="J739" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="M739" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N739" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O739" t="inlineStr">
         <is>
-          <t>Darshan Tiwari</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y739" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Z739" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323641797323</t>
         </is>
       </c>
     </row>
@@ -55239,27 +55412,27 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>317945474767</t>
+          <t>323238331080</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>RFP # 26-26</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>ServiceNow Technical Services</t>
+          <t>OFF - Helpdesk Partner</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>City of Sacramento</t>
-        </is>
-      </c>
-      <c r="F740" t="inlineStr">
-        <is>
-          <t>California</t>
+          <t>Massbay Community College</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
@@ -55269,22 +55442,40 @@
       </c>
       <c r="J740" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="L740" s="65" t="n">
+        <v>168500</v>
+      </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N740" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O740" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y740" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z740" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323238331080</t>
         </is>
       </c>
     </row>
@@ -55294,22 +55485,22 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>325178884841</t>
+          <t>323517789884</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>Test RFX (Please Ignore)</t>
+          <t>OFF: Information Technology Support Services</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>Test associated agency for trello</t>
+          <t xml:space="preserve">City of South Bay </t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
@@ -55319,27 +55510,37 @@
       </c>
       <c r="J741" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="M741" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N741" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O741" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y741" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Z741" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323517789884</t>
         </is>
       </c>
     </row>
@@ -55349,17 +55550,17 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>321690935004</t>
+          <t>324287792854</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>CoManaged Managed Service Provider (MSP) Services</t>
+          <t>OFFLINE - Cybersecurity Management Program Services</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>Foothills Regional Housing</t>
+          <t>City of Trenton</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
@@ -55374,12 +55575,17 @@
       </c>
       <c r="J742" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="M742" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O742" t="inlineStr">
@@ -55389,12 +55595,12 @@
       </c>
       <c r="Y742" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="Z742" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321690935004</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/324287792854</t>
         </is>
       </c>
     </row>
@@ -55404,22 +55610,27 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>317911067336</t>
+          <t>323642399419</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse</t>
+          <t>Cybersecurity Assessment</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>Michigan Department of Technology Management and Budget</t>
+          <t>Michigan State University</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
@@ -55429,22 +55640,32 @@
       </c>
       <c r="J743" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O743" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y743" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Z743" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323642399419</t>
         </is>
       </c>
     </row>
@@ -55454,27 +55675,22 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>321765371626</t>
-        </is>
-      </c>
-      <c r="C744" t="inlineStr">
-        <is>
-          <t>207-26</t>
+          <t>318930504417</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>Professional and Consulting Services for Strategy and Technology Division</t>
+          <t xml:space="preserve">IAM Managed Services </t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>Fulton County Schools</t>
+          <t>The City of Boston</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
@@ -55484,22 +55700,37 @@
       </c>
       <c r="J744" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>Staff Augmentation;Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N744" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O744" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y744" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z744" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765371626</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/318930504417</t>
         </is>
       </c>
     </row>
@@ -55509,50 +55740,1985 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
+          <t>325724065471</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Test Environment Configuration Services</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Kodiak Island Borough</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N745" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O745" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y745" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z745" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325724065471</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="n">
+        <v>745</v>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>323642412751</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>OFFLINE On-Call Information Technology Services</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>City of Artesia</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="O746" t="inlineStr">
+        <is>
+          <t>Savya Atrey</t>
+        </is>
+      </c>
+      <c r="Y746" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z746" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323642412751</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="n">
+        <v>746</v>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>322527283932</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Test RFX (please ignore)</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>Intent to Award</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="O747" t="inlineStr">
+        <is>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="S747" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="Y747" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z747" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="n">
+        <v>747</v>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>116977709771</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>RFP-25-0005</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>NeighborWorks America</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="O748" t="inlineStr">
+        <is>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="S748" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="U748" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Y748" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z748" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+        </is>
+      </c>
+      <c r="AA748" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="n">
+        <v>748</v>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>145081112265</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Technology Strategic Management Consulting</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>State of Colorado, the Office of Information Technology (OIT)</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="O749" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y749" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="Z749" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="n">
+        <v>749</v>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>166098266830</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Mecklenburg County</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>Audits and Assessment</t>
+        </is>
+      </c>
+      <c r="O750" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y750" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z750" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="n">
+        <v>750</v>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>180166400720</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>Central Ohio Transit Authority</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="O751" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y751" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z751" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="n">
+        <v>751</v>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>182404957915</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>PWE-10.08.2025</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>PWE Power BI Dashboard</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>City of Issaquah</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="M752" t="inlineStr">
+        <is>
+          <t>Modernization / Migration</t>
+        </is>
+      </c>
+      <c r="O752" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y752" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z752" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="n">
+        <v>752</v>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>108771177151</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>791202505005</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Government Consulting Services</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>North Central Texas Council of Governments</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>TEXAS</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="N753" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="O753" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y753" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="Z753" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="n">
+        <v>753</v>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>120893940416</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>DQ SAAA #2026000004</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Online Content Learning</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>State of Colorado Department of Regulatory Agencies</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="L754" s="65" t="n">
+        <v>67300</v>
+      </c>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="O754" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y754" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="Z754" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="n">
+        <v>754</v>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>199601365715</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Contracted IT Support Services</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>ECS4Kids</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="L755" s="65" t="n">
+        <v>291141</v>
+      </c>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N755" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="O755" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y755" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="Z755" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="n">
+        <v>755</v>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>140123456196</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>24-RFP-10</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>Intent to Award</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L756" s="65" t="n">
+        <v>18620</v>
+      </c>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="O756" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P756" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q756" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="S756" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="U756" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="V756" t="inlineStr">
+        <is>
+          <t>In Process</t>
+        </is>
+      </c>
+      <c r="Y756" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Z756" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
+        </is>
+      </c>
+      <c r="AA756" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="n">
+        <v>756</v>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>261982669555</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>IT Backfill for ERP Configuration (SOW 2)</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>Madison Metropolitan Sewerage District</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="L757" s="65" t="n">
+        <v>157000</v>
+      </c>
+      <c r="M757" t="inlineStr">
+        <is>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="O757" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S757" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="U757" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="V757" t="inlineStr">
+        <is>
+          <t>In Process</t>
+        </is>
+      </c>
+      <c r="Y757" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="Z757" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
+        </is>
+      </c>
+      <c r="AA757" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="n">
+        <v>757</v>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>278519751386</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Data Warehousing Services</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allen Town School District </t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="M758" t="inlineStr">
+        <is>
+          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N758" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O758" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y758" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="Z758" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="n">
+        <v>758</v>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>259790359234</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>601440000049523</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Managed Application Services: Application Development and Maintenance Services</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>Texas Department of Transportation</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="M759" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="O759" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y759" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="Z759" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="n">
+        <v>759</v>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>277652547262</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>DCHFA-25-0087 - Microsoft 365 Training and Consulting Services</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>District of Columbia Housing Finance Agency</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="M760" t="inlineStr">
+        <is>
+          <t>Consulting;Training</t>
+        </is>
+      </c>
+      <c r="N760" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O760" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y760" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="Z760" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277652547262</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="n">
+        <v>760</v>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>269507522240</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>Central Midlands Regional Transit Authority</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="M761" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="O761" t="inlineStr">
+        <is>
+          <t>Savya Atrey</t>
+        </is>
+      </c>
+      <c r="Y761" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z761" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="n">
+        <v>761</v>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>294055526085</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Oracle Managed Services and Testing as a Service Support</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>CITY OF DURHAM</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="O762" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y762" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="Z762" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="n">
+        <v>762</v>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>305430641393</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>OFF - Information Technology Managed Services</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>County of Montcalm</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="M763" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="O763" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y763" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="Z763" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="n">
+        <v>763</v>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>311307032268</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>Housing Authority of the City of Passaic</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="M764" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="O764" t="inlineStr">
+        <is>
+          <t>Savya Atrey</t>
+        </is>
+      </c>
+      <c r="Y764" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z764" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="n">
+        <v>764</v>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>135161266908</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>RFQ1757840</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>25-51-A-PMO-ES-SSN</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>U.S. Department of the Treasury</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="N765" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O765" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y765" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z765" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="n">
+        <v>765</v>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>110691507903</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="L766" s="65" t="n">
+        <v>96200</v>
+      </c>
+      <c r="O766" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y766" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z766" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="n">
+        <v>766</v>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>110691507909</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O767" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y767" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z767" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="n">
+        <v>767</v>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>108771377911</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Facilities and Information Technology Infrastructure Assessment</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O768" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y768" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z768" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="n">
+        <v>768</v>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>120893940419</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>#25-038-RFP)</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="M769" t="inlineStr">
+        <is>
+          <t>Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="O769" t="inlineStr">
+        <is>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="Y769" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="Z769" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="n">
+        <v>769</v>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>114864654049</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>M365 Tenant backup</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O770" t="inlineStr">
+        <is>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="Y770" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z770" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="n">
+        <v>770</v>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>317194645231</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>BCH-C25-008</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Data Migration (CMAS RFP)</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>Business, Consumer Services and Housing Agency</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="M771" t="inlineStr">
+        <is>
+          <t>Modernization / Migration</t>
+        </is>
+      </c>
+      <c r="O771" t="inlineStr">
+        <is>
+          <t>Darshan Tiwari</t>
+        </is>
+      </c>
+      <c r="Y771" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z771" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="n">
+        <v>771</v>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>317945474767</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>ServiceNow Technical Services</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>City of Sacramento</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J772" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O772" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y772" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z772" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="n">
+        <v>772</v>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>325178884841</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>Test RFX (Please Ignore)</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>Test associated agency for trello</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J773" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M773" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="O773" t="inlineStr">
+        <is>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="Y773" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z773" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="n">
+        <v>773</v>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>321690935004</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>CoManaged Managed Service Provider (MSP) Services</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>Foothills Regional Housing</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J774" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="M774" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="O774" t="inlineStr">
+        <is>
+          <t>Savya Atrey</t>
+        </is>
+      </c>
+      <c r="Y774" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="Z774" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321690935004</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="n">
+        <v>774</v>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>317911067336</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>Enterprise Data Warehouse</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>Michigan Department of Technology Management and Budget</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J775" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O775" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y775" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z775" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="n">
+        <v>775</v>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>321765371626</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>207-26</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Professional and Consulting Services for Strategy and Technology Division</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>Fulton County Schools</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J776" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="O776" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y776" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="Z776" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765371626</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="n">
+        <v>776</v>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
           <t>321905743581</t>
         </is>
       </c>
-      <c r="D745" t="inlineStr">
+      <c r="D777" t="inlineStr">
         <is>
           <t>ERP Needs Assessment Consulting Services</t>
         </is>
       </c>
-      <c r="E745" t="inlineStr">
+      <c r="E777" t="inlineStr">
         <is>
           <t>Greater Dayton Regional Transit Authority</t>
         </is>
       </c>
-      <c r="G745" t="inlineStr">
+      <c r="G777" t="inlineStr">
         <is>
           <t>RFx Cancelled</t>
         </is>
       </c>
-      <c r="H745" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J745" t="inlineStr">
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J777" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="M745" t="inlineStr">
+      <c r="M777" t="inlineStr">
         <is>
           <t>Consulting</t>
         </is>
       </c>
-      <c r="O745" t="inlineStr">
+      <c r="O777" t="inlineStr">
         <is>
           <t>Ashutosh Chauhan</t>
         </is>
       </c>
-      <c r="Y745" t="inlineStr">
+      <c r="Y777" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="Z745" t="inlineStr">
+      <c r="Z777" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/321905743581</t>
         </is>

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-01 16:29 EDT</t>
+          <t>2026-06-04 06:35 EDT</t>
         </is>
       </c>
     </row>

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-04 06:35 EDT</t>
+          <t>2026-06-09 06:01 EDT</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>717</v>
+        <v>733</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA814"/>
+  <dimension ref="A1:AA830"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -21267,6 +21267,11 @@
           <t>209420244717</t>
         </is>
       </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>P26001</t>
+        </is>
+      </c>
       <c r="D258" t="inlineStr">
         <is>
           <t>IT Services</t>
@@ -21284,7 +21289,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Interview</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -21325,9 +21330,19 @@
           <t>Ashutosh Chauhan</t>
         </is>
       </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
       <c r="Q258" t="inlineStr">
         <is>
           <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="Y258" t="inlineStr">
@@ -52998,22 +53013,22 @@
       </c>
       <c r="G703" t="inlineStr">
         <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
           <t>Interview</t>
         </is>
       </c>
-      <c r="H703" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I703" t="inlineStr">
-        <is>
-          <t>Interview</t>
-        </is>
-      </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="K703" t="inlineStr">
@@ -56920,6 +56935,14 @@
           <t>2026-05-28</t>
         </is>
       </c>
+      <c r="L762" s="65" t="n">
+        <v>172460</v>
+      </c>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>Custom development</t>
+        </is>
+      </c>
       <c r="N762" t="inlineStr">
         <is>
           <t>Portal</t>
@@ -58416,17 +58439,27 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>322527283932</t>
+          <t>325724111572</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>Test RFX (please ignore)</t>
+          <t>IT Network Installation Services</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>Wake County Board of Education [NC]</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G785" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H785" t="inlineStr">
@@ -58434,29 +58467,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M785" t="inlineStr">
-        <is>
-          <t>Training</t>
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="O785" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
-        </is>
-      </c>
-      <c r="S785" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y785" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z785" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325724111572</t>
         </is>
       </c>
     </row>
@@ -58466,32 +58499,22 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>116977709771</t>
-        </is>
-      </c>
-      <c r="C786" t="inlineStr">
-        <is>
-          <t>RFP-25-0005</t>
+          <t>325179333340</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
+          <t>Security Information and Event Management System</t>
         </is>
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>NeighborWorks America</t>
-        </is>
-      </c>
-      <c r="F786" t="inlineStr">
-        <is>
-          <t>Washington, D.C.</t>
+          <t>City of Homer</t>
         </is>
       </c>
       <c r="G786" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H786" t="inlineStr">
@@ -58499,39 +58522,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
       <c r="M786" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting;Custom development</t>
         </is>
       </c>
       <c r="O786" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
-        </is>
-      </c>
-      <c r="S786" t="inlineStr">
-        <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="U786" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y786" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z786" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
-        </is>
-      </c>
-      <c r="AA786" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325179333340</t>
         </is>
       </c>
     </row>
@@ -58541,22 +58559,22 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>145081112265</t>
+          <t>324067736284</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>Technology Strategic Management Consulting</t>
+          <t>APA Microsoft SharePoint Maintenance RFP</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>State of Colorado, the Office of Information Technology (OIT)</t>
-        </is>
-      </c>
-      <c r="F787" t="inlineStr">
-        <is>
-          <t>Colorado</t>
+          <t xml:space="preserve">Office of the Auditors of Public Accounts (APA)	</t>
         </is>
       </c>
       <c r="G787" t="inlineStr">
@@ -58571,27 +58589,37 @@
       </c>
       <c r="J787" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="M787" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N787" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O787" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y787" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Z787" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/324067736284</t>
         </is>
       </c>
     </row>
@@ -58601,22 +58629,17 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>166098266830</t>
+          <t>326400089829</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
+          <t xml:space="preserve">Deliverable-Based Artificial Intelligence (AI) Assessment, Strategy, Implementation and Managed Services </t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>Mecklenburg County</t>
-        </is>
-      </c>
-      <c r="F788" t="inlineStr">
-        <is>
-          <t>North Carolina</t>
+          <t>State of Ohio - Department of Administrative Services</t>
         </is>
       </c>
       <c r="G788" t="inlineStr">
@@ -58631,12 +58654,12 @@
       </c>
       <c r="J788" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="M788" t="inlineStr">
-        <is>
-          <t>Audits and Assessment</t>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="O788" t="inlineStr">
@@ -58646,12 +58669,12 @@
       </c>
       <c r="Y788" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="Z788" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/326400089829</t>
         </is>
       </c>
     </row>
@@ -58661,27 +58684,27 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>180166400720</t>
+          <t>326613630693</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>26.0026</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>Central Ohio Transit Authority</t>
-        </is>
-      </c>
-      <c r="F789" t="inlineStr">
-        <is>
-          <t>Ohio</t>
+          <t>Ann Arbor Public Schools</t>
         </is>
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H789" t="inlineStr">
@@ -58691,22 +58714,27 @@
       </c>
       <c r="J789" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="O789" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y789" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z789" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/326613630693</t>
         </is>
       </c>
     </row>
@@ -58716,32 +58744,22 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>182404957915</t>
-        </is>
-      </c>
-      <c r="C790" t="inlineStr">
-        <is>
-          <t>PWE-10.08.2025</t>
+          <t>325800181469</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>PWE Power BI Dashboard</t>
+          <t>Lake Tahoe Info Software Consultant</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>City of Issaquah</t>
-        </is>
-      </c>
-      <c r="F790" t="inlineStr">
-        <is>
-          <t>Washington</t>
+          <t>Tahoe Regional Planning Agency</t>
         </is>
       </c>
       <c r="G790" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H790" t="inlineStr">
@@ -58751,12 +58769,22 @@
       </c>
       <c r="J790" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="M790" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="N790" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O790" t="inlineStr">
@@ -58766,12 +58794,12 @@
       </c>
       <c r="Y790" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="Z790" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325800181469</t>
         </is>
       </c>
     </row>
@@ -58781,32 +58809,22 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>108771177151</t>
-        </is>
-      </c>
-      <c r="C791" t="inlineStr">
-        <is>
-          <t>791202505005</t>
+          <t>323518613209</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>Government Consulting Services</t>
+          <t>IT Managed Services Provider RFP</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>North Central Texas Council of Governments</t>
-        </is>
-      </c>
-      <c r="F791" t="inlineStr">
-        <is>
-          <t>TEXAS</t>
+          <t>Southeastern Colorado Water Conservancy District (SECWCD</t>
         </is>
       </c>
       <c r="G791" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H791" t="inlineStr">
@@ -58816,27 +58834,32 @@
       </c>
       <c r="J791" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="N791" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="M791" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O791" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Srikrishnadeva D</t>
         </is>
       </c>
       <c r="Y791" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Z791" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323518613209</t>
         </is>
       </c>
     </row>
@@ -58846,32 +58869,27 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>120893940416</t>
+          <t>321926822619</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>DQ SAAA #2026000004</t>
+          <t>IT0420-2662</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>Online Content Learning</t>
+          <t>OFF - Cyber Security Consultant</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>State of Colorado Department of Regulatory Agencies</t>
-        </is>
-      </c>
-      <c r="F792" t="inlineStr">
-        <is>
-          <t>Colorado</t>
+          <t>Nassau County Procurement</t>
         </is>
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H792" t="inlineStr">
@@ -58881,30 +58899,40 @@
       </c>
       <c r="J792" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="L792" s="65" t="n">
-        <v>67300</v>
+        <v>749050</v>
       </c>
       <c r="M792" t="inlineStr">
         <is>
-          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
+          <t>Consulting;Audits and Assessment</t>
+        </is>
+      </c>
+      <c r="N792" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O792" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y792" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Z792" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321926822619</t>
         </is>
       </c>
     </row>
@@ -58914,22 +58942,17 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>199601365715</t>
+          <t>325250685643</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>Contracted IT Support Services</t>
+          <t>Microsoft Support Services</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>ECS4Kids</t>
-        </is>
-      </c>
-      <c r="F793" t="inlineStr">
-        <is>
-          <t>Florida</t>
+          <t>Princeton University</t>
         </is>
       </c>
       <c r="G793" t="inlineStr">
@@ -58944,11 +58967,13 @@
       </c>
       <c r="J793" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="L793" s="65" t="n">
-        <v>291141</v>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
       </c>
       <c r="M793" t="inlineStr">
         <is>
@@ -58967,12 +58992,12 @@
       </c>
       <c r="Y793" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z793" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325250685643</t>
         </is>
       </c>
     </row>
@@ -58982,100 +59007,62 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>140123456196</t>
+          <t>326366112465</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>24-RFP-10</t>
+          <t>2526-309</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+          <t>Microsoft Licensing</t>
         </is>
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
-        </is>
-      </c>
-      <c r="F794" t="inlineStr">
-        <is>
-          <t>Chicago</t>
+          <t>SUPERIOR COURT OF CALFORNIA - COUNTY OF VENTURA</t>
         </is>
       </c>
       <c r="G794" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I794" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J794" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L794" s="65" t="n">
-        <v>18620</v>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
       </c>
       <c r="M794" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Consulting;Reseller</t>
         </is>
       </c>
       <c r="O794" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="P794" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q794" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="S794" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="U794" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="V794" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y794" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="Z794" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
-        </is>
-      </c>
-      <c r="AA794" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/326366112465</t>
         </is>
       </c>
     </row>
@@ -59085,27 +59072,27 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>261982669555</t>
+          <t>323641794238</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>RFQ 2025-001</t>
         </is>
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>IT Backfill for ERP Configuration (SOW 2)</t>
+          <t>OFF - Information Technology Managed Services</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>Madison Metropolitan Sewerage District</t>
-        </is>
-      </c>
-      <c r="F795" t="inlineStr">
-        <is>
-          <t>Wisconsin</t>
+          <t xml:space="preserve">TOWN OF LITCHFIELD	</t>
         </is>
       </c>
       <c r="G795" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H795" t="inlineStr">
@@ -59115,50 +59102,40 @@
       </c>
       <c r="J795" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="L795" s="65" t="n">
-        <v>157000</v>
+        <v>142200</v>
       </c>
       <c r="M795" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N795" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O795" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="S795" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="U795" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="V795" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y795" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Z795" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
-        </is>
-      </c>
-      <c r="AA795" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323641794238</t>
         </is>
       </c>
     </row>
@@ -59168,22 +59145,17 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>278519751386</t>
+          <t>323237521095</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>Data Warehousing Services</t>
+          <t>Support Service</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allen Town School District </t>
-        </is>
-      </c>
-      <c r="F796" t="inlineStr">
-        <is>
-          <t>Pennsylvania</t>
+          <t>Massachusetts Clean Energy Center (MassCEC)</t>
         </is>
       </c>
       <c r="G796" t="inlineStr">
@@ -59198,32 +59170,32 @@
       </c>
       <c r="J796" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="M796" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N796" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O796" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y796" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z796" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323237521095</t>
         </is>
       </c>
     </row>
@@ -59233,32 +59205,22 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>259790359234</t>
-        </is>
-      </c>
-      <c r="C797" t="inlineStr">
-        <is>
-          <t>601440000049523</t>
+          <t>324817243890</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>Managed Application Services: Application Development and Maintenance Services</t>
+          <t>Software Training Services</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>Texas Department of Transportation</t>
-        </is>
-      </c>
-      <c r="F797" t="inlineStr">
-        <is>
-          <t>Texas</t>
+          <t>City of Castle Pines</t>
         </is>
       </c>
       <c r="G797" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H797" t="inlineStr">
@@ -59268,27 +59230,32 @@
       </c>
       <c r="J797" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="M797" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O797" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y797" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="Z797" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/324817243890</t>
         </is>
       </c>
     </row>
@@ -59298,22 +59265,17 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>269507522240</t>
+          <t>324841723629</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
+          <t>Enterprise Resource Planning (ERP) Assessment Consulting Services</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>Central Midlands Regional Transit Authority</t>
-        </is>
-      </c>
-      <c r="F798" t="inlineStr">
-        <is>
-          <t>South Carolina</t>
+          <t>City of Thousand Oaks</t>
         </is>
       </c>
       <c r="G798" t="inlineStr">
@@ -59328,27 +59290,27 @@
       </c>
       <c r="J798" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="M798" t="inlineStr">
-        <is>
-          <t>Managed Services (MSP)</t>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="O798" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y798" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="Z798" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/324841723629</t>
         </is>
       </c>
     </row>
@@ -59358,22 +59320,17 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>294055526085</t>
+          <t>326399881922</t>
         </is>
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>Oracle Managed Services and Testing as a Service Support</t>
+          <t>Adaptation Clearinghouse Modernization Services</t>
         </is>
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>CITY OF DURHAM</t>
-        </is>
-      </c>
-      <c r="F799" t="inlineStr">
-        <is>
-          <t>North Carolina</t>
+          <t>Governor’s Office of Land Use and Climate Innovation</t>
         </is>
       </c>
       <c r="G799" t="inlineStr">
@@ -59388,12 +59345,12 @@
       </c>
       <c r="J799" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="M799" t="inlineStr">
-        <is>
-          <t>Support &amp; Maintenance</t>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="O799" t="inlineStr">
@@ -59403,12 +59360,12 @@
       </c>
       <c r="Y799" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z799" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/326399881922</t>
         </is>
       </c>
     </row>
@@ -59418,22 +59375,22 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>305430641393</t>
+          <t>324845234878</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>IT_RFP_20260428</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>OFF - Information Technology Managed Services</t>
+          <t>Penetration Testing Services</t>
         </is>
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>County of Montcalm</t>
-        </is>
-      </c>
-      <c r="F800" t="inlineStr">
-        <is>
-          <t>Michigan</t>
+          <t>Grand Traverse County</t>
         </is>
       </c>
       <c r="G800" t="inlineStr">
@@ -59448,12 +59405,25 @@
       </c>
       <c r="J800" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
-        </is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L800" s="65" t="n">
+        <v>58500</v>
       </c>
       <c r="M800" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Audits and Assessment</t>
+        </is>
+      </c>
+      <c r="N800" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O800" t="inlineStr">
@@ -59463,12 +59433,12 @@
       </c>
       <c r="Y800" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="Z800" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/324845234878</t>
         </is>
       </c>
     </row>
@@ -59478,22 +59448,17 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>311307032268</t>
+          <t>322527283932</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
-        </is>
-      </c>
-      <c r="E801" t="inlineStr">
-        <is>
-          <t>Housing Authority of the City of Passaic</t>
+          <t>Test RFX (please ignore)</t>
         </is>
       </c>
       <c r="G801" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H801" t="inlineStr">
@@ -59501,29 +59466,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J801" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
       <c r="M801" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O801" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="S801" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y801" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z801" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
         </is>
       </c>
     </row>
@@ -59533,22 +59498,22 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>135161266908</t>
+          <t>116977709771</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>RFQ1757840</t>
+          <t>RFP-25-0005</t>
         </is>
       </c>
       <c r="D802" t="inlineStr">
         <is>
-          <t>25-51-A-PMO-ES-SSN</t>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
         </is>
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>U.S. Department of the Treasury</t>
+          <t>NeighborWorks America</t>
         </is>
       </c>
       <c r="F802" t="inlineStr">
@@ -59558,7 +59523,7 @@
       </c>
       <c r="G802" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H802" t="inlineStr">
@@ -59566,29 +59531,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J802" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="N802" t="inlineStr">
-        <is>
-          <t>Email</t>
+      <c r="M802" t="inlineStr">
+        <is>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O802" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="S802" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="U802" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Y802" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z802" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+        </is>
+      </c>
+      <c r="AA802" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -59598,17 +59573,27 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>110691507903</t>
+          <t>145081112265</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
+          <t>Technology Strategic Management Consulting</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>State of Colorado, the Office of Information Technology (OIT)</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G803" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H803" t="inlineStr">
@@ -59618,11 +59603,13 @@
       </c>
       <c r="J803" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="L803" s="65" t="n">
-        <v>96200</v>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M803" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
       </c>
       <c r="O803" t="inlineStr">
         <is>
@@ -59631,12 +59618,12 @@
       </c>
       <c r="Y803" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z803" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
         </is>
       </c>
     </row>
@@ -59646,17 +59633,27 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>110691507909</t>
+          <t>166098266830</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
+          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>Mecklenburg County</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G804" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H804" t="inlineStr">
@@ -59666,22 +59663,27 @@
       </c>
       <c r="J804" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="M804" t="inlineStr">
+        <is>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O804" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y804" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z804" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
         </is>
       </c>
     </row>
@@ -59691,12 +59693,22 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>108771377911</t>
+          <t>180166400720</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>Facilities and Information Technology Infrastructure Assessment</t>
+          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>Central Ohio Transit Authority</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G805" t="inlineStr">
@@ -59711,7 +59723,7 @@
       </c>
       <c r="J805" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="O805" t="inlineStr">
@@ -59721,12 +59733,12 @@
       </c>
       <c r="Y805" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="Z805" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
         </is>
       </c>
     </row>
@@ -59736,17 +59748,27 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>120893940419</t>
+          <t>182404957915</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>#25-038-RFP)</t>
+          <t>PWE-10.08.2025</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
+          <t>PWE Power BI Dashboard</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>City of Issaquah</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G806" t="inlineStr">
@@ -59761,27 +59783,27 @@
       </c>
       <c r="J806" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="M806" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O806" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y806" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Z806" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
         </is>
       </c>
     </row>
@@ -59791,12 +59813,27 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>114864654049</t>
+          <t>108771177151</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>791202505005</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>M365 Tenant backup</t>
+          <t>Government Consulting Services</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>North Central Texas Council of Governments</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>TEXAS</t>
         </is>
       </c>
       <c r="G807" t="inlineStr">
@@ -59811,22 +59848,27 @@
       </c>
       <c r="J807" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="N807" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O807" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y807" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="Z807" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
         </is>
       </c>
     </row>
@@ -59836,27 +59878,32 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>317194645231</t>
+          <t>120893940416</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>BCH-C25-008</t>
+          <t>DQ SAAA #2026000004</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>Data Migration (CMAS RFP)</t>
+          <t>Online Content Learning</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>Business, Consumer Services and Housing Agency</t>
+          <t>State of Colorado Department of Regulatory Agencies</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G808" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H808" t="inlineStr">
@@ -59866,27 +59913,30 @@
       </c>
       <c r="J808" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="L808" s="65" t="n">
+        <v>67300</v>
       </c>
       <c r="M808" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O808" t="inlineStr">
         <is>
-          <t>Darshan Tiwari</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y808" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z808" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
         </is>
       </c>
     </row>
@@ -59896,27 +59946,27 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>317945474767</t>
+          <t>199601365715</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>ServiceNow Technical Services</t>
+          <t>Contracted IT Support Services</t>
         </is>
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>City of Sacramento</t>
+          <t>ECS4Kids</t>
         </is>
       </c>
       <c r="F809" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G809" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H809" t="inlineStr">
@@ -59926,22 +59976,35 @@
       </c>
       <c r="J809" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="L809" s="65" t="n">
+        <v>291141</v>
+      </c>
+      <c r="M809" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N809" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O809" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y809" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z809" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
         </is>
       </c>
     </row>
@@ -59951,60 +60014,100 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>323239766721</t>
+          <t>140123456196</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>24-RFP-10</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t xml:space="preserve">Information Technology Services for Computing and Networking Infrastructure Support </t>
+          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
         </is>
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>Great Parks of Hamilton County</t>
+          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="G810" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J810" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L810" s="65" t="n">
-        <v>184700</v>
+        <v>18620</v>
       </c>
       <c r="M810" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N810" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O810" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P810" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q810" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="S810" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="U810" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="V810" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y810" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z810" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323239766721</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
+        </is>
+      </c>
+      <c r="AA810" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -60014,17 +60117,22 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>325178884841</t>
+          <t>261982669555</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>Test RFX (Please Ignore)</t>
+          <t>IT Backfill for ERP Configuration (SOW 2)</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>Test associated agency for trello</t>
+          <t>Madison Metropolitan Sewerage District</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G811" t="inlineStr">
@@ -60039,27 +60147,50 @@
       </c>
       <c r="J811" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="L811" s="65" t="n">
+        <v>157000</v>
       </c>
       <c r="M811" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O811" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S811" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="U811" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="V811" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y811" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z811" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
+        </is>
+      </c>
+      <c r="AA811" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -60069,22 +60200,27 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>317911067336</t>
+          <t>278519751386</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse</t>
+          <t>Data Warehousing Services</t>
         </is>
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>Michigan Department of Technology Management and Budget</t>
+          <t xml:space="preserve">Allen Town School District </t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G812" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H812" t="inlineStr">
@@ -60094,22 +60230,32 @@
       </c>
       <c r="J812" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="M812" t="inlineStr">
+        <is>
+          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N812" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O812" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y812" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Z812" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
         </is>
       </c>
     </row>
@@ -60119,22 +60265,27 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>321765371626</t>
+          <t>259790359234</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>207-26</t>
+          <t>601440000049523</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>Professional and Consulting Services for Strategy and Technology Division</t>
+          <t>Managed Application Services: Application Development and Maintenance Services</t>
         </is>
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>Fulton County Schools</t>
+          <t>Texas Department of Transportation</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G813" t="inlineStr">
@@ -60149,22 +60300,27 @@
       </c>
       <c r="J813" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="M813" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O813" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y813" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z813" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765371626</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
         </is>
       </c>
     </row>
@@ -60174,50 +60330,926 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
+          <t>269507522240</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>Central Midlands Regional Transit Authority</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="M814" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="O814" t="inlineStr">
+        <is>
+          <t>Savya Atrey</t>
+        </is>
+      </c>
+      <c r="Y814" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z814" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="n">
+        <v>814</v>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>294055526085</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Oracle Managed Services and Testing as a Service Support</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>CITY OF DURHAM</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="M815" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="O815" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y815" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="Z815" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="n">
+        <v>815</v>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>305430641393</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>OFF - Information Technology Managed Services</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>County of Montcalm</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="M816" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="O816" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y816" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="Z816" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="n">
+        <v>816</v>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>311307032268</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>Housing Authority of the City of Passaic</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="M817" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="O817" t="inlineStr">
+        <is>
+          <t>Savya Atrey</t>
+        </is>
+      </c>
+      <c r="Y817" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z817" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="n">
+        <v>817</v>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>135161266908</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>RFQ1757840</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>25-51-A-PMO-ES-SSN</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>U.S. Department of the Treasury</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="N818" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O818" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y818" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z818" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="n">
+        <v>818</v>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>110691507903</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="L819" s="65" t="n">
+        <v>96200</v>
+      </c>
+      <c r="O819" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y819" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z819" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="n">
+        <v>819</v>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>110691507909</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O820" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y820" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z820" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="n">
+        <v>820</v>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>108771377911</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Facilities and Information Technology Infrastructure Assessment</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O821" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y821" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z821" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="n">
+        <v>821</v>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>120893940419</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>#25-038-RFP)</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="M822" t="inlineStr">
+        <is>
+          <t>Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="O822" t="inlineStr">
+        <is>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="Y822" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="Z822" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="n">
+        <v>822</v>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>114864654049</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>M365 Tenant backup</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O823" t="inlineStr">
+        <is>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="Y823" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z823" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="n">
+        <v>823</v>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>317194645231</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>BCH-C25-008</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>Data Migration (CMAS RFP)</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>Business, Consumer Services and Housing Agency</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="M824" t="inlineStr">
+        <is>
+          <t>Modernization / Migration</t>
+        </is>
+      </c>
+      <c r="O824" t="inlineStr">
+        <is>
+          <t>Darshan Tiwari</t>
+        </is>
+      </c>
+      <c r="Y824" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z824" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="n">
+        <v>824</v>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>317945474767</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>ServiceNow Technical Services</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>City of Sacramento</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O825" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y825" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z825" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="n">
+        <v>825</v>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>323239766721</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information Technology Services for Computing and Networking Infrastructure Support </t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>Great Parks of Hamilton County</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L826" s="65" t="n">
+        <v>184700</v>
+      </c>
+      <c r="M826" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N826" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O826" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y826" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z826" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323239766721</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="n">
+        <v>826</v>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>325178884841</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Test RFX (Please Ignore)</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>Test associated agency for trello</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M827" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="O827" t="inlineStr">
+        <is>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="Y827" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z827" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="n">
+        <v>827</v>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>317911067336</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>Enterprise Data Warehouse</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>Michigan Department of Technology Management and Budget</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O828" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y828" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z828" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="n">
+        <v>828</v>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>321765371626</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>207-26</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>Professional and Consulting Services for Strategy and Technology Division</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>Fulton County Schools</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="O829" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y829" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="Z829" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765371626</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="n">
+        <v>829</v>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
           <t>321905743581</t>
         </is>
       </c>
-      <c r="D814" t="inlineStr">
+      <c r="D830" t="inlineStr">
         <is>
           <t>ERP Needs Assessment Consulting Services</t>
         </is>
       </c>
-      <c r="E814" t="inlineStr">
+      <c r="E830" t="inlineStr">
         <is>
           <t>Greater Dayton Regional Transit Authority</t>
         </is>
       </c>
-      <c r="G814" t="inlineStr">
+      <c r="G830" t="inlineStr">
         <is>
           <t>RFx Cancelled</t>
         </is>
       </c>
-      <c r="H814" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J814" t="inlineStr">
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J830" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="M814" t="inlineStr">
+      <c r="M830" t="inlineStr">
         <is>
           <t>Consulting</t>
         </is>
       </c>
-      <c r="O814" t="inlineStr">
+      <c r="O830" t="inlineStr">
         <is>
           <t>Ashutosh Chauhan</t>
         </is>
       </c>
-      <c r="Y814" t="inlineStr">
+      <c r="Y830" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="Z814" t="inlineStr">
+      <c r="Z830" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/321905743581</t>
         </is>
@@ -60240,7 +61272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA89"/>
+  <dimension ref="A1:AA90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -65153,27 +66185,32 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>202061536982</t>
+          <t>209420244717</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>P26001</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY (IT)MANAGED SERVICE PROVIDER AND NETWORK OPERATIONS CENTER (NOC)</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Mexico Finance Authority (“NMFA”) </t>
+          <t>Allen Metropolitan Housing Authority</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -65183,21 +66220,21 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>BAFO</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L53" s="65" t="n">
-        <v>84000</v>
+        <v>33200</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -65206,7 +66243,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -65221,37 +66258,22 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/202061536982</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/209420244717</t>
         </is>
       </c>
     </row>
@@ -65261,22 +66283,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>231581420260</t>
+          <t>202061536982</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Information Technology Services</t>
+          <t>INFORMATION TECHNOLOGY (IT)MANAGED SERVICE PROVIDER AND NETWORK OPERATIONS CENTER (NOC)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>New Castle County</t>
+          <t xml:space="preserve">New Mexico Finance Authority (“NMFA”) </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -65286,57 +66308,80 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>BAFO</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="L54" s="65" t="n">
+        <v>84000</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/231581420260</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/202061536982</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -65346,22 +66391,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>225906283257</t>
+          <t>231581420260</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Information Systems Consultant</t>
+          <t>Information Technology Services</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Community Action Partnership of Kern</t>
+          <t>New Castle County</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -65376,60 +66421,52 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="L55" s="65" t="n">
-        <v>100</v>
+          <t>2025-12-08</t>
+        </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Awarded</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/225906283257</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/231581420260</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -65439,27 +66476,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>212696339180</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>AI02-26</t>
+          <t>225906283257</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>AI Consulting Services</t>
+          <t>Information Systems Consultant</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Houston-Galveston Area Council</t>
+          <t>Community Action Partnership of Kern</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -65474,7 +66506,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -65482,14 +66514,17 @@
           <t>2025-12-18</t>
         </is>
       </c>
+      <c r="L56" s="65" t="n">
+        <v>100</v>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Consulting;Staff Augmentation</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -65499,27 +66534,32 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Awarded</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/212696339180</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/225906283257</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -65529,27 +66569,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>235886616288</t>
+          <t>212696339180</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AI02-26</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Rebid- Information Technology Services</t>
+          <t>AI Consulting Services</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>LEAD CHARTER SCHOOL</t>
+          <t>Houston-Galveston Area Council</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -65559,55 +66604,52 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="L57" s="65" t="n">
-        <v>24750</v>
+          <t>2025-12-18</t>
+        </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting;Staff Augmentation</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/235886616288</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/212696339180</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -65617,27 +66659,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>235964612297</t>
+          <t>235886616288</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AI Governance, Compliance, and Enablement Platform</t>
+          <t>Rebid- Information Technology Services</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>North Central Texas Council of Governments</t>
+          <t>LEAD CHARTER SCHOOL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TEXAS</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -65647,42 +66689,40 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="L58" s="65" t="n">
+        <v>24750</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Awarded</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -65692,12 +66732,12 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/235964612297</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/235886616288</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -65707,27 +66747,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>225906287352</t>
+          <t>235964612297</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Small Software Application Development</t>
+          <t>AI Governance, Compliance, and Enablement Platform</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Insurance Reserve Fund </t>
+          <t>North Central Texas Council of Governments</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>TEXAS</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -65737,17 +66777,17 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -65762,22 +66802,32 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Awarded</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/225906287352</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/235964612297</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -65787,27 +66837,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>275926212329</t>
+          <t>225906287352</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MICROSOFT OFFICE 365 LICENSING</t>
+          <t>Small Software Application Development</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Village of Tinley Park</t>
+          <t xml:space="preserve">Insurance Reserve Fund </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -65817,55 +66867,47 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="L60" s="65" t="n">
-        <v>114400</v>
+          <t>2026-01-26</t>
+        </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Reseller</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/275926212329</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/225906287352</t>
         </is>
       </c>
     </row>
@@ -65875,22 +66917,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>267386743501</t>
+          <t>275926212329</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FPB – Direct Placement Staffing Services for IT Positions</t>
+          <t>MICROSOFT OFFICE 365 LICENSING</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>University of South Carolina</t>
+          <t>Village of Tinley Park</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -65905,7 +66947,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -65913,14 +66955,17 @@
           <t>2026-02-06</t>
         </is>
       </c>
+      <c r="L61" s="65" t="n">
+        <v>114400</v>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Reseller</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -65930,22 +66975,22 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/267386743501</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/275926212329</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -65960,22 +67005,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>277951244006</t>
+          <t>267386743501</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>offline + online IT Disaster Response Plan</t>
+          <t>FPB – Direct Placement Staffing Services for IT Positions</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>City of Kenai</t>
+          <t>University of South Carolina</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -65990,60 +67035,52 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="L62" s="65" t="n">
-        <v>16800</v>
+          <t>2026-02-06</t>
+        </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Awarded</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277951244006</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/267386743501</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -66053,22 +67090,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>285814477558</t>
+          <t>277951244006</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>RFQ - 1400 Long Beach Cybersecurity Grant Program</t>
+          <t>offline + online IT Disaster Response Plan</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>City of Long Beach</t>
+          <t>City of Kenai</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mississippi</t>
+          <t>Alaska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -66083,50 +67120,55 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="L63" s="65" t="n">
-        <v>123785</v>
+        <v>16800</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Abhishek Zalani</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Awarded</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/285814477558</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/277951244006</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -66141,22 +67183,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>290824554187</t>
+          <t>285814477558</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Cybersecurity Policy and Protocol Consultant Services</t>
+          <t>RFQ - 1400 Long Beach Cybersecurity Grant Program</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Navojo Housing Authority</t>
+          <t>City of Long Beach</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>Mississippi</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -66171,55 +67213,50 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="L64" s="65" t="n">
-        <v>7825</v>
+        <v>123785</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Awarded</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/290824554187</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/285814477558</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -66234,22 +67271,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>305108054745</t>
+          <t>290824554187</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Technology Data Architect Services</t>
+          <t>Cybersecurity Policy and Protocol Consultant Services</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>City of Stamford</t>
+          <t>Navojo Housing Authority</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -66259,35 +67296,30 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="L65" s="65" t="n">
-        <v>47775</v>
+        <v>7825</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Consulting;Staff Augmentation</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -66295,29 +67327,29 @@
           <t>Savya Atrey</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Awarded</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305108054745</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/290824554187</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -66332,22 +67364,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>323517591239</t>
+          <t>305108054745</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CAPK SOW 1</t>
+          <t>Technology Data Architect Services</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Community Action Partnership of Kern</t>
+          <t>City of Stamford</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Connecticut</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -66357,42 +67389,70 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="L66" s="65" t="n">
+        <v>47775</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Consulting;Managed Services (MSP)</t>
+          <t>Consulting;Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
+          <t>Savya Atrey</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323517591239</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305108054745</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -66402,27 +67462,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>323528390341</t>
+          <t>323517591239</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>IT MSP &amp; NOC NMFA Additional SOW</t>
+          <t>CAPK SOW 1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Mexico Finance Authority (“NMFA”) </t>
+          <t>Community Action Partnership of Kern</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -66432,17 +67492,17 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Consulting;Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -66450,19 +67510,19 @@
           <t>Ashutosh Chauhan</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323528390341</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323517591239</t>
         </is>
       </c>
     </row>
@@ -66472,22 +67532,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>320213008064</t>
+          <t>323528390341</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ONLINE WEB-BASED TRAINING</t>
+          <t>IT MSP &amp; NOC NMFA Additional SOW</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Alaska Department of Administration</t>
+          <t xml:space="preserve">New Mexico Finance Authority (“NMFA”) </t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -66507,45 +67567,32 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="L68" s="65" t="n">
-        <v>37800</v>
+          <t>2026-04-22</t>
+        </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320213008064</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323528390341</t>
         </is>
       </c>
     </row>
@@ -66555,32 +67602,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>116977709757</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>RCA-017-25010066</t>
+          <t>320213008064</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ON-LINE MARKETPLACE FOR CLOUD SERVICES AND SOFTWARE</t>
+          <t>ONLINE WEB-BASED TRAINING</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Orange County</t>
+          <t>Alaska Department of Administration</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Alaska</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -66588,34 +67630,52 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="L69" s="65" t="n">
+        <v>37800</v>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Consulting;Reseller</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709757</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320213008064</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -66625,27 +67685,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>116977709771</t>
+          <t>116977709757</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>RFP-25-0005</t>
+          <t>RCA-017-25010066</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
+          <t>ON-LINE MARKETPLACE FOR CLOUD SERVICES AND SOFTWARE</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>NeighborWorks America</t>
+          <t>Orange County</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -66660,7 +67720,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting;Reseller</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -66670,12 +67730,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -66685,7 +67740,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709757</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -66700,22 +67755,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>116977709756</t>
+          <t>116977709771</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>RFP-25-0005</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Hazelwood Information Technology Audit Services</t>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hazelwood School District</t>
+          <t>NeighborWorks America</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -66728,12 +67788,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L71" s="65" t="n">
-        <v>48500</v>
-      </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -66743,12 +67800,12 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -66758,12 +67815,12 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709756</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -66773,27 +67830,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>269389012723</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>COVB-25-101486</t>
+          <t>116977709756</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Hazelwood Information Technology Audit Services</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">City of Virginia Beach </t>
+          <t>Hazelwood School District</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -66806,9 +67858,12 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L72" s="65" t="n">
+        <v>48500</v>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -66818,27 +67873,27 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269389012723</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709756</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -66848,17 +67903,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>322527283932</t>
+          <t>269389012723</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>COVB-25-101486</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Test RFX (please ignore)</t>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">City of Virginia Beach </t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -66868,27 +67938,37 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269389012723</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -66898,27 +67978,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>127590445803</t>
+          <t>322527283932</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>IT Staffing and Professional Services</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Roswell Park Comprehensive Cancer Centre</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>New York</t>
+          <t>Test RFX (please ignore)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -66926,44 +67996,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Consulting;Staff Augmentation</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Akshat Tripathi</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>2025-02-18</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445803</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
         </is>
       </c>
     </row>
@@ -66973,27 +68028,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>123670192881</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>24-31</t>
+          <t>127590445803</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Arapahoe County - IT RECRUITMENT AND STAFFING</t>
+          <t>IT Staffing and Professional Services</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Arapahoe County</t>
+          <t>Roswell Park Comprehensive Cancer Centre</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -67008,37 +68058,37 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting;Staff Augmentation</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/123670192881</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445803</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -67053,27 +68103,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>114864632551</t>
+          <t>123670192881</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>F25-077</t>
+          <t>24-31</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>City of Sunnyvale - Group 4, Software/Application/Database Development, Business Requirements Analysis, and Integration Services</t>
+          <t>Arapahoe County - IT RECRUITMENT AND STAFFING</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>City of Sunnyvale</t>
+          <t>Arapahoe County</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -67088,7 +68138,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -67096,11 +68146,6 @@
           <t>Staff Augmentation</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
       <c r="O76" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
@@ -67108,22 +68153,22 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864632551</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/123670192881</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -67138,27 +68183,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>127678196421</t>
+          <t>114864632551</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>RFQ 24 - 00332</t>
+          <t>F25-077</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>HRT - Workday HCM Staffing Services</t>
+          <t>City of Sunnyvale - Group 4, Software/Application/Database Development, Business Requirements Analysis, and Integration Services</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hampton Roads Transit</t>
+          <t>City of Sunnyvale</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -67168,70 +68213,52 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="L77" s="65" t="n">
-        <v>10000</v>
+          <t>2024-11-14</t>
+        </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
           <t>Staff Augmentation</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>2025-02-07</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127678196421</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864632551</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -67241,22 +68268,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>127590445777</t>
+          <t>127678196421</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>RFQ 24 - 00332</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Temporary Professional Staff Services 2</t>
+          <t>HRT - Workday HCM Staffing Services</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>State of South Dakota Department of Social Services</t>
+          <t>Hampton Roads Transit</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>South Dakota</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -67266,13 +68298,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
-        </is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="L78" s="65" t="n">
+        <v>10000</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -67281,17 +68321,32 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Arshdeep Kaur</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
@@ -67301,12 +68356,12 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445777</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127678196421</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -67316,27 +68371,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>142851074788</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>RFQ-DH-1394</t>
+          <t>127590445777</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ON-CALL INFORMATION TECHNOLOGY INFRASTRUCTURE SERVICES</t>
+          <t>Temporary Professional Staff Services 2</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Metropolitan Water District of Southern California</t>
+          <t>State of South Dakota Department of Social Services</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>South Dakota</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -67351,7 +68401,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -67359,34 +68409,29 @@
           <t>Staff Augmentation</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/142851074788</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445777</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -67401,12 +68446,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>132776626904</t>
+          <t>142851074788</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>RFQ-DH-1394</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ON-CALL INFORMATION TECHNOLOGY (IT) APPLICATION SUPPORT SERVICES (RFQ-DS-1397)</t>
+          <t>ON-CALL INFORMATION TECHNOLOGY INFRASTRUCTURE SERVICES</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -67431,7 +68481,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -67439,29 +68489,34 @@
           <t>Staff Augmentation</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/132776626904</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/142851074788</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -67476,22 +68531,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>127678196440</t>
+          <t>132776626904</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>MINNESOTA JUDICIAL BRANCH - IT Technical/infrastructure Services, Information Technology Application Development And Support Services &amp; Data Science And Machine Learning Services</t>
+          <t>ON-CALL INFORMATION TECHNOLOGY (IT) APPLICATION SUPPORT SERVICES (RFQ-DS-1397)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Minnesota Judicial Branch</t>
+          <t>Metropolitan Water District of Southern California</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -67506,7 +68561,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -67516,27 +68571,27 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127678196440</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/132776626904</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -67551,22 +68606,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>127590445789</t>
+          <t>127678196440</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Retainer Contract Opportunity for Information Technology (IT) Services</t>
+          <t>MINNESOTA JUDICIAL BRANCH - IT Technical/infrastructure Services, Information Technology Application Development And Support Services &amp; Data Science And Machine Learning Services</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>State of Vermont (Department of Buildings and General Services)</t>
+          <t>Minnesota Judicial Branch</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vermont</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -67581,7 +68636,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -67591,17 +68646,17 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Arshdeep Kaur</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
@@ -67611,7 +68666,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445789</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127678196440</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -67626,27 +68681,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>135198825206</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>24-25-78</t>
+          <t>127590445789</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>IT Project Management &amp; Consulting Services</t>
+          <t>Retainer Contract Opportunity for Information Technology (IT) Services</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>City of Santa Clara</t>
+          <t>State of Vermont (Department of Buildings and General Services)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Vermont</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -67656,22 +68706,17 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -67679,34 +68724,24 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135198825206</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445789</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -67721,27 +68756,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>168988159693</t>
+          <t>135198825206</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>6000002323</t>
+          <t>24-25-78</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Performance of Expert Professional Airport Data Analysis and Business Intelligence Consulting Services during 2025 through 2029</t>
+          <t>IT Project Management &amp; Consulting Services</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Port Authority of New York New Jersey</t>
+          <t>City of Santa Clara</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -67751,37 +68786,62 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/168988159693</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135198825206</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -67791,17 +68851,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>169111068380</t>
+          <t>168988159693</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>6000002328</t>
+          <t>6000002323</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Performance of Expert Professional Airport Information Technology and Innovation Consulting Services</t>
+          <t>Performance of Expert Professional Airport Data Analysis and Business Intelligence Consulting Services during 2025 through 2029</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -67851,12 +68911,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/169111068380</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/168988159693</t>
         </is>
       </c>
     </row>
@@ -67866,27 +68921,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>169108930291</t>
+          <t>169111068380</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>RFQ-AR-1399</t>
+          <t>6000002328</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ON-CALL INFORMATION TECHNOLOGY SOFTWARE ASSET MANAGEMENT SERVICES</t>
+          <t>Performance of Expert Professional Airport Information Technology and Innovation Consulting Services</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Metropolitan Water District of Southern California</t>
+          <t>Port Authority of New York New Jersey</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -67906,37 +68961,32 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/169108930291</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/169111068380</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -67946,55 +68996,47 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>140123456196</t>
+          <t>169108930291</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>24-RFP-10</t>
+          <t>RFQ-AR-1399</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+          <t>ON-CALL INFORMATION TECHNOLOGY SOFTWARE ASSET MANAGEMENT SERVICES</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+          <t>Metropolitan Water District of Southern California</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L87" s="65" t="n">
-        <v>18620</v>
+          <t>2025-09-24</t>
+        </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -68002,39 +69044,24 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/169108930291</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -68049,45 +69076,55 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>261982669555</t>
+          <t>140123456196</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>24-RFP-10</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>IT Backfill for ERP Configuration (SOW 2)</t>
+          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Madison Metropolitan Sewerage District</t>
+          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L88" s="65" t="n">
-        <v>157000</v>
+        <v>18620</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -68095,14 +69132,24 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -68112,12 +69159,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -68132,50 +69179,133 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
+          <t>261982669555</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>IT Backfill for ERP Configuration (SOW 2)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Madison Metropolitan Sewerage District</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="L89" s="65" t="n">
+        <v>157000</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>In Process</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>325178884841</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>Test RFX (Please Ignore)</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>Test associated agency for trello</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>Closed Won</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>Akshat Tripathi</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
+      <c r="Y90" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
         </is>

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-15 07:41 EDT</t>
+          <t>2026-06-15 08:37 EDT</t>
         </is>
       </c>
     </row>
@@ -47927,22 +47927,22 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>320490435282</t>
+          <t>316928723643</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>Microsoft Office 365</t>
+          <t>OFF - Information Technology Managed Services</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>City of Morristown</t>
+          <t>City of Leominster</t>
         </is>
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Masssachusetts</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
@@ -47965,32 +47965,24 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="L630" s="65" t="n">
-        <v>75000</v>
-      </c>
       <c r="M630" t="inlineStr">
         <is>
-          <t>Reseller</t>
-        </is>
-      </c>
-      <c r="N630" t="inlineStr">
-        <is>
-          <t>Offline</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O630" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y630" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Z630" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320490435282</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316928723643</t>
         </is>
       </c>
     </row>
@@ -48000,27 +47992,27 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>316928723643</t>
+          <t>320490435282</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>OFF - Information Technology Managed Services</t>
+          <t>Microsoft Office 365</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>City of Leominster</t>
+          <t>City of Morristown</t>
         </is>
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>Masssachusetts</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
@@ -48030,7 +48022,7 @@
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="K631" t="inlineStr">
@@ -48038,24 +48030,37 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="L631" s="65" t="n">
+        <v>37782.48</v>
+      </c>
       <c r="M631" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Reseller</t>
+        </is>
+      </c>
+      <c r="N631" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O631" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="S631" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="Y631" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="Z631" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/316928723643</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320490435282</t>
         </is>
       </c>
     </row>
@@ -48304,12 +48309,17 @@
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J635" t="inlineStr">
@@ -48333,6 +48343,16 @@
       <c r="O635" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="P635" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q635" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="Y635" t="inlineStr">
@@ -49659,12 +49679,17 @@
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J654" t="inlineStr">
@@ -49677,6 +49702,9 @@
           <t>2026-04-24</t>
         </is>
       </c>
+      <c r="L654" s="65" t="n">
+        <v>440510</v>
+      </c>
       <c r="M654" t="inlineStr">
         <is>
           <t>Modernization / Migration</t>
@@ -49690,6 +49718,11 @@
       <c r="O654" t="inlineStr">
         <is>
           <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Q654" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="Y654" t="inlineStr">
@@ -49989,12 +50022,17 @@
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
@@ -50023,6 +50061,11 @@
       <c r="O659" t="inlineStr">
         <is>
           <t>Savya Atrey</t>
+        </is>
+      </c>
+      <c r="Q659" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="Y659" t="inlineStr">
@@ -52834,12 +52877,17 @@
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J700" t="inlineStr">
@@ -52868,6 +52916,16 @@
       <c r="O700" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="P700" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q700" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="Y700" t="inlineStr">
@@ -53204,12 +53262,17 @@
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J705" t="inlineStr">
@@ -53238,6 +53301,16 @@
       <c r="O705" t="inlineStr">
         <is>
           <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="P705" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q705" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Y705" t="inlineStr">
@@ -56470,7 +56543,7 @@
       </c>
       <c r="G754" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H754" t="inlineStr">
@@ -56488,6 +56561,14 @@
           <t>2026-05-26</t>
         </is>
       </c>
+      <c r="L754" s="65" t="n">
+        <v>13440</v>
+      </c>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>Modernization / Migration</t>
+        </is>
+      </c>
       <c r="N754" t="inlineStr">
         <is>
           <t>Email</t>
@@ -56496,6 +56577,11 @@
       <c r="O754" t="inlineStr">
         <is>
           <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="S754" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Y754" t="inlineStr">
@@ -62860,7 +62946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA91"/>
+  <dimension ref="A1:AA92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -69273,32 +69359,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>116977709757</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>RCA-017-25010066</t>
+          <t>325724065471</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ON-LINE MARKETPLACE FOR CLOUD SERVICES AND SOFTWARE</t>
+          <t>Test Environment Configuration Services</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Orange County</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>California</t>
+          <t>Kodiak Island Borough</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -69306,34 +69382,47 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="L70" s="65" t="n">
+        <v>13440</v>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Consulting;Reseller</t>
+          <t>Modernization / Migration</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709757</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325724065471</t>
         </is>
       </c>
     </row>
@@ -69343,27 +69432,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>116977709771</t>
+          <t>116977709757</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>RFP-25-0005</t>
+          <t>RCA-017-25010066</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
+          <t>ON-LINE MARKETPLACE FOR CLOUD SERVICES AND SOFTWARE</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>NeighborWorks America</t>
+          <t>Orange County</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -69378,7 +69467,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting;Reseller</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -69388,12 +69477,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -69403,7 +69487,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709757</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -69418,22 +69502,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>116977709756</t>
+          <t>116977709771</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>RFP-25-0005</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Hazelwood Information Technology Audit Services</t>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hazelwood School District</t>
+          <t>NeighborWorks America</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -69446,12 +69535,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L72" s="65" t="n">
-        <v>48500</v>
-      </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -69461,12 +69547,12 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
@@ -69476,12 +69562,12 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709756</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -69491,27 +69577,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>269389012723</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>COVB-25-101486</t>
+          <t>116977709756</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Hazelwood Information Technology Audit Services</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">City of Virginia Beach </t>
+          <t>Hazelwood School District</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -69524,9 +69605,12 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L73" s="65" t="n">
+        <v>48500</v>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -69536,27 +69620,27 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269389012723</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709756</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -69566,17 +69650,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>322527283932</t>
+          <t>269389012723</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>COVB-25-101486</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Test RFX (please ignore)</t>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">City of Virginia Beach </t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -69586,27 +69685,37 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269389012723</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -69616,27 +69725,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>127590445803</t>
+          <t>322527283932</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>IT Staffing and Professional Services</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Roswell Park Comprehensive Cancer Centre</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>New York</t>
+          <t>Test RFX (please ignore)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -69644,44 +69743,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Consulting;Staff Augmentation</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Akshat Tripathi</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>2025-02-18</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445803</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
         </is>
       </c>
     </row>
@@ -69691,27 +69775,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>123670192881</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>24-31</t>
+          <t>127590445803</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Arapahoe County - IT RECRUITMENT AND STAFFING</t>
+          <t>IT Staffing and Professional Services</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Arapahoe County</t>
+          <t>Roswell Park Comprehensive Cancer Centre</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -69726,37 +69805,37 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting;Staff Augmentation</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/123670192881</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445803</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -69771,27 +69850,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>114864632551</t>
+          <t>123670192881</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>F25-077</t>
+          <t>24-31</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>City of Sunnyvale - Group 4, Software/Application/Database Development, Business Requirements Analysis, and Integration Services</t>
+          <t>Arapahoe County - IT RECRUITMENT AND STAFFING</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>City of Sunnyvale</t>
+          <t>Arapahoe County</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -69806,7 +69885,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -69814,11 +69893,6 @@
           <t>Staff Augmentation</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
       <c r="O77" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
@@ -69826,22 +69900,22 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864632551</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/123670192881</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -69856,27 +69930,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>127678196421</t>
+          <t>114864632551</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>RFQ 24 - 00332</t>
+          <t>F25-077</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>HRT - Workday HCM Staffing Services</t>
+          <t>City of Sunnyvale - Group 4, Software/Application/Database Development, Business Requirements Analysis, and Integration Services</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hampton Roads Transit</t>
+          <t>City of Sunnyvale</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -69886,70 +69960,52 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="L78" s="65" t="n">
-        <v>10000</v>
+          <t>2024-11-14</t>
+        </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
           <t>Staff Augmentation</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>2025-02-07</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127678196421</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864632551</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -69959,22 +70015,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>127590445777</t>
+          <t>127678196421</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>RFQ 24 - 00332</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Temporary Professional Staff Services 2</t>
+          <t>HRT - Workday HCM Staffing Services</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>State of South Dakota Department of Social Services</t>
+          <t>Hampton Roads Transit</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>South Dakota</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -69984,13 +70045,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
-        </is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="L79" s="65" t="n">
+        <v>10000</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -69999,17 +70068,32 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Arshdeep Kaur</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -70019,12 +70103,12 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445777</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127678196421</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -70034,27 +70118,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>142851074788</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>RFQ-DH-1394</t>
+          <t>127590445777</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ON-CALL INFORMATION TECHNOLOGY INFRASTRUCTURE SERVICES</t>
+          <t>Temporary Professional Staff Services 2</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Metropolitan Water District of Southern California</t>
+          <t>State of South Dakota Department of Social Services</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>South Dakota</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -70069,7 +70148,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -70077,34 +70156,29 @@
           <t>Staff Augmentation</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/142851074788</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445777</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -70119,12 +70193,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>132776626904</t>
+          <t>142851074788</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>RFQ-DH-1394</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ON-CALL INFORMATION TECHNOLOGY (IT) APPLICATION SUPPORT SERVICES (RFQ-DS-1397)</t>
+          <t>ON-CALL INFORMATION TECHNOLOGY INFRASTRUCTURE SERVICES</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -70149,7 +70228,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -70157,29 +70236,34 @@
           <t>Staff Augmentation</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/132776626904</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/142851074788</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -70194,22 +70278,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>127678196440</t>
+          <t>132776626904</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>MINNESOTA JUDICIAL BRANCH - IT Technical/infrastructure Services, Information Technology Application Development And Support Services &amp; Data Science And Machine Learning Services</t>
+          <t>ON-CALL INFORMATION TECHNOLOGY (IT) APPLICATION SUPPORT SERVICES (RFQ-DS-1397)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Minnesota Judicial Branch</t>
+          <t>Metropolitan Water District of Southern California</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -70224,7 +70308,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -70234,27 +70318,27 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Arshdeep Kaur</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127678196440</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/132776626904</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -70269,22 +70353,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>127590445789</t>
+          <t>127678196440</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Retainer Contract Opportunity for Information Technology (IT) Services</t>
+          <t>MINNESOTA JUDICIAL BRANCH - IT Technical/infrastructure Services, Information Technology Application Development And Support Services &amp; Data Science And Machine Learning Services</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>State of Vermont (Department of Buildings and General Services)</t>
+          <t>Minnesota Judicial Branch</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vermont</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -70299,7 +70383,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -70309,17 +70393,17 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Arshdeep Kaur</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
@@ -70329,7 +70413,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445789</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127678196440</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -70344,27 +70428,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>135198825206</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>24-25-78</t>
+          <t>127590445789</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>IT Project Management &amp; Consulting Services</t>
+          <t>Retainer Contract Opportunity for Information Technology (IT) Services</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>City of Santa Clara</t>
+          <t>State of Vermont (Department of Buildings and General Services)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Vermont</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -70374,22 +70453,17 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -70397,34 +70471,24 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135198825206</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/127590445789</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -70439,27 +70503,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>168988159693</t>
+          <t>135198825206</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>6000002323</t>
+          <t>24-25-78</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Performance of Expert Professional Airport Data Analysis and Business Intelligence Consulting Services during 2025 through 2029</t>
+          <t>IT Project Management &amp; Consulting Services</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Port Authority of New York New Jersey</t>
+          <t>City of Santa Clara</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -70469,37 +70533,62 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/168988159693</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135198825206</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -70509,17 +70598,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>169111068380</t>
+          <t>168988159693</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>6000002328</t>
+          <t>6000002323</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Performance of Expert Professional Airport Information Technology and Innovation Consulting Services</t>
+          <t>Performance of Expert Professional Airport Data Analysis and Business Intelligence Consulting Services during 2025 through 2029</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -70569,12 +70658,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/169111068380</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/168988159693</t>
         </is>
       </c>
     </row>
@@ -70584,27 +70668,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>169108930291</t>
+          <t>169111068380</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RFQ-AR-1399</t>
+          <t>6000002328</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ON-CALL INFORMATION TECHNOLOGY SOFTWARE ASSET MANAGEMENT SERVICES</t>
+          <t>Performance of Expert Professional Airport Information Technology and Innovation Consulting Services</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Metropolitan Water District of Southern California</t>
+          <t>Port Authority of New York New Jersey</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -70624,37 +70708,32 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/169108930291</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/169111068380</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -70664,55 +70743,47 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>140123456196</t>
+          <t>169108930291</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>24-RFP-10</t>
+          <t>RFQ-AR-1399</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+          <t>ON-CALL INFORMATION TECHNOLOGY SOFTWARE ASSET MANAGEMENT SERVICES</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+          <t>Metropolitan Water District of Southern California</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L88" s="65" t="n">
-        <v>18620</v>
+          <t>2025-09-24</t>
+        </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -70720,39 +70791,24 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/169108930291</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -70767,45 +70823,55 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>261982669555</t>
+          <t>140123456196</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>24-RFP-10</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>IT Backfill for ERP Configuration (SOW 2)</t>
+          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Madison Metropolitan Sewerage District</t>
+          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L89" s="65" t="n">
-        <v>157000</v>
+        <v>18620</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -70813,14 +70879,24 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -70830,12 +70906,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -70850,17 +70926,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>325178884841</t>
+          <t>261982669555</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Test RFX (Please Ignore)</t>
+          <t>IT Backfill for ERP Configuration (SOW 2)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Test associated agency for trello</t>
+          <t>Madison Metropolitan Sewerage District</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -70875,27 +70956,50 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="L90" s="65" t="n">
+        <v>157000</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -70905,58 +71009,113 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
+          <t>325178884841</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Test RFX (Please Ignore)</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Test associated agency for trello</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
           <t>328510794433</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>Workday BA Services (SOW 4)</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>Madison Metropolitan Sewerage District</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Wisconsin</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>Closed Won</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="L91" s="65" t="n">
+      <c r="L92" s="65" t="n">
         <v>170560</v>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="U92" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="Y92" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/328510794433</t>
         </is>

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-15 08:37 EDT</t>
+          <t>2026-06-16 10:02 EDT</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA854"/>
+  <dimension ref="A1:AA855"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -22164,22 +22164,22 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>213938568948</t>
+          <t>225968263907</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Managed Detection and Response (MDR) Services</t>
+          <t xml:space="preserve"> Information Technology Microsoft 365 Licensing for 2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>City of Pasadena</t>
+          <t xml:space="preserve">Barton County </t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Reseller</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -22219,12 +22219,12 @@
       </c>
       <c r="Y270" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/213938568948</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/225968263907</t>
         </is>
       </c>
     </row>
@@ -22234,47 +22234,55 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>225968263907</t>
+          <t>197783925452</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Information Technology Microsoft 365 Licensing for 2026</t>
+          <t>IT Assessment &amp; Modernization at CU Boulder</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barton County </t>
+          <t>University of Colorado</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
+      <c r="L271" s="65" t="n">
+        <v>184215</v>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Reseller</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -22284,17 +22292,27 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="Y271" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z271" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/225968263907</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/197783925452</t>
         </is>
       </c>
     </row>
@@ -22304,42 +22322,37 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>197783925452</t>
+          <t>181354391289</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>IT Assessment &amp; Modernization at CU Boulder</t>
+          <t>Salesforce Customer Relationship Management (CRM) Implementation Services</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>University of Colorado</t>
+          <t>San Mateo County Transit District</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Interview</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -22348,11 +22361,11 @@
         </is>
       </c>
       <c r="L272" s="65" t="n">
-        <v>184215</v>
+        <v>65784</v>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -22362,27 +22375,17 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
-        </is>
-      </c>
-      <c r="P272" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q272" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y272" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/197783925452</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/181354391289</t>
         </is>
       </c>
     </row>
@@ -22392,37 +22395,42 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>181354391289</t>
+          <t>202061536982</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Salesforce Customer Relationship Management (CRM) Implementation Services</t>
+          <t>INFORMATION TECHNOLOGY (IT)MANAGED SERVICE PROVIDER AND NETWORK OPERATIONS CENTER (NOC)</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>San Mateo County Transit District</t>
+          <t xml:space="preserve">New Mexico Finance Authority (“NMFA”) </t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>BAFO</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -22431,16 +22439,16 @@
         </is>
       </c>
       <c r="L273" s="65" t="n">
-        <v>65784</v>
+        <v>84000</v>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
@@ -22448,14 +22456,44 @@
           <t>Ashutosh Chauhan</t>
         </is>
       </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
       <c r="Y273" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/181354391289</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/202061536982</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -22465,42 +22503,37 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>202061536982</t>
+          <t>213938568948</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY (IT)MANAGED SERVICE PROVIDER AND NETWORK OPERATIONS CENTER (NOC)</t>
+          <t>Managed Detection and Response (MDR) Services</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Mexico Finance Authority (“NMFA”) </t>
+          <t>City of Pasadena</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>BAFO</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -22508,9 +22541,6 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="L274" s="65" t="n">
-        <v>84000</v>
-      </c>
       <c r="M274" t="inlineStr">
         <is>
           <t>Managed Services (MSP)</t>
@@ -22518,7 +22548,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
@@ -22526,44 +22556,14 @@
           <t>Ashutosh Chauhan</t>
         </is>
       </c>
-      <c r="P274" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q274" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="R274" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="S274" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="U274" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
       <c r="Y274" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/202061536982</t>
-        </is>
-      </c>
-      <c r="AA274" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/213938568948</t>
         </is>
       </c>
     </row>
@@ -42603,6 +42603,11 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="U554" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
       <c r="Y554" t="inlineStr">
         <is>
           <t>2026-02-24</t>
@@ -48964,7 +48969,7 @@
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
@@ -48974,7 +48979,7 @@
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="K644" t="inlineStr">
@@ -48982,6 +48987,9 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="L644" s="65" t="n">
+        <v>67440</v>
+      </c>
       <c r="M644" t="inlineStr">
         <is>
           <t>Managed Services (MSP)</t>
@@ -48995,6 +49003,11 @@
       <c r="S644" t="inlineStr">
         <is>
           <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="U644" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Y644" t="inlineStr">
@@ -55128,75 +55141,57 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>322355521244</t>
+          <t>324091329224</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>Information Technology Oversight</t>
+          <t>OFFLINE - Municipal IT Managed Services</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>Early Learning Coalition of Osceola County</t>
+          <t>Town of Ipswic</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>Interview</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I733" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J733" t="inlineStr">
         <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="L733" s="65" t="n">
-        <v>38820</v>
-      </c>
       <c r="M733" t="inlineStr">
         <is>
-          <t>Managed Services (MSP);Consulting</t>
+          <t>Consulting;Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O733" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
-        </is>
-      </c>
-      <c r="P733" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q733" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y733" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Z733" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322355521244</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/324091329224</t>
         </is>
       </c>
     </row>
@@ -55206,17 +55201,22 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>324091329224</t>
+          <t>325512086219</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>OFFLINE - Municipal IT Managed Services</t>
+          <t>RFQ : AI Development Tool</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>Town of Ipswic</t>
+          <t>Orange County</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>California</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
@@ -55231,7 +55231,7 @@
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="K734" t="inlineStr">
@@ -55239,24 +55239,32 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="L734" s="65" t="n">
+        <v>1341.78</v>
+      </c>
       <c r="M734" t="inlineStr">
         <is>
-          <t>Consulting;Managed Services (MSP)</t>
+          <t>Reseller</t>
+        </is>
+      </c>
+      <c r="N734" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O734" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y734" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z734" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/324091329224</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325512086219</t>
         </is>
       </c>
     </row>
@@ -55266,37 +55274,37 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>325512086219</t>
+          <t>322355521244</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>RFQ : AI Development Tool</t>
+          <t>Information Technology Oversight</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>Orange County</t>
-        </is>
-      </c>
-      <c r="F735" t="inlineStr">
-        <is>
-          <t>California</t>
+          <t>Early Learning Coalition of Osceola County</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="K735" t="inlineStr">
@@ -55305,31 +55313,36 @@
         </is>
       </c>
       <c r="L735" s="65" t="n">
-        <v>1341.78</v>
+        <v>38820</v>
       </c>
       <c r="M735" t="inlineStr">
         <is>
-          <t>Reseller</t>
-        </is>
-      </c>
-      <c r="N735" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Managed Services (MSP);Consulting</t>
         </is>
       </c>
       <c r="O735" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="P735" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q735" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="Y735" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z735" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325512086219</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322355521244</t>
         </is>
       </c>
     </row>
@@ -62926,6 +62939,66 @@
       <c r="Z854" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/328510794433</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="n">
+        <v>854</v>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>330005222132</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>Rocketlane test</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="M855" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="O855" t="inlineStr">
+        <is>
+          <t>Abhishek Zalani</t>
+        </is>
+      </c>
+      <c r="S855" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Y855" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z855" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/330005222132</t>
         </is>
       </c>
     </row>
@@ -62946,7 +63019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA92"/>
+  <dimension ref="A1:AA93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -65327,7 +65400,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -69114,6 +69187,11 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
       <c r="Y66" t="inlineStr">
         <is>
           <t>2026-02-24</t>
@@ -69226,7 +69304,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -69236,7 +69314,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -69244,6 +69322,9 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="L68" s="65" t="n">
+        <v>67440</v>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t>Managed Services (MSP)</t>
@@ -69257,6 +69338,11 @@
       <c r="S68" t="inlineStr">
         <is>
           <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
@@ -71118,6 +71204,66 @@
       <c r="Z92" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/328510794433</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>330005222132</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Rocketlane test</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Abhishek Zalani</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/330005222132</t>
         </is>
       </c>
     </row>

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-16 10:02 EDT</t>
+          <t>2026-06-19 08:34 EDT</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>754</v>
+        <v>769</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA855"/>
+  <dimension ref="A1:AA871"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -61004,17 +61004,32 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>322527283932</t>
+          <t>328233005798</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>14162 - FY27</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
         <is>
-          <t>Test RFX (please ignore)</t>
+          <t>Microsoft 365 Government</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>City of Kirkwood</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="G823" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H823" t="inlineStr">
@@ -61022,29 +61037,42 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="L823" s="65" t="n">
+        <v>75900.67999999999</v>
+      </c>
       <c r="M823" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Reseller</t>
+        </is>
+      </c>
+      <c r="N823" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O823" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
-        </is>
-      </c>
-      <c r="S823" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y823" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="Z823" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/328233005798</t>
         </is>
       </c>
     </row>
@@ -61054,32 +61082,27 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>116977709771</t>
-        </is>
-      </c>
-      <c r="C824" t="inlineStr">
-        <is>
-          <t>RFP-25-0005</t>
+          <t>326063596263</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
         <is>
-          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
+          <t>Managed Security Service Provider</t>
         </is>
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>NeighborWorks America</t>
+          <t>City of Winston- Salem</t>
         </is>
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G824" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H824" t="inlineStr">
@@ -61087,39 +61110,34 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
       <c r="M824" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O824" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
-        </is>
-      </c>
-      <c r="S824" t="inlineStr">
-        <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="U824" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y824" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="Z824" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
-        </is>
-      </c>
-      <c r="AA824" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/326063596263</t>
         </is>
       </c>
     </row>
@@ -61129,22 +61147,22 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>145081112265</t>
+          <t>322910023405</t>
         </is>
       </c>
       <c r="D825" t="inlineStr">
         <is>
-          <t>Technology Strategic Management Consulting</t>
+          <t>OPERATIONAL TECHNOLOGY CYBERSECURITY CONSULTANT SERVICES</t>
         </is>
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>State of Colorado, the Office of Information Technology (OIT)</t>
+          <t>University of Connecticut UCONN</t>
         </is>
       </c>
       <c r="F825" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Connecticut</t>
         </is>
       </c>
       <c r="G825" t="inlineStr">
@@ -61159,27 +61177,27 @@
       </c>
       <c r="J825" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="M825" t="inlineStr">
-        <is>
-          <t>Consulting</t>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="O825" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y825" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="Z825" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322910023405</t>
         </is>
       </c>
     </row>
@@ -61189,22 +61207,27 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>166098266830</t>
+          <t>320622483180</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>ITN-25-016-PM</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
+          <t>Security Information &amp; Event Management (SIEM)</t>
         </is>
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>Mecklenburg County</t>
+          <t>Miami-Dade County Public Schools</t>
         </is>
       </c>
       <c r="F826" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G826" t="inlineStr">
@@ -61219,27 +61242,40 @@
       </c>
       <c r="J826" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="L826" s="65" t="n">
+        <v>280000</v>
       </c>
       <c r="M826" t="inlineStr">
         <is>
-          <t>Audits and Assessment</t>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N826" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O826" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y826" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z826" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/320622483180</t>
         </is>
       </c>
     </row>
@@ -61249,27 +61285,27 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>180166400720</t>
+          <t>328507896507</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
+          <t>Microsoft Intune Deployment</t>
         </is>
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>Central Ohio Transit Authority</t>
+          <t>Massachusetts Water Resource Authority</t>
         </is>
       </c>
       <c r="F827" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="G827" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H827" t="inlineStr">
@@ -61279,22 +61315,35 @@
       </c>
       <c r="J827" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="L827" s="65" t="n">
+        <v>99000</v>
+      </c>
+      <c r="M827" t="inlineStr">
+        <is>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O827" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y827" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Z827" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/328507896507</t>
         </is>
       </c>
     </row>
@@ -61304,32 +61353,27 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>182404957915</t>
-        </is>
-      </c>
-      <c r="C828" t="inlineStr">
-        <is>
-          <t>PWE-10.08.2025</t>
+          <t>327926990528</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
         <is>
-          <t>PWE Power BI Dashboard</t>
+          <t>CYBERSECURITY VULNERABILITY ANALYSIS</t>
         </is>
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>City of Issaquah</t>
+          <t>Suffolk County Water Authority (SCWA)</t>
         </is>
       </c>
       <c r="F828" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G828" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H828" t="inlineStr">
@@ -61339,27 +61383,35 @@
       </c>
       <c r="J828" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="L828" s="65" t="n">
+        <v>282500</v>
       </c>
       <c r="M828" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O828" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y828" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="Z828" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/327926990528</t>
         </is>
       </c>
     </row>
@@ -61369,32 +61421,27 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>108771177151</t>
-        </is>
-      </c>
-      <c r="C829" t="inlineStr">
-        <is>
-          <t>791202505005</t>
+          <t>328510515928</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>Government Consulting Services</t>
+          <t>UC DAVIS GRADUATE STUDIES SLATE CURRENT SYSTEM UPGRADE</t>
         </is>
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>North Central Texas Council of Governments</t>
+          <t xml:space="preserve"> University of California, Davis</t>
         </is>
       </c>
       <c r="F829" t="inlineStr">
         <is>
-          <t>TEXAS</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G829" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H829" t="inlineStr">
@@ -61404,27 +61451,27 @@
       </c>
       <c r="J829" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="N829" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="O829" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y829" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="Z829" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/328510515928</t>
         </is>
       </c>
     </row>
@@ -61434,32 +61481,27 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>120893940416</t>
-        </is>
-      </c>
-      <c r="C830" t="inlineStr">
-        <is>
-          <t>DQ SAAA #2026000004</t>
+          <t>327714173632</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>Online Content Learning</t>
+          <t>OpenText Support Services</t>
         </is>
       </c>
       <c r="E830" t="inlineStr">
         <is>
-          <t>State of Colorado Department of Regulatory Agencies</t>
+          <t>Philadelphia Gas Works</t>
         </is>
       </c>
       <c r="F830" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G830" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H830" t="inlineStr">
@@ -61469,30 +61511,27 @@
       </c>
       <c r="J830" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L830" s="65" t="n">
-        <v>67300</v>
-      </c>
-      <c r="M830" t="inlineStr">
-        <is>
-          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="O830" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y830" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="Z830" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/327714173632</t>
         </is>
       </c>
     </row>
@@ -61502,22 +61541,17 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>199601365715</t>
+          <t>325178876663</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>061726</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
         <is>
-          <t>Contracted IT Support Services</t>
-        </is>
-      </c>
-      <c r="E831" t="inlineStr">
-        <is>
-          <t>ECS4Kids</t>
-        </is>
-      </c>
-      <c r="F831" t="inlineStr">
-        <is>
-          <t>Florida</t>
+          <t>Enterprise Artificial Intelligence: Platforms, Services, and Integrated Delivery</t>
         </is>
       </c>
       <c r="G831" t="inlineStr">
@@ -61532,15 +61566,17 @@
       </c>
       <c r="J831" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="L831" s="65" t="n">
-        <v>291141</v>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
       </c>
       <c r="M831" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Custom development;Consulting;Modernization / Migration</t>
         </is>
       </c>
       <c r="N831" t="inlineStr">
@@ -61555,12 +61591,12 @@
       </c>
       <c r="Y831" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Z831" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178876663</t>
         </is>
       </c>
     </row>
@@ -61570,100 +61606,67 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>140123456196</t>
+          <t>326398760669</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>24-RFP-10</t>
+          <t>RFP26-016</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+          <t>ENTERPRISE RESOURCE PLANNING (ERP) CONSULTING SERVICES</t>
         </is>
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+          <t>City of Grand Island</t>
         </is>
       </c>
       <c r="F832" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="G832" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H832" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I832" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J832" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L832" s="65" t="n">
-        <v>18620</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
       </c>
       <c r="M832" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O832" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="P832" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q832" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="S832" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="U832" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="V832" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y832" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z832" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
-        </is>
-      </c>
-      <c r="AA832" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/326398760669</t>
         </is>
       </c>
     </row>
@@ -61673,27 +61676,27 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>261982669555</t>
+          <t>328510777069</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>IT Backfill for ERP Configuration (SOW 2)</t>
+          <t>NETWORK PENETRATION TESTING SERVICES</t>
         </is>
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>Madison Metropolitan Sewerage District</t>
+          <t>Village of Ossining</t>
         </is>
       </c>
       <c r="F833" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G833" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H833" t="inlineStr">
@@ -61703,50 +61706,37 @@
       </c>
       <c r="J833" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="L833" s="65" t="n">
-        <v>157000</v>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
       </c>
       <c r="M833" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Audits and Assessment</t>
+        </is>
+      </c>
+      <c r="N833" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O833" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="S833" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="U833" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="V833" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y833" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Z833" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
-        </is>
-      </c>
-      <c r="AA833" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/328510777069</t>
         </is>
       </c>
     </row>
@@ -61756,22 +61746,27 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>278519751386</t>
+          <t>330695319270</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>FY'26-RFQ-DOH</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>Data Warehousing Services</t>
+          <t>WIC-PLATFORM DESIGN, LICENSING AND SUPPORT</t>
         </is>
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allen Town School District </t>
+          <t>District of Columbia Department of Health</t>
         </is>
       </c>
       <c r="F834" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G834" t="inlineStr">
@@ -61786,32 +61781,40 @@
       </c>
       <c r="J834" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="L834" s="65" t="n">
+        <v>184462</v>
       </c>
       <c r="M834" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
+          <t>Platform Implementation (ERP, CRMs);Custom development;Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N834" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email;Portal</t>
         </is>
       </c>
       <c r="O834" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y834" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z834" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/330695319270</t>
         </is>
       </c>
     </row>
@@ -61821,32 +61824,27 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>259790359234</t>
-        </is>
-      </c>
-      <c r="C835" t="inlineStr">
-        <is>
-          <t>601440000049523</t>
+          <t>328510050040</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>Managed Application Services: Application Development and Maintenance Services</t>
+          <t>Technology Transfer Consulting Service - Rebid</t>
         </is>
       </c>
       <c r="E835" t="inlineStr">
         <is>
-          <t>Texas Department of Transportation</t>
+          <t>College of Charleston</t>
         </is>
       </c>
       <c r="F835" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G835" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H835" t="inlineStr">
@@ -61856,12 +61854,17 @@
       </c>
       <c r="J835" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="M835" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O835" t="inlineStr">
@@ -61871,12 +61874,12 @@
       </c>
       <c r="Y835" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Z835" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/328510050040</t>
         </is>
       </c>
     </row>
@@ -61886,22 +61889,27 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>269507522240</t>
+          <t>321924668130</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>Event ID # 1251</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
+          <t>Infor Financials v10 On-Demand Support Services</t>
         </is>
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>Central Midlands Regional Transit Authority</t>
+          <t>Bexar County</t>
         </is>
       </c>
       <c r="F836" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G836" t="inlineStr">
@@ -61916,27 +61924,32 @@
       </c>
       <c r="J836" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="M836" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O836" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y836" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Z836" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321924668130</t>
         </is>
       </c>
     </row>
@@ -61946,22 +61959,22 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>294055526085</t>
+          <t>328510625495</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>Oracle Managed Services and Testing as a Service Support</t>
+          <t>Managed Network Services Provider</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>CITY OF DURHAM</t>
+          <t>ALPINE UNION SCHOOL DISTRICT</t>
         </is>
       </c>
       <c r="F837" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G837" t="inlineStr">
@@ -61976,12 +61989,20 @@
       </c>
       <c r="J837" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="L837" s="65" t="n">
+        <v>136280</v>
       </c>
       <c r="M837" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O837" t="inlineStr">
@@ -61991,12 +62012,12 @@
       </c>
       <c r="Y837" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z837" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/328510625495</t>
         </is>
       </c>
     </row>
@@ -62006,27 +62027,17 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>305430641393</t>
+          <t>322527283932</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>OFF - Information Technology Managed Services</t>
-        </is>
-      </c>
-      <c r="E838" t="inlineStr">
-        <is>
-          <t>County of Montcalm</t>
-        </is>
-      </c>
-      <c r="F838" t="inlineStr">
-        <is>
-          <t>Michigan</t>
+          <t>Test RFX (please ignore)</t>
         </is>
       </c>
       <c r="G838" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H838" t="inlineStr">
@@ -62034,29 +62045,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J838" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
       <c r="M838" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O838" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="S838" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y838" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z838" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
         </is>
       </c>
     </row>
@@ -62066,22 +62077,32 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>311307032268</t>
+          <t>116977709771</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>RFP-25-0005</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
         </is>
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>Housing Authority of the City of Passaic</t>
+          <t>NeighborWorks America</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G839" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H839" t="inlineStr">
@@ -62089,29 +62110,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J839" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
       <c r="M839" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O839" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="S839" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="U839" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Y839" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z839" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+        </is>
+      </c>
+      <c r="AA839" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -62121,32 +62152,27 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>135161266908</t>
-        </is>
-      </c>
-      <c r="C840" t="inlineStr">
-        <is>
-          <t>RFQ1757840</t>
+          <t>145081112265</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>25-51-A-PMO-ES-SSN</t>
+          <t>Technology Strategic Management Consulting</t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>U.S. Department of the Treasury</t>
+          <t>State of Colorado, the Office of Information Technology (OIT)</t>
         </is>
       </c>
       <c r="F840" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G840" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H840" t="inlineStr">
@@ -62156,12 +62182,12 @@
       </c>
       <c r="J840" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="N840" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M840" t="inlineStr">
+        <is>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O840" t="inlineStr">
@@ -62171,12 +62197,12 @@
       </c>
       <c r="Y840" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z840" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
         </is>
       </c>
     </row>
@@ -62186,17 +62212,27 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>110691507903</t>
+          <t>166098266830</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
+          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>Mecklenburg County</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G841" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H841" t="inlineStr">
@@ -62206,25 +62242,27 @@
       </c>
       <c r="J841" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="L841" s="65" t="n">
-        <v>96200</v>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="M841" t="inlineStr">
+        <is>
+          <t>Audits and Assessment</t>
+        </is>
       </c>
       <c r="O841" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y841" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z841" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
         </is>
       </c>
     </row>
@@ -62234,12 +62272,22 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>110691507909</t>
+          <t>180166400720</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
+          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>Central Ohio Transit Authority</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G842" t="inlineStr">
@@ -62254,7 +62302,7 @@
       </c>
       <c r="J842" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="O842" t="inlineStr">
@@ -62264,12 +62312,12 @@
       </c>
       <c r="Y842" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="Z842" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
         </is>
       </c>
     </row>
@@ -62279,12 +62327,27 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>108771377911</t>
+          <t>182404957915</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>PWE-10.08.2025</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>Facilities and Information Technology Infrastructure Assessment</t>
+          <t>PWE Power BI Dashboard</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>City of Issaquah</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G843" t="inlineStr">
@@ -62299,22 +62362,27 @@
       </c>
       <c r="J843" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="M843" t="inlineStr">
+        <is>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O843" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y843" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Z843" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
         </is>
       </c>
     </row>
@@ -62324,17 +62392,27 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>120893940419</t>
+          <t>108771177151</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>#25-038-RFP)</t>
+          <t>791202505005</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
+          <t>Government Consulting Services</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>North Central Texas Council of Governments</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>TEXAS</t>
         </is>
       </c>
       <c r="G844" t="inlineStr">
@@ -62349,27 +62427,27 @@
       </c>
       <c r="J844" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="M844" t="inlineStr">
-        <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="N844" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O844" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y844" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="Z844" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
         </is>
       </c>
     </row>
@@ -62379,12 +62457,27 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>114864654049</t>
+          <t>120893940416</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>DQ SAAA #2026000004</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>M365 Tenant backup</t>
+          <t>Online Content Learning</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>State of Colorado Department of Regulatory Agencies</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G845" t="inlineStr">
@@ -62399,22 +62492,30 @@
       </c>
       <c r="J845" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="L845" s="65" t="n">
+        <v>67300</v>
+      </c>
+      <c r="M845" t="inlineStr">
+        <is>
+          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O845" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y845" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z845" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
         </is>
       </c>
     </row>
@@ -62424,27 +62525,27 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>317194645231</t>
-        </is>
-      </c>
-      <c r="C846" t="inlineStr">
-        <is>
-          <t>BCH-C25-008</t>
+          <t>199601365715</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>Data Migration (CMAS RFP)</t>
+          <t>Contracted IT Support Services</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>Business, Consumer Services and Housing Agency</t>
+          <t>ECS4Kids</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G846" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H846" t="inlineStr">
@@ -62454,27 +62555,35 @@
       </c>
       <c r="J846" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="L846" s="65" t="n">
+        <v>291141</v>
       </c>
       <c r="M846" t="inlineStr">
         <is>
-          <t>Modernization / Migration</t>
+          <t>Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N846" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O846" t="inlineStr">
         <is>
-          <t>Darshan Tiwari</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y846" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z846" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
         </is>
       </c>
     </row>
@@ -62484,52 +62593,100 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>317945474767</t>
+          <t>140123456196</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>24-RFP-10</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>ServiceNow Technical Services</t>
+          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
         </is>
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>City of Sacramento</t>
+          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
         </is>
       </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="G847" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H847" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J847" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L847" s="65" t="n">
+        <v>18620</v>
+      </c>
+      <c r="M847" t="inlineStr">
+        <is>
+          <t>Training</t>
         </is>
       </c>
       <c r="O847" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P847" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q847" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="S847" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="U847" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="V847" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y847" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z847" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
+        </is>
+      </c>
+      <c r="AA847" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -62539,22 +62696,27 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>323239766721</t>
+          <t>261982669555</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t xml:space="preserve">Information Technology Services for Computing and Networking Infrastructure Support </t>
+          <t>IT Backfill for ERP Configuration (SOW 2)</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>Great Parks of Hamilton County</t>
+          <t>Madison Metropolitan Sewerage District</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G848" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H848" t="inlineStr">
@@ -62564,35 +62726,50 @@
       </c>
       <c r="J848" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="L848" s="65" t="n">
-        <v>184700</v>
+        <v>157000</v>
       </c>
       <c r="M848" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N848" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O848" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S848" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="U848" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="V848" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y848" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z848" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323239766721</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
+        </is>
+      </c>
+      <c r="AA848" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -62602,22 +62779,27 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>325178884841</t>
+          <t>278519751386</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>Test RFX (Please Ignore)</t>
+          <t>Data Warehousing Services</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>Test associated agency for trello</t>
+          <t xml:space="preserve">Allen Town School District </t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G849" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H849" t="inlineStr">
@@ -62627,27 +62809,32 @@
       </c>
       <c r="J849" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="M849" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="N849" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O849" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y849" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Z849" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
         </is>
       </c>
     </row>
@@ -62657,17 +62844,27 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>317911067336</t>
+          <t>259790359234</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>601440000049523</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse</t>
+          <t>Managed Application Services: Application Development and Maintenance Services</t>
         </is>
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>Michigan Department of Technology Management and Budget</t>
+          <t>Texas Department of Transportation</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G850" t="inlineStr">
@@ -62682,7 +62879,12 @@
       </c>
       <c r="J850" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="M850" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O850" t="inlineStr">
@@ -62692,12 +62894,12 @@
       </c>
       <c r="Y850" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z850" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
         </is>
       </c>
     </row>
@@ -62707,27 +62909,27 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>321765371626</t>
-        </is>
-      </c>
-      <c r="C851" t="inlineStr">
-        <is>
-          <t>207-26</t>
+          <t>269507522240</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>Professional and Consulting Services for Strategy and Technology Division</t>
+          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
         </is>
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>Fulton County Schools</t>
+          <t>Central Midlands Regional Transit Authority</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G851" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H851" t="inlineStr">
@@ -62737,22 +62939,27 @@
       </c>
       <c r="J851" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="M851" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O851" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y851" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z851" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765371626</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
         </is>
       </c>
     </row>
@@ -62762,22 +62969,27 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>321905743581</t>
+          <t>294055526085</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>ERP Needs Assessment Consulting Services</t>
+          <t>Oracle Managed Services and Testing as a Service Support</t>
         </is>
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>Greater Dayton Regional Transit Authority</t>
+          <t>CITY OF DURHAM</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G852" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H852" t="inlineStr">
@@ -62787,27 +62999,27 @@
       </c>
       <c r="J852" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="M852" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O852" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y852" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Z852" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321905743581</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
         </is>
       </c>
     </row>
@@ -62817,22 +63029,22 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>324841842382</t>
-        </is>
-      </c>
-      <c r="C853" t="inlineStr">
-        <is>
-          <t>2026.13</t>
+          <t>305430641393</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>OFF - Information Technology Services</t>
+          <t>OFF - Information Technology Managed Services</t>
         </is>
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>St. John the Baptist Parish Government</t>
+          <t>County of Montcalm</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G853" t="inlineStr">
@@ -62847,22 +63059,14 @@
       </c>
       <c r="J853" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="L853" s="65" t="n">
-        <v>424440</v>
+          <t>2026-03-16</t>
+        </is>
       </c>
       <c r="M853" t="inlineStr">
         <is>
           <t>Managed Services (MSP)</t>
         </is>
       </c>
-      <c r="N853" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
       <c r="O853" t="inlineStr">
         <is>
           <t>Ashutosh Chauhan</t>
@@ -62870,12 +63074,12 @@
       </c>
       <c r="Y853" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="Z853" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/324841842382</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
         </is>
       </c>
     </row>
@@ -62885,27 +63089,22 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>328510794433</t>
+          <t>311307032268</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>Workday BA Services (SOW 4)</t>
+          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>Madison Metropolitan Sewerage District</t>
-        </is>
-      </c>
-      <c r="F854" t="inlineStr">
-        <is>
-          <t>Wisconsin</t>
+          <t>Housing Authority of the City of Passaic</t>
         </is>
       </c>
       <c r="G854" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H854" t="inlineStr">
@@ -62915,30 +63114,27 @@
       </c>
       <c r="J854" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="L854" s="65" t="n">
-        <v>170560</v>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="M854" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
       </c>
       <c r="O854" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="U854" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y854" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Z854" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/328510794433</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
         </is>
       </c>
     </row>
@@ -62948,57 +63144,939 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
+          <t>135161266908</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>RFQ1757840</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>25-51-A-PMO-ES-SSN</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>U.S. Department of the Treasury</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="N855" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O855" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y855" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z855" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="n">
+        <v>855</v>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>110691507903</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J856" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="L856" s="65" t="n">
+        <v>96200</v>
+      </c>
+      <c r="O856" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y856" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z856" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="n">
+        <v>856</v>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>110691507909</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J857" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O857" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y857" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z857" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="n">
+        <v>857</v>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>108771377911</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>Facilities and Information Technology Infrastructure Assessment</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O858" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="Y858" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z858" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="n">
+        <v>858</v>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>120893940419</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>#25-038-RFP)</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J859" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="M859" t="inlineStr">
+        <is>
+          <t>Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="O859" t="inlineStr">
+        <is>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="Y859" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="Z859" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="n">
+        <v>859</v>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>114864654049</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>M365 Tenant backup</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J860" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="O860" t="inlineStr">
+        <is>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="Y860" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z860" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="n">
+        <v>860</v>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>317194645231</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>BCH-C25-008</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>Data Migration (CMAS RFP)</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>Business, Consumer Services and Housing Agency</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J861" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="M861" t="inlineStr">
+        <is>
+          <t>Modernization / Migration</t>
+        </is>
+      </c>
+      <c r="O861" t="inlineStr">
+        <is>
+          <t>Darshan Tiwari</t>
+        </is>
+      </c>
+      <c r="Y861" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z861" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="n">
+        <v>861</v>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>317945474767</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>ServiceNow Technical Services</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>City of Sacramento</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J862" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O862" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y862" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z862" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="n">
+        <v>862</v>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>323239766721</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information Technology Services for Computing and Networking Infrastructure Support </t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>Great Parks of Hamilton County</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J863" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="L863" s="65" t="n">
+        <v>184700</v>
+      </c>
+      <c r="M863" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N863" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O863" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y863" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z863" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323239766721</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="n">
+        <v>863</v>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>325178884841</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>Test RFX (Please Ignore)</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>Test associated agency for trello</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J864" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M864" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="O864" t="inlineStr">
+        <is>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="Y864" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z864" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="n">
+        <v>864</v>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>317911067336</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>Enterprise Data Warehouse</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>Michigan Department of Technology Management and Budget</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J865" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O865" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y865" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z865" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="n">
+        <v>865</v>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>321765371626</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>207-26</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>Professional and Consulting Services for Strategy and Technology Division</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>Fulton County Schools</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J866" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="O866" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y866" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="Z866" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765371626</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="n">
+        <v>866</v>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>321905743581</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>ERP Needs Assessment Consulting Services</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>Greater Dayton Regional Transit Authority</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J867" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="M867" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="O867" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y867" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z867" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321905743581</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="n">
+        <v>867</v>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>324841842382</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>2026.13</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>OFF - Information Technology Services</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>St. John the Baptist Parish Government</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J868" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L868" s="65" t="n">
+        <v>424440</v>
+      </c>
+      <c r="M868" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N868" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="O868" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y868" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z868" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/324841842382</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="n">
+        <v>868</v>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>328510794433</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>Workday BA Services (SOW 4)</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>Madison Metropolitan Sewerage District</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J869" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L869" s="65" t="n">
+        <v>170560</v>
+      </c>
+      <c r="O869" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="U869" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Y869" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="Z869" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/328510794433</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="n">
+        <v>869</v>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
           <t>330005222132</t>
         </is>
       </c>
-      <c r="C855" t="inlineStr">
+      <c r="C870" t="inlineStr">
         <is>
           <t>1234</t>
         </is>
       </c>
-      <c r="D855" t="inlineStr">
+      <c r="D870" t="inlineStr">
         <is>
           <t>Rocketlane test</t>
         </is>
       </c>
-      <c r="G855" t="inlineStr">
+      <c r="G870" t="inlineStr">
         <is>
           <t>Closed Won</t>
         </is>
       </c>
-      <c r="H855" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J855" t="inlineStr">
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J870" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="M855" t="inlineStr">
+      <c r="M870" t="inlineStr">
         <is>
           <t>Consulting</t>
         </is>
       </c>
-      <c r="O855" t="inlineStr">
+      <c r="O870" t="inlineStr">
         <is>
           <t>Abhishek Zalani</t>
         </is>
       </c>
-      <c r="S855" t="inlineStr">
+      <c r="S870" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="Y855" t="inlineStr">
+      <c r="Y870" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="Z855" t="inlineStr">
+      <c r="Z870" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/330005222132</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="n">
+        <v>870</v>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>328510627557</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>Information Technology Services Contract</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>New Mexico Crime Victims Reparations Commission</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="O871" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y871" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="Z871" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/328510627557</t>
         </is>
       </c>
     </row>

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-19 08:34 EDT</t>
+          <t>2026-06-23 11:45 EDT</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>769</v>
+        <v>775</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA871"/>
+  <dimension ref="A1:AA878"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -53431,12 +53431,17 @@
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J707" t="inlineStr">
@@ -53465,6 +53470,11 @@
       <c r="O707" t="inlineStr">
         <is>
           <t>Savya Atrey</t>
+        </is>
+      </c>
+      <c r="Q707" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Y707" t="inlineStr">
@@ -62027,17 +62037,27 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>322527283932</t>
+          <t>331477789421</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>Test RFX (please ignore)</t>
+          <t>Renewal for FY 2026-2027 WordPress Website Maintenance, Hosting, and Technical Support</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>Collier County</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G838" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H838" t="inlineStr">
@@ -62045,29 +62065,32 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M838" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="L838" s="65" t="n">
+        <v>4630</v>
       </c>
       <c r="O838" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
-        </is>
-      </c>
-      <c r="S838" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y838" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z838" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/331477789421</t>
         </is>
       </c>
     </row>
@@ -62077,32 +62100,32 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>116977709771</t>
+          <t>323642506986</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>RFP-25-0005</t>
+          <t>RFP #2026-109</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
+          <t>OFF: Digital Accessibility &amp; ADA Compliance Services</t>
         </is>
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>NeighborWorks America</t>
+          <t>Genesee County</t>
         </is>
       </c>
       <c r="F839" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G839" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H839" t="inlineStr">
@@ -62110,39 +62133,42 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L839" s="65" t="n">
+        <v>234000</v>
+      </c>
       <c r="M839" t="inlineStr">
         <is>
-          <t>Staff Augmentation</t>
+          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance;Modernization / Migration</t>
+        </is>
+      </c>
+      <c r="N839" t="inlineStr">
+        <is>
+          <t>Offline</t>
         </is>
       </c>
       <c r="O839" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
-        </is>
-      </c>
-      <c r="S839" t="inlineStr">
-        <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="U839" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y839" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Z839" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
-        </is>
-      </c>
-      <c r="AA839" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323642506986</t>
         </is>
       </c>
     </row>
@@ -62152,22 +62178,22 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>145081112265</t>
+          <t>329984145091</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>Technology Strategic Management Consulting</t>
+          <t>Veeam Licenses Renewal (Previous Award Renewal)</t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>State of Colorado, the Office of Information Technology (OIT)</t>
+          <t>St. Johns County</t>
         </is>
       </c>
       <c r="F840" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G840" t="inlineStr">
@@ -62182,27 +62208,32 @@
       </c>
       <c r="J840" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="M840" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Reseller</t>
         </is>
       </c>
       <c r="O840" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y840" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="Z840" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/329984145091</t>
         </is>
       </c>
     </row>
@@ -62212,22 +62243,22 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>166098266830</t>
+          <t>330340706039</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
+          <t>FY27 Library Automation Statewide OCSS OSC 714 RJL OCSS</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>Mecklenburg County</t>
+          <t>Ohio Department of Rehabilitation &amp; Corrections</t>
         </is>
       </c>
       <c r="F841" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G841" t="inlineStr">
@@ -62242,27 +62273,27 @@
       </c>
       <c r="J841" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="M841" t="inlineStr">
-        <is>
-          <t>Audits and Assessment</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="O841" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y841" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Z841" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/330340706039</t>
         </is>
       </c>
     </row>
@@ -62272,27 +62303,32 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>180166400720</t>
+          <t>326363911906</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>P26-59</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
+          <t>Enterprise Resource Planning Consulting Services</t>
         </is>
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>Central Ohio Transit Authority</t>
+          <t>City of Bangor</t>
         </is>
       </c>
       <c r="F842" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Maine</t>
         </is>
       </c>
       <c r="G842" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H842" t="inlineStr">
@@ -62302,22 +62338,32 @@
       </c>
       <c r="J842" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="M842" t="inlineStr">
+        <is>
+          <t>Consulting;Audits and Assessment</t>
         </is>
       </c>
       <c r="O842" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y842" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z842" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/326363911906</t>
         </is>
       </c>
     </row>
@@ -62327,32 +62373,27 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>182404957915</t>
-        </is>
-      </c>
-      <c r="C843" t="inlineStr">
-        <is>
-          <t>PWE-10.08.2025</t>
+          <t>328507898596</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>PWE Power BI Dashboard</t>
+          <t xml:space="preserve">Managed Detection and Response/Endpoint Detection and Response Solution </t>
         </is>
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>City of Issaquah</t>
+          <t xml:space="preserve">Tuscola Intermediate School District </t>
         </is>
       </c>
       <c r="F843" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G843" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H843" t="inlineStr">
@@ -62362,27 +62403,27 @@
       </c>
       <c r="J843" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="M843" t="inlineStr">
-        <is>
-          <t>Modernization / Migration</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="O843" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y843" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Z843" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/328507898596</t>
         </is>
       </c>
     </row>
@@ -62392,32 +62433,17 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>108771177151</t>
-        </is>
-      </c>
-      <c r="C844" t="inlineStr">
-        <is>
-          <t>791202505005</t>
+          <t>322527283932</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>Government Consulting Services</t>
-        </is>
-      </c>
-      <c r="E844" t="inlineStr">
-        <is>
-          <t>North Central Texas Council of Governments</t>
-        </is>
-      </c>
-      <c r="F844" t="inlineStr">
-        <is>
-          <t>TEXAS</t>
+          <t>Test RFX (please ignore)</t>
         </is>
       </c>
       <c r="G844" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H844" t="inlineStr">
@@ -62425,29 +62451,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J844" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="N844" t="inlineStr">
-        <is>
-          <t>Portal</t>
+      <c r="M844" t="inlineStr">
+        <is>
+          <t>Training</t>
         </is>
       </c>
       <c r="O844" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Akshat Tripathi</t>
+        </is>
+      </c>
+      <c r="S844" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y844" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z844" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/322527283932</t>
         </is>
       </c>
     </row>
@@ -62457,32 +62483,32 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>120893940416</t>
+          <t>116977709771</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>DQ SAAA #2026000004</t>
+          <t>RFP-25-0005</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>Online Content Learning</t>
+          <t>Certified Partner - NEIGHBORWORKS AMERICA, IT  SERVICES</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>State of Colorado Department of Regulatory Agencies</t>
+          <t>NeighborWorks America</t>
         </is>
       </c>
       <c r="F845" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G845" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H845" t="inlineStr">
@@ -62490,32 +62516,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J845" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L845" s="65" t="n">
-        <v>67300</v>
-      </c>
       <c r="M845" t="inlineStr">
         <is>
-          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O845" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Yashaswini Gautam</t>
+        </is>
+      </c>
+      <c r="S845" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="U845" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Y845" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z845" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/116977709771</t>
+        </is>
+      </c>
+      <c r="AA845" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -62525,22 +62558,22 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>199601365715</t>
+          <t>145081112265</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>Contracted IT Support Services</t>
+          <t>Technology Strategic Management Consulting</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>ECS4Kids</t>
+          <t>State of Colorado, the Office of Information Technology (OIT)</t>
         </is>
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G846" t="inlineStr">
@@ -62555,35 +62588,27 @@
       </c>
       <c r="J846" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="L846" s="65" t="n">
-        <v>291141</v>
+          <t>2025-10-01</t>
+        </is>
       </c>
       <c r="M846" t="inlineStr">
         <is>
-          <t>Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N846" t="inlineStr">
-        <is>
-          <t>Portal</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="O846" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y846" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z846" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/145081112265</t>
         </is>
       </c>
     </row>
@@ -62593,100 +62618,57 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>140123456196</t>
-        </is>
-      </c>
-      <c r="C847" t="inlineStr">
-        <is>
-          <t>24-RFP-10</t>
+          <t>166098266830</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
+          <t>Enterprise Resource Planning (ERP) System Assessment.</t>
         </is>
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
+          <t>Mecklenburg County</t>
         </is>
       </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G847" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H847" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I847" t="inlineStr">
-        <is>
-          <t>Interview</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J847" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L847" s="65" t="n">
-        <v>18620</v>
+          <t>2025-10-07</t>
+        </is>
       </c>
       <c r="M847" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Audits and Assessment</t>
         </is>
       </c>
       <c r="O847" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="P847" t="inlineStr">
-        <is>
-          <t>Interview Scheduled</t>
-        </is>
-      </c>
-      <c r="Q847" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="S847" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="U847" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="V847" t="inlineStr">
-        <is>
-          <t>In Process</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y847" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z847" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
-        </is>
-      </c>
-      <c r="AA847" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/166098266830</t>
         </is>
       </c>
     </row>
@@ -62696,27 +62678,27 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>261982669555</t>
+          <t>180166400720</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>IT Backfill for ERP Configuration (SOW 2)</t>
+          <t xml:space="preserve"> 25-012 Data Engineering Phase II</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>Madison Metropolitan Sewerage District</t>
+          <t>Central Ohio Transit Authority</t>
         </is>
       </c>
       <c r="F848" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G848" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H848" t="inlineStr">
@@ -62726,15 +62708,7 @@
       </c>
       <c r="J848" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="L848" s="65" t="n">
-        <v>157000</v>
-      </c>
-      <c r="M848" t="inlineStr">
-        <is>
-          <t>Staff Augmentation</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="O848" t="inlineStr">
@@ -62742,34 +62716,14 @@
           <t>Madhav Mitruka</t>
         </is>
       </c>
-      <c r="S848" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="U848" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="V848" t="inlineStr">
-        <is>
-          <t>In Process</t>
-        </is>
-      </c>
       <c r="Y848" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="Z848" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
-        </is>
-      </c>
-      <c r="AA848" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/180166400720</t>
         </is>
       </c>
     </row>
@@ -62779,27 +62733,32 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>278519751386</t>
+          <t>182404957915</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>PWE-10.08.2025</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>Data Warehousing Services</t>
+          <t>PWE Power BI Dashboard</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allen Town School District </t>
+          <t>City of Issaquah</t>
         </is>
       </c>
       <c r="F849" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G849" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H849" t="inlineStr">
@@ -62809,32 +62768,27 @@
       </c>
       <c r="J849" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="M849" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="N849" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O849" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y849" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Z849" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/182404957915</t>
         </is>
       </c>
     </row>
@@ -62844,32 +62798,32 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>259790359234</t>
+          <t>108771177151</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>601440000049523</t>
+          <t>791202505005</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>Managed Application Services: Application Development and Maintenance Services</t>
+          <t>Government Consulting Services</t>
         </is>
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>Texas Department of Transportation</t>
+          <t>North Central Texas Council of Governments</t>
         </is>
       </c>
       <c r="F850" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>TEXAS</t>
         </is>
       </c>
       <c r="G850" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H850" t="inlineStr">
@@ -62879,27 +62833,27 @@
       </c>
       <c r="J850" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="M850" t="inlineStr">
-        <is>
-          <t>Support &amp; Maintenance</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="N850" t="inlineStr">
+        <is>
+          <t>Portal</t>
         </is>
       </c>
       <c r="O850" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y850" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="Z850" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771177151</t>
         </is>
       </c>
     </row>
@@ -62909,27 +62863,32 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>269507522240</t>
+          <t>120893940416</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>DQ SAAA #2026000004</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
+          <t>Online Content Learning</t>
         </is>
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>Central Midlands Regional Transit Authority</t>
+          <t>State of Colorado Department of Regulatory Agencies</t>
         </is>
       </c>
       <c r="F851" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G851" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H851" t="inlineStr">
@@ -62939,27 +62898,30 @@
       </c>
       <c r="J851" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
-        </is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="L851" s="65" t="n">
+        <v>67300</v>
       </c>
       <c r="M851" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Modernization / Migration;Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O851" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y851" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z851" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940416</t>
         </is>
       </c>
     </row>
@@ -62969,22 +62931,22 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>294055526085</t>
+          <t>199601365715</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>Oracle Managed Services and Testing as a Service Support</t>
+          <t>Contracted IT Support Services</t>
         </is>
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>CITY OF DURHAM</t>
+          <t>ECS4Kids</t>
         </is>
       </c>
       <c r="F852" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G852" t="inlineStr">
@@ -62999,27 +62961,35 @@
       </c>
       <c r="J852" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="L852" s="65" t="n">
+        <v>291141</v>
       </c>
       <c r="M852" t="inlineStr">
         <is>
           <t>Support &amp; Maintenance</t>
         </is>
       </c>
+      <c r="N852" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
       <c r="O852" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y852" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z852" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/199601365715</t>
         </is>
       </c>
     </row>
@@ -63029,57 +62999,100 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>305430641393</t>
+          <t>140123456196</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>24-RFP-10</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>OFF - Information Technology Managed Services</t>
+          <t>Agreement for Professional Development Program for Management Development and IT (Years 2025–2027)</t>
         </is>
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>County of Montcalm</t>
+          <t>Metropolitan Water Reclamation District of Greater Chicago</t>
         </is>
       </c>
       <c r="F853" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="G853" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H853" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J853" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
-        </is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L853" s="65" t="n">
+        <v>18620</v>
       </c>
       <c r="M853" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O853" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="P853" t="inlineStr">
+        <is>
+          <t>Interview Scheduled</t>
+        </is>
+      </c>
+      <c r="Q853" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="S853" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="U853" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="V853" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y853" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z853" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/140123456196</t>
+        </is>
+      </c>
+      <c r="AA853" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -63089,22 +63102,27 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>311307032268</t>
+          <t>261982669555</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+          <t>IT Backfill for ERP Configuration (SOW 2)</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>Housing Authority of the City of Passaic</t>
+          <t>Madison Metropolitan Sewerage District</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G854" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H854" t="inlineStr">
@@ -63114,27 +63132,50 @@
       </c>
       <c r="J854" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="L854" s="65" t="n">
+        <v>157000</v>
       </c>
       <c r="M854" t="inlineStr">
         <is>
-          <t>Managed Services (MSP)</t>
+          <t>Staff Augmentation</t>
         </is>
       </c>
       <c r="O854" t="inlineStr">
         <is>
-          <t>Savya Atrey</t>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S854" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="U854" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="V854" t="inlineStr">
+        <is>
+          <t>In Process</t>
         </is>
       </c>
       <c r="Y854" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z854" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/261982669555</t>
+        </is>
+      </c>
+      <c r="AA854" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -63144,32 +63185,27 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>135161266908</t>
-        </is>
-      </c>
-      <c r="C855" t="inlineStr">
-        <is>
-          <t>RFQ1757840</t>
+          <t>278519751386</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>25-51-A-PMO-ES-SSN</t>
+          <t>Data Warehousing Services</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>U.S. Department of the Treasury</t>
+          <t xml:space="preserve">Allen Town School District </t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="G855" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H855" t="inlineStr">
@@ -63179,7 +63215,12 @@
       </c>
       <c r="J855" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="M855" t="inlineStr">
+        <is>
+          <t>Platform Implementation (ERP, CRMs);Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="N855" t="inlineStr">
@@ -63189,17 +63230,17 @@
       </c>
       <c r="O855" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y855" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Z855" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/278519751386</t>
         </is>
       </c>
     </row>
@@ -63209,17 +63250,32 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>110691507903</t>
+          <t>259790359234</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>601440000049523</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
+          <t>Managed Application Services: Application Development and Maintenance Services</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>Texas Department of Transportation</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G856" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H856" t="inlineStr">
@@ -63229,25 +63285,27 @@
       </c>
       <c r="J856" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="L856" s="65" t="n">
-        <v>96200</v>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="M856" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance</t>
+        </is>
       </c>
       <c r="O856" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y856" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Z856" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/259790359234</t>
         </is>
       </c>
     </row>
@@ -63257,17 +63315,27 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>110691507909</t>
+          <t>269507522240</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
+          <t>OFFLINE - INFORMATION TECHNOLOGY MANAGED SERVICES PROVIDER</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>Central Midlands Regional Transit Authority</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G857" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H857" t="inlineStr">
@@ -63277,22 +63345,27 @@
       </c>
       <c r="J857" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="M857" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O857" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y857" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z857" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/269507522240</t>
         </is>
       </c>
     </row>
@@ -63302,17 +63375,27 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>108771377911</t>
+          <t>294055526085</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>Facilities and Information Technology Infrastructure Assessment</t>
+          <t>Oracle Managed Services and Testing as a Service Support</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>CITY OF DURHAM</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G858" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H858" t="inlineStr">
@@ -63322,22 +63405,27 @@
       </c>
       <c r="J858" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="M858" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance</t>
         </is>
       </c>
       <c r="O858" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y858" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Z858" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/294055526085</t>
         </is>
       </c>
     </row>
@@ -63347,22 +63435,27 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>120893940419</t>
-        </is>
-      </c>
-      <c r="C859" t="inlineStr">
-        <is>
-          <t>#25-038-RFP)</t>
+          <t>305430641393</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
         <is>
-          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
+          <t>OFF - Information Technology Managed Services</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>County of Montcalm</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G859" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H859" t="inlineStr">
@@ -63372,27 +63465,27 @@
       </c>
       <c r="J859" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="M859" t="inlineStr">
         <is>
-          <t>Platform Implementation (ERP, CRMs)</t>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O859" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y859" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="Z859" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/305430641393</t>
         </is>
       </c>
     </row>
@@ -63402,17 +63495,22 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>114864654049</t>
+          <t>311307032268</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
         <is>
-          <t>M365 Tenant backup</t>
+          <t>RPF-MANAGED IT SERVICES RESOLICITATION</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>Housing Authority of the City of Passaic</t>
         </is>
       </c>
       <c r="G860" t="inlineStr">
         <is>
-          <t>Closed Lost</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H860" t="inlineStr">
@@ -63422,22 +63520,27 @@
       </c>
       <c r="J860" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="M860" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
         </is>
       </c>
       <c r="O860" t="inlineStr">
         <is>
-          <t>Yashaswini Gautam</t>
+          <t>Savya Atrey</t>
         </is>
       </c>
       <c r="Y860" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Z860" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/311307032268</t>
         </is>
       </c>
     </row>
@@ -63447,27 +63550,32 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>317194645231</t>
+          <t>135161266908</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>BCH-C25-008</t>
+          <t>RFQ1757840</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>Data Migration (CMAS RFP)</t>
+          <t>25-51-A-PMO-ES-SSN</t>
         </is>
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>Business, Consumer Services and Housing Agency</t>
+          <t>U.S. Department of the Treasury</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
         </is>
       </c>
       <c r="G861" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H861" t="inlineStr">
@@ -63477,27 +63585,27 @@
       </c>
       <c r="J861" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="M861" t="inlineStr">
-        <is>
-          <t>Modernization / Migration</t>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="N861" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="O861" t="inlineStr">
         <is>
-          <t>Darshan Tiwari</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y861" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z861" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/135161266908</t>
         </is>
       </c>
     </row>
@@ -63507,27 +63615,17 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>317945474767</t>
+          <t>110691507903</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>ServiceNow Technical Services</t>
-        </is>
-      </c>
-      <c r="E862" t="inlineStr">
-        <is>
-          <t>City of Sacramento</t>
-        </is>
-      </c>
-      <c r="F862" t="inlineStr">
-        <is>
-          <t>California</t>
+          <t>020-25 - GIS Services: Data, Metadata, Application Development, and Training</t>
         </is>
       </c>
       <c r="G862" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H862" t="inlineStr">
@@ -63537,22 +63635,25 @@
       </c>
       <c r="J862" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
-        </is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="L862" s="65" t="n">
+        <v>96200</v>
       </c>
       <c r="O862" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y862" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z862" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507903</t>
         </is>
       </c>
     </row>
@@ -63562,22 +63663,17 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>323239766721</t>
+          <t>110691507909</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t xml:space="preserve">Information Technology Services for Computing and Networking Infrastructure Support </t>
-        </is>
-      </c>
-      <c r="E863" t="inlineStr">
-        <is>
-          <t>Great Parks of Hamilton County</t>
+          <t>CONSULTATION AND INFORMATION TECHNOLOGY SUPPORT SERVICES</t>
         </is>
       </c>
       <c r="G863" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H863" t="inlineStr">
@@ -63587,35 +63683,22 @@
       </c>
       <c r="J863" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="L863" s="65" t="n">
-        <v>184700</v>
-      </c>
-      <c r="M863" t="inlineStr">
-        <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N863" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="O863" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y863" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z863" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323239766721</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/110691507909</t>
         </is>
       </c>
     </row>
@@ -63625,22 +63708,17 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>325178884841</t>
+          <t>108771377911</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>Test RFX (Please Ignore)</t>
-        </is>
-      </c>
-      <c r="E864" t="inlineStr">
-        <is>
-          <t>Test associated agency for trello</t>
+          <t>Facilities and Information Technology Infrastructure Assessment</t>
         </is>
       </c>
       <c r="G864" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H864" t="inlineStr">
@@ -63650,27 +63728,22 @@
       </c>
       <c r="J864" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="M864" t="inlineStr">
-        <is>
-          <t>Training</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="O864" t="inlineStr">
         <is>
-          <t>Akshat Tripathi</t>
+          <t>Madhav Mitruka</t>
         </is>
       </c>
       <c r="Y864" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="Z864" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/108771377911</t>
         </is>
       </c>
     </row>
@@ -63680,22 +63753,22 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>317911067336</t>
+          <t>120893940419</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>#25-038-RFP)</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse</t>
-        </is>
-      </c>
-      <c r="E865" t="inlineStr">
-        <is>
-          <t>Michigan Department of Technology Management and Budget</t>
+          <t>HUMAN RESOURCES INFORMATION SYSTEM (“HRIS”) &amp; LEARNING MANAGEMENT SYSTEM (“LMS”) REPLACEMENT</t>
         </is>
       </c>
       <c r="G865" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H865" t="inlineStr">
@@ -63705,22 +63778,27 @@
       </c>
       <c r="J865" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="M865" t="inlineStr">
+        <is>
+          <t>Platform Implementation (ERP, CRMs)</t>
         </is>
       </c>
       <c r="O865" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="Y865" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Z865" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/120893940419</t>
         </is>
       </c>
     </row>
@@ -63730,27 +63808,17 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>321765371626</t>
-        </is>
-      </c>
-      <c r="C866" t="inlineStr">
-        <is>
-          <t>207-26</t>
+          <t>114864654049</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>Professional and Consulting Services for Strategy and Technology Division</t>
-        </is>
-      </c>
-      <c r="E866" t="inlineStr">
-        <is>
-          <t>Fulton County Schools</t>
+          <t>M365 Tenant backup</t>
         </is>
       </c>
       <c r="G866" t="inlineStr">
         <is>
-          <t>RFx Cancelled</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H866" t="inlineStr">
@@ -63760,22 +63828,22 @@
       </c>
       <c r="J866" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="O866" t="inlineStr">
         <is>
-          <t>Jyothsna Nanda kishore</t>
+          <t>Yashaswini Gautam</t>
         </is>
       </c>
       <c r="Y866" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Z866" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765371626</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/114864654049</t>
         </is>
       </c>
     </row>
@@ -63785,17 +63853,22 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>321905743581</t>
+          <t>317194645231</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>BCH-C25-008</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>ERP Needs Assessment Consulting Services</t>
+          <t>Data Migration (CMAS RFP)</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>Greater Dayton Regional Transit Authority</t>
+          <t>Business, Consumer Services and Housing Agency</t>
         </is>
       </c>
       <c r="G867" t="inlineStr">
@@ -63810,27 +63883,27 @@
       </c>
       <c r="J867" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="M867" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Modernization / Migration</t>
         </is>
       </c>
       <c r="O867" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Darshan Tiwari</t>
         </is>
       </c>
       <c r="Y867" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="Z867" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321905743581</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317194645231</t>
         </is>
       </c>
     </row>
@@ -63840,27 +63913,27 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>324841842382</t>
-        </is>
-      </c>
-      <c r="C868" t="inlineStr">
-        <is>
-          <t>2026.13</t>
+          <t>317945474767</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>OFF - Information Technology Services</t>
+          <t>ServiceNow Technical Services</t>
         </is>
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>St. John the Baptist Parish Government</t>
+          <t>City of Sacramento</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>California</t>
         </is>
       </c>
       <c r="G868" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H868" t="inlineStr">
@@ -63870,35 +63943,22 @@
       </c>
       <c r="J868" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="L868" s="65" t="n">
-        <v>424440</v>
-      </c>
-      <c r="M868" t="inlineStr">
-        <is>
-          <t>Managed Services (MSP)</t>
-        </is>
-      </c>
-      <c r="N868" t="inlineStr">
-        <is>
-          <t>Offline</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="O868" t="inlineStr">
         <is>
-          <t>Ashutosh Chauhan</t>
+          <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
       <c r="Y868" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z868" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/324841842382</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317945474767</t>
         </is>
       </c>
     </row>
@@ -63908,27 +63968,22 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>328510794433</t>
+          <t>323239766721</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>Workday BA Services (SOW 4)</t>
+          <t xml:space="preserve">Information Technology Services for Computing and Networking Infrastructure Support </t>
         </is>
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>Madison Metropolitan Sewerage District</t>
-        </is>
-      </c>
-      <c r="F869" t="inlineStr">
-        <is>
-          <t>Wisconsin</t>
+          <t>Great Parks of Hamilton County</t>
         </is>
       </c>
       <c r="G869" t="inlineStr">
         <is>
-          <t>Closed Won</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="H869" t="inlineStr">
@@ -63938,30 +63993,35 @@
       </c>
       <c r="J869" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="L869" s="65" t="n">
-        <v>170560</v>
+        <v>184700</v>
+      </c>
+      <c r="M869" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N869" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
       </c>
       <c r="O869" t="inlineStr">
         <is>
-          <t>Madhav Mitruka</t>
-        </is>
-      </c>
-      <c r="U869" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+          <t>Ashutosh Chauhan</t>
         </is>
       </c>
       <c r="Y869" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z869" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/328510794433</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/323239766721</t>
         </is>
       </c>
     </row>
@@ -63971,17 +64031,17 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>330005222132</t>
-        </is>
-      </c>
-      <c r="C870" t="inlineStr">
-        <is>
-          <t>1234</t>
+          <t>325178884841</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
         <is>
-          <t>Rocketlane test</t>
+          <t>Test RFX (Please Ignore)</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>Test associated agency for trello</t>
         </is>
       </c>
       <c r="G870" t="inlineStr">
@@ -63996,32 +64056,27 @@
       </c>
       <c r="J870" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M870" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="O870" t="inlineStr">
         <is>
-          <t>Abhishek Zalani</t>
-        </is>
-      </c>
-      <c r="S870" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
+          <t>Akshat Tripathi</t>
         </is>
       </c>
       <c r="Y870" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Z870" t="inlineStr">
         <is>
-          <t>https://app.hubspot.com/contacts/243046792/record/0-3/330005222132</t>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/325178884841</t>
         </is>
       </c>
     </row>
@@ -64031,50 +64086,461 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
+          <t>317911067336</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>Enterprise Data Warehouse</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>Michigan Department of Technology Management and Budget</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O871" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y871" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z871" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/317911067336</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="n">
+        <v>871</v>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>321765371626</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>207-26</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>Professional and Consulting Services for Strategy and Technology Division</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>Fulton County Schools</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="O872" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y872" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="Z872" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321765371626</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="n">
+        <v>872</v>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>321905743581</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>ERP Needs Assessment Consulting Services</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>Greater Dayton Regional Transit Authority</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J873" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="M873" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="O873" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y873" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z873" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/321905743581</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="n">
+        <v>873</v>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>324841842382</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>2026.13</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>OFF - Information Technology Services</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>St. John the Baptist Parish Government</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L874" s="65" t="n">
+        <v>424440</v>
+      </c>
+      <c r="M874" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N874" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="O874" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y874" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z874" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/324841842382</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="n">
+        <v>874</v>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>328510794433</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>Workday BA Services (SOW 4)</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>Madison Metropolitan Sewerage District</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J875" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="L875" s="65" t="n">
+        <v>170560</v>
+      </c>
+      <c r="O875" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="U875" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Y875" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="Z875" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/328510794433</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="n">
+        <v>875</v>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>330005222132</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>Rocketlane test</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J876" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="M876" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="O876" t="inlineStr">
+        <is>
+          <t>Abhishek Zalani</t>
+        </is>
+      </c>
+      <c r="S876" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Y876" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z876" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/330005222132</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="n">
+        <v>876</v>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>327712756453</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>Vendor Service Contract for IT Professional Services</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>City of milwaukee</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J877" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="N877" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="O877" t="inlineStr">
+        <is>
+          <t>Jyothsna Nanda kishore</t>
+        </is>
+      </c>
+      <c r="Y877" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="Z877" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/327712756453</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="n">
+        <v>877</v>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
           <t>328510627557</t>
         </is>
       </c>
-      <c r="D871" t="inlineStr">
+      <c r="D878" t="inlineStr">
         <is>
           <t>Information Technology Services Contract</t>
         </is>
       </c>
-      <c r="E871" t="inlineStr">
+      <c r="E878" t="inlineStr">
         <is>
           <t>New Mexico Crime Victims Reparations Commission</t>
         </is>
       </c>
-      <c r="F871" t="inlineStr">
+      <c r="F878" t="inlineStr">
         <is>
           <t>New Mexico</t>
         </is>
       </c>
-      <c r="G871" t="inlineStr">
+      <c r="G878" t="inlineStr">
         <is>
           <t>RFx Cancelled</t>
         </is>
       </c>
-      <c r="H871" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J871" t="inlineStr">
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J878" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="O871" t="inlineStr">
+      <c r="O878" t="inlineStr">
         <is>
           <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
-      <c r="Y871" t="inlineStr">
+      <c r="Y878" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="Z871" t="inlineStr">
+      <c r="Z878" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/328510627557</t>
         </is>

--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -2083,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA878"/>
+  <dimension ref="A1:AA910"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5391,6 +5391,11 @@
           <t>New York City Department of Education (NYCDOE)</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>Closed Lost</t>
@@ -6803,15 +6808,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
+      <c r="J61" s="96" t="n">
+        <v>45931</v>
+      </c>
+      <c r="K61" s="96" t="n">
+        <v>45930</v>
       </c>
       <c r="L61" s="65" t="n">
         <v>563816</v>
@@ -6831,10 +6832,8 @@
           <t>Jyothsna Nanda kishore</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2025-09-12</t>
-        </is>
+      <c r="Y61" s="96" t="n">
+        <v>45912</v>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
@@ -8889,15 +8888,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>2025-10-10</t>
-        </is>
+      <c r="J89" s="96" t="n">
+        <v>45940</v>
+      </c>
+      <c r="K89" s="96" t="n">
+        <v>45940</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -8914,10 +8909,8 @@
           <t>Ashutosh Chauhan</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
+      <c r="Y89" s="96" t="n">
+        <v>45915</v>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
@@ -10593,25 +10586,19 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
+      <c r="J111" s="96" t="n">
+        <v>45947</v>
+      </c>
+      <c r="K111" s="96" t="n">
+        <v>45947</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
           <t>Abhishek Zalani</t>
         </is>
       </c>
-      <c r="Y111" t="inlineStr">
-        <is>
-          <t>2025-09-17</t>
-        </is>
+      <c r="Y111" s="96" t="n">
+        <v>45917</v>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
@@ -10984,15 +10971,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>2025-10-20</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>2025-10-20</t>
-        </is>
+      <c r="J116" s="96" t="n">
+        <v>45950</v>
+      </c>
+      <c r="K116" s="96" t="n">
+        <v>45950</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
@@ -11004,10 +10987,8 @@
           <t>Ashutosh Chauhan</t>
         </is>
       </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
+      <c r="Y116" s="96" t="n">
+        <v>45911</v>
       </c>
       <c r="Z116" t="inlineStr">
         <is>
@@ -12115,15 +12096,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
+      <c r="J131" s="96" t="n">
+        <v>45957</v>
+      </c>
+      <c r="K131" s="96" t="n">
+        <v>45957</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
@@ -12135,10 +12112,8 @@
           <t>Abhishek Zalani</t>
         </is>
       </c>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
+      <c r="Y131" s="96" t="n">
+        <v>45915</v>
       </c>
  